--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -115,11 +115,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,64 +641,62 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-16</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30539.75</v>
+        <v>30006.75</v>
       </c>
       <c r="C2" t="n">
-        <v>30664.5</v>
+        <v>30268.5</v>
       </c>
       <c r="D2" t="n">
-        <v>29956.75</v>
+        <v>29616</v>
       </c>
       <c r="E2" t="n">
-        <v>29995</v>
+        <v>29687.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-564.25</v>
+        <v>-307.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0185</v>
+        <v>-0.0103</v>
       </c>
       <c r="H2" t="n">
-        <v>707.75</v>
+        <v>652.5</v>
       </c>
       <c r="I2" t="n">
-        <v>29201.5</v>
+        <v>29249</v>
       </c>
       <c r="J2" t="n">
-        <v>30003.5</v>
+        <v>29129.44</v>
       </c>
       <c r="K2" t="n">
-        <v>30206.5</v>
+        <v>29641.12</v>
       </c>
       <c r="L2" t="n">
-        <v>30409.5</v>
+        <v>30152.81</v>
       </c>
       <c r="M2" t="n">
-        <v>30912</v>
+        <v>30348.88</v>
       </c>
       <c r="N2" t="n">
-        <v>31414.5</v>
+        <v>30544.94</v>
       </c>
       <c r="O2" t="n">
-        <v>31318</v>
+        <v>31372.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -715,62 +713,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30006.75</v>
+        <v>29758.5</v>
       </c>
       <c r="C3" t="n">
-        <v>30268.5</v>
+        <v>30285.75</v>
       </c>
       <c r="D3" t="n">
-        <v>29616</v>
+        <v>29758.5</v>
       </c>
       <c r="E3" t="n">
-        <v>29687.5</v>
+        <v>30263.35</v>
       </c>
       <c r="F3" t="n">
-        <v>-307.5</v>
+        <v>575.85</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0194</v>
       </c>
       <c r="H3" t="n">
-        <v>652.5</v>
+        <v>527.25</v>
       </c>
       <c r="I3" t="n">
-        <v>29249</v>
+        <v>28963.5</v>
       </c>
       <c r="J3" t="n">
-        <v>29129.44</v>
+        <v>28907.62</v>
       </c>
       <c r="K3" t="n">
-        <v>29641.12</v>
+        <v>29361.25</v>
       </c>
       <c r="L3" t="n">
-        <v>30152.81</v>
+        <v>29814.88</v>
       </c>
       <c r="M3" t="n">
-        <v>30348.88</v>
+        <v>30013.75</v>
       </c>
       <c r="N3" t="n">
-        <v>30544.94</v>
+        <v>30212.62</v>
       </c>
       <c r="O3" t="n">
-        <v>31372.25</v>
+        <v>30921</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -778,28 +776,30 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -807,50 +807,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29758.5</v>
+        <v>30577</v>
       </c>
       <c r="C4" t="n">
-        <v>30285.75</v>
+        <v>30968</v>
       </c>
       <c r="D4" t="n">
-        <v>29758.5</v>
+        <v>30337.5</v>
       </c>
       <c r="E4" t="n">
-        <v>30263.35</v>
+        <v>30653.5</v>
       </c>
       <c r="F4" t="n">
-        <v>575.85</v>
+        <v>390.15</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0194</v>
+        <v>0.0129</v>
       </c>
       <c r="H4" t="n">
-        <v>527.25</v>
+        <v>630.5</v>
       </c>
       <c r="I4" t="n">
-        <v>28963.5</v>
+        <v>29231.25</v>
       </c>
       <c r="J4" t="n">
-        <v>28907.62</v>
+        <v>29856.71</v>
       </c>
       <c r="K4" t="n">
-        <v>29361.25</v>
+        <v>29999.72</v>
       </c>
       <c r="L4" t="n">
-        <v>29814.88</v>
+        <v>30142.74</v>
       </c>
       <c r="M4" t="n">
-        <v>30013.75</v>
+        <v>30526.97</v>
       </c>
       <c r="N4" t="n">
-        <v>30212.62</v>
+        <v>30911.21</v>
       </c>
       <c r="O4" t="n">
-        <v>30921</v>
+        <v>30813</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -868,18 +868,20 @@
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="V4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -889,83 +891,83 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30577</v>
+        <v>30662.75</v>
       </c>
       <c r="C5" t="n">
-        <v>30968</v>
+        <v>30701.25</v>
       </c>
       <c r="D5" t="n">
-        <v>30337.5</v>
+        <v>29577.25</v>
       </c>
       <c r="E5" t="n">
-        <v>30653.5</v>
+        <v>29666</v>
       </c>
       <c r="F5" t="n">
-        <v>390.15</v>
+        <v>-987.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0322</v>
       </c>
       <c r="H5" t="n">
-        <v>630.5</v>
+        <v>1124</v>
       </c>
       <c r="I5" t="n">
-        <v>29231.25</v>
+        <v>29707</v>
       </c>
       <c r="J5" t="n">
-        <v>29856.71</v>
+        <v>30023.38</v>
       </c>
       <c r="K5" t="n">
-        <v>29999.72</v>
+        <v>30338.25</v>
       </c>
       <c r="L5" t="n">
-        <v>30142.74</v>
+        <v>30653.12</v>
       </c>
       <c r="M5" t="n">
-        <v>30526.97</v>
+        <v>30968.75</v>
       </c>
       <c r="N5" t="n">
-        <v>30911.21</v>
+        <v>31284.38</v>
       </c>
       <c r="O5" t="n">
-        <v>30813</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+        <v>31598.5</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U5" s="8" t="inlineStr">
+      <c r="Q5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V5" s="8" t="inlineStr">
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V5" s="8" t="n">
+        <v/>
+      </c>
       <c r="W5" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -973,69 +975,63 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30662.75</v>
+        <v>29770</v>
       </c>
       <c r="C6" t="n">
-        <v>30701.25</v>
+        <v>30157.75</v>
       </c>
       <c r="D6" t="n">
-        <v>29577.25</v>
+        <v>29264.75</v>
       </c>
       <c r="E6" t="n">
-        <v>29666</v>
+        <v>29514.25</v>
       </c>
       <c r="F6" t="n">
-        <v>-987.5</v>
+        <v>-151.75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0051</v>
       </c>
       <c r="H6" t="n">
-        <v>1124</v>
+        <v>893</v>
       </c>
       <c r="I6" t="n">
-        <v>29707</v>
+        <v>28453.25</v>
       </c>
       <c r="J6" t="n">
-        <v>30023.38</v>
+        <v>28305.38</v>
       </c>
       <c r="K6" t="n">
-        <v>30338.25</v>
+        <v>29104</v>
       </c>
       <c r="L6" t="n">
-        <v>30653.12</v>
+        <v>29902.62</v>
       </c>
       <c r="M6" t="n">
-        <v>30968.75</v>
+        <v>30228</v>
       </c>
       <c r="N6" t="n">
-        <v>31284.38</v>
+        <v>30553.38</v>
       </c>
       <c r="O6" t="n">
-        <v>31598.5</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31825.25</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1047,7 +1043,7 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1057,50 +1053,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29770</v>
+        <v>30089.75</v>
       </c>
       <c r="C7" t="n">
-        <v>30157.75</v>
+        <v>30263.75</v>
       </c>
       <c r="D7" t="n">
-        <v>29264.75</v>
+        <v>29295.75</v>
       </c>
       <c r="E7" t="n">
-        <v>29514.25</v>
+        <v>29724.75</v>
       </c>
       <c r="F7" t="n">
-        <v>-151.75</v>
+        <v>210.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0071</v>
       </c>
       <c r="H7" t="n">
-        <v>893</v>
+        <v>968</v>
       </c>
       <c r="I7" t="n">
-        <v>28453.25</v>
+        <v>28371.75</v>
       </c>
       <c r="J7" t="n">
-        <v>28305.38</v>
+        <v>28522.75</v>
       </c>
       <c r="K7" t="n">
-        <v>29104</v>
+        <v>29067.75</v>
       </c>
       <c r="L7" t="n">
-        <v>29902.62</v>
+        <v>29612.75</v>
       </c>
       <c r="M7" t="n">
-        <v>30228</v>
+        <v>29960.75</v>
       </c>
       <c r="N7" t="n">
-        <v>30553.38</v>
+        <v>30308.75</v>
       </c>
       <c r="O7" t="n">
-        <v>31825.25</v>
+        <v>31050.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1111,13 +1107,15 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1125,60 +1123,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30089.75</v>
+        <v>29742</v>
       </c>
       <c r="C8" t="n">
-        <v>30263.75</v>
+        <v>29892.75</v>
       </c>
       <c r="D8" t="n">
-        <v>29295.75</v>
+        <v>29160.5</v>
       </c>
       <c r="E8" t="n">
-        <v>29724.75</v>
+        <v>29368.25</v>
       </c>
       <c r="F8" t="n">
-        <v>210.5</v>
+        <v>-356.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.012</v>
       </c>
       <c r="H8" t="n">
-        <v>968</v>
+        <v>732.25</v>
       </c>
       <c r="I8" t="n">
-        <v>28371.75</v>
+        <v>28327.75</v>
       </c>
       <c r="J8" t="n">
-        <v>28522.75</v>
+        <v>28729.25</v>
       </c>
       <c r="K8" t="n">
-        <v>29067.75</v>
+        <v>29240.75</v>
       </c>
       <c r="L8" t="n">
-        <v>29612.75</v>
+        <v>29752.25</v>
       </c>
       <c r="M8" t="n">
-        <v>29960.75</v>
+        <v>30208.75</v>
       </c>
       <c r="N8" t="n">
-        <v>30308.75</v>
+        <v>30665.25</v>
       </c>
       <c r="O8" t="n">
-        <v>31050.75</v>
+        <v>31231.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,18 +1188,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1205,64 +1207,60 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29742</v>
+        <v>29282.5</v>
       </c>
       <c r="C9" t="n">
-        <v>29892.75</v>
+        <v>30069.5</v>
       </c>
       <c r="D9" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E9" t="n">
-        <v>29368.25</v>
+        <v>30052.75</v>
       </c>
       <c r="F9" t="n">
-        <v>-356.5</v>
+        <v>684.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0233</v>
       </c>
       <c r="H9" t="n">
-        <v>732.25</v>
+        <v>795.75</v>
       </c>
       <c r="I9" t="n">
-        <v>28327.75</v>
+        <v>28428.25</v>
       </c>
       <c r="J9" t="n">
-        <v>28729.25</v>
+        <v>28556.81</v>
       </c>
       <c r="K9" t="n">
-        <v>29240.75</v>
+        <v>29002.12</v>
       </c>
       <c r="L9" t="n">
-        <v>29752.25</v>
+        <v>29447.44</v>
       </c>
       <c r="M9" t="n">
-        <v>30208.75</v>
+        <v>29734.38</v>
       </c>
       <c r="N9" t="n">
-        <v>30665.25</v>
+        <v>30021.31</v>
       </c>
       <c r="O9" t="n">
-        <v>31231.75</v>
+        <v>30625</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1270,28 +1268,30 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U9" s="8" t="n">
-        <v/>
-      </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
       <c r="W9" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr"/>
@@ -1299,50 +1299,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29282.5</v>
+        <v>30007.25</v>
       </c>
       <c r="C10" t="n">
-        <v>30069.5</v>
+        <v>30599.75</v>
       </c>
       <c r="D10" t="n">
-        <v>29273.75</v>
+        <v>29934.75</v>
       </c>
       <c r="E10" t="n">
-        <v>30052.75</v>
+        <v>30523.5</v>
       </c>
       <c r="F10" t="n">
-        <v>684.5</v>
+        <v>470.75</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0157</v>
       </c>
       <c r="H10" t="n">
-        <v>795.75</v>
+        <v>665</v>
       </c>
       <c r="I10" t="n">
-        <v>28428.25</v>
+        <v>28478</v>
       </c>
       <c r="J10" t="n">
-        <v>28556.81</v>
+        <v>29447.56</v>
       </c>
       <c r="K10" t="n">
-        <v>29002.12</v>
+        <v>29654.88</v>
       </c>
       <c r="L10" t="n">
-        <v>29447.44</v>
+        <v>29862.19</v>
       </c>
       <c r="M10" t="n">
-        <v>29734.38</v>
+        <v>30450.62</v>
       </c>
       <c r="N10" t="n">
-        <v>30021.31</v>
+        <v>31039.06</v>
       </c>
       <c r="O10" t="n">
-        <v>30625</v>
+        <v>30865.25</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1360,18 +1360,16 @@
       </c>
       <c r="T10" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U10" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U10" s="8" t="n">
+        <v/>
+      </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1381,50 +1379,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C11" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D11" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E11" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F11" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H11" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I11" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J11" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K11" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L11" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M11" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N11" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O11" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1432,89 +1430,97 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C12" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D12" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E12" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F12" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H12" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I12" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J12" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K12" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L12" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M12" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N12" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O12" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
@@ -1531,172 +1537,172 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C13" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D13" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E13" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F13" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H13" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I13" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J13" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K13" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L13" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M13" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N13" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O13" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C14" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D14" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E14" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F14" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H14" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I14" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J14" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K14" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L14" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M14" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N14" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O14" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+        <v>30505</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1705,81 +1711,73 @@
       </c>
       <c r="W14" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C15" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D15" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E15" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F15" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H15" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I15" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J15" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K15" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L15" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M15" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N15" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O15" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q15" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1791,60 +1789,64 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C16" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D16" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E16" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F16" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H16" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I16" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J16" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K16" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L16" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M16" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N16" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O16" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1852,18 +1854,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1871,64 +1873,64 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C17" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D17" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E17" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F17" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H17" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I17" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J17" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K17" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L17" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M17" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N17" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O17" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1955,7 +1957,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1969,218 +1971,218 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C18" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D18" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E18" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F18" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H18" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I18" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J18" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K18" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L18" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M18" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N18" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O18" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+        <v>30480.5</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C19" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D19" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E19" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H19" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I19" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J19" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K19" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L19" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M19" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N19" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O19" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
       <c r="U19" s="8" t="n">
         <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C20" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D20" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E20" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F20" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H20" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I20" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J20" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K20" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L20" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M20" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N20" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O20" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,18 +2190,18 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2207,64 +2209,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C21" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D21" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E21" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F21" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H21" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I21" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J21" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K21" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L21" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M21" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N21" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O21" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2274,12 +2276,12 @@
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S21" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2291,64 +2293,60 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C22" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D22" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E22" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H22" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I22" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J22" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K22" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L22" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M22" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N22" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O22" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2375,7 +2373,7 @@
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2385,50 +2383,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C23" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D23" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E23" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H23" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I23" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J23" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K23" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L23" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M23" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N23" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O23" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2436,18 +2434,18 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R23" s="6" t="n">
+        <v/>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U23" s="8" t="n">
         <v/>
@@ -2455,60 +2453,64 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C24" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D24" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E24" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F24" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H24" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I24" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J24" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K24" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L24" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M24" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N24" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O24" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2519,9 +2521,9 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T24" s="8" t="inlineStr">
@@ -2529,70 +2531,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C25" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D25" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E25" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F25" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H25" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I25" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J25" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K25" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L25" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M25" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N25" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O25" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,100 +2604,102 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C26" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D26" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E26" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F26" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H26" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I26" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J26" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K26" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L26" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M26" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N26" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O26" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P26" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2707,78 +2713,70 @@
       </c>
       <c r="W26" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C27" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D27" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E27" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F27" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H27" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I27" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J27" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K27" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L27" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M27" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N27" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O27" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P27" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2793,7 +2791,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2803,50 +2801,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C28" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D28" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E28" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F28" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H28" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I28" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J28" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K28" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L28" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M28" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N28" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O28" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2864,69 +2862,77 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C29" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D29" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E29" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F29" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H29" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I29" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J29" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K29" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L29" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M29" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N29" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O29" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2944,87 +2950,81 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C30" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D30" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E30" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F30" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H30" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I30" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J30" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K30" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L30" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M30" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N30" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O30" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R30" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S30" s="7" t="inlineStr">
@@ -3041,7 +3041,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3051,81 +3051,81 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C31" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D31" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E31" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F31" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H31" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I31" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J31" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K31" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L31" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M31" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N31" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O31" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
       </c>
-      <c r="Q31" s="6" t="inlineStr">
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
       <c r="W31" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X31" t="inlineStr"/>
@@ -3133,50 +3133,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C32" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D32" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E32" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F32" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H32" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I32" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J32" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K32" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L32" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M32" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N32" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O32" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3189,23 +3189,19 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3215,50 +3211,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C33" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D33" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E33" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F33" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H33" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I33" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J33" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K33" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L33" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M33" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N33" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O33" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3271,19 +3267,23 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3293,50 +3293,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C34" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D34" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E34" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F34" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H34" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I34" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J34" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K34" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L34" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M34" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N34" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O34" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3362,10 +3362,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="V34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3375,50 +3377,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C35" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D35" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E35" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F35" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H35" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I35" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J35" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K35" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L35" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M35" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N35" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O35" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3429,80 +3431,78 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C36" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D36" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E36" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F36" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H36" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I36" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J36" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K36" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L36" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M36" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N36" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O36" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3510,12 +3510,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3527,64 +3529,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C37" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D37" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E37" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F37" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H37" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I37" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J37" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K37" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L37" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M37" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N37" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O37" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3592,83 +3594,81 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C38" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D38" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E38" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F38" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H38" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I38" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J38" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K38" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L38" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M38" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N38" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O38" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3679,78 +3679,78 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C39" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D39" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E39" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F39" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H39" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I39" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J39" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K39" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L39" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M39" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N39" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O39" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3758,16 +3758,20 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3775,64 +3779,64 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C40" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D40" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E40" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F40" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H40" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I40" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J40" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K40" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L40" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M40" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N40" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O40" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3840,85 +3844,81 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
+      <c r="U40" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U40" s="8" t="n">
-        <v/>
-      </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C41" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D41" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E41" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F41" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H41" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I41" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J41" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K41" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L41" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M41" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N41" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O41" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3936,18 +3936,18 @@
       </c>
       <c r="T41" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
+      <c r="W41" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3957,50 +3957,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C42" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D42" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E42" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F42" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H42" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I42" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J42" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K42" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L42" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M42" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N42" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O42" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4013,76 +4013,76 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C43" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D43" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E43" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F43" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G43" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H43" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I43" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J43" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K43" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L43" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M43" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N43" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O43" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4093,13 +4093,15 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4107,7 +4109,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4121,69 +4123,73 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C44" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D44" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E44" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F44" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H44" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I44" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J44" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K44" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L44" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M44" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N44" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O44" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+        <v>30631.5</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4193,81 +4199,71 @@
       </c>
       <c r="W44" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C45" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D45" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E45" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F45" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H45" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I45" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J45" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K45" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L45" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M45" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N45" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O45" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30728.5</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4279,7 +4275,7 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4289,50 +4285,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C46" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D46" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E46" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F46" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H46" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I46" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J46" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K46" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L46" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M46" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N46" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O46" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4340,12 +4336,14 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4357,7 +4355,7 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4367,50 +4365,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C47" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D47" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E47" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F47" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H47" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I47" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J47" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K47" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L47" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M47" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N47" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O47" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4418,14 +4416,12 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4437,73 +4433,81 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C48" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D48" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E48" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F48" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I48" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J48" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K48" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L48" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M48" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N48" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O48" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4515,146 +4519,144 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C49" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D49" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E49" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F49" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H49" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I49" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J49" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K49" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L49" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M49" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N49" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O49" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C50" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D50" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E50" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F50" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H50" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I50" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J50" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K50" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L50" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M50" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N50" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O50" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4667,13 +4669,11 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4681,64 +4681,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C51" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D51" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E51" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F51" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H51" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I51" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J51" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K51" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L51" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M51" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N51" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O51" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4751,166 +4751,168 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C52" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D52" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E52" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F52" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H52" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I52" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J52" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K52" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L52" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M52" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N52" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O52" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C53" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D53" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E53" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F53" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H53" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I53" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J53" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K53" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L53" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M53" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N53" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O53" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
@@ -4919,7 +4921,7 @@
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4931,70 +4933,74 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C54" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D54" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E54" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F54" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H54" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I54" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J54" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K54" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L54" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M54" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N54" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O54" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
@@ -5003,7 +5009,7 @@
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5017,81 +5023,75 @@
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C55" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D55" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E55" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F55" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H55" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I55" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J55" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K55" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L55" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M55" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N55" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O55" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P55" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30140.5</v>
+      </c>
+      <c r="P55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T55" s="8" t="n">
@@ -5103,7 +5103,7 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5117,50 +5117,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C56" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D56" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E56" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F56" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H56" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I56" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J56" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K56" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L56" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M56" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N56" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O56" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5171,78 +5171,84 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C57" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D57" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E57" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F57" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H57" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I57" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J57" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K57" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L57" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M57" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N57" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O57" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5255,25 +5261,19 @@
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W57" s="9" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5287,50 +5287,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C58" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D58" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E58" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F58" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H58" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I58" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J58" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K58" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L58" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M58" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N58" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O58" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5338,16 +5338,20 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5355,64 +5359,64 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C59" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D59" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E59" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F59" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H59" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I59" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J59" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K59" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L59" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M59" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N59" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O59" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5422,18 +5426,16 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5441,74 +5443,72 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C60" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D60" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E60" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F60" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H60" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I60" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J60" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K60" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L60" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M60" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N60" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O60" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
@@ -5525,7 +5525,7 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5535,194 +5535,112 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C61" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D61" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E61" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F61" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H61" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I61" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J61" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K61" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L61" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M61" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N61" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O61" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>29141</v>
-      </c>
-      <c r="C62" t="n">
-        <v>29500.25</v>
-      </c>
-      <c r="D62" t="n">
-        <v>29040.5</v>
-      </c>
-      <c r="E62" t="n">
-        <v>29387</v>
-      </c>
-      <c r="F62" t="n">
-        <v>251.75</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0086</v>
-      </c>
-      <c r="H62" t="n">
-        <v>459.75</v>
-      </c>
-      <c r="I62" t="n">
-        <v>28578.25</v>
-      </c>
-      <c r="J62" t="n">
-        <v>28600</v>
-      </c>
-      <c r="K62" t="n">
-        <v>28902.75</v>
-      </c>
-      <c r="L62" t="n">
-        <v>29205.5</v>
-      </c>
-      <c r="M62" t="n">
-        <v>29367.75</v>
-      </c>
-      <c r="N62" t="n">
-        <v>29530</v>
-      </c>
-      <c r="O62" t="n">
-        <v>29973.25</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
+      <c r="I62" s="13" t="n">
         <v>28580.75</v>
       </c>
-      <c r="J63" s="13" t="n">
+      <c r="J62" s="13" t="n">
         <v>28985.56</v>
       </c>
-      <c r="K63" s="13" t="n">
+      <c r="K62" s="13" t="n">
         <v>29157.12</v>
       </c>
-      <c r="L63" s="13" t="n">
+      <c r="L62" s="13" t="n">
         <v>29328.69</v>
       </c>
-      <c r="M63" s="13" t="n">
+      <c r="M62" s="13" t="n">
         <v>29616.88</v>
       </c>
-      <c r="N63" s="13" t="n">
+      <c r="N62" s="13" t="n">
         <v>29905.06</v>
       </c>
-      <c r="O63" s="13" t="n">
+      <c r="O62" s="13" t="n">
         <v>29960</v>
       </c>
     </row>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -109,14 +109,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30006.75</v>
+        <v>29758.5</v>
       </c>
       <c r="C2" t="n">
-        <v>30268.5</v>
+        <v>30285.75</v>
       </c>
       <c r="D2" t="n">
-        <v>29616</v>
+        <v>29758.5</v>
       </c>
       <c r="E2" t="n">
-        <v>29687.5</v>
+        <v>30263.35</v>
       </c>
       <c r="F2" t="n">
-        <v>-307.5</v>
+        <v>575.85</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0103</v>
+        <v>0.0194</v>
       </c>
       <c r="H2" t="n">
-        <v>652.5</v>
+        <v>527.25</v>
       </c>
       <c r="I2" t="n">
-        <v>29249</v>
+        <v>28963.5</v>
       </c>
       <c r="J2" t="n">
-        <v>29129.44</v>
+        <v>28907.62</v>
       </c>
       <c r="K2" t="n">
-        <v>29641.12</v>
+        <v>29361.25</v>
       </c>
       <c r="L2" t="n">
-        <v>30152.81</v>
+        <v>29814.88</v>
       </c>
       <c r="M2" t="n">
-        <v>30348.88</v>
+        <v>30013.75</v>
       </c>
       <c r="N2" t="n">
-        <v>30544.94</v>
+        <v>30212.62</v>
       </c>
       <c r="O2" t="n">
-        <v>31372.25</v>
+        <v>30921</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -692,22 +692,24 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -716,59 +718,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29758.5</v>
+        <v>30577</v>
       </c>
       <c r="C3" t="n">
-        <v>30285.75</v>
+        <v>30968</v>
       </c>
       <c r="D3" t="n">
-        <v>29758.5</v>
+        <v>30337.5</v>
       </c>
       <c r="E3" t="n">
-        <v>30263.35</v>
+        <v>30653.5</v>
       </c>
       <c r="F3" t="n">
-        <v>575.85</v>
+        <v>390.15</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0194</v>
+        <v>0.0129</v>
       </c>
       <c r="H3" t="n">
-        <v>527.25</v>
+        <v>630.5</v>
       </c>
       <c r="I3" t="n">
-        <v>28963.5</v>
+        <v>29231.25</v>
       </c>
       <c r="J3" t="n">
-        <v>28907.62</v>
+        <v>29856.71</v>
       </c>
       <c r="K3" t="n">
-        <v>29361.25</v>
+        <v>29999.72</v>
       </c>
       <c r="L3" t="n">
-        <v>29814.88</v>
+        <v>30142.74</v>
       </c>
       <c r="M3" t="n">
-        <v>30013.75</v>
+        <v>30526.97</v>
       </c>
       <c r="N3" t="n">
-        <v>30212.62</v>
+        <v>30911.21</v>
       </c>
       <c r="O3" t="n">
-        <v>30921</v>
+        <v>30813</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -779,23 +777,25 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V3" s="8" t="n">
-        <v/>
+      <c r="V3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
@@ -807,83 +807,83 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30577</v>
+        <v>30662.75</v>
       </c>
       <c r="C4" t="n">
-        <v>30968</v>
+        <v>30701.25</v>
       </c>
       <c r="D4" t="n">
-        <v>30337.5</v>
+        <v>29577.25</v>
       </c>
       <c r="E4" t="n">
-        <v>30653.5</v>
+        <v>29666</v>
       </c>
       <c r="F4" t="n">
-        <v>390.15</v>
+        <v>-987.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0322</v>
       </c>
       <c r="H4" t="n">
-        <v>630.5</v>
+        <v>1124</v>
       </c>
       <c r="I4" t="n">
-        <v>29231.25</v>
+        <v>29707</v>
       </c>
       <c r="J4" t="n">
-        <v>29856.71</v>
+        <v>30023.38</v>
       </c>
       <c r="K4" t="n">
-        <v>29999.72</v>
+        <v>30338.25</v>
       </c>
       <c r="L4" t="n">
-        <v>30142.74</v>
+        <v>30653.12</v>
       </c>
       <c r="M4" t="n">
-        <v>30526.97</v>
+        <v>30968.75</v>
       </c>
       <c r="N4" t="n">
-        <v>30911.21</v>
+        <v>31284.38</v>
       </c>
       <c r="O4" t="n">
-        <v>30813</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+        <v>31598.5</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V4" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -891,69 +891,63 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30662.75</v>
+        <v>29770</v>
       </c>
       <c r="C5" t="n">
-        <v>30701.25</v>
+        <v>30157.75</v>
       </c>
       <c r="D5" t="n">
-        <v>29577.25</v>
+        <v>29264.75</v>
       </c>
       <c r="E5" t="n">
-        <v>29666</v>
+        <v>29514.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-987.5</v>
+        <v>-151.75</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0051</v>
       </c>
       <c r="H5" t="n">
-        <v>1124</v>
+        <v>893</v>
       </c>
       <c r="I5" t="n">
-        <v>29707</v>
+        <v>28453.25</v>
       </c>
       <c r="J5" t="n">
-        <v>30023.38</v>
+        <v>28305.38</v>
       </c>
       <c r="K5" t="n">
-        <v>30338.25</v>
+        <v>29104</v>
       </c>
       <c r="L5" t="n">
-        <v>30653.12</v>
+        <v>29902.62</v>
       </c>
       <c r="M5" t="n">
-        <v>30968.75</v>
+        <v>30228</v>
       </c>
       <c r="N5" t="n">
-        <v>31284.38</v>
+        <v>30553.38</v>
       </c>
       <c r="O5" t="n">
-        <v>31598.5</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>31825.25</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -975,50 +969,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29770</v>
+        <v>30089.75</v>
       </c>
       <c r="C6" t="n">
-        <v>30157.75</v>
+        <v>30263.75</v>
       </c>
       <c r="D6" t="n">
-        <v>29264.75</v>
+        <v>29295.75</v>
       </c>
       <c r="E6" t="n">
-        <v>29514.25</v>
+        <v>29724.75</v>
       </c>
       <c r="F6" t="n">
-        <v>-151.75</v>
+        <v>210.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0071</v>
       </c>
       <c r="H6" t="n">
-        <v>893</v>
+        <v>968</v>
       </c>
       <c r="I6" t="n">
-        <v>28453.25</v>
+        <v>28371.75</v>
       </c>
       <c r="J6" t="n">
-        <v>28305.38</v>
+        <v>28522.75</v>
       </c>
       <c r="K6" t="n">
-        <v>29104</v>
+        <v>29067.75</v>
       </c>
       <c r="L6" t="n">
-        <v>29902.62</v>
+        <v>29612.75</v>
       </c>
       <c r="M6" t="n">
-        <v>30228</v>
+        <v>29960.75</v>
       </c>
       <c r="N6" t="n">
-        <v>30553.38</v>
+        <v>30308.75</v>
       </c>
       <c r="O6" t="n">
-        <v>31825.25</v>
+        <v>31050.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1031,11 +1025,13 @@
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1048,55 +1044,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30089.75</v>
+        <v>29742</v>
       </c>
       <c r="C7" t="n">
-        <v>30263.75</v>
+        <v>29892.75</v>
       </c>
       <c r="D7" t="n">
-        <v>29295.75</v>
+        <v>29160.5</v>
       </c>
       <c r="E7" t="n">
-        <v>29724.75</v>
+        <v>29368.25</v>
       </c>
       <c r="F7" t="n">
-        <v>210.5</v>
+        <v>-356.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.012</v>
       </c>
       <c r="H7" t="n">
-        <v>968</v>
+        <v>732.25</v>
       </c>
       <c r="I7" t="n">
-        <v>28371.75</v>
+        <v>28327.75</v>
       </c>
       <c r="J7" t="n">
-        <v>28522.75</v>
+        <v>28729.25</v>
       </c>
       <c r="K7" t="n">
-        <v>29067.75</v>
+        <v>29240.75</v>
       </c>
       <c r="L7" t="n">
-        <v>29612.75</v>
+        <v>29752.25</v>
       </c>
       <c r="M7" t="n">
-        <v>29960.75</v>
+        <v>30208.75</v>
       </c>
       <c r="N7" t="n">
-        <v>30308.75</v>
+        <v>30665.25</v>
       </c>
       <c r="O7" t="n">
-        <v>31050.75</v>
+        <v>31231.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1104,18 +1104,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1128,59 +1128,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29742</v>
+        <v>29282.5</v>
       </c>
       <c r="C8" t="n">
-        <v>29892.75</v>
+        <v>30069.5</v>
       </c>
       <c r="D8" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E8" t="n">
-        <v>29368.25</v>
+        <v>30052.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-356.5</v>
+        <v>684.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0233</v>
       </c>
       <c r="H8" t="n">
-        <v>732.25</v>
+        <v>795.75</v>
       </c>
       <c r="I8" t="n">
-        <v>28327.75</v>
+        <v>28428.25</v>
       </c>
       <c r="J8" t="n">
-        <v>28729.25</v>
+        <v>28556.81</v>
       </c>
       <c r="K8" t="n">
-        <v>29240.75</v>
+        <v>29002.12</v>
       </c>
       <c r="L8" t="n">
-        <v>29752.25</v>
+        <v>29447.44</v>
       </c>
       <c r="M8" t="n">
-        <v>30208.75</v>
+        <v>29734.38</v>
       </c>
       <c r="N8" t="n">
-        <v>30665.25</v>
+        <v>30021.31</v>
       </c>
       <c r="O8" t="n">
-        <v>31231.75</v>
+        <v>30625</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1188,28 +1184,30 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U8" s="8" t="n">
-        <v/>
-      </c>
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W8" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr"/>
@@ -1217,50 +1215,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29282.5</v>
+        <v>30007.25</v>
       </c>
       <c r="C9" t="n">
-        <v>30069.5</v>
+        <v>30599.75</v>
       </c>
       <c r="D9" t="n">
-        <v>29273.75</v>
+        <v>29934.75</v>
       </c>
       <c r="E9" t="n">
-        <v>30052.75</v>
+        <v>30523.5</v>
       </c>
       <c r="F9" t="n">
-        <v>684.5</v>
+        <v>470.75</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0157</v>
       </c>
       <c r="H9" t="n">
-        <v>795.75</v>
+        <v>665</v>
       </c>
       <c r="I9" t="n">
-        <v>28428.25</v>
+        <v>28478</v>
       </c>
       <c r="J9" t="n">
-        <v>28556.81</v>
+        <v>29447.56</v>
       </c>
       <c r="K9" t="n">
-        <v>29002.12</v>
+        <v>29654.88</v>
       </c>
       <c r="L9" t="n">
-        <v>29447.44</v>
+        <v>29862.19</v>
       </c>
       <c r="M9" t="n">
-        <v>29734.38</v>
+        <v>30450.62</v>
       </c>
       <c r="N9" t="n">
-        <v>30021.31</v>
+        <v>31039.06</v>
       </c>
       <c r="O9" t="n">
-        <v>30625</v>
+        <v>30865.25</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,20 +1269,18 @@
       <c r="R9" s="6" t="n">
         <v/>
       </c>
-      <c r="S9" s="10" t="inlineStr">
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T9" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U9" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U9" s="8" t="n">
+        <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
@@ -1299,50 +1295,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C10" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D10" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E10" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F10" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H10" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I10" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J10" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K10" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L10" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M10" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N10" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O10" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1350,18 +1346,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1374,68 +1370,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C11" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D11" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E11" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F11" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H11" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I11" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J11" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K11" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L11" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M11" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N11" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O11" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1456,81 +1460,77 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C12" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D12" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E12" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F12" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H12" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I12" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J12" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K12" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L12" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M12" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N12" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O12" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1544,76 +1544,80 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C13" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D13" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E13" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F13" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H13" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I13" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J13" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K13" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L13" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M13" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N13" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O13" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+        <v>30505</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1621,83 +1625,75 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W13" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C14" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D14" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E14" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F14" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H14" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I14" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J14" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K14" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L14" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M14" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N14" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O14" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q14" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1714,55 +1710,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C15" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D15" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E15" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F15" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H15" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I15" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J15" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K15" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L15" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M15" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N15" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O15" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1770,18 +1770,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1796,57 +1796,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C16" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D16" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E16" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F16" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H16" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I16" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J16" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K16" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L16" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M16" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N16" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O16" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1857,7 +1857,7 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1887,69 +1887,73 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C17" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D17" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E17" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F17" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H17" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I17" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J17" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K17" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L17" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M17" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N17" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O17" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+        <v>30480.5</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1962,83 +1966,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C18" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D18" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E18" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H18" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I18" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J18" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K18" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L18" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M18" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N18" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O18" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
       <c r="U18" s="8" t="n">
         <v/>
       </c>
@@ -2050,55 +2046,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C19" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D19" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E19" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F19" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H19" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I19" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J19" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K19" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L19" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M19" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N19" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O19" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,18 +2106,18 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2132,57 +2132,57 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C20" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D20" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E20" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F20" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H20" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I20" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J20" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K20" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L20" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M20" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N20" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O20" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2192,12 +2192,12 @@
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2214,59 +2214,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C21" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D21" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E21" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F21" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H21" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I21" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J21" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K21" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L21" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M21" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N21" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O21" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,7 +2275,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2303,50 +2299,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C22" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D22" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E22" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F22" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H22" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I22" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J22" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K22" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L22" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M22" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N22" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O22" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2354,18 +2350,18 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U22" s="8" t="n">
         <v/>
@@ -2378,55 +2374,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C23" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D23" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E23" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F23" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H23" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I23" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J23" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K23" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L23" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M23" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N23" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O23" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T23" s="8" t="inlineStr">
@@ -2447,70 +2447,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C24" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D24" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E24" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F24" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H24" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I24" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J24" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K24" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L24" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M24" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N24" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O24" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2518,23 +2520,21 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2546,63 +2546,67 @@
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C25" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D25" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E25" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F25" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H25" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I25" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J25" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K25" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L25" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M25" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N25" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O25" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
@@ -2611,7 +2615,7 @@
       </c>
       <c r="S25" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2623,81 +2627,73 @@
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W25" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C26" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D26" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E26" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H26" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I26" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J26" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K26" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L26" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M26" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N26" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O26" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P26" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
+      <c r="S26" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2721,50 +2717,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C27" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D27" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E27" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F27" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H27" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I27" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J27" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K27" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L27" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M27" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N27" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O27" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2777,16 +2773,20 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
+      <c r="S27" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2796,55 +2796,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C28" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D28" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E28" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F28" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H28" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I28" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J28" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K28" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L28" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M28" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N28" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O28" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2857,20 +2861,16 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2880,72 +2880,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C29" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D29" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E29" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F29" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H29" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I29" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J29" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K29" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L29" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M29" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N29" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O29" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="n">
-        <v/>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R29" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2969,81 +2967,81 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C30" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D30" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E30" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H30" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I30" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J30" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K30" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L30" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M30" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N30" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O30" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
       </c>
-      <c r="Q30" s="6" t="inlineStr">
+      <c r="Q30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R30" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W30" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X30" t="inlineStr"/>
@@ -3051,50 +3049,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C31" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D31" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E31" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F31" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H31" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I31" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J31" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K31" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L31" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M31" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N31" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O31" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3105,20 +3103,16 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3133,50 +3127,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C32" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D32" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E32" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F32" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H32" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I32" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J32" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K32" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L32" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M32" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N32" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O32" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3187,16 +3181,20 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3211,50 +3209,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C33" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D33" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E33" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F33" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H33" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I33" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J33" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K33" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L33" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M33" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N33" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O33" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3265,7 +3263,7 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
+      <c r="S33" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3280,8 +3278,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V33" s="8" t="n">
-        <v/>
+      <c r="V33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
@@ -3293,50 +3293,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C34" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D34" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E34" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F34" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H34" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I34" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J34" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K34" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L34" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M34" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N34" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O34" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3349,78 +3349,76 @@
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V34" s="8" t="n">
+        <v/>
       </c>
       <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C35" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D35" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E35" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F35" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H35" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I35" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J35" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K35" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L35" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M35" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N35" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O35" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3428,12 +3426,14 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3452,57 +3452,57 @@
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C36" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D36" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E36" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F36" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H36" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I36" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J36" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K36" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L36" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M36" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N36" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O36" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3510,22 +3510,24 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
@@ -3534,59 +3536,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C37" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D37" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E37" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F37" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H37" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I37" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J37" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K37" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L37" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M37" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N37" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O37" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3599,18 +3597,14 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3620,55 +3614,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C38" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D38" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E38" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F38" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H38" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I38" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J38" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K38" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L38" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M38" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N38" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O38" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3676,16 +3674,20 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3700,57 +3702,57 @@
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C39" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D39" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E39" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F39" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H39" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I39" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J39" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K39" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L39" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M39" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N39" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O39" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3758,24 +3760,24 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="U39" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="n">
-        <v/>
-      </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
@@ -3784,59 +3786,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C40" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D40" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E40" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F40" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H40" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I40" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J40" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K40" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L40" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M40" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N40" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O40" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3847,19 +3845,19 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
+      <c r="S40" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T40" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V40" s="8" t="n">
@@ -3875,50 +3873,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C41" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D41" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E41" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F41" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H41" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I41" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J41" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K41" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L41" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M41" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N41" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O41" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3929,20 +3927,16 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3952,55 +3946,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C42" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D42" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E42" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F42" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G42" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H42" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I42" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J42" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K42" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L42" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M42" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N42" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O42" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4013,11 +4011,13 @@
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4039,153 +4039,147 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C43" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D43" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E43" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F43" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H43" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I43" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J43" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K43" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L43" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M43" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N43" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O43" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
+        <v>30631.5</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C44" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D44" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E44" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F44" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H44" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I44" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J44" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K44" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L44" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M44" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N44" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O44" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30728.5</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4207,50 +4201,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C45" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D45" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E45" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F45" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H45" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I45" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J45" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K45" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L45" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M45" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N45" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O45" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4258,12 +4252,14 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4285,50 +4281,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C46" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D46" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E46" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F46" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H46" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I46" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J46" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K46" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L46" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M46" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N46" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O46" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4336,14 +4332,12 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R46" s="6" t="n">
+        <v/>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4360,68 +4354,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C47" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D47" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E47" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F47" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I47" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J47" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K47" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L47" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M47" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N47" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O47" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4438,81 +4440,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C48" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D48" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E48" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F48" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H48" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I48" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J48" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K48" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L48" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M48" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N48" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O48" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
@@ -4524,55 +4520,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C49" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D49" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E49" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F49" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H49" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I49" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J49" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K49" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L49" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M49" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N49" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O49" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4583,15 +4583,13 @@
       <c r="R49" s="6" t="n">
         <v/>
       </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4606,57 +4604,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C50" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D50" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E50" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F50" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H50" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I50" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J50" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K50" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L50" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M50" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N50" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O50" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4667,102 +4665,102 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W50" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C51" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D51" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E51" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F51" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H51" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I51" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J51" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K51" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L51" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M51" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N51" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O51" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
@@ -4772,72 +4770,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C52" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D52" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E52" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F52" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H52" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I52" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J52" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K52" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L52" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M52" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N52" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O52" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4856,72 +4856,76 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C53" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D53" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E53" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F53" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H53" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I53" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J53" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K53" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L53" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M53" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N53" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O53" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4933,83 +4937,77 @@
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W53" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C54" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D54" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E54" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F54" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H54" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I54" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J54" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K54" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L54" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M54" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N54" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O54" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P54" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30140.5</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T54" s="8" t="n">
@@ -5035,50 +5033,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C55" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D55" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E55" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F55" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H55" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I55" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J55" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K55" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L55" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M55" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N55" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O55" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5091,17 +5089,23 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
@@ -5110,57 +5114,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C56" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D56" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E56" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F56" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H56" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I56" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J56" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K56" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L56" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M56" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N56" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O56" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5171,25 +5175,19 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
       </c>
       <c r="W56" s="11" t="inlineStr">
         <is>
@@ -5205,50 +5203,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C57" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D57" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E57" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F57" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H57" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I57" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J57" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K57" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L57" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M57" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N57" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O57" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5256,16 +5254,20 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5280,57 +5282,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C58" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D58" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E58" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H58" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I58" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J58" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K58" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L58" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M58" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N58" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O58" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5340,18 +5342,16 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5364,72 +5364,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C59" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D59" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E59" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F59" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H59" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I59" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J59" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K59" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L59" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M59" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N59" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O59" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5453,72 +5451,70 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C60" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D60" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E60" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F60" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H60" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I60" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J60" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K60" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L60" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M60" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N60" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O60" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5530,55 +5526,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C61" t="n">
-        <v>29500.25</v>
+        <v>29604.5</v>
       </c>
       <c r="D61" t="n">
-        <v>29040.5</v>
+        <v>29107.25</v>
       </c>
       <c r="E61" t="n">
-        <v>29387</v>
+        <v>29489.75</v>
       </c>
       <c r="F61" t="n">
-        <v>251.75</v>
+        <v>102.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0086</v>
+        <v>0.0035</v>
       </c>
       <c r="H61" t="n">
-        <v>459.75</v>
+        <v>497.25</v>
       </c>
       <c r="I61" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J61" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K61" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L61" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M61" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N61" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O61" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5586,10 +5586,12 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -5612,7 +5614,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
@@ -5623,25 +5625,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>28580.75</v>
+        <v>28610</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>28985.56</v>
+        <v>29059.44</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>29157.12</v>
+        <v>29241.12</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>29328.69</v>
+        <v>29422.81</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>29616.88</v>
+        <v>29738.38</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>29905.06</v>
+        <v>30053.94</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>29960</v>
+        <v>30101.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5539,25 +5539,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28997.75</v>
+        <v>29488.5</v>
       </c>
       <c r="C61" t="n">
-        <v>29604.5</v>
+        <v>29495.25</v>
       </c>
       <c r="D61" t="n">
-        <v>29107.25</v>
+        <v>29426.75</v>
       </c>
       <c r="E61" t="n">
-        <v>29489.75</v>
+        <v>29448</v>
       </c>
       <c r="F61" t="n">
-        <v>102.75</v>
+        <v>61</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0035</v>
+        <v>0.0021</v>
       </c>
       <c r="H61" t="n">
-        <v>497.25</v>
+        <v>68.5</v>
       </c>
       <c r="I61" t="n">
         <v>28580.75</v>
@@ -5586,20 +5586,16 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5614,7 +5610,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5625,25 +5621,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>28610</v>
+        <v>29358.25</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>29059.44</v>
+        <v>29373</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>29241.12</v>
+        <v>29413.75</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>29422.81</v>
+        <v>29454.5</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>29738.38</v>
+        <v>29482.25</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>30053.94</v>
+        <v>29510</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>30101.75</v>
+        <v>29563.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5548,13 +5548,13 @@
         <v>29426.75</v>
       </c>
       <c r="E61" t="n">
-        <v>29448</v>
+        <v>29464.25</v>
       </c>
       <c r="F61" t="n">
-        <v>61</v>
+        <v>77.25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0026</v>
       </c>
       <c r="H61" t="n">
         <v>68.5</v>
@@ -5624,19 +5624,19 @@
         <v>29358.25</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>29373</v>
+        <v>29397.38</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>29413.75</v>
+        <v>29430</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>29454.5</v>
+        <v>29462.62</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>29482.25</v>
+        <v>29498.5</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>29510</v>
+        <v>29534.38</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>29563.75</v>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5548,13 +5548,13 @@
         <v>29426.75</v>
       </c>
       <c r="E61" t="n">
-        <v>29464.25</v>
+        <v>29455.75</v>
       </c>
       <c r="F61" t="n">
-        <v>77.25</v>
+        <v>68.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0023</v>
       </c>
       <c r="H61" t="n">
         <v>68.5</v>
@@ -5624,19 +5624,19 @@
         <v>29358.25</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>29397.38</v>
+        <v>29384.62</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>29430</v>
+        <v>29421.5</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>29462.62</v>
+        <v>29458.38</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>29498.5</v>
+        <v>29490</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>29534.38</v>
+        <v>29521.62</v>
       </c>
       <c r="O62" s="13" t="n">
         <v>29563.75</v>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5539,25 +5539,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29488.5</v>
+        <v>28997.75</v>
       </c>
       <c r="C61" t="n">
-        <v>29495.25</v>
+        <v>29303</v>
       </c>
       <c r="D61" t="n">
-        <v>29426.75</v>
+        <v>28816.25</v>
       </c>
       <c r="E61" t="n">
-        <v>29455.75</v>
+        <v>29152.25</v>
       </c>
       <c r="F61" t="n">
-        <v>68.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0023</v>
+        <v>-0.008</v>
       </c>
       <c r="H61" t="n">
-        <v>68.5</v>
+        <v>486.75</v>
       </c>
       <c r="I61" t="n">
         <v>28580.75</v>
@@ -5583,15 +5583,19 @@
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5608,11 +5612,7 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5621,25 +5621,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>29358.25</v>
+        <v>28329.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>29384.62</v>
+        <v>28711.81</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>29421.5</v>
+        <v>28908.88</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>29458.38</v>
+        <v>29105.94</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>29490</v>
+        <v>29395.62</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>29521.62</v>
+        <v>29685.31</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>29563.75</v>
+        <v>29789.75</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -641,50 +641,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29758.5</v>
+        <v>30577</v>
       </c>
       <c r="C2" t="n">
-        <v>30285.75</v>
+        <v>30968</v>
       </c>
       <c r="D2" t="n">
-        <v>29758.5</v>
+        <v>30337.5</v>
       </c>
       <c r="E2" t="n">
-        <v>30263.35</v>
+        <v>30653.5</v>
       </c>
       <c r="F2" t="n">
-        <v>575.85</v>
+        <v>390.15</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0194</v>
+        <v>0.0129</v>
       </c>
       <c r="H2" t="n">
-        <v>527.25</v>
+        <v>630.5</v>
       </c>
       <c r="I2" t="n">
-        <v>28963.5</v>
+        <v>29231.25</v>
       </c>
       <c r="J2" t="n">
-        <v>28907.62</v>
+        <v>29856.71</v>
       </c>
       <c r="K2" t="n">
-        <v>29361.25</v>
+        <v>29999.72</v>
       </c>
       <c r="L2" t="n">
-        <v>29814.88</v>
+        <v>30142.74</v>
       </c>
       <c r="M2" t="n">
-        <v>30013.75</v>
+        <v>30526.97</v>
       </c>
       <c r="N2" t="n">
-        <v>30212.62</v>
+        <v>30911.21</v>
       </c>
       <c r="O2" t="n">
-        <v>30921</v>
+        <v>30813</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -702,16 +702,18 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="n">
-        <v/>
+      <c r="V2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
@@ -723,83 +725,83 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30577</v>
+        <v>30662.75</v>
       </c>
       <c r="C3" t="n">
-        <v>30968</v>
+        <v>30701.25</v>
       </c>
       <c r="D3" t="n">
-        <v>30337.5</v>
+        <v>29577.25</v>
       </c>
       <c r="E3" t="n">
-        <v>30653.5</v>
+        <v>29666</v>
       </c>
       <c r="F3" t="n">
-        <v>390.15</v>
+        <v>-987.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0322</v>
       </c>
       <c r="H3" t="n">
-        <v>630.5</v>
+        <v>1124</v>
       </c>
       <c r="I3" t="n">
-        <v>29231.25</v>
+        <v>29707</v>
       </c>
       <c r="J3" t="n">
-        <v>29856.71</v>
+        <v>30023.38</v>
       </c>
       <c r="K3" t="n">
-        <v>29999.72</v>
+        <v>30338.25</v>
       </c>
       <c r="L3" t="n">
-        <v>30142.74</v>
+        <v>30653.12</v>
       </c>
       <c r="M3" t="n">
-        <v>30526.97</v>
+        <v>30968.75</v>
       </c>
       <c r="N3" t="n">
-        <v>30911.21</v>
+        <v>31284.38</v>
       </c>
       <c r="O3" t="n">
-        <v>30813</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+        <v>31598.5</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U3" s="8" t="inlineStr">
+      <c r="Q3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V3" s="8" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V3" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -807,69 +809,63 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30662.75</v>
+        <v>29770</v>
       </c>
       <c r="C4" t="n">
-        <v>30701.25</v>
+        <v>30157.75</v>
       </c>
       <c r="D4" t="n">
-        <v>29577.25</v>
+        <v>29264.75</v>
       </c>
       <c r="E4" t="n">
-        <v>29666</v>
+        <v>29514.25</v>
       </c>
       <c r="F4" t="n">
-        <v>-987.5</v>
+        <v>-151.75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0051</v>
       </c>
       <c r="H4" t="n">
-        <v>1124</v>
+        <v>893</v>
       </c>
       <c r="I4" t="n">
-        <v>29707</v>
+        <v>28453.25</v>
       </c>
       <c r="J4" t="n">
-        <v>30023.38</v>
+        <v>28305.38</v>
       </c>
       <c r="K4" t="n">
-        <v>30338.25</v>
+        <v>29104</v>
       </c>
       <c r="L4" t="n">
-        <v>30653.12</v>
+        <v>29902.62</v>
       </c>
       <c r="M4" t="n">
-        <v>30968.75</v>
+        <v>30228</v>
       </c>
       <c r="N4" t="n">
-        <v>31284.38</v>
+        <v>30553.38</v>
       </c>
       <c r="O4" t="n">
-        <v>31598.5</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31825.25</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -891,50 +887,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29770</v>
+        <v>30089.75</v>
       </c>
       <c r="C5" t="n">
-        <v>30157.75</v>
+        <v>30263.75</v>
       </c>
       <c r="D5" t="n">
-        <v>29264.75</v>
+        <v>29295.75</v>
       </c>
       <c r="E5" t="n">
-        <v>29514.25</v>
+        <v>29724.75</v>
       </c>
       <c r="F5" t="n">
-        <v>-151.75</v>
+        <v>210.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0071</v>
       </c>
       <c r="H5" t="n">
-        <v>893</v>
+        <v>968</v>
       </c>
       <c r="I5" t="n">
-        <v>28453.25</v>
+        <v>28371.75</v>
       </c>
       <c r="J5" t="n">
-        <v>28305.38</v>
+        <v>28522.75</v>
       </c>
       <c r="K5" t="n">
-        <v>29104</v>
+        <v>29067.75</v>
       </c>
       <c r="L5" t="n">
-        <v>29902.62</v>
+        <v>29612.75</v>
       </c>
       <c r="M5" t="n">
-        <v>30228</v>
+        <v>29960.75</v>
       </c>
       <c r="N5" t="n">
-        <v>30553.38</v>
+        <v>30308.75</v>
       </c>
       <c r="O5" t="n">
-        <v>31825.25</v>
+        <v>31050.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -945,13 +941,15 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -964,55 +962,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30089.75</v>
+        <v>29742</v>
       </c>
       <c r="C6" t="n">
-        <v>30263.75</v>
+        <v>29892.75</v>
       </c>
       <c r="D6" t="n">
-        <v>29295.75</v>
+        <v>29160.5</v>
       </c>
       <c r="E6" t="n">
-        <v>29724.75</v>
+        <v>29368.25</v>
       </c>
       <c r="F6" t="n">
-        <v>210.5</v>
+        <v>-356.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.012</v>
       </c>
       <c r="H6" t="n">
-        <v>968</v>
+        <v>732.25</v>
       </c>
       <c r="I6" t="n">
-        <v>28371.75</v>
+        <v>28327.75</v>
       </c>
       <c r="J6" t="n">
-        <v>28522.75</v>
+        <v>28729.25</v>
       </c>
       <c r="K6" t="n">
-        <v>29067.75</v>
+        <v>29240.75</v>
       </c>
       <c r="L6" t="n">
-        <v>29612.75</v>
+        <v>29752.25</v>
       </c>
       <c r="M6" t="n">
-        <v>29960.75</v>
+        <v>30208.75</v>
       </c>
       <c r="N6" t="n">
-        <v>30308.75</v>
+        <v>30665.25</v>
       </c>
       <c r="O6" t="n">
-        <v>31050.75</v>
+        <v>31231.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1020,18 +1022,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1044,59 +1046,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29742</v>
+        <v>29282.5</v>
       </c>
       <c r="C7" t="n">
-        <v>29892.75</v>
+        <v>30069.5</v>
       </c>
       <c r="D7" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E7" t="n">
-        <v>29368.25</v>
+        <v>30052.75</v>
       </c>
       <c r="F7" t="n">
-        <v>-356.5</v>
+        <v>684.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0233</v>
       </c>
       <c r="H7" t="n">
-        <v>732.25</v>
+        <v>795.75</v>
       </c>
       <c r="I7" t="n">
-        <v>28327.75</v>
+        <v>28428.25</v>
       </c>
       <c r="J7" t="n">
-        <v>28729.25</v>
+        <v>28556.81</v>
       </c>
       <c r="K7" t="n">
-        <v>29240.75</v>
+        <v>29002.12</v>
       </c>
       <c r="L7" t="n">
-        <v>29752.25</v>
+        <v>29447.44</v>
       </c>
       <c r="M7" t="n">
-        <v>30208.75</v>
+        <v>29734.38</v>
       </c>
       <c r="N7" t="n">
-        <v>30665.25</v>
+        <v>30021.31</v>
       </c>
       <c r="O7" t="n">
-        <v>31231.75</v>
+        <v>30625</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1104,28 +1102,30 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U7" s="8" t="n">
-        <v/>
-      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W7" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr"/>
@@ -1133,50 +1133,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29282.5</v>
+        <v>30007.25</v>
       </c>
       <c r="C8" t="n">
-        <v>30069.5</v>
+        <v>30599.75</v>
       </c>
       <c r="D8" t="n">
-        <v>29273.75</v>
+        <v>29934.75</v>
       </c>
       <c r="E8" t="n">
-        <v>30052.75</v>
+        <v>30523.5</v>
       </c>
       <c r="F8" t="n">
-        <v>684.5</v>
+        <v>470.75</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0157</v>
       </c>
       <c r="H8" t="n">
-        <v>795.75</v>
+        <v>665</v>
       </c>
       <c r="I8" t="n">
-        <v>28428.25</v>
+        <v>28478</v>
       </c>
       <c r="J8" t="n">
-        <v>28556.81</v>
+        <v>29447.56</v>
       </c>
       <c r="K8" t="n">
-        <v>29002.12</v>
+        <v>29654.88</v>
       </c>
       <c r="L8" t="n">
-        <v>29447.44</v>
+        <v>29862.19</v>
       </c>
       <c r="M8" t="n">
-        <v>29734.38</v>
+        <v>30450.62</v>
       </c>
       <c r="N8" t="n">
-        <v>30021.31</v>
+        <v>31039.06</v>
       </c>
       <c r="O8" t="n">
-        <v>30625</v>
+        <v>30865.25</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1194,13 +1194,11 @@
       </c>
       <c r="T8" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U8" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U8" s="8" t="n">
+        <v/>
       </c>
       <c r="V8" s="8" t="n">
         <v/>
@@ -1215,50 +1213,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C9" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D9" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E9" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F9" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H9" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I9" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J9" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K9" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L9" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M9" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N9" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O9" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1266,19 +1264,19 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
+      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1290,65 +1288,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C10" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D10" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E10" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F10" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H10" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I10" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J10" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K10" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L10" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M10" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N10" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O10" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S10" s="10" t="inlineStr">
@@ -1372,81 +1378,77 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C11" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D11" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E11" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F11" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H11" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I11" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J11" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K11" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L11" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M11" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N11" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O11" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1460,160 +1462,156 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C12" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D12" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E12" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F12" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H12" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I12" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J12" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K12" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L12" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M12" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N12" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O12" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
+        <v>30505</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C13" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D13" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E13" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F13" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H13" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I13" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J13" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K13" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L13" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M13" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N13" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O13" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q13" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1630,55 +1628,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C14" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D14" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E14" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F14" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H14" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I14" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J14" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K14" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L14" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M14" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N14" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O14" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1686,18 +1688,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1712,57 +1714,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C15" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D15" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E15" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F15" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H15" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I15" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J15" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K15" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L15" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M15" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N15" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O15" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1803,70 +1805,74 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C16" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D16" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E16" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F16" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H16" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I16" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J16" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K16" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L16" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M16" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N16" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O16" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+        <v>30480.5</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
@@ -1878,83 +1884,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C17" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D17" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E17" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H17" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I17" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J17" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K17" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L17" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M17" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N17" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O17" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
       <c r="U17" s="8" t="n">
         <v/>
       </c>
@@ -1966,55 +1964,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C18" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D18" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E18" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F18" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H18" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I18" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J18" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K18" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L18" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M18" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N18" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O18" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2022,18 +2024,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2048,57 +2050,57 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C19" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D19" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E19" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H19" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I19" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J19" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K19" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L19" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M19" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N19" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O19" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2108,12 +2110,12 @@
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2130,59 +2132,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C20" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D20" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E20" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F20" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H20" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I20" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J20" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K20" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L20" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M20" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N20" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O20" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2219,50 +2217,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C21" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D21" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E21" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F21" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H21" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I21" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J21" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K21" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L21" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M21" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N21" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O21" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2270,18 +2268,18 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R21" s="6" t="n">
+        <v/>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U21" s="8" t="n">
         <v/>
@@ -2294,55 +2292,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C22" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D22" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E22" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F22" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H22" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I22" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J22" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K22" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L22" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M22" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N22" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O22" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2353,9 +2355,9 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T22" s="8" t="inlineStr">
@@ -2363,70 +2365,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C23" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D23" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E23" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F23" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H23" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I23" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J23" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K23" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L23" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M23" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N23" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O23" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2434,23 +2438,21 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2462,72 +2464,76 @@
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C24" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D24" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E24" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F24" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H24" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I24" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J24" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K24" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L24" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M24" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N24" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O24" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2539,78 +2545,70 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W24" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C25" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D25" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E25" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H25" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I25" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J25" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K25" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L25" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M25" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N25" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O25" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P25" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S25" s="10" t="inlineStr">
@@ -2637,50 +2635,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C26" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D26" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E26" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F26" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H26" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I26" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J26" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K26" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L26" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M26" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N26" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O26" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2698,11 +2696,15 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2712,55 +2714,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C27" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D27" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E27" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F27" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H27" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I27" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J27" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K27" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L27" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M27" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N27" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O27" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2778,15 +2784,11 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2796,69 +2798,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C28" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D28" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E28" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F28" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H28" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I28" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J28" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K28" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L28" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M28" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N28" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O28" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="n">
-        <v/>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R28" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
@@ -2885,81 +2885,81 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C29" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D29" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E29" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F29" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H29" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I29" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J29" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K29" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L29" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M29" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N29" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O29" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
       </c>
-      <c r="Q29" s="6" t="inlineStr">
+      <c r="Q29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R29" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W29" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X29" t="inlineStr"/>
@@ -2967,50 +2967,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C30" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D30" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E30" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F30" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H30" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I30" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J30" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K30" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L30" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M30" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N30" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O30" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,18 +3023,14 @@
       </c>
       <c r="S30" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3049,50 +3045,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C31" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D31" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E31" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F31" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H31" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I31" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J31" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K31" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L31" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M31" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N31" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O31" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3105,14 +3101,18 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3127,50 +3127,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C32" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D32" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E32" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F32" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H32" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I32" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J32" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K32" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L32" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M32" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N32" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O32" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3196,8 +3196,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V32" s="8" t="n">
-        <v/>
+      <c r="V32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
@@ -3209,50 +3211,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C33" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D33" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E33" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F33" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H33" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I33" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J33" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K33" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L33" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M33" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N33" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O33" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3263,80 +3265,78 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V33" s="8" t="n">
+        <v/>
       </c>
       <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C34" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D34" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E34" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F34" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H34" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I34" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J34" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K34" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L34" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M34" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N34" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O34" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3344,12 +3344,14 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3368,57 +3370,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C35" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D35" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E35" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F35" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H35" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I35" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J35" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K35" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L35" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M35" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N35" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O35" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3426,22 +3428,24 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3450,59 +3454,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C36" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D36" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E36" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F36" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H36" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I36" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J36" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K36" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L36" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M36" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N36" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O36" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3513,20 +3513,16 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3536,55 +3532,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C37" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D37" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E37" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F37" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H37" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I37" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J37" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K37" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L37" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M37" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N37" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O37" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3592,16 +3592,20 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3616,57 +3620,57 @@
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C38" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D38" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E38" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F38" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H38" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I38" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J38" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K38" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L38" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M38" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N38" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O38" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3674,24 +3678,24 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+      <c r="U38" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U38" s="8" t="n">
-        <v/>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
@@ -3700,59 +3704,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C39" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D39" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E39" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F39" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H39" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I39" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J39" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K39" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L39" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M39" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N39" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O39" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3770,12 +3770,12 @@
       </c>
       <c r="T39" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V39" s="8" t="n">
@@ -3791,50 +3791,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C40" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D40" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E40" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F40" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H40" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I40" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J40" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K40" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L40" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M40" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N40" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O40" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3847,18 +3847,14 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
@@ -3868,55 +3864,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C41" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D41" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E41" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F41" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G41" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H41" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I41" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J41" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K41" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L41" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M41" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N41" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O41" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3927,13 +3927,15 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3955,69 +3957,73 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C42" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D42" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E42" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F42" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H42" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I42" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J42" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K42" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L42" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M42" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N42" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O42" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+        <v>30631.5</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4025,83 +4031,73 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C43" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D43" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E43" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F43" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H43" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I43" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J43" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K43" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L43" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M43" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N43" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O43" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30728.5</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4123,50 +4119,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C44" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D44" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E44" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F44" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H44" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I44" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J44" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K44" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L44" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M44" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N44" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O44" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4174,12 +4170,14 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="n">
-        <v/>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4201,50 +4199,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C45" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D45" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E45" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F45" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H45" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I45" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J45" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K45" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L45" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M45" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N45" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O45" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4252,14 +4250,12 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4276,68 +4272,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C46" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D46" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E46" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F46" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H46" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I46" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J46" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K46" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L46" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M46" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N46" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O46" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4354,81 +4358,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C47" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D47" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E47" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F47" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H47" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I47" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J47" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K47" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L47" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M47" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N47" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O47" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
       <c r="U47" s="8" t="n">
         <v/>
       </c>
@@ -4440,55 +4438,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C48" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D48" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E48" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F48" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H48" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I48" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J48" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K48" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L48" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M48" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N48" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O48" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4501,13 +4503,11 @@
       </c>
       <c r="S48" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4522,57 +4522,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C49" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D49" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E49" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F49" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H49" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I49" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J49" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K49" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L49" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M49" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N49" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O49" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4585,100 +4585,100 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W49" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C50" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D50" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E50" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F50" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H50" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I50" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J50" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K50" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L50" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M50" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N50" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O50" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
       </c>
       <c r="V50" s="8" t="n">
         <v/>
@@ -4688,63 +4688,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C51" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D51" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E51" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F51" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H51" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I51" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J51" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K51" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L51" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M51" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N51" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O51" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
@@ -4753,7 +4755,7 @@
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4772,63 +4774,67 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C52" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D52" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E52" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F52" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H52" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I52" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J52" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K52" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L52" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M52" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N52" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O52" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
@@ -4837,7 +4843,7 @@
       </c>
       <c r="S52" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4849,83 +4855,77 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W52" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C53" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D53" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E53" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F53" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H53" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I53" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J53" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K53" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L53" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M53" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N53" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O53" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P53" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30140.5</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T53" s="8" t="n">
@@ -4951,50 +4951,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C54" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D54" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E54" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F54" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H54" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I54" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J54" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K54" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L54" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M54" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N54" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O54" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5005,19 +5005,25 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W54" s="11" t="inlineStr">
         <is>
@@ -5026,57 +5032,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C55" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D55" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E55" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F55" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H55" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I55" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J55" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K55" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L55" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M55" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N55" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O55" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5089,23 +5095,17 @@
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
       </c>
       <c r="W55" s="11" t="inlineStr">
         <is>
@@ -5121,50 +5121,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C56" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D56" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E56" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F56" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H56" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I56" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J56" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K56" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L56" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M56" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N56" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O56" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5172,16 +5172,20 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5196,57 +5200,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C57" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D57" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E57" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F57" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H57" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I57" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J57" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K57" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L57" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M57" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N57" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O57" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5256,18 +5260,16 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5280,69 +5282,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C58" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D58" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F58" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H58" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I58" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J58" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K58" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L58" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M58" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N58" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O58" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
@@ -5369,72 +5369,70 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C59" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D59" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E59" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F59" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H59" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I59" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J59" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K59" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L59" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M59" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N59" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O59" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
+      <c r="Q59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5446,75 +5444,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C60" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D60" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E60" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F60" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H60" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I60" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J60" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K60" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L60" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M60" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N60" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O60" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
+      </c>
       <c r="U60" s="8" t="n">
         <v/>
       </c>
@@ -5526,81 +5530,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28997.75</v>
+        <v>29488.5</v>
       </c>
       <c r="C61" t="n">
-        <v>29303</v>
+        <v>29495.25</v>
       </c>
       <c r="D61" t="n">
-        <v>28816.25</v>
+        <v>29207.5</v>
       </c>
       <c r="E61" t="n">
-        <v>29152.25</v>
+        <v>29277</v>
       </c>
       <c r="F61" t="n">
-        <v>-234.75</v>
+        <v>124.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.008</v>
+        <v>0.0043</v>
       </c>
       <c r="H61" t="n">
-        <v>486.75</v>
+        <v>287.75</v>
       </c>
       <c r="I61" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J61" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K61" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L61" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M61" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N61" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O61" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5612,7 +5610,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="12" t="inlineStr">
@@ -5621,25 +5623,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>28329.5</v>
+        <v>28919.75</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>28711.81</v>
+        <v>28952.06</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>28908.88</v>
+        <v>29133.12</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>29105.94</v>
+        <v>29314.19</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>29395.62</v>
+        <v>29420.88</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>29685.31</v>
+        <v>29527.56</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>29789.75</v>
+        <v>29783</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5539,25 +5539,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29488.5</v>
+        <v>29263.75</v>
       </c>
       <c r="C61" t="n">
-        <v>29495.25</v>
+        <v>29289.25</v>
       </c>
       <c r="D61" t="n">
-        <v>29207.5</v>
+        <v>29240.5</v>
       </c>
       <c r="E61" t="n">
-        <v>29277</v>
+        <v>29254.25</v>
       </c>
       <c r="F61" t="n">
-        <v>124.75</v>
+        <v>102</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0043</v>
+        <v>0.0035</v>
       </c>
       <c r="H61" t="n">
-        <v>287.75</v>
+        <v>48.75</v>
       </c>
       <c r="I61" t="n">
         <v>28329.5</v>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
@@ -5623,25 +5623,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>28919.75</v>
+        <v>29191.75</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>28952.06</v>
+        <v>29200.19</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>29133.12</v>
+        <v>29229.88</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>29314.19</v>
+        <v>29259.56</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>29420.88</v>
+        <v>29278.62</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>29527.56</v>
+        <v>29297.69</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>29783</v>
+        <v>29338</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5539,25 +5539,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29263.75</v>
+        <v>29200</v>
       </c>
       <c r="C61" t="n">
-        <v>29289.25</v>
+        <v>29200</v>
       </c>
       <c r="D61" t="n">
-        <v>29240.5</v>
+        <v>28918.75</v>
       </c>
       <c r="E61" t="n">
-        <v>29254.25</v>
+        <v>28955</v>
       </c>
       <c r="F61" t="n">
-        <v>102</v>
+        <v>-197.25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0035</v>
+        <v>-0.0068</v>
       </c>
       <c r="H61" t="n">
-        <v>48.75</v>
+        <v>281.25</v>
       </c>
       <c r="I61" t="n">
         <v>28329.5</v>
@@ -5586,62 +5586,144 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>29263.75</v>
+      </c>
+      <c r="C62" t="n">
+        <v>29358.5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>29226</v>
+      </c>
+      <c r="E62" t="n">
+        <v>29323.5</v>
+      </c>
+      <c r="F62" t="n">
+        <v>368.5</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0127</v>
+      </c>
+      <c r="H62" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="I62" t="n">
+        <v>28637.5</v>
+      </c>
+      <c r="J62" t="n">
+        <v>28621.56</v>
+      </c>
+      <c r="K62" t="n">
+        <v>28814.38</v>
+      </c>
+      <c r="L62" t="n">
+        <v>29007.19</v>
+      </c>
+      <c r="M62" t="n">
+        <v>29095.62</v>
+      </c>
+      <c r="N62" t="n">
+        <v>29184.06</v>
+      </c>
+      <c r="O62" t="n">
+        <v>29481.25</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W61" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>29191.75</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>29200.19</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>29229.88</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>29259.56</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>29278.62</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>29297.69</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>29338</v>
+      <c r="I63" s="13" t="n">
+        <v>29093.5</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>29206.62</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>29257.25</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>29307.88</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>29389.75</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>29471.62</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>29491</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5626,22 +5626,22 @@
         <v>29263.75</v>
       </c>
       <c r="C62" t="n">
-        <v>29358.5</v>
+        <v>29419.25</v>
       </c>
       <c r="D62" t="n">
         <v>29226</v>
       </c>
       <c r="E62" t="n">
-        <v>29323.5</v>
+        <v>29382</v>
       </c>
       <c r="F62" t="n">
-        <v>368.5</v>
+        <v>427</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0127</v>
+        <v>0.0147</v>
       </c>
       <c r="H62" t="n">
-        <v>132.5</v>
+        <v>193.25</v>
       </c>
       <c r="I62" t="n">
         <v>28637.5</v>
@@ -5685,11 +5685,13 @@
       </c>
       <c r="U62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
@@ -5705,25 +5707,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>29093.5</v>
+        <v>29032.75</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>29206.62</v>
+        <v>29218.44</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>29257.25</v>
+        <v>29285.38</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>29307.88</v>
+        <v>29352.31</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>29389.75</v>
+        <v>29478.62</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>29471.62</v>
+        <v>29604.94</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>29491</v>
+        <v>29612.5</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5632,13 +5632,13 @@
         <v>29226</v>
       </c>
       <c r="E62" t="n">
-        <v>29382</v>
+        <v>29413.25</v>
       </c>
       <c r="F62" t="n">
-        <v>427</v>
+        <v>458.25</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0147</v>
+        <v>0.0158</v>
       </c>
       <c r="H62" t="n">
         <v>193.25</v>
@@ -5710,19 +5710,19 @@
         <v>29032.75</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>29218.44</v>
+        <v>29265.31</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>29285.38</v>
+        <v>29316.62</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>29352.31</v>
+        <v>29367.94</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>29478.62</v>
+        <v>29509.88</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>29604.94</v>
+        <v>29651.81</v>
       </c>
       <c r="O63" s="13" t="n">
         <v>29612.5</v>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5626,22 +5626,22 @@
         <v>29263.75</v>
       </c>
       <c r="C62" t="n">
-        <v>29419.25</v>
+        <v>29439</v>
       </c>
       <c r="D62" t="n">
         <v>29226</v>
       </c>
       <c r="E62" t="n">
-        <v>29413.25</v>
+        <v>29432.75</v>
       </c>
       <c r="F62" t="n">
-        <v>458.25</v>
+        <v>477.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0158</v>
+        <v>0.0165</v>
       </c>
       <c r="H62" t="n">
-        <v>193.25</v>
+        <v>213</v>
       </c>
       <c r="I62" t="n">
         <v>28637.5</v>
@@ -5707,25 +5707,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>29032.75</v>
+        <v>29013</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>29265.31</v>
+        <v>29269.88</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>29316.62</v>
+        <v>29326.25</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>29367.94</v>
+        <v>29382.62</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>29509.88</v>
+        <v>29539.25</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>29651.81</v>
+        <v>29695.88</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>29612.5</v>
+        <v>29652</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -109,17 +109,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -641,83 +641,83 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-23</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30577</v>
+        <v>30662.75</v>
       </c>
       <c r="C2" t="n">
-        <v>30968</v>
+        <v>30701.25</v>
       </c>
       <c r="D2" t="n">
-        <v>30337.5</v>
+        <v>29577.25</v>
       </c>
       <c r="E2" t="n">
-        <v>30653.5</v>
+        <v>29666</v>
       </c>
       <c r="F2" t="n">
-        <v>390.15</v>
+        <v>-987.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0129</v>
+        <v>-0.0322</v>
       </c>
       <c r="H2" t="n">
-        <v>630.5</v>
+        <v>1124</v>
       </c>
       <c r="I2" t="n">
-        <v>29231.25</v>
+        <v>29707</v>
       </c>
       <c r="J2" t="n">
-        <v>29856.71</v>
+        <v>30023.38</v>
       </c>
       <c r="K2" t="n">
-        <v>29999.72</v>
+        <v>30338.25</v>
       </c>
       <c r="L2" t="n">
-        <v>30142.74</v>
+        <v>30653.12</v>
       </c>
       <c r="M2" t="n">
-        <v>30526.97</v>
+        <v>30968.75</v>
       </c>
       <c r="N2" t="n">
-        <v>30911.21</v>
+        <v>31284.38</v>
       </c>
       <c r="O2" t="n">
-        <v>30813</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>31598.5</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V2" s="8" t="n">
+        <v/>
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X2" t="inlineStr"/>
@@ -725,69 +725,63 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30662.75</v>
+        <v>29770</v>
       </c>
       <c r="C3" t="n">
-        <v>30701.25</v>
+        <v>30157.75</v>
       </c>
       <c r="D3" t="n">
-        <v>29577.25</v>
+        <v>29264.75</v>
       </c>
       <c r="E3" t="n">
-        <v>29666</v>
+        <v>29514.25</v>
       </c>
       <c r="F3" t="n">
-        <v>-987.5</v>
+        <v>-151.75</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0051</v>
       </c>
       <c r="H3" t="n">
-        <v>1124</v>
+        <v>893</v>
       </c>
       <c r="I3" t="n">
-        <v>29707</v>
+        <v>28453.25</v>
       </c>
       <c r="J3" t="n">
-        <v>30023.38</v>
+        <v>28305.38</v>
       </c>
       <c r="K3" t="n">
-        <v>30338.25</v>
+        <v>29104</v>
       </c>
       <c r="L3" t="n">
-        <v>30653.12</v>
+        <v>29902.62</v>
       </c>
       <c r="M3" t="n">
-        <v>30968.75</v>
+        <v>30228</v>
       </c>
       <c r="N3" t="n">
-        <v>31284.38</v>
+        <v>30553.38</v>
       </c>
       <c r="O3" t="n">
-        <v>31598.5</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>31825.25</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -799,7 +793,7 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -809,50 +803,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29770</v>
+        <v>30089.75</v>
       </c>
       <c r="C4" t="n">
-        <v>30157.75</v>
+        <v>30263.75</v>
       </c>
       <c r="D4" t="n">
-        <v>29264.75</v>
+        <v>29295.75</v>
       </c>
       <c r="E4" t="n">
-        <v>29514.25</v>
+        <v>29724.75</v>
       </c>
       <c r="F4" t="n">
-        <v>-151.75</v>
+        <v>210.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0071</v>
       </c>
       <c r="H4" t="n">
-        <v>893</v>
+        <v>968</v>
       </c>
       <c r="I4" t="n">
-        <v>28453.25</v>
+        <v>28371.75</v>
       </c>
       <c r="J4" t="n">
-        <v>28305.38</v>
+        <v>28522.75</v>
       </c>
       <c r="K4" t="n">
-        <v>29104</v>
+        <v>29067.75</v>
       </c>
       <c r="L4" t="n">
-        <v>29902.62</v>
+        <v>29612.75</v>
       </c>
       <c r="M4" t="n">
-        <v>30228</v>
+        <v>29960.75</v>
       </c>
       <c r="N4" t="n">
-        <v>30553.38</v>
+        <v>30308.75</v>
       </c>
       <c r="O4" t="n">
-        <v>31825.25</v>
+        <v>31050.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -865,11 +859,13 @@
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -877,60 +873,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30089.75</v>
+        <v>29742</v>
       </c>
       <c r="C5" t="n">
-        <v>30263.75</v>
+        <v>29892.75</v>
       </c>
       <c r="D5" t="n">
-        <v>29295.75</v>
+        <v>29160.5</v>
       </c>
       <c r="E5" t="n">
-        <v>29724.75</v>
+        <v>29368.25</v>
       </c>
       <c r="F5" t="n">
-        <v>210.5</v>
+        <v>-356.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.012</v>
       </c>
       <c r="H5" t="n">
-        <v>968</v>
+        <v>732.25</v>
       </c>
       <c r="I5" t="n">
-        <v>28371.75</v>
+        <v>28327.75</v>
       </c>
       <c r="J5" t="n">
-        <v>28522.75</v>
+        <v>28729.25</v>
       </c>
       <c r="K5" t="n">
-        <v>29067.75</v>
+        <v>29240.75</v>
       </c>
       <c r="L5" t="n">
-        <v>29612.75</v>
+        <v>29752.25</v>
       </c>
       <c r="M5" t="n">
-        <v>29960.75</v>
+        <v>30208.75</v>
       </c>
       <c r="N5" t="n">
-        <v>30308.75</v>
+        <v>30665.25</v>
       </c>
       <c r="O5" t="n">
-        <v>31050.75</v>
+        <v>31231.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -938,18 +938,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -957,64 +957,60 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29742</v>
+        <v>29282.5</v>
       </c>
       <c r="C6" t="n">
-        <v>29892.75</v>
+        <v>30069.5</v>
       </c>
       <c r="D6" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E6" t="n">
-        <v>29368.25</v>
+        <v>30052.75</v>
       </c>
       <c r="F6" t="n">
-        <v>-356.5</v>
+        <v>684.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0233</v>
       </c>
       <c r="H6" t="n">
-        <v>732.25</v>
+        <v>795.75</v>
       </c>
       <c r="I6" t="n">
-        <v>28327.75</v>
+        <v>28428.25</v>
       </c>
       <c r="J6" t="n">
-        <v>28729.25</v>
+        <v>28556.81</v>
       </c>
       <c r="K6" t="n">
-        <v>29240.75</v>
+        <v>29002.12</v>
       </c>
       <c r="L6" t="n">
-        <v>29752.25</v>
+        <v>29447.44</v>
       </c>
       <c r="M6" t="n">
-        <v>30208.75</v>
+        <v>29734.38</v>
       </c>
       <c r="N6" t="n">
-        <v>30665.25</v>
+        <v>30021.31</v>
       </c>
       <c r="O6" t="n">
-        <v>31231.75</v>
+        <v>30625</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1022,28 +1018,30 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U6" s="8" t="n">
-        <v/>
-      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
       <c r="W6" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X6" t="inlineStr"/>
@@ -1051,50 +1049,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29282.5</v>
+        <v>30007.25</v>
       </c>
       <c r="C7" t="n">
-        <v>30069.5</v>
+        <v>30599.75</v>
       </c>
       <c r="D7" t="n">
-        <v>29273.75</v>
+        <v>29934.75</v>
       </c>
       <c r="E7" t="n">
-        <v>30052.75</v>
+        <v>30523.5</v>
       </c>
       <c r="F7" t="n">
-        <v>684.5</v>
+        <v>470.75</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0157</v>
       </c>
       <c r="H7" t="n">
-        <v>795.75</v>
+        <v>665</v>
       </c>
       <c r="I7" t="n">
-        <v>28428.25</v>
+        <v>28478</v>
       </c>
       <c r="J7" t="n">
-        <v>28556.81</v>
+        <v>29447.56</v>
       </c>
       <c r="K7" t="n">
-        <v>29002.12</v>
+        <v>29654.88</v>
       </c>
       <c r="L7" t="n">
-        <v>29447.44</v>
+        <v>29862.19</v>
       </c>
       <c r="M7" t="n">
-        <v>29734.38</v>
+        <v>30450.62</v>
       </c>
       <c r="N7" t="n">
-        <v>30021.31</v>
+        <v>31039.06</v>
       </c>
       <c r="O7" t="n">
-        <v>30625</v>
+        <v>30865.25</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,25 +1103,23 @@
       <c r="R7" s="6" t="n">
         <v/>
       </c>
-      <c r="S7" s="7" t="inlineStr">
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T7" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U7" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U7" s="8" t="n">
+        <v/>
+      </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1133,50 +1129,50 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C8" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D8" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E8" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F8" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H8" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I8" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J8" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K8" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L8" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M8" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N8" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O8" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1184,18 +1180,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1203,73 +1199,81 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C9" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D9" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E9" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F9" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H9" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I9" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J9" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K9" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L9" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M9" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N9" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O9" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1283,171 +1287,171 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C10" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D10" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E10" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F10" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H10" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I10" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J10" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K10" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L10" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M10" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N10" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O10" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C11" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D11" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E11" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F11" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H11" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I11" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J11" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K11" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L11" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M11" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N11" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O11" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>30505</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1457,81 +1461,73 @@
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C12" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D12" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E12" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F12" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H12" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I12" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J12" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K12" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L12" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M12" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N12" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O12" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q12" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1543,60 +1539,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C13" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D13" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E13" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F13" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H13" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I13" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J13" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K13" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L13" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M13" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N13" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O13" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1604,18 +1604,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1623,64 +1623,64 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
+      <c r="W13" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C14" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D14" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E14" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F14" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H14" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I14" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J14" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K14" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L14" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M14" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N14" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O14" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1691,7 +1691,7 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1707,7 +1707,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
+      <c r="W14" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1721,69 +1721,73 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C15" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D15" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E15" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F15" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H15" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I15" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J15" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K15" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L15" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M15" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N15" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O15" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+        <v>30480.5</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1791,148 +1795,144 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C16" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D16" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E16" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H16" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I16" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J16" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K16" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L16" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M16" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N16" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O16" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
       <c r="U16" s="8" t="n">
         <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C17" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D17" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E17" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F17" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H17" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I17" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J17" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K17" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L17" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M17" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N17" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O17" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,18 +1940,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1959,64 +1959,64 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C18" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D18" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E18" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F18" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H18" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I18" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J18" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K18" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L18" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M18" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N18" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O18" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2026,12 +2026,12 @@
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2043,64 +2043,60 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C19" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D19" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E19" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H19" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I19" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J19" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K19" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L19" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M19" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N19" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O19" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2113,7 +2109,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2127,7 +2123,7 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2137,50 +2133,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C20" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D20" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E20" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F20" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H20" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I20" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J20" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K20" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L20" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M20" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N20" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O20" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,18 +2184,18 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U20" s="8" t="n">
         <v/>
@@ -2207,60 +2203,64 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C21" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D21" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E21" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F21" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H21" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I21" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J21" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K21" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L21" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M21" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N21" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O21" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2273,7 +2273,7 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T21" s="8" t="inlineStr">
@@ -2281,70 +2281,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
       <c r="W21" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C22" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D22" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E22" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F22" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H22" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I22" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J22" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K22" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L22" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M22" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N22" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O22" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2352,91 +2354,93 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C23" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D23" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E23" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H23" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I23" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J23" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K23" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L23" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M23" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N23" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O23" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P23" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
@@ -2445,7 +2449,7 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2459,79 +2463,71 @@
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C24" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D24" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E24" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H24" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I24" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J24" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K24" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L24" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M24" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N24" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O24" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P24" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2545,7 +2541,7 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2555,50 +2551,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C25" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D25" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E25" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F25" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H25" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I25" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J25" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K25" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L25" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M25" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N25" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O25" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2611,74 +2607,82 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
+      <c r="S25" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C26" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D26" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E26" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F26" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H26" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I26" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J26" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K26" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L26" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M26" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N26" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O26" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2691,95 +2695,89 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="10" t="inlineStr">
+      <c r="S26" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C27" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D27" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E27" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F27" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H27" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I27" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J27" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K27" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L27" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M27" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N27" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O27" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="n">
-        <v/>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R27" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2793,7 +2791,7 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2803,81 +2801,81 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C28" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D28" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E28" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F28" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H28" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I28" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J28" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K28" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L28" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M28" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N28" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O28" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
       </c>
-      <c r="Q28" s="6" t="inlineStr">
+      <c r="Q28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R28" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
       <c r="W28" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X28" t="inlineStr"/>
@@ -2885,50 +2883,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C29" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D29" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E29" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F29" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H29" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I29" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J29" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K29" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L29" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M29" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N29" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O29" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2939,25 +2937,21 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2967,50 +2961,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C30" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D30" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E30" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F30" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H30" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I30" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J30" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K30" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L30" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M30" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N30" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O30" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3021,21 +3015,25 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3045,50 +3043,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C31" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D31" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E31" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F31" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H31" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I31" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J31" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K31" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L31" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M31" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N31" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O31" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3099,7 +3097,7 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="7" t="inlineStr">
+      <c r="S31" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -3114,10 +3112,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="V31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3127,50 +3127,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C32" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D32" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E32" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F32" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H32" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I32" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J32" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K32" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L32" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M32" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N32" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O32" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3183,78 +3183,76 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W32" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C33" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D33" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E33" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F33" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H33" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I33" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J33" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K33" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L33" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M33" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N33" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O33" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3262,12 +3260,14 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3279,64 +3279,64 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C34" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D34" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E34" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F34" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H34" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I34" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J34" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K34" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L34" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M34" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N34" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O34" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3344,83 +3344,81 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C35" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D35" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E35" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F35" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H35" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I35" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J35" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K35" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L35" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M35" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N35" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O35" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3433,76 +3431,76 @@
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C36" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D36" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E36" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F36" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H36" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I36" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J36" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K36" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L36" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M36" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N36" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O36" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3510,16 +3508,20 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3527,64 +3529,64 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C37" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D37" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E37" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F37" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H37" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I37" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J37" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K37" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L37" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M37" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N37" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O37" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3592,85 +3594,81 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+      <c r="U37" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U37" s="8" t="n">
-        <v/>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C38" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D38" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E38" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F38" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H38" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I38" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J38" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K38" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L38" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M38" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N38" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O38" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3681,25 +3679,25 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
+      <c r="S38" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T38" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
+      <c r="W38" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3709,50 +3707,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C39" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D39" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E39" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F39" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H39" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I39" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J39" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K39" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L39" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M39" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N39" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O39" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3763,78 +3761,78 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
+      <c r="W39" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C40" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D40" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E40" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F40" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G40" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H40" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I40" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J40" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K40" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L40" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M40" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N40" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O40" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3847,11 +3845,13 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3859,7 +3859,7 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3873,70 +3873,74 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C41" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D41" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E41" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F41" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H41" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I41" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J41" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K41" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L41" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M41" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N41" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O41" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
+        <v>30631.5</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3945,81 +3949,71 @@
       </c>
       <c r="W41" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C42" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D42" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E42" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F42" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H42" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I42" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J42" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K42" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L42" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M42" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N42" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O42" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30728.5</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4031,7 +4025,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
+      <c r="W42" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4041,50 +4035,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C43" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D43" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E43" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F43" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H43" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I43" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J43" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K43" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L43" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M43" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N43" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O43" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4092,12 +4086,14 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4109,7 +4105,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4119,50 +4115,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C44" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D44" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E44" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F44" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H44" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I44" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J44" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K44" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L44" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M44" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N44" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O44" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4170,14 +4166,12 @@
       <c r="Q44" s="6" t="n">
         <v/>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R44" s="6" t="n">
+        <v/>
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4189,73 +4183,81 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C45" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D45" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E45" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F45" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H45" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I45" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J45" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K45" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L45" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M45" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N45" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O45" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4267,146 +4269,144 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C46" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D46" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E46" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F46" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H46" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I46" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J46" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K46" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L46" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M46" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N46" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O46" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
       <c r="U46" s="8" t="n">
         <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C47" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D47" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E47" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F47" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H47" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I47" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J47" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K47" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L47" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M47" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N47" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O47" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4417,15 +4417,13 @@
       <c r="R47" s="6" t="n">
         <v/>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4433,64 +4431,64 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C48" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D48" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E48" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F48" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H48" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I48" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J48" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K48" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L48" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M48" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N48" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O48" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4501,177 +4499,179 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C49" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D49" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E49" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F49" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H49" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I49" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J49" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K49" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L49" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M49" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N49" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O49" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C50" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D50" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E50" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F50" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H50" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I50" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J50" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K50" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L50" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M50" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N50" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O50" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4683,79 +4683,83 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C51" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D51" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E51" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F51" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H51" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I51" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J51" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K51" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L51" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M51" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N51" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O51" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S51" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4769,81 +4773,75 @@
       </c>
       <c r="W51" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C52" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D52" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E52" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F52" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H52" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I52" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J52" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K52" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L52" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M52" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N52" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O52" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P52" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30140.5</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T52" s="8" t="n">
@@ -4855,7 +4853,7 @@
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4869,50 +4867,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C53" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D53" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E53" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F53" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H53" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I53" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J53" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K53" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L53" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M53" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N53" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O53" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4925,76 +4923,82 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W53" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C54" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D54" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E54" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F54" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H54" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I54" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J54" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K54" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L54" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M54" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N54" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O54" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5005,27 +5009,21 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V54" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5039,50 +5037,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C55" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D55" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E55" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F55" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H55" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I55" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J55" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K55" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L55" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M55" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N55" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O55" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5090,16 +5088,20 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5107,64 +5109,64 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C56" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D56" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E56" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F56" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H56" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I56" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J56" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K56" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L56" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M56" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N56" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O56" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5174,18 +5176,16 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5193,77 +5193,75 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C57" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D57" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E57" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F57" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H57" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I57" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J57" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K57" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L57" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M57" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N57" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O57" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5277,7 +5275,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5287,151 +5285,155 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C58" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D58" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E58" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F58" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H58" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I58" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J58" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K58" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L58" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M58" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N58" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O58" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
+      <c r="Q58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C59" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D59" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E59" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F59" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H59" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I59" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J59" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K59" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L59" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M59" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N59" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O59" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S59" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5439,79 +5441,73 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
+      <c r="W59" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C60" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D60" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E60" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F60" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H60" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I60" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J60" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K60" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L60" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M60" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N60" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O60" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5525,60 +5521,64 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
+      <c r="W60" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29200</v>
+        <v>29271</v>
       </c>
       <c r="C61" t="n">
-        <v>29200</v>
+        <v>29288.5</v>
       </c>
       <c r="D61" t="n">
-        <v>28918.75</v>
+        <v>29247.75</v>
       </c>
       <c r="E61" t="n">
-        <v>28955</v>
+        <v>29260.25</v>
       </c>
       <c r="F61" t="n">
-        <v>-197.25</v>
+        <v>305.25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0105</v>
       </c>
       <c r="H61" t="n">
-        <v>281.25</v>
+        <v>40.75</v>
       </c>
       <c r="I61" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J61" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K61" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L61" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M61" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N61" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O61" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5586,146 +5586,60 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
       <c r="V61" s="8" t="n">
         <v/>
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>29263.75</v>
-      </c>
-      <c r="C62" t="n">
-        <v>29439</v>
-      </c>
-      <c r="D62" t="n">
-        <v>29226</v>
-      </c>
-      <c r="E62" t="n">
-        <v>29432.75</v>
-      </c>
-      <c r="F62" t="n">
-        <v>477.75</v>
-      </c>
-      <c r="G62" s="5" t="n">
-        <v>0.0165</v>
-      </c>
-      <c r="H62" t="n">
-        <v>213</v>
-      </c>
-      <c r="I62" t="n">
-        <v>28637.5</v>
-      </c>
-      <c r="J62" t="n">
-        <v>28621.56</v>
-      </c>
-      <c r="K62" t="n">
-        <v>28814.38</v>
-      </c>
-      <c r="L62" t="n">
-        <v>29007.19</v>
-      </c>
-      <c r="M62" t="n">
-        <v>29095.62</v>
-      </c>
-      <c r="N62" t="n">
-        <v>29184.06</v>
-      </c>
-      <c r="O62" t="n">
-        <v>29481.25</v>
-      </c>
-      <c r="P62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
+      <c r="A62" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I63" s="13" t="n">
-        <v>29013</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>29269.88</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>29326.25</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>29382.62</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>29539.25</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>29695.88</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>29652</v>
+      <c r="I62" s="13" t="n">
+        <v>29207</v>
+      </c>
+      <c r="J62" s="13" t="n">
+        <v>29215.56</v>
+      </c>
+      <c r="K62" s="13" t="n">
+        <v>29239.88</v>
+      </c>
+      <c r="L62" s="13" t="n">
+        <v>29264.19</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>29280.62</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>29297.06</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>29329.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5542,22 +5542,22 @@
         <v>29271</v>
       </c>
       <c r="C61" t="n">
-        <v>29288.5</v>
+        <v>29478</v>
       </c>
       <c r="D61" t="n">
         <v>29247.75</v>
       </c>
       <c r="E61" t="n">
-        <v>29260.25</v>
+        <v>29443.25</v>
       </c>
       <c r="F61" t="n">
-        <v>305.25</v>
+        <v>488.25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0105</v>
+        <v>0.0169</v>
       </c>
       <c r="H61" t="n">
-        <v>40.75</v>
+        <v>230.25</v>
       </c>
       <c r="I61" t="n">
         <v>28637.5</v>
@@ -5601,11 +5601,13 @@
       </c>
       <c r="U61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
       </c>
       <c r="W61" s="11" t="inlineStr">
         <is>
@@ -5621,25 +5623,25 @@
         </is>
       </c>
       <c r="I62" s="13" t="n">
-        <v>29207</v>
+        <v>29017.5</v>
       </c>
       <c r="J62" s="13" t="n">
-        <v>29215.56</v>
+        <v>29253.19</v>
       </c>
       <c r="K62" s="13" t="n">
-        <v>29239.88</v>
+        <v>29328.12</v>
       </c>
       <c r="L62" s="13" t="n">
-        <v>29264.19</v>
+        <v>29403.06</v>
       </c>
       <c r="M62" s="13" t="n">
-        <v>29280.62</v>
+        <v>29558.38</v>
       </c>
       <c r="N62" s="13" t="n">
-        <v>29297.06</v>
+        <v>29713.69</v>
       </c>
       <c r="O62" s="13" t="n">
-        <v>29329.25</v>
+        <v>29708.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -487,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5539,25 +5539,25 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29271</v>
+        <v>28978.25</v>
       </c>
       <c r="C61" t="n">
-        <v>29478</v>
+        <v>29252.25</v>
       </c>
       <c r="D61" t="n">
-        <v>29247.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E61" t="n">
-        <v>29443.25</v>
+        <v>28963.5</v>
       </c>
       <c r="F61" t="n">
-        <v>488.25</v>
+        <v>8.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0169</v>
+        <v>0.0003</v>
       </c>
       <c r="H61" t="n">
-        <v>230.25</v>
+        <v>488.5</v>
       </c>
       <c r="I61" t="n">
         <v>28637.5</v>
@@ -5586,62 +5586,150 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W61" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-17</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>29723.75</v>
+      </c>
+      <c r="C62" t="n">
+        <v>29728.5</v>
+      </c>
+      <c r="D62" t="n">
+        <v>29706.75</v>
+      </c>
+      <c r="E62" t="n">
+        <v>29707</v>
+      </c>
+      <c r="F62" t="n">
+        <v>743.5</v>
+      </c>
+      <c r="G62" s="5" t="n">
+        <v>0.0257</v>
+      </c>
+      <c r="H62" t="n">
+        <v>21.75</v>
+      </c>
+      <c r="I62" t="n">
+        <v>28275.25</v>
+      </c>
+      <c r="J62" t="n">
+        <v>28452.75</v>
+      </c>
+      <c r="K62" t="n">
+        <v>28719.25</v>
+      </c>
+      <c r="L62" t="n">
+        <v>28985.75</v>
+      </c>
+      <c r="M62" t="n">
+        <v>29207.75</v>
+      </c>
+      <c r="N62" t="n">
+        <v>29429.75</v>
+      </c>
+      <c r="O62" t="n">
+        <v>29740.75</v>
+      </c>
+      <c r="P62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="T62" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U61" s="8" t="inlineStr">
+      <c r="U62" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="V61" s="8" t="inlineStr">
+      <c r="V62" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" s="12" t="inlineStr">
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="12" t="inlineStr">
         <is>
           <t>明日預測</t>
         </is>
       </c>
-      <c r="I62" s="13" t="n">
-        <v>29017.5</v>
-      </c>
-      <c r="J62" s="13" t="n">
-        <v>29253.19</v>
-      </c>
-      <c r="K62" s="13" t="n">
-        <v>29328.12</v>
-      </c>
-      <c r="L62" s="13" t="n">
-        <v>29403.06</v>
-      </c>
-      <c r="M62" s="13" t="n">
-        <v>29558.38</v>
-      </c>
-      <c r="N62" s="13" t="n">
-        <v>29713.69</v>
-      </c>
-      <c r="O62" s="13" t="n">
-        <v>29708.25</v>
+      <c r="I63" s="13" t="n">
+        <v>29685</v>
+      </c>
+      <c r="J63" s="13" t="n">
+        <v>29679.94</v>
+      </c>
+      <c r="K63" s="13" t="n">
+        <v>29696.12</v>
+      </c>
+      <c r="L63" s="13" t="n">
+        <v>29712.31</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>29717.88</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>29723.44</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>29750.25</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5633,19 +5633,19 @@
         <v>29728.5</v>
       </c>
       <c r="D62" t="n">
-        <v>29706.75</v>
+        <v>29674</v>
       </c>
       <c r="E62" t="n">
-        <v>29707</v>
+        <v>29694.25</v>
       </c>
       <c r="F62" t="n">
-        <v>743.5</v>
+        <v>730.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0257</v>
+        <v>0.0252</v>
       </c>
       <c r="H62" t="n">
-        <v>21.75</v>
+        <v>54.5</v>
       </c>
       <c r="I62" t="n">
         <v>28275.25</v>
@@ -5711,25 +5711,25 @@
         </is>
       </c>
       <c r="I63" s="13" t="n">
-        <v>29685</v>
+        <v>29619.5</v>
       </c>
       <c r="J63" s="13" t="n">
-        <v>29679.94</v>
+        <v>29636.25</v>
       </c>
       <c r="K63" s="13" t="n">
-        <v>29696.12</v>
+        <v>29667</v>
       </c>
       <c r="L63" s="13" t="n">
-        <v>29712.31</v>
+        <v>29697.75</v>
       </c>
       <c r="M63" s="13" t="n">
-        <v>29717.88</v>
+        <v>29721.5</v>
       </c>
       <c r="N63" s="13" t="n">
-        <v>29723.44</v>
+        <v>29745.25</v>
       </c>
       <c r="O63" s="13" t="n">
-        <v>29750.25</v>
+        <v>29783</v>
       </c>
     </row>
   </sheetData>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -46,7 +46,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,11 +73,6 @@
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -91,7 +86,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -120,8 +115,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -487,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5636,13 +5629,13 @@
         <v>29674</v>
       </c>
       <c r="E62" t="n">
-        <v>29694.25</v>
+        <v>29685</v>
       </c>
       <c r="F62" t="n">
-        <v>730.75</v>
+        <v>721.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0252</v>
+        <v>0.0249</v>
       </c>
       <c r="H62" t="n">
         <v>54.5</v>
@@ -5703,34 +5696,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" s="12" t="inlineStr">
-        <is>
-          <t>明日預測</t>
-        </is>
-      </c>
-      <c r="I63" s="13" t="n">
-        <v>29619.5</v>
-      </c>
-      <c r="J63" s="13" t="n">
-        <v>29636.25</v>
-      </c>
-      <c r="K63" s="13" t="n">
-        <v>29667</v>
-      </c>
-      <c r="L63" s="13" t="n">
-        <v>29697.75</v>
-      </c>
-      <c r="M63" s="13" t="n">
-        <v>29721.5</v>
-      </c>
-      <c r="N63" s="13" t="n">
-        <v>29745.25</v>
-      </c>
-      <c r="O63" s="13" t="n">
-        <v>29783</v>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5626,19 +5626,19 @@
         <v>29728.5</v>
       </c>
       <c r="D62" t="n">
-        <v>29674</v>
+        <v>29662.25</v>
       </c>
       <c r="E62" t="n">
-        <v>29685</v>
+        <v>29679.75</v>
       </c>
       <c r="F62" t="n">
-        <v>721.5</v>
+        <v>716.25</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0249</v>
+        <v>0.0247</v>
       </c>
       <c r="H62" t="n">
-        <v>54.5</v>
+        <v>66.25</v>
       </c>
       <c r="I62" t="n">
         <v>28275.25</v>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,69 +634,63 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-23</t>
+          <t>2026-06-24</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30662.75</v>
+        <v>29770</v>
       </c>
       <c r="C2" t="n">
-        <v>30701.25</v>
+        <v>30157.75</v>
       </c>
       <c r="D2" t="n">
-        <v>29577.25</v>
+        <v>29264.75</v>
       </c>
       <c r="E2" t="n">
-        <v>29666</v>
+        <v>29514.25</v>
       </c>
       <c r="F2" t="n">
-        <v>-987.5</v>
+        <v>-151.75</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0322</v>
+        <v>-0.0051</v>
       </c>
       <c r="H2" t="n">
-        <v>1124</v>
+        <v>893</v>
       </c>
       <c r="I2" t="n">
-        <v>29707</v>
+        <v>28453.25</v>
       </c>
       <c r="J2" t="n">
-        <v>30023.38</v>
+        <v>28305.38</v>
       </c>
       <c r="K2" t="n">
-        <v>30338.25</v>
+        <v>29104</v>
       </c>
       <c r="L2" t="n">
-        <v>30653.12</v>
+        <v>29902.62</v>
       </c>
       <c r="M2" t="n">
-        <v>30968.75</v>
+        <v>30228</v>
       </c>
       <c r="N2" t="n">
-        <v>31284.38</v>
+        <v>30553.38</v>
       </c>
       <c r="O2" t="n">
-        <v>31598.5</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31825.25</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -710,58 +704,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29770</v>
+        <v>30089.75</v>
       </c>
       <c r="C3" t="n">
-        <v>30157.75</v>
+        <v>30263.75</v>
       </c>
       <c r="D3" t="n">
-        <v>29264.75</v>
+        <v>29295.75</v>
       </c>
       <c r="E3" t="n">
-        <v>29514.25</v>
+        <v>29724.75</v>
       </c>
       <c r="F3" t="n">
-        <v>-151.75</v>
+        <v>210.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0071</v>
       </c>
       <c r="H3" t="n">
-        <v>893</v>
+        <v>968</v>
       </c>
       <c r="I3" t="n">
-        <v>28453.25</v>
+        <v>28371.75</v>
       </c>
       <c r="J3" t="n">
-        <v>28305.38</v>
+        <v>28522.75</v>
       </c>
       <c r="K3" t="n">
-        <v>29104</v>
+        <v>29067.75</v>
       </c>
       <c r="L3" t="n">
-        <v>29902.62</v>
+        <v>29612.75</v>
       </c>
       <c r="M3" t="n">
-        <v>30228</v>
+        <v>29960.75</v>
       </c>
       <c r="N3" t="n">
-        <v>30553.38</v>
+        <v>30308.75</v>
       </c>
       <c r="O3" t="n">
-        <v>31825.25</v>
+        <v>31050.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,13 +770,15 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -788,7 +788,7 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X3" t="inlineStr"/>
@@ -796,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30089.75</v>
+        <v>29742</v>
       </c>
       <c r="C4" t="n">
-        <v>30263.75</v>
+        <v>29892.75</v>
       </c>
       <c r="D4" t="n">
-        <v>29295.75</v>
+        <v>29160.5</v>
       </c>
       <c r="E4" t="n">
-        <v>29724.75</v>
+        <v>29368.25</v>
       </c>
       <c r="F4" t="n">
-        <v>210.5</v>
+        <v>-356.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.012</v>
       </c>
       <c r="H4" t="n">
-        <v>968</v>
+        <v>732.25</v>
       </c>
       <c r="I4" t="n">
-        <v>28371.75</v>
+        <v>28327.75</v>
       </c>
       <c r="J4" t="n">
-        <v>28522.75</v>
+        <v>28729.25</v>
       </c>
       <c r="K4" t="n">
-        <v>29067.75</v>
+        <v>29240.75</v>
       </c>
       <c r="L4" t="n">
-        <v>29612.75</v>
+        <v>29752.25</v>
       </c>
       <c r="M4" t="n">
-        <v>29960.75</v>
+        <v>30208.75</v>
       </c>
       <c r="N4" t="n">
-        <v>30308.75</v>
+        <v>30665.25</v>
       </c>
       <c r="O4" t="n">
-        <v>31050.75</v>
+        <v>31231.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,18 +847,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -868,7 +868,7 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -880,50 +880,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29742</v>
+        <v>29282.5</v>
       </c>
       <c r="C5" t="n">
-        <v>29892.75</v>
+        <v>30069.5</v>
       </c>
       <c r="D5" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E5" t="n">
-        <v>29368.25</v>
+        <v>30052.75</v>
       </c>
       <c r="F5" t="n">
-        <v>-356.5</v>
+        <v>684.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0233</v>
       </c>
       <c r="H5" t="n">
-        <v>732.25</v>
+        <v>795.75</v>
       </c>
       <c r="I5" t="n">
-        <v>28327.75</v>
+        <v>28428.25</v>
       </c>
       <c r="J5" t="n">
-        <v>28729.25</v>
+        <v>28556.81</v>
       </c>
       <c r="K5" t="n">
-        <v>29240.75</v>
+        <v>29002.12</v>
       </c>
       <c r="L5" t="n">
-        <v>29752.25</v>
+        <v>29447.44</v>
       </c>
       <c r="M5" t="n">
-        <v>30208.75</v>
+        <v>29734.38</v>
       </c>
       <c r="N5" t="n">
-        <v>30665.25</v>
+        <v>30021.31</v>
       </c>
       <c r="O5" t="n">
-        <v>31231.75</v>
+        <v>30625</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -931,28 +931,30 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U5" s="8" t="n">
-        <v/>
-      </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
       <c r="W5" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X5" t="inlineStr"/>
@@ -960,50 +962,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29282.5</v>
+        <v>30007.25</v>
       </c>
       <c r="C6" t="n">
-        <v>30069.5</v>
+        <v>30599.75</v>
       </c>
       <c r="D6" t="n">
-        <v>29273.75</v>
+        <v>29934.75</v>
       </c>
       <c r="E6" t="n">
-        <v>30052.75</v>
+        <v>30523.5</v>
       </c>
       <c r="F6" t="n">
-        <v>684.5</v>
+        <v>470.75</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0157</v>
       </c>
       <c r="H6" t="n">
-        <v>795.75</v>
+        <v>665</v>
       </c>
       <c r="I6" t="n">
-        <v>28428.25</v>
+        <v>28478</v>
       </c>
       <c r="J6" t="n">
-        <v>28556.81</v>
+        <v>29447.56</v>
       </c>
       <c r="K6" t="n">
-        <v>29002.12</v>
+        <v>29654.88</v>
       </c>
       <c r="L6" t="n">
-        <v>29447.44</v>
+        <v>29862.19</v>
       </c>
       <c r="M6" t="n">
-        <v>29734.38</v>
+        <v>30450.62</v>
       </c>
       <c r="N6" t="n">
-        <v>30021.31</v>
+        <v>31039.06</v>
       </c>
       <c r="O6" t="n">
-        <v>30625</v>
+        <v>30865.25</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1021,18 +1023,16 @@
       </c>
       <c r="T6" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U6" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U6" s="8" t="n">
+        <v/>
+      </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -1042,50 +1042,50 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C7" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D7" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E7" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F7" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H7" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I7" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J7" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K7" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L7" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M7" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N7" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O7" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1093,89 +1093,97 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
+      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C8" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D8" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E8" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F8" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H8" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I8" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J8" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K8" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L8" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M8" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N8" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O8" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
@@ -1192,172 +1200,172 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C9" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D9" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E9" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F9" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H9" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I9" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J9" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K9" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L9" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M9" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N9" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O9" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C10" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D10" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E10" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F10" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H10" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I10" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J10" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K10" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L10" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M10" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N10" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O10" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+        <v>30505</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1366,81 +1374,73 @@
       </c>
       <c r="W10" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C11" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D11" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E11" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F11" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H11" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I11" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J11" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K11" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L11" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M11" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N11" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O11" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q11" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1452,60 +1452,64 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="9" t="inlineStr">
+      <c r="W11" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C12" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D12" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E12" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F12" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H12" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I12" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J12" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K12" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L12" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M12" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N12" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O12" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1513,18 +1517,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1532,64 +1536,64 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
+      <c r="W12" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C13" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D13" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E13" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F13" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H13" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I13" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J13" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K13" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L13" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M13" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N13" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O13" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1616,7 +1620,7 @@
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1630,218 +1634,218 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C14" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D14" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E14" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F14" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H14" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I14" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J14" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K14" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L14" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M14" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N14" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O14" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+        <v>30480.5</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C15" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D15" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E15" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H15" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I15" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J15" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K15" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L15" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M15" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N15" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O15" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
       <c r="U15" s="8" t="n">
         <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C16" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D16" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E16" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F16" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H16" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I16" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J16" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K16" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L16" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M16" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N16" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O16" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1849,18 +1853,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1868,64 +1872,64 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C17" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D17" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E17" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F17" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H17" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I17" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J17" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K17" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L17" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M17" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N17" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O17" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1935,12 +1939,12 @@
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1952,64 +1956,60 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C18" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D18" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E18" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H18" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I18" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J18" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K18" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L18" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M18" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N18" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O18" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2036,7 +2036,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
+      <c r="W18" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2046,50 +2046,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C19" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D19" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E19" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H19" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I19" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J19" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K19" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L19" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M19" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N19" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O19" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2097,18 +2097,18 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R19" s="6" t="n">
+        <v/>
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U19" s="8" t="n">
         <v/>
@@ -2116,60 +2116,64 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
+      <c r="W19" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C20" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D20" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E20" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F20" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H20" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I20" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J20" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K20" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L20" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M20" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N20" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O20" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2180,9 +2184,9 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T20" s="8" t="inlineStr">
@@ -2190,70 +2194,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C21" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D21" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E21" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F21" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H21" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I21" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J21" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K21" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L21" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M21" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N21" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O21" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2261,100 +2267,102 @@
       <c r="Q21" s="6" t="n">
         <v/>
       </c>
-      <c r="R21" s="6" t="n">
-        <v/>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C22" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D22" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E22" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F22" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H22" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I22" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J22" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K22" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L22" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M22" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N22" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O22" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2368,78 +2376,70 @@
       </c>
       <c r="W22" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C23" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D23" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E23" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H23" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I23" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J23" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K23" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L23" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M23" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N23" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O23" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P23" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -2454,7 +2454,7 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="9" t="inlineStr">
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2464,50 +2464,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C24" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D24" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E24" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F24" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H24" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I24" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J24" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K24" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L24" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M24" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N24" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O24" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2525,69 +2525,77 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C25" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D25" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E25" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F25" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H25" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I25" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J25" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K25" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L25" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M25" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N25" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O25" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2605,87 +2613,81 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C26" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D26" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E26" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F26" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H26" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I26" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J26" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K26" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L26" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M26" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N26" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O26" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="n">
-        <v/>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R26" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
@@ -2702,7 +2704,7 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2712,81 +2714,81 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C27" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D27" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E27" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F27" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H27" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I27" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J27" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K27" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L27" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M27" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N27" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O27" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
       </c>
-      <c r="Q27" s="6" t="inlineStr">
+      <c r="Q27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R27" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr"/>
@@ -2794,50 +2796,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C28" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D28" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E28" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F28" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H28" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I28" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J28" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K28" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L28" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M28" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N28" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O28" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2850,23 +2852,19 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2876,50 +2874,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C29" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D29" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E29" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F29" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H29" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I29" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J29" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K29" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L29" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M29" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N29" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O29" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2932,19 +2930,23 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2954,50 +2956,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C30" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D30" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E30" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F30" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H30" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I30" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J30" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K30" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L30" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M30" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N30" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O30" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3023,10 +3025,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="V30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3036,50 +3040,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C31" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D31" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E31" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F31" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H31" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I31" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J31" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K31" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L31" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M31" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N31" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O31" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3090,80 +3094,78 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W31" s="11" t="inlineStr">
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W31" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C32" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D32" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E32" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F32" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H32" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I32" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J32" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K32" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L32" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M32" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N32" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O32" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3171,12 +3173,14 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3188,64 +3192,64 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="11" t="inlineStr">
+      <c r="W32" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C33" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D33" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E33" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F33" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H33" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I33" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J33" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K33" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L33" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M33" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N33" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O33" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3253,83 +3257,81 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C34" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D34" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E34" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F34" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H34" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I34" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J34" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K34" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L34" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M34" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N34" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O34" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3340,78 +3342,78 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C35" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D35" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E35" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F35" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H35" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I35" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J35" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K35" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L35" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M35" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N35" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O35" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3419,16 +3421,20 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3436,64 +3442,64 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X35" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C36" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D36" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E36" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F36" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H36" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I36" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J36" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K36" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L36" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M36" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N36" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O36" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3501,85 +3507,81 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
+      <c r="U36" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U36" s="8" t="n">
-        <v/>
-      </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C37" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D37" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E37" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F37" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H37" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I37" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J37" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K37" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L37" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M37" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N37" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O37" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3597,18 +3599,18 @@
       </c>
       <c r="T37" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3618,50 +3620,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C38" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D38" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E38" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F38" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H38" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I38" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J38" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K38" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L38" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M38" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N38" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O38" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3674,76 +3676,76 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U38" s="8" t="n">
+        <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C39" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D39" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E39" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F39" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G39" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H39" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I39" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J39" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K39" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L39" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M39" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N39" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O39" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3754,13 +3756,15 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3768,7 +3772,7 @@
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3782,69 +3786,73 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C40" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D40" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E40" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F40" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H40" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I40" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J40" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K40" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L40" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M40" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N40" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O40" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+        <v>30631.5</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3854,81 +3862,71 @@
       </c>
       <c r="W40" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C41" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D41" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E41" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F41" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H41" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I41" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J41" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K41" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L41" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M41" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N41" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O41" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30728.5</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3940,7 +3938,7 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3950,50 +3948,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C42" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D42" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E42" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F42" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H42" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I42" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J42" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K42" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L42" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M42" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N42" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O42" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4001,12 +3999,14 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4018,7 +4018,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4028,50 +4028,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C43" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D43" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E43" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F43" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H43" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I43" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J43" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K43" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L43" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M43" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N43" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O43" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4079,14 +4079,12 @@
       <c r="Q43" s="6" t="n">
         <v/>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4098,73 +4096,81 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C44" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D44" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E44" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F44" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H44" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I44" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J44" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K44" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L44" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M44" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N44" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O44" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4176,146 +4182,144 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C45" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D45" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E45" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F45" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H45" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I45" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J45" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K45" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L45" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M45" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N45" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O45" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
       <c r="U45" s="8" t="n">
         <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C46" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D46" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E46" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F46" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H46" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I46" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J46" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K46" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L46" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M46" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N46" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O46" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4328,13 +4332,11 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4342,64 +4344,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C47" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D47" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E47" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F47" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H47" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I47" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J47" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K47" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L47" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M47" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N47" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O47" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4412,166 +4414,168 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
       </c>
       <c r="W47" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C48" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D48" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E48" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F48" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H48" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I48" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J48" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K48" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L48" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M48" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N48" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O48" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C49" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D49" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E49" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F49" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H49" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I49" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J49" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K49" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L49" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M49" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N49" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O49" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q49" s="6" t="n">
+        <v/>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
@@ -4580,7 +4584,7 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4592,70 +4596,74 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C50" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D50" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E50" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F50" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H50" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I50" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J50" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K50" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L50" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M50" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N50" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O50" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
@@ -4664,7 +4672,7 @@
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4678,81 +4686,75 @@
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C51" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D51" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E51" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F51" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H51" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I51" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J51" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K51" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L51" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M51" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N51" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O51" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P51" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30140.5</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T51" s="8" t="n">
@@ -4764,7 +4766,7 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4778,50 +4780,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C52" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D52" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E52" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F52" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H52" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I52" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J52" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K52" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L52" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M52" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N52" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O52" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4832,78 +4834,84 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W52" s="9" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W52" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C53" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D53" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E53" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F53" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H53" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I53" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J53" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K53" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L53" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M53" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N53" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O53" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4916,25 +4924,19 @@
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W53" s="9" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V53" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W53" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4948,50 +4950,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C54" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D54" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E54" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F54" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H54" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I54" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J54" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K54" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L54" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M54" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N54" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O54" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -4999,16 +5001,20 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
+      <c r="R54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5016,64 +5022,64 @@
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C55" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D55" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E55" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F55" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H55" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I55" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J55" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K55" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L55" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M55" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N55" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O55" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5083,18 +5089,16 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S55" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5102,74 +5106,72 @@
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C56" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D56" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E56" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F56" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H56" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I56" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J56" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K56" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L56" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M56" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N56" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O56" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
@@ -5186,7 +5188,7 @@
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5196,224 +5198,222 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C57" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D57" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E57" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F57" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H57" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I57" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J57" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K57" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L57" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M57" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N57" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O57" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
+      <c r="Q57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
       <c r="U57" s="8" t="n">
         <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D58" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E58" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F58" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H58" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I58" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J58" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K58" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L58" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M58" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N58" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O58" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
+      </c>
       <c r="U58" s="8" t="n">
         <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C59" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D59" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E59" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F59" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H59" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I59" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J59" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K59" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L59" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M59" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N59" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O59" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q59" s="6" t="n">
+        <v/>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
@@ -5434,60 +5434,64 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C60" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D60" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E60" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F60" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H60" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I60" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J60" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K60" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L60" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M60" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N60" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O60" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5497,81 +5501,85 @@
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U60" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C61" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D61" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E61" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F61" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H61" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I61" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J61" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K61" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L61" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M61" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N61" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O61" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5579,24 +5587,22 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V61" s="8" t="n">
@@ -5604,62 +5610,58 @@
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>29723.75</v>
+        <v>29438.75</v>
       </c>
       <c r="C62" t="n">
-        <v>29728.5</v>
+        <v>29665.25</v>
       </c>
       <c r="D62" t="n">
-        <v>29662.25</v>
+        <v>29352.75</v>
       </c>
       <c r="E62" t="n">
-        <v>29679.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F62" t="n">
-        <v>716.25</v>
+        <v>166.93</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0247</v>
+        <v>0.0057</v>
       </c>
       <c r="H62" t="n">
-        <v>66.25</v>
+        <v>312.5</v>
       </c>
       <c r="I62" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J62" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K62" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L62" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M62" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N62" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O62" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5677,25 +5679,103 @@
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W62" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>29938</v>
+      </c>
+      <c r="C63" t="n">
+        <v>29944.5</v>
+      </c>
+      <c r="D63" t="n">
+        <v>29904</v>
+      </c>
+      <c r="E63" t="n">
+        <v>29917.25</v>
+      </c>
+      <c r="F63" t="n">
+        <v>303.57</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0103</v>
+      </c>
+      <c r="H63" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>29040.25</v>
+      </c>
+      <c r="J63" t="n">
+        <v>29353.52</v>
+      </c>
+      <c r="K63" t="n">
+        <v>29457.43</v>
+      </c>
+      <c r="L63" t="n">
+        <v>29561.34</v>
+      </c>
+      <c r="M63" t="n">
+        <v>29769.93</v>
+      </c>
+      <c r="N63" t="n">
+        <v>29978.52</v>
+      </c>
+      <c r="O63" t="n">
+        <v>29977.75</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="V62" s="8" t="inlineStr">
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W63" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-24</t>
+          <t>2026-06-25</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29770</v>
+        <v>30089.75</v>
       </c>
       <c r="C2" t="n">
-        <v>30157.75</v>
+        <v>30263.75</v>
       </c>
       <c r="D2" t="n">
-        <v>29264.75</v>
+        <v>29295.75</v>
       </c>
       <c r="E2" t="n">
-        <v>29514.25</v>
+        <v>29724.75</v>
       </c>
       <c r="F2" t="n">
-        <v>-151.75</v>
+        <v>210.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0051</v>
+        <v>0.0071</v>
       </c>
       <c r="H2" t="n">
-        <v>893</v>
+        <v>968</v>
       </c>
       <c r="I2" t="n">
-        <v>28453.25</v>
+        <v>28371.75</v>
       </c>
       <c r="J2" t="n">
-        <v>28305.38</v>
+        <v>28522.75</v>
       </c>
       <c r="K2" t="n">
-        <v>29104</v>
+        <v>29067.75</v>
       </c>
       <c r="L2" t="n">
-        <v>29902.62</v>
+        <v>29612.75</v>
       </c>
       <c r="M2" t="n">
-        <v>30228</v>
+        <v>29960.75</v>
       </c>
       <c r="N2" t="n">
-        <v>30553.38</v>
+        <v>30308.75</v>
       </c>
       <c r="O2" t="n">
-        <v>31825.25</v>
+        <v>31050.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -690,11 +690,13 @@
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -707,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30089.75</v>
+        <v>29742</v>
       </c>
       <c r="C3" t="n">
-        <v>30263.75</v>
+        <v>29892.75</v>
       </c>
       <c r="D3" t="n">
-        <v>29295.75</v>
+        <v>29160.5</v>
       </c>
       <c r="E3" t="n">
-        <v>29724.75</v>
+        <v>29368.25</v>
       </c>
       <c r="F3" t="n">
-        <v>210.5</v>
+        <v>-356.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.012</v>
       </c>
       <c r="H3" t="n">
-        <v>968</v>
+        <v>732.25</v>
       </c>
       <c r="I3" t="n">
-        <v>28371.75</v>
+        <v>28327.75</v>
       </c>
       <c r="J3" t="n">
-        <v>28522.75</v>
+        <v>28729.25</v>
       </c>
       <c r="K3" t="n">
-        <v>29067.75</v>
+        <v>29240.75</v>
       </c>
       <c r="L3" t="n">
-        <v>29612.75</v>
+        <v>29752.25</v>
       </c>
       <c r="M3" t="n">
-        <v>29960.75</v>
+        <v>30208.75</v>
       </c>
       <c r="N3" t="n">
-        <v>30308.75</v>
+        <v>30665.25</v>
       </c>
       <c r="O3" t="n">
-        <v>31050.75</v>
+        <v>31231.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,18 +765,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -791,55 +789,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29742</v>
+        <v>29282.5</v>
       </c>
       <c r="C4" t="n">
-        <v>29892.75</v>
+        <v>30069.5</v>
       </c>
       <c r="D4" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E4" t="n">
-        <v>29368.25</v>
+        <v>30052.75</v>
       </c>
       <c r="F4" t="n">
-        <v>-356.5</v>
+        <v>684.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0233</v>
       </c>
       <c r="H4" t="n">
-        <v>732.25</v>
+        <v>795.75</v>
       </c>
       <c r="I4" t="n">
-        <v>28327.75</v>
+        <v>28428.25</v>
       </c>
       <c r="J4" t="n">
-        <v>28729.25</v>
+        <v>28556.81</v>
       </c>
       <c r="K4" t="n">
-        <v>29240.75</v>
+        <v>29002.12</v>
       </c>
       <c r="L4" t="n">
-        <v>29752.25</v>
+        <v>29447.44</v>
       </c>
       <c r="M4" t="n">
-        <v>30208.75</v>
+        <v>29734.38</v>
       </c>
       <c r="N4" t="n">
-        <v>30665.25</v>
+        <v>30021.31</v>
       </c>
       <c r="O4" t="n">
-        <v>31231.75</v>
+        <v>30625</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -847,22 +849,24 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U4" s="8" t="n">
-        <v/>
-      </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
@@ -871,59 +875,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29282.5</v>
+        <v>30007.25</v>
       </c>
       <c r="C5" t="n">
-        <v>30069.5</v>
+        <v>30599.75</v>
       </c>
       <c r="D5" t="n">
-        <v>29273.75</v>
+        <v>29934.75</v>
       </c>
       <c r="E5" t="n">
-        <v>30052.75</v>
+        <v>30523.5</v>
       </c>
       <c r="F5" t="n">
-        <v>684.5</v>
+        <v>470.75</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0157</v>
       </c>
       <c r="H5" t="n">
-        <v>795.75</v>
+        <v>665</v>
       </c>
       <c r="I5" t="n">
-        <v>28428.25</v>
+        <v>28478</v>
       </c>
       <c r="J5" t="n">
-        <v>28556.81</v>
+        <v>29447.56</v>
       </c>
       <c r="K5" t="n">
-        <v>29002.12</v>
+        <v>29654.88</v>
       </c>
       <c r="L5" t="n">
-        <v>29447.44</v>
+        <v>29862.19</v>
       </c>
       <c r="M5" t="n">
-        <v>29734.38</v>
+        <v>30450.62</v>
       </c>
       <c r="N5" t="n">
-        <v>30021.31</v>
+        <v>31039.06</v>
       </c>
       <c r="O5" t="n">
-        <v>30625</v>
+        <v>30865.25</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -934,20 +934,18 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="10" t="inlineStr">
+      <c r="S5" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T5" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U5" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U5" s="8" t="n">
+        <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
@@ -962,50 +960,50 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C6" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D6" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E6" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F6" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H6" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I6" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J6" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K6" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L6" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M6" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N6" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O6" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1013,18 +1011,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1037,68 +1035,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C7" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D7" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E7" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F7" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H7" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I7" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J7" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K7" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L7" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M7" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N7" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O7" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1119,81 +1125,77 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C8" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D8" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E8" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F8" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H8" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I8" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J8" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K8" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L8" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M8" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N8" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O8" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1207,76 +1209,80 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C9" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D9" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E9" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F9" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H9" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I9" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J9" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K9" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L9" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M9" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N9" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O9" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>30505</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1284,83 +1290,75 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W9" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C10" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D10" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E10" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F10" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H10" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I10" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J10" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K10" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L10" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M10" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N10" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O10" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q10" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1377,55 +1375,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C11" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D11" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E11" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F11" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H11" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I11" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J11" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K11" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L11" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M11" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N11" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O11" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1433,18 +1435,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R11" s="6" t="n">
+        <v/>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1459,57 +1461,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C12" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D12" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E12" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F12" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H12" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I12" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J12" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K12" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L12" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M12" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N12" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O12" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1520,7 +1522,7 @@
       <c r="R12" s="6" t="n">
         <v/>
       </c>
-      <c r="S12" s="10" t="inlineStr">
+      <c r="S12" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1550,69 +1552,73 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C13" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D13" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E13" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F13" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H13" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I13" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J13" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K13" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L13" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M13" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N13" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O13" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+        <v>30480.5</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1625,83 +1631,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C14" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D14" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E14" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H14" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I14" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J14" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K14" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L14" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M14" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N14" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O14" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
       <c r="U14" s="8" t="n">
         <v/>
       </c>
@@ -1713,55 +1711,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C15" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D15" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E15" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F15" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H15" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I15" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J15" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K15" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L15" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M15" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N15" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O15" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1769,18 +1771,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1795,57 +1797,57 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C16" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D16" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E16" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F16" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H16" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I16" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J16" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K16" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L16" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M16" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N16" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O16" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1855,12 +1857,12 @@
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1877,59 +1879,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C17" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D17" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E17" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H17" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I17" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J17" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K17" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L17" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M17" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N17" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O17" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1942,7 +1940,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1966,50 +1964,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C18" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D18" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E18" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F18" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H18" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I18" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J18" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K18" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L18" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M18" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N18" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O18" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2017,18 +2015,18 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U18" s="8" t="n">
         <v/>
@@ -2041,55 +2039,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C19" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D19" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E19" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F19" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H19" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I19" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J19" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K19" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L19" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M19" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N19" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O19" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2102,7 +2104,7 @@
       </c>
       <c r="S19" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T19" s="8" t="inlineStr">
@@ -2110,70 +2112,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W19" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C20" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D20" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E20" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F20" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H20" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I20" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J20" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K20" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L20" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M20" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N20" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O20" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2181,23 +2185,21 @@
       <c r="Q20" s="6" t="n">
         <v/>
       </c>
-      <c r="R20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2209,63 +2211,67 @@
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C21" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D21" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E21" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F21" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H21" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I21" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J21" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K21" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L21" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M21" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N21" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O21" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P21" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
@@ -2274,7 +2280,7 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T21" s="8" t="n">
@@ -2286,81 +2292,73 @@
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W21" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C22" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D22" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E22" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H22" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I22" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J22" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K22" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L22" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M22" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N22" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O22" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P22" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2384,50 +2382,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C23" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D23" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E23" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F23" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H23" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I23" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J23" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K23" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L23" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M23" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N23" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O23" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,16 +2438,20 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2459,55 +2461,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C24" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D24" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E24" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F24" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H24" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I24" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J24" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K24" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L24" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M24" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N24" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O24" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2520,20 +2526,16 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
+      <c r="S24" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2543,72 +2545,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C25" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D25" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E25" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F25" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H25" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I25" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J25" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K25" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L25" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M25" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N25" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O25" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="n">
-        <v/>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R25" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2632,81 +2632,81 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C26" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D26" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E26" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F26" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H26" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I26" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J26" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K26" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L26" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M26" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N26" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O26" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
       </c>
-      <c r="Q26" s="6" t="inlineStr">
+      <c r="Q26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R26" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W26" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr"/>
@@ -2714,50 +2714,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C27" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D27" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E27" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F27" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H27" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I27" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J27" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K27" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L27" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M27" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N27" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O27" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2768,20 +2768,16 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2796,50 +2792,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C28" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D28" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E28" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F28" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H28" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I28" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J28" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K28" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L28" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M28" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N28" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O28" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2850,16 +2846,20 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2874,50 +2874,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C29" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D29" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E29" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F29" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H29" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I29" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J29" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K29" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L29" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M29" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N29" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O29" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2928,7 +2928,7 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="10" t="inlineStr">
+      <c r="S29" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2943,8 +2943,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V29" s="8" t="n">
-        <v/>
+      <c r="V29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
@@ -2956,50 +2958,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C30" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D30" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E30" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F30" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H30" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I30" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J30" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K30" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L30" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M30" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N30" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O30" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3012,78 +3014,76 @@
       </c>
       <c r="S30" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V30" s="8" t="n">
+        <v/>
       </c>
       <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C31" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D31" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E31" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F31" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H31" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I31" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J31" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K31" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L31" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M31" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N31" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O31" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3091,12 +3091,14 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3115,57 +3117,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C32" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D32" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E32" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H32" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I32" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J32" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K32" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L32" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M32" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N32" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O32" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3173,22 +3175,24 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
@@ -3197,59 +3201,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C33" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D33" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E33" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F33" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H33" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I33" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J33" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K33" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L33" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M33" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N33" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O33" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3262,18 +3262,14 @@
       </c>
       <c r="S33" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3283,55 +3279,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C34" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D34" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E34" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F34" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H34" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I34" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J34" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K34" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L34" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M34" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N34" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O34" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3339,16 +3339,20 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3363,57 +3367,57 @@
       </c>
       <c r="X34" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C35" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D35" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E35" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F35" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H35" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I35" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J35" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K35" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L35" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M35" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N35" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O35" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3421,24 +3425,24 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+      <c r="U35" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U35" s="8" t="n">
-        <v/>
-      </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
@@ -3447,59 +3451,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C36" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D36" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E36" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F36" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H36" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I36" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J36" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K36" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L36" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M36" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N36" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O36" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3510,19 +3510,19 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
+      <c r="S36" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T36" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U36" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V36" s="8" t="n">
@@ -3538,50 +3538,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C37" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D37" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E37" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F37" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H37" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I37" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J37" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K37" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L37" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M37" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N37" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O37" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3592,20 +3592,16 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U37" s="8" t="n">
+        <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
@@ -3615,55 +3611,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C38" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D38" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E38" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F38" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G38" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H38" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I38" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J38" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K38" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L38" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M38" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N38" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O38" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3676,11 +3676,13 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3702,153 +3704,147 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C39" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D39" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E39" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F39" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H39" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I39" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J39" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K39" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L39" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M39" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N39" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O39" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+        <v>30631.5</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W39" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C40" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D40" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E40" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F40" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H40" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I40" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J40" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K40" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L40" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M40" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N40" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O40" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30728.5</v>
+      </c>
+      <c r="P40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3870,50 +3866,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C41" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D41" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E41" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F41" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H41" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I41" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J41" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K41" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L41" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M41" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N41" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O41" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3921,12 +3917,14 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3948,50 +3946,50 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C42" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D42" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E42" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F42" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H42" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I42" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J42" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K42" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L42" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M42" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N42" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O42" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -3999,14 +3997,12 @@
       <c r="Q42" s="6" t="n">
         <v/>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4023,68 +4019,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C43" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D43" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E43" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F43" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H43" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I43" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J43" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K43" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L43" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M43" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N43" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O43" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4101,81 +4105,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C44" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D44" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E44" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F44" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H44" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I44" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J44" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K44" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L44" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M44" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N44" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O44" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
       <c r="U44" s="8" t="n">
         <v/>
       </c>
@@ -4187,55 +4185,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C45" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D45" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E45" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F45" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H45" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I45" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J45" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K45" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L45" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M45" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N45" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O45" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4246,15 +4248,13 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4269,57 +4269,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C46" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D46" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E46" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F46" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H46" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I46" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J46" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K46" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L46" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M46" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N46" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O46" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4330,102 +4330,102 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W46" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C47" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D47" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E47" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F47" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H47" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I47" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J47" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K47" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L47" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M47" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N47" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O47" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
       </c>
       <c r="V47" s="8" t="n">
         <v/>
@@ -4435,72 +4435,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr"/>
+      <c r="X47" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C48" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D48" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E48" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F48" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H48" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I48" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J48" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K48" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L48" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M48" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N48" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O48" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q48" s="6" t="n">
+        <v/>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4519,72 +4521,76 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C49" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D49" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E49" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F49" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H49" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I49" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J49" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K49" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L49" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M49" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N49" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O49" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S49" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4596,83 +4602,77 @@
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W49" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C50" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D50" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E50" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F50" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H50" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I50" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J50" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K50" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L50" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M50" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N50" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O50" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P50" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30140.5</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T50" s="8" t="n">
@@ -4698,50 +4698,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C51" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D51" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E51" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F51" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H51" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I51" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J51" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K51" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L51" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M51" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N51" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O51" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4754,17 +4754,23 @@
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V51" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
@@ -4773,57 +4779,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C52" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D52" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E52" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F52" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H52" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I52" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J52" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K52" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L52" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M52" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N52" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O52" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4834,25 +4840,19 @@
       <c r="R52" s="6" t="n">
         <v/>
       </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U52" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U52" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V52" s="8" t="n">
+        <v/>
       </c>
       <c r="W52" s="11" t="inlineStr">
         <is>
@@ -4868,50 +4868,50 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C53" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D53" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E53" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F53" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H53" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I53" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J53" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K53" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L53" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M53" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N53" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O53" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4919,16 +4919,20 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S53" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4943,57 +4947,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C54" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D54" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E54" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F54" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H54" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I54" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J54" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K54" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L54" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M54" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N54" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O54" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5003,18 +5007,16 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
       </c>
       <c r="U54" s="8" t="n">
         <v/>
@@ -5027,72 +5029,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C55" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D55" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E55" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F55" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H55" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I55" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J55" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K55" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L55" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M55" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N55" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O55" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5116,72 +5116,70 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C56" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D56" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E56" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F56" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H56" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I56" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J56" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K56" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L56" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M56" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N56" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O56" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
+      <c r="Q56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S56" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
@@ -5193,74 +5191,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C57" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D57" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E57" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F57" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H57" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I57" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J57" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K57" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L57" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M57" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N57" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O57" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S57" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5273,74 +5277,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C58" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D58" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E58" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F58" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H58" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I58" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J58" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K58" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L58" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M58" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N58" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O58" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5359,55 +5357,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C59" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D59" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E59" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F59" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H59" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I59" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J59" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K59" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L59" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M59" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N59" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O59" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5417,19 +5419,23 @@
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U59" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5441,57 +5447,57 @@
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C60" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D60" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E60" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F60" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H60" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I60" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J60" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K60" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L60" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M60" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N60" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O60" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5499,87 +5505,81 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W60" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>28967.5</v>
+        <v>29438.75</v>
       </c>
       <c r="C61" t="n">
-        <v>29498.25</v>
+        <v>29665.25</v>
       </c>
       <c r="D61" t="n">
-        <v>28957.75</v>
+        <v>29352.75</v>
       </c>
       <c r="E61" t="n">
-        <v>29446.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F61" t="n">
-        <v>483.25</v>
+        <v>166.93</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0057</v>
       </c>
       <c r="H61" t="n">
-        <v>540.5</v>
+        <v>312.5</v>
       </c>
       <c r="I61" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J61" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K61" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L61" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M61" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N61" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O61" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5590,20 +5590,18 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U61" s="8" t="n">
+        <v/>
       </c>
       <c r="V61" s="8" t="n">
         <v/>
@@ -5618,50 +5616,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>29438.75</v>
+        <v>30780</v>
       </c>
       <c r="C62" t="n">
-        <v>29665.25</v>
+        <v>30821.25</v>
       </c>
       <c r="D62" t="n">
-        <v>29352.75</v>
+        <v>30778.5</v>
       </c>
       <c r="E62" t="n">
-        <v>29613.68</v>
+        <v>30816.75</v>
       </c>
       <c r="F62" t="n">
-        <v>166.93</v>
+        <v>1203.07</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0406</v>
       </c>
       <c r="H62" t="n">
-        <v>312.5</v>
+        <v>42.75</v>
       </c>
       <c r="I62" t="n">
-        <v>28417.25</v>
+        <v>29040.25</v>
       </c>
       <c r="J62" t="n">
-        <v>29015.62</v>
+        <v>29353.52</v>
       </c>
       <c r="K62" t="n">
-        <v>29176.5</v>
+        <v>29457.43</v>
       </c>
       <c r="L62" t="n">
-        <v>29337.38</v>
+        <v>29561.34</v>
       </c>
       <c r="M62" t="n">
-        <v>29717</v>
+        <v>29769.93</v>
       </c>
       <c r="N62" t="n">
-        <v>30096.62</v>
+        <v>29978.52</v>
       </c>
       <c r="O62" t="n">
-        <v>30038.75</v>
+        <v>29977.75</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5672,21 +5670,25 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="10" t="inlineStr">
+      <c r="S62" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U62" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V62" s="8" t="n">
-        <v/>
+      <c r="V62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
@@ -5694,88 +5696,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-20</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>29938</v>
-      </c>
-      <c r="C63" t="n">
-        <v>29944.5</v>
-      </c>
-      <c r="D63" t="n">
-        <v>29904</v>
-      </c>
-      <c r="E63" t="n">
-        <v>29917.25</v>
-      </c>
-      <c r="F63" t="n">
-        <v>303.57</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0103</v>
-      </c>
-      <c r="H63" t="n">
-        <v>40.5</v>
-      </c>
-      <c r="I63" t="n">
-        <v>29040.25</v>
-      </c>
-      <c r="J63" t="n">
-        <v>29353.52</v>
-      </c>
-      <c r="K63" t="n">
-        <v>29457.43</v>
-      </c>
-      <c r="L63" t="n">
-        <v>29561.34</v>
-      </c>
-      <c r="M63" t="n">
-        <v>29769.93</v>
-      </c>
-      <c r="N63" t="n">
-        <v>29978.52</v>
-      </c>
-      <c r="O63" t="n">
-        <v>29977.75</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5620,25 +5620,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30780</v>
+        <v>29938</v>
       </c>
       <c r="C62" t="n">
-        <v>30821.25</v>
+        <v>30862.75</v>
       </c>
       <c r="D62" t="n">
-        <v>30778.5</v>
+        <v>29904</v>
       </c>
       <c r="E62" t="n">
-        <v>30816.75</v>
+        <v>30784.75</v>
       </c>
       <c r="F62" t="n">
-        <v>1203.07</v>
+        <v>1171.07</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0406</v>
+        <v>0.0395</v>
       </c>
       <c r="H62" t="n">
-        <v>42.75</v>
+        <v>958.75</v>
       </c>
       <c r="I62" t="n">
         <v>29040.25</v>
@@ -5696,6 +5696,84 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>30780</v>
+      </c>
+      <c r="C63" t="n">
+        <v>30945</v>
+      </c>
+      <c r="D63" t="n">
+        <v>30670</v>
+      </c>
+      <c r="E63" t="n">
+        <v>30922.25</v>
+      </c>
+      <c r="F63" t="n">
+        <v>137.5</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0045</v>
+      </c>
+      <c r="H63" t="n">
+        <v>275</v>
+      </c>
+      <c r="I63" t="n">
+        <v>28945.25</v>
+      </c>
+      <c r="J63" t="n">
+        <v>30026.69</v>
+      </c>
+      <c r="K63" t="n">
+        <v>30305.38</v>
+      </c>
+      <c r="L63" t="n">
+        <v>30584.06</v>
+      </c>
+      <c r="M63" t="n">
+        <v>31264.12</v>
+      </c>
+      <c r="N63" t="n">
+        <v>31944.19</v>
+      </c>
+      <c r="O63" t="n">
+        <v>31821.5</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5707,22 +5707,22 @@
         <v>30780</v>
       </c>
       <c r="C63" t="n">
-        <v>30945</v>
+        <v>30997.5</v>
       </c>
       <c r="D63" t="n">
         <v>30670</v>
       </c>
       <c r="E63" t="n">
-        <v>30922.25</v>
+        <v>30910</v>
       </c>
       <c r="F63" t="n">
-        <v>137.5</v>
+        <v>125.25</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0045</v>
+        <v>0.0041</v>
       </c>
       <c r="H63" t="n">
-        <v>275</v>
+        <v>327.5</v>
       </c>
       <c r="I63" t="n">
         <v>28945.25</v>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30089.75</v>
+        <v>29742</v>
       </c>
       <c r="C2" t="n">
-        <v>30263.75</v>
+        <v>29892.75</v>
       </c>
       <c r="D2" t="n">
-        <v>29295.75</v>
+        <v>29160.5</v>
       </c>
       <c r="E2" t="n">
-        <v>29724.75</v>
+        <v>29368.25</v>
       </c>
       <c r="F2" t="n">
-        <v>210.5</v>
+        <v>-356.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0071</v>
+        <v>-0.012</v>
       </c>
       <c r="H2" t="n">
-        <v>968</v>
+        <v>732.25</v>
       </c>
       <c r="I2" t="n">
-        <v>28371.75</v>
+        <v>28327.75</v>
       </c>
       <c r="J2" t="n">
-        <v>28522.75</v>
+        <v>28729.25</v>
       </c>
       <c r="K2" t="n">
-        <v>29067.75</v>
+        <v>29240.75</v>
       </c>
       <c r="L2" t="n">
-        <v>29612.75</v>
+        <v>29752.25</v>
       </c>
       <c r="M2" t="n">
-        <v>29960.75</v>
+        <v>30208.75</v>
       </c>
       <c r="N2" t="n">
-        <v>30308.75</v>
+        <v>30665.25</v>
       </c>
       <c r="O2" t="n">
-        <v>31050.75</v>
+        <v>31231.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,55 +709,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29742</v>
+        <v>29282.5</v>
       </c>
       <c r="C3" t="n">
-        <v>29892.75</v>
+        <v>30069.5</v>
       </c>
       <c r="D3" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E3" t="n">
-        <v>29368.25</v>
+        <v>30052.75</v>
       </c>
       <c r="F3" t="n">
-        <v>-356.5</v>
+        <v>684.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0233</v>
       </c>
       <c r="H3" t="n">
-        <v>732.25</v>
+        <v>795.75</v>
       </c>
       <c r="I3" t="n">
-        <v>28327.75</v>
+        <v>28428.25</v>
       </c>
       <c r="J3" t="n">
-        <v>28729.25</v>
+        <v>28556.81</v>
       </c>
       <c r="K3" t="n">
-        <v>29240.75</v>
+        <v>29002.12</v>
       </c>
       <c r="L3" t="n">
-        <v>29752.25</v>
+        <v>29447.44</v>
       </c>
       <c r="M3" t="n">
-        <v>30208.75</v>
+        <v>29734.38</v>
       </c>
       <c r="N3" t="n">
-        <v>30665.25</v>
+        <v>30021.31</v>
       </c>
       <c r="O3" t="n">
-        <v>31231.75</v>
+        <v>30625</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -765,22 +769,24 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U3" s="8" t="n">
-        <v/>
-      </c>
       <c r="V3" s="8" t="n">
         <v/>
       </c>
@@ -789,59 +795,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29282.5</v>
+        <v>30007.25</v>
       </c>
       <c r="C4" t="n">
-        <v>30069.5</v>
+        <v>30599.75</v>
       </c>
       <c r="D4" t="n">
-        <v>29273.75</v>
+        <v>29934.75</v>
       </c>
       <c r="E4" t="n">
-        <v>30052.75</v>
+        <v>30523.5</v>
       </c>
       <c r="F4" t="n">
-        <v>684.5</v>
+        <v>470.75</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0157</v>
       </c>
       <c r="H4" t="n">
-        <v>795.75</v>
+        <v>665</v>
       </c>
       <c r="I4" t="n">
-        <v>28428.25</v>
+        <v>28478</v>
       </c>
       <c r="J4" t="n">
-        <v>28556.81</v>
+        <v>29447.56</v>
       </c>
       <c r="K4" t="n">
-        <v>29002.12</v>
+        <v>29654.88</v>
       </c>
       <c r="L4" t="n">
-        <v>29447.44</v>
+        <v>29862.19</v>
       </c>
       <c r="M4" t="n">
-        <v>29734.38</v>
+        <v>30450.62</v>
       </c>
       <c r="N4" t="n">
-        <v>30021.31</v>
+        <v>31039.06</v>
       </c>
       <c r="O4" t="n">
-        <v>30625</v>
+        <v>30865.25</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -852,20 +854,18 @@
       <c r="R4" s="6" t="n">
         <v/>
       </c>
-      <c r="S4" s="7" t="inlineStr">
+      <c r="S4" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T4" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U4" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U4" s="8" t="n">
+        <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
@@ -880,50 +880,50 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C5" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D5" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E5" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F5" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H5" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I5" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J5" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K5" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L5" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M5" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N5" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O5" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -931,18 +931,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -955,68 +955,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C6" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D6" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E6" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F6" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H6" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I6" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J6" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K6" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L6" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M6" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N6" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O6" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R6" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1037,81 +1045,77 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C7" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D7" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E7" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F7" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H7" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I7" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J7" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K7" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L7" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M7" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N7" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O7" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
@@ -1125,76 +1129,80 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C8" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D8" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E8" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F8" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H8" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I8" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J8" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K8" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L8" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M8" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N8" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O8" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+        <v>30505</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1202,83 +1210,75 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W8" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C9" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D9" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E9" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F9" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H9" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I9" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J9" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K9" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L9" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M9" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N9" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O9" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q9" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1295,55 +1295,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C10" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D10" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E10" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F10" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H10" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I10" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J10" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K10" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L10" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M10" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N10" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O10" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1351,18 +1355,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1377,57 +1381,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C11" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D11" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E11" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F11" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H11" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I11" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J11" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K11" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L11" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M11" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N11" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O11" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1438,7 +1442,7 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1468,69 +1472,73 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C12" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D12" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E12" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F12" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H12" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I12" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J12" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K12" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L12" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M12" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N12" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O12" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+        <v>30480.5</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1543,83 +1551,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C13" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D13" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E13" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H13" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I13" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J13" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K13" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L13" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M13" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N13" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O13" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
-      </c>
       <c r="U13" s="8" t="n">
         <v/>
       </c>
@@ -1631,55 +1631,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C14" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D14" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E14" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F14" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H14" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I14" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J14" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K14" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L14" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M14" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N14" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O14" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1687,18 +1691,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1713,57 +1717,57 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C15" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D15" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E15" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F15" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H15" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I15" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J15" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K15" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L15" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M15" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N15" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O15" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,12 +1777,12 @@
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S15" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1795,59 +1799,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C16" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D16" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E16" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H16" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I16" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J16" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K16" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L16" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M16" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N16" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O16" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,7 +1860,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1884,50 +1884,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C17" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D17" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E17" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F17" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H17" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I17" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J17" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K17" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L17" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M17" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N17" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O17" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1935,18 +1935,18 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S17" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U17" s="8" t="n">
         <v/>
@@ -1959,55 +1959,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C18" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D18" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E18" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F18" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H18" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I18" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J18" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K18" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L18" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M18" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N18" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O18" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2020,7 +2024,7 @@
       </c>
       <c r="S18" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T18" s="8" t="inlineStr">
@@ -2028,70 +2032,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W18" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C19" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D19" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E19" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F19" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H19" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I19" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J19" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K19" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L19" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M19" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N19" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O19" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2099,23 +2105,21 @@
       <c r="Q19" s="6" t="n">
         <v/>
       </c>
-      <c r="R19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2127,63 +2131,67 @@
       </c>
       <c r="X19" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C20" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D20" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E20" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F20" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H20" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I20" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J20" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K20" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L20" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M20" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N20" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O20" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P20" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
@@ -2192,7 +2200,7 @@
       </c>
       <c r="S20" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T20" s="8" t="n">
@@ -2204,81 +2212,73 @@
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W20" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C21" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D21" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E21" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F21" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H21" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I21" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J21" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K21" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L21" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M21" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N21" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O21" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P21" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2302,50 +2302,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C22" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D22" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E22" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F22" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H22" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I22" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J22" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K22" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L22" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M22" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N22" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O22" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,16 +2358,20 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="10" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2377,55 +2381,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C23" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D23" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E23" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F23" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H23" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I23" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J23" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K23" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L23" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M23" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N23" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O23" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2438,20 +2446,16 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2461,72 +2465,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C24" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D24" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E24" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F24" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H24" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I24" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J24" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K24" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L24" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M24" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N24" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O24" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="n">
-        <v/>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R24" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2550,81 +2552,81 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C25" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D25" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E25" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F25" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H25" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I25" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J25" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K25" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L25" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M25" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N25" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O25" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
       </c>
-      <c r="Q25" s="6" t="inlineStr">
+      <c r="Q25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R25" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W25" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X25" t="inlineStr"/>
@@ -2632,50 +2634,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C26" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D26" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E26" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F26" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H26" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I26" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J26" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K26" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L26" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M26" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N26" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O26" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2686,20 +2688,16 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2714,50 +2712,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C27" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D27" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E27" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F27" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H27" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I27" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J27" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K27" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L27" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M27" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N27" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O27" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2768,16 +2766,20 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2792,50 +2794,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C28" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D28" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E28" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F28" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H28" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I28" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J28" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K28" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L28" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M28" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N28" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O28" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2846,7 +2848,7 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="7" t="inlineStr">
+      <c r="S28" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2861,8 +2863,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V28" s="8" t="n">
-        <v/>
+      <c r="V28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
@@ -2874,50 +2878,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C29" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D29" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E29" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F29" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H29" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I29" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J29" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K29" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L29" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M29" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N29" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O29" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2930,78 +2934,76 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V29" s="8" t="n">
+        <v/>
       </c>
       <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C30" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D30" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E30" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F30" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H30" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I30" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J30" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K30" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L30" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M30" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N30" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O30" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3009,12 +3011,14 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T30" s="8" t="n">
@@ -3033,57 +3037,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C31" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D31" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E31" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F31" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H31" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I31" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J31" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K31" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L31" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M31" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N31" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O31" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3091,22 +3095,24 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
@@ -3115,59 +3121,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C32" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D32" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E32" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F32" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H32" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I32" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J32" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K32" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L32" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M32" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N32" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O32" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3180,18 +3182,14 @@
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3201,55 +3199,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C33" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D33" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E33" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F33" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H33" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I33" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J33" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K33" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L33" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M33" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N33" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O33" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3257,16 +3259,20 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3281,57 +3287,57 @@
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C34" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D34" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E34" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F34" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H34" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I34" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J34" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K34" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L34" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M34" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N34" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O34" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3339,24 +3345,24 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
+      <c r="U34" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U34" s="8" t="n">
-        <v/>
-      </c>
       <c r="V34" s="8" t="n">
         <v/>
       </c>
@@ -3365,59 +3371,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C35" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D35" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E35" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F35" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H35" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I35" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J35" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K35" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L35" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M35" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N35" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O35" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3428,19 +3430,19 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
+      <c r="S35" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T35" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U35" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V35" s="8" t="n">
@@ -3456,50 +3458,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C36" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D36" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E36" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F36" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H36" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I36" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J36" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K36" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L36" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M36" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N36" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O36" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3510,20 +3512,16 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U36" s="8" t="n">
+        <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
@@ -3533,55 +3531,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C37" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D37" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E37" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F37" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G37" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H37" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I37" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J37" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K37" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L37" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M37" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N37" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O37" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3594,11 +3596,13 @@
       </c>
       <c r="S37" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3620,153 +3624,147 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C38" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D38" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E38" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F38" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H38" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I38" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J38" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K38" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L38" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M38" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N38" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O38" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
+        <v>30631.5</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
+      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W38" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C39" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D39" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E39" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F39" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H39" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I39" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J39" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K39" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L39" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M39" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N39" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O39" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30728.5</v>
+      </c>
+      <c r="P39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3788,50 +3786,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C40" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D40" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E40" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F40" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H40" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I40" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J40" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K40" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L40" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M40" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N40" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O40" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3839,12 +3837,14 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3866,50 +3866,50 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C41" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D41" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E41" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F41" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H41" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I41" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J41" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K41" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L41" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M41" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N41" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O41" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3917,14 +3917,12 @@
       <c r="Q41" s="6" t="n">
         <v/>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R41" s="6" t="n">
+        <v/>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3941,68 +3939,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C42" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D42" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E42" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F42" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H42" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I42" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J42" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K42" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L42" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M42" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N42" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O42" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4019,81 +4025,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C43" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D43" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E43" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F43" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H43" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I43" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J43" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K43" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L43" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M43" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N43" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O43" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
       <c r="U43" s="8" t="n">
         <v/>
       </c>
@@ -4105,55 +4105,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C44" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D44" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E44" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F44" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H44" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I44" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J44" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K44" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L44" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M44" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N44" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O44" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4164,15 +4168,13 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
       </c>
       <c r="U44" s="8" t="n">
         <v/>
@@ -4187,57 +4189,57 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C45" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D45" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E45" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F45" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H45" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I45" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J45" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K45" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L45" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M45" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N45" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O45" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4248,102 +4250,102 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X45" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W45" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C46" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D46" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E46" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F46" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H46" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I46" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J46" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K46" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L46" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M46" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N46" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O46" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
       </c>
       <c r="V46" s="8" t="n">
         <v/>
@@ -4353,72 +4355,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr"/>
+      <c r="X46" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C47" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D47" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E47" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F47" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H47" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I47" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J47" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K47" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L47" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M47" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N47" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O47" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q47" s="6" t="n">
+        <v/>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4437,72 +4441,76 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C48" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D48" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E48" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F48" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H48" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I48" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J48" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K48" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L48" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M48" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N48" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O48" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4514,83 +4522,77 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W48" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C49" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D49" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E49" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F49" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H49" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I49" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J49" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K49" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L49" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M49" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N49" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O49" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P49" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30140.5</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T49" s="8" t="n">
@@ -4616,50 +4618,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C50" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D50" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E50" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F50" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H50" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I50" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J50" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K50" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L50" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M50" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N50" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O50" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4672,17 +4674,23 @@
       </c>
       <c r="S50" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U50" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V50" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U50" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
@@ -4691,57 +4699,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C51" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D51" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E51" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F51" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H51" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I51" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J51" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K51" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L51" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M51" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N51" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O51" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4752,25 +4760,19 @@
       <c r="R51" s="6" t="n">
         <v/>
       </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U51" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V51" s="8" t="n">
+        <v/>
       </c>
       <c r="W51" s="11" t="inlineStr">
         <is>
@@ -4786,50 +4788,50 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C52" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D52" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E52" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F52" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H52" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I52" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J52" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K52" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L52" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M52" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N52" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O52" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4837,16 +4839,20 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="n">
-        <v/>
+      <c r="R52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S52" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4861,57 +4867,57 @@
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C53" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D53" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E53" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F53" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H53" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I53" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J53" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K53" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L53" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M53" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N53" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O53" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4921,18 +4927,16 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4945,72 +4949,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C54" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D54" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E54" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F54" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H54" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I54" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J54" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K54" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L54" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M54" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N54" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O54" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S54" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5034,72 +5036,70 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C55" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D55" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E55" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F55" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H55" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I55" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J55" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K55" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L55" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M55" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N55" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O55" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
+      <c r="Q55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
       <c r="U55" s="8" t="n">
         <v/>
       </c>
@@ -5111,74 +5111,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C56" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D56" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E56" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F56" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H56" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I56" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J56" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K56" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L56" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M56" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N56" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O56" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S56" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
       </c>
       <c r="U56" s="8" t="n">
         <v/>
@@ -5191,74 +5197,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C57" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D57" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E57" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F57" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H57" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I57" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J57" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K57" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L57" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M57" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N57" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O57" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q57" s="6" t="n">
+        <v/>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5277,55 +5277,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C58" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D58" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E58" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F58" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H58" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I58" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J58" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K58" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L58" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M58" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N58" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O58" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5335,19 +5339,23 @@
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U58" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5359,57 +5367,57 @@
       </c>
       <c r="X58" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C59" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D59" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E59" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F59" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H59" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I59" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J59" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K59" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L59" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M59" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N59" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O59" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5417,87 +5425,81 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
+      <c r="R59" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W59" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28967.5</v>
+        <v>29438.75</v>
       </c>
       <c r="C60" t="n">
-        <v>29498.25</v>
+        <v>29665.25</v>
       </c>
       <c r="D60" t="n">
-        <v>28957.75</v>
+        <v>29352.75</v>
       </c>
       <c r="E60" t="n">
-        <v>29446.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F60" t="n">
-        <v>483.25</v>
+        <v>166.93</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0057</v>
       </c>
       <c r="H60" t="n">
-        <v>540.5</v>
+        <v>312.5</v>
       </c>
       <c r="I60" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J60" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K60" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L60" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M60" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N60" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O60" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5508,20 +5510,18 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="7" t="inlineStr">
+      <c r="S60" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U60" s="8" t="n">
+        <v/>
       </c>
       <c r="V60" s="8" t="n">
         <v/>
@@ -5536,50 +5536,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29438.75</v>
+        <v>29938</v>
       </c>
       <c r="C61" t="n">
-        <v>29665.25</v>
+        <v>30862.75</v>
       </c>
       <c r="D61" t="n">
-        <v>29352.75</v>
+        <v>29904</v>
       </c>
       <c r="E61" t="n">
-        <v>29613.68</v>
+        <v>30784.75</v>
       </c>
       <c r="F61" t="n">
-        <v>166.93</v>
+        <v>1171.07</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0395</v>
       </c>
       <c r="H61" t="n">
-        <v>312.5</v>
+        <v>958.75</v>
       </c>
       <c r="I61" t="n">
-        <v>28417.25</v>
+        <v>29040.25</v>
       </c>
       <c r="J61" t="n">
-        <v>29015.62</v>
+        <v>29353.52</v>
       </c>
       <c r="K61" t="n">
-        <v>29176.5</v>
+        <v>29457.43</v>
       </c>
       <c r="L61" t="n">
-        <v>29337.38</v>
+        <v>29561.34</v>
       </c>
       <c r="M61" t="n">
-        <v>29717</v>
+        <v>29769.93</v>
       </c>
       <c r="N61" t="n">
-        <v>30096.62</v>
+        <v>29978.52</v>
       </c>
       <c r="O61" t="n">
-        <v>30038.75</v>
+        <v>29977.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5590,21 +5590,25 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="7" t="inlineStr">
+      <c r="S61" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U61" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U61" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V61" s="8" t="n">
-        <v/>
+      <c r="V61" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
@@ -5616,50 +5620,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>29938</v>
+        <v>31008.5</v>
       </c>
       <c r="C62" t="n">
-        <v>30862.75</v>
+        <v>31033</v>
       </c>
       <c r="D62" t="n">
-        <v>29904</v>
+        <v>30997.5</v>
       </c>
       <c r="E62" t="n">
-        <v>30784.75</v>
+        <v>31020.25</v>
       </c>
       <c r="F62" t="n">
-        <v>1171.07</v>
+        <v>235.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.0076</v>
       </c>
       <c r="H62" t="n">
-        <v>958.75</v>
+        <v>35.5</v>
       </c>
       <c r="I62" t="n">
-        <v>29040.25</v>
+        <v>28945.25</v>
       </c>
       <c r="J62" t="n">
-        <v>29353.52</v>
+        <v>30026.69</v>
       </c>
       <c r="K62" t="n">
-        <v>29457.43</v>
+        <v>30305.38</v>
       </c>
       <c r="L62" t="n">
-        <v>29561.34</v>
+        <v>30584.06</v>
       </c>
       <c r="M62" t="n">
-        <v>29769.93</v>
+        <v>31264.12</v>
       </c>
       <c r="N62" t="n">
-        <v>29978.52</v>
+        <v>31944.19</v>
       </c>
       <c r="O62" t="n">
-        <v>29977.75</v>
+        <v>31821.5</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5670,25 +5674,21 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
+      <c r="S62" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V62" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U62" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V62" s="8" t="n">
+        <v/>
       </c>
       <c r="W62" s="9" t="inlineStr">
         <is>
@@ -5696,84 +5696,6 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-22</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>30780</v>
-      </c>
-      <c r="C63" t="n">
-        <v>30997.5</v>
-      </c>
-      <c r="D63" t="n">
-        <v>30670</v>
-      </c>
-      <c r="E63" t="n">
-        <v>30910</v>
-      </c>
-      <c r="F63" t="n">
-        <v>125.25</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0.0041</v>
-      </c>
-      <c r="H63" t="n">
-        <v>327.5</v>
-      </c>
-      <c r="I63" t="n">
-        <v>28945.25</v>
-      </c>
-      <c r="J63" t="n">
-        <v>30026.69</v>
-      </c>
-      <c r="K63" t="n">
-        <v>30305.38</v>
-      </c>
-      <c r="L63" t="n">
-        <v>30584.06</v>
-      </c>
-      <c r="M63" t="n">
-        <v>31264.12</v>
-      </c>
-      <c r="N63" t="n">
-        <v>31944.19</v>
-      </c>
-      <c r="O63" t="n">
-        <v>31821.5</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5627,22 +5627,22 @@
         <v>31008.5</v>
       </c>
       <c r="C62" t="n">
-        <v>31033</v>
+        <v>31070.5</v>
       </c>
       <c r="D62" t="n">
         <v>30997.5</v>
       </c>
       <c r="E62" t="n">
-        <v>31020.25</v>
+        <v>31047.75</v>
       </c>
       <c r="F62" t="n">
-        <v>235.5</v>
+        <v>263</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0076</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>35.5</v>
+        <v>73</v>
       </c>
       <c r="I62" t="n">
         <v>28945.25</v>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5633,13 +5633,13 @@
         <v>30997.5</v>
       </c>
       <c r="E62" t="n">
-        <v>31047.75</v>
+        <v>31014.5</v>
       </c>
       <c r="F62" t="n">
-        <v>263</v>
+        <v>229.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.0075</v>
       </c>
       <c r="H62" t="n">
         <v>73</v>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5630,19 +5630,19 @@
         <v>31070.5</v>
       </c>
       <c r="D62" t="n">
-        <v>30997.5</v>
+        <v>30982.75</v>
       </c>
       <c r="E62" t="n">
-        <v>31014.5</v>
+        <v>31002</v>
       </c>
       <c r="F62" t="n">
-        <v>229.75</v>
+        <v>217.25</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0075</v>
+        <v>0.0071</v>
       </c>
       <c r="H62" t="n">
-        <v>73</v>
+        <v>87.75</v>
       </c>
       <c r="I62" t="n">
         <v>28945.25</v>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -5633,13 +5633,13 @@
         <v>30982.75</v>
       </c>
       <c r="E62" t="n">
-        <v>31002</v>
+        <v>31001.25</v>
       </c>
       <c r="F62" t="n">
-        <v>217.25</v>
+        <v>216.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0071</v>
+        <v>0.007</v>
       </c>
       <c r="H62" t="n">
         <v>87.75</v>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5624,25 +5624,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>31008.5</v>
+        <v>30780</v>
       </c>
       <c r="C62" t="n">
-        <v>31070.5</v>
+        <v>31065.5</v>
       </c>
       <c r="D62" t="n">
-        <v>30982.75</v>
+        <v>30670</v>
       </c>
       <c r="E62" t="n">
-        <v>31001.25</v>
+        <v>31028.5</v>
       </c>
       <c r="F62" t="n">
-        <v>216.5</v>
+        <v>243.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.007</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H62" t="n">
-        <v>87.75</v>
+        <v>395.5</v>
       </c>
       <c r="I62" t="n">
         <v>28945.25</v>
@@ -5696,6 +5696,88 @@
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>31008.5</v>
+      </c>
+      <c r="C63" t="n">
+        <v>31094.75</v>
+      </c>
+      <c r="D63" t="n">
+        <v>30910.75</v>
+      </c>
+      <c r="E63" t="n">
+        <v>30956.75</v>
+      </c>
+      <c r="F63" t="n">
+        <v>-71.75</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>-0.0023</v>
+      </c>
+      <c r="H63" t="n">
+        <v>184</v>
+      </c>
+      <c r="I63" t="n">
+        <v>30274.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>30713.38</v>
+      </c>
+      <c r="K63" t="n">
+        <v>30830.75</v>
+      </c>
+      <c r="L63" t="n">
+        <v>30948.12</v>
+      </c>
+      <c r="M63" t="n">
+        <v>31226.25</v>
+      </c>
+      <c r="N63" t="n">
+        <v>31504.38</v>
+      </c>
+      <c r="O63" t="n">
+        <v>31461</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-29</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29742</v>
+        <v>29282.5</v>
       </c>
       <c r="C2" t="n">
-        <v>29892.75</v>
+        <v>30069.5</v>
       </c>
       <c r="D2" t="n">
-        <v>29160.5</v>
+        <v>29273.75</v>
       </c>
       <c r="E2" t="n">
-        <v>29368.25</v>
+        <v>30052.75</v>
       </c>
       <c r="F2" t="n">
-        <v>-356.5</v>
+        <v>684.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.012</v>
+        <v>0.0233</v>
       </c>
       <c r="H2" t="n">
-        <v>732.25</v>
+        <v>795.75</v>
       </c>
       <c r="I2" t="n">
-        <v>28327.75</v>
+        <v>28428.25</v>
       </c>
       <c r="J2" t="n">
-        <v>28729.25</v>
+        <v>28556.81</v>
       </c>
       <c r="K2" t="n">
-        <v>29240.75</v>
+        <v>29002.12</v>
       </c>
       <c r="L2" t="n">
-        <v>29752.25</v>
+        <v>29447.44</v>
       </c>
       <c r="M2" t="n">
-        <v>30208.75</v>
+        <v>29734.38</v>
       </c>
       <c r="N2" t="n">
-        <v>30665.25</v>
+        <v>30021.31</v>
       </c>
       <c r="O2" t="n">
-        <v>31231.75</v>
+        <v>30625</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,22 +685,24 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U2" s="8" t="n">
-        <v/>
-      </c>
       <c r="V2" s="8" t="n">
         <v/>
       </c>
@@ -709,59 +711,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29282.5</v>
+        <v>30007.25</v>
       </c>
       <c r="C3" t="n">
-        <v>30069.5</v>
+        <v>30599.75</v>
       </c>
       <c r="D3" t="n">
-        <v>29273.75</v>
+        <v>29934.75</v>
       </c>
       <c r="E3" t="n">
-        <v>30052.75</v>
+        <v>30523.5</v>
       </c>
       <c r="F3" t="n">
-        <v>684.5</v>
+        <v>470.75</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0157</v>
       </c>
       <c r="H3" t="n">
-        <v>795.75</v>
+        <v>665</v>
       </c>
       <c r="I3" t="n">
-        <v>28428.25</v>
+        <v>28478</v>
       </c>
       <c r="J3" t="n">
-        <v>28556.81</v>
+        <v>29447.56</v>
       </c>
       <c r="K3" t="n">
-        <v>29002.12</v>
+        <v>29654.88</v>
       </c>
       <c r="L3" t="n">
-        <v>29447.44</v>
+        <v>29862.19</v>
       </c>
       <c r="M3" t="n">
-        <v>29734.38</v>
+        <v>30450.62</v>
       </c>
       <c r="N3" t="n">
-        <v>30021.31</v>
+        <v>31039.06</v>
       </c>
       <c r="O3" t="n">
-        <v>30625</v>
+        <v>30865.25</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,20 +770,18 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T3" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U3" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U3" s="8" t="n">
+        <v/>
       </c>
       <c r="V3" s="8" t="n">
         <v/>
@@ -800,50 +796,50 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C4" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D4" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E4" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F4" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H4" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I4" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J4" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K4" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L4" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M4" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N4" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O4" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -851,18 +847,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -875,68 +871,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C5" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D5" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E5" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F5" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H5" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I5" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J5" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K5" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L5" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M5" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N5" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O5" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R5" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -957,81 +961,77 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C6" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D6" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E6" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F6" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H6" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I6" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J6" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K6" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L6" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M6" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N6" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O6" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
@@ -1045,76 +1045,80 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C7" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D7" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E7" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F7" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H7" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I7" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J7" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K7" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L7" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M7" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N7" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O7" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>30505</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1122,83 +1126,75 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W7" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C8" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D8" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E8" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F8" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H8" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I8" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J8" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K8" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L8" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M8" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N8" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O8" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q8" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S8" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1215,55 +1211,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C9" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D9" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E9" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F9" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H9" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I9" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J9" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K9" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L9" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M9" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N9" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O9" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1271,18 +1271,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R9" s="6" t="n">
+        <v/>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1297,57 +1297,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C10" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D10" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E10" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F10" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H10" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I10" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J10" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K10" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L10" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M10" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N10" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O10" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1358,7 +1358,7 @@
       <c r="R10" s="6" t="n">
         <v/>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1388,69 +1388,73 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C11" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D11" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E11" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F11" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H11" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I11" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J11" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K11" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L11" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M11" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N11" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O11" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+        <v>30480.5</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1463,83 +1467,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C12" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D12" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E12" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H12" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I12" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J12" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K12" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L12" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M12" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N12" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O12" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P12" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
-      </c>
       <c r="U12" s="8" t="n">
         <v/>
       </c>
@@ -1551,55 +1547,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C13" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D13" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E13" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F13" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H13" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I13" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J13" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K13" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L13" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M13" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N13" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O13" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1607,18 +1607,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1633,57 +1633,57 @@
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C14" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D14" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E14" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F14" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H14" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I14" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J14" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K14" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L14" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M14" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N14" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O14" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1693,12 +1693,12 @@
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1715,59 +1715,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C15" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D15" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E15" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H15" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I15" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J15" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K15" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L15" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M15" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N15" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O15" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1780,7 +1776,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1804,50 +1800,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C16" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D16" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E16" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F16" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H16" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I16" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J16" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K16" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L16" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M16" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N16" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O16" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1855,18 +1851,18 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="n">
-        <v/>
+      <c r="R16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U16" s="8" t="n">
         <v/>
@@ -1879,55 +1875,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C17" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D17" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E17" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F17" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H17" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I17" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J17" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K17" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L17" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M17" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N17" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O17" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T17" s="8" t="inlineStr">
@@ -1948,70 +1948,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C18" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D18" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E18" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F18" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H18" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I18" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J18" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K18" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L18" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M18" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N18" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O18" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2019,23 +2021,21 @@
       <c r="Q18" s="6" t="n">
         <v/>
       </c>
-      <c r="R18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2047,63 +2047,67 @@
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C19" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D19" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E19" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H19" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I19" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J19" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K19" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L19" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M19" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N19" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O19" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P19" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
@@ -2112,7 +2116,7 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T19" s="8" t="n">
@@ -2124,81 +2128,73 @@
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W19" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C20" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D20" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E20" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F20" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H20" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I20" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J20" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K20" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L20" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M20" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N20" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O20" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P20" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
+      <c r="S20" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2222,50 +2218,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C21" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D21" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E21" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F21" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H21" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I21" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J21" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K21" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L21" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M21" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N21" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O21" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2278,16 +2274,20 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S21" s="7" t="inlineStr">
+      <c r="S21" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2297,55 +2297,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C22" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D22" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E22" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F22" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H22" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I22" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J22" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K22" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L22" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M22" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N22" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O22" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,20 +2362,16 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2381,72 +2381,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C23" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D23" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E23" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F23" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H23" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I23" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J23" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K23" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L23" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M23" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N23" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O23" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="n">
-        <v/>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R23" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S23" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2470,81 +2468,81 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C24" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D24" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E24" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F24" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H24" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I24" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J24" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K24" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L24" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M24" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N24" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O24" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
       </c>
-      <c r="Q24" s="6" t="inlineStr">
+      <c r="Q24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W24" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr"/>
@@ -2552,50 +2550,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C25" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D25" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E25" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F25" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H25" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I25" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J25" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K25" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L25" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M25" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N25" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O25" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2606,20 +2604,16 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2634,50 +2628,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C26" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D26" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E26" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F26" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H26" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I26" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J26" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K26" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L26" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M26" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N26" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O26" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2688,16 +2682,20 @@
       <c r="R26" s="6" t="n">
         <v/>
       </c>
-      <c r="S26" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
@@ -2712,50 +2710,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C27" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D27" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E27" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F27" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H27" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I27" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J27" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K27" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L27" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M27" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N27" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O27" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2766,7 +2764,7 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2781,8 +2779,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V27" s="8" t="n">
-        <v/>
+      <c r="V27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
@@ -2794,50 +2794,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C28" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D28" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E28" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F28" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H28" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I28" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J28" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K28" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L28" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M28" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N28" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O28" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2850,78 +2850,76 @@
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V28" s="8" t="n">
+        <v/>
       </c>
       <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C29" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D29" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E29" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F29" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H29" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I29" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J29" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K29" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L29" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M29" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N29" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O29" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2929,12 +2927,14 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S29" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T29" s="8" t="n">
@@ -2953,57 +2953,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C30" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D30" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E30" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F30" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H30" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I30" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J30" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K30" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L30" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M30" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N30" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O30" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3011,22 +3011,24 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3035,59 +3037,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C31" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D31" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E31" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F31" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H31" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I31" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J31" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K31" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L31" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M31" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N31" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O31" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3100,18 +3098,14 @@
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3121,55 +3115,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C32" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D32" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E32" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F32" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H32" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I32" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J32" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K32" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L32" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M32" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N32" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O32" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3177,16 +3175,20 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3201,57 +3203,57 @@
       </c>
       <c r="X32" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C33" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D33" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E33" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F33" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H33" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I33" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J33" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K33" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L33" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M33" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N33" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O33" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3259,24 +3261,24 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+      <c r="U33" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U33" s="8" t="n">
-        <v/>
-      </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
@@ -3285,59 +3287,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C34" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D34" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E34" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F34" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H34" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I34" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J34" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K34" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L34" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M34" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N34" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O34" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3348,19 +3346,19 @@
       <c r="R34" s="6" t="n">
         <v/>
       </c>
-      <c r="S34" s="10" t="inlineStr">
+      <c r="S34" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T34" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U34" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V34" s="8" t="n">
@@ -3376,50 +3374,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C35" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D35" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E35" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F35" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H35" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I35" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J35" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K35" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L35" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M35" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N35" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O35" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3430,20 +3428,16 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U35" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U35" s="8" t="n">
+        <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
@@ -3453,55 +3447,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C36" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D36" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E36" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F36" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G36" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H36" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I36" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J36" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K36" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L36" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M36" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N36" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O36" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3514,11 +3512,13 @@
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3540,153 +3540,147 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C37" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D37" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E37" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F37" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H37" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I37" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J37" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K37" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L37" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M37" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N37" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O37" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
+        <v>30631.5</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
+      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W37" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C38" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D38" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E38" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F38" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H38" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I38" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J38" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K38" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L38" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M38" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N38" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O38" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30728.5</v>
+      </c>
+      <c r="P38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3708,50 +3702,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C39" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D39" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E39" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F39" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H39" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I39" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J39" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K39" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L39" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M39" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N39" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O39" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3759,12 +3753,14 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3786,50 +3782,50 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C40" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D40" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E40" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F40" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H40" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I40" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J40" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K40" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L40" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M40" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N40" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O40" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3837,14 +3833,12 @@
       <c r="Q40" s="6" t="n">
         <v/>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R40" s="6" t="n">
+        <v/>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3861,68 +3855,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C41" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D41" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E41" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F41" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I41" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J41" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K41" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L41" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M41" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N41" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O41" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3939,81 +3941,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C42" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D42" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E42" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F42" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H42" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I42" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J42" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K42" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L42" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M42" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N42" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O42" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
       <c r="U42" s="8" t="n">
         <v/>
       </c>
@@ -4025,55 +4021,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C43" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D43" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E43" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F43" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H43" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I43" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J43" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K43" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L43" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M43" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N43" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O43" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4084,15 +4084,13 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
       </c>
       <c r="U43" s="8" t="n">
         <v/>
@@ -4107,57 +4105,57 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C44" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D44" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E44" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F44" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H44" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I44" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J44" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K44" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L44" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M44" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N44" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O44" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4168,102 +4166,102 @@
       <c r="R44" s="6" t="n">
         <v/>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X44" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W44" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C45" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D45" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E45" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F45" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H45" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I45" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J45" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K45" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L45" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M45" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N45" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O45" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R45" s="6" t="n">
-        <v/>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
       </c>
       <c r="V45" s="8" t="n">
         <v/>
@@ -4273,72 +4271,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X45" t="inlineStr"/>
+      <c r="X45" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C46" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D46" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E46" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F46" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H46" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I46" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J46" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K46" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L46" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M46" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N46" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O46" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
       </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q46" s="6" t="n">
+        <v/>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4357,72 +4357,76 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C47" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D47" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E47" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F47" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H47" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I47" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J47" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K47" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L47" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M47" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N47" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O47" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P47" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S47" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S47" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4434,83 +4438,77 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W47" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C48" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D48" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E48" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F48" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H48" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I48" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J48" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K48" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L48" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M48" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N48" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O48" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P48" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30140.5</v>
+      </c>
+      <c r="P48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T48" s="8" t="n">
@@ -4536,50 +4534,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C49" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D49" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E49" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F49" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H49" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I49" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J49" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K49" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L49" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M49" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N49" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O49" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4592,17 +4590,23 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U49" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V49" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U49" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W49" s="11" t="inlineStr">
         <is>
@@ -4611,57 +4615,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C50" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D50" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E50" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F50" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H50" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I50" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J50" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K50" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L50" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M50" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N50" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O50" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4672,25 +4676,19 @@
       <c r="R50" s="6" t="n">
         <v/>
       </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U50" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V50" s="8" t="n">
+        <v/>
       </c>
       <c r="W50" s="11" t="inlineStr">
         <is>
@@ -4706,50 +4704,50 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C51" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D51" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E51" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F51" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H51" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I51" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J51" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K51" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L51" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M51" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N51" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O51" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4757,16 +4755,20 @@
       <c r="Q51" s="6" t="n">
         <v/>
       </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4781,57 +4783,57 @@
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C52" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D52" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E52" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F52" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H52" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I52" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J52" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K52" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L52" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M52" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N52" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O52" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4841,18 +4843,16 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
       </c>
       <c r="U52" s="8" t="n">
         <v/>
@@ -4865,72 +4865,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C53" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D53" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E53" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F53" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H53" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I53" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J53" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K53" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L53" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M53" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N53" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O53" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4954,72 +4952,70 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C54" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D54" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E54" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F54" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H54" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I54" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J54" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K54" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L54" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M54" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N54" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O54" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
+      <c r="Q54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5031,74 +5027,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C55" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D55" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E55" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F55" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H55" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I55" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J55" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K55" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L55" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M55" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N55" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O55" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R55" s="6" t="n">
-        <v/>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R55" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S55" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="n">
+        <v/>
       </c>
       <c r="U55" s="8" t="n">
         <v/>
@@ -5111,74 +5113,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C56" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D56" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E56" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F56" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H56" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I56" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J56" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K56" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L56" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M56" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N56" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O56" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q56" s="6" t="n">
+        <v/>
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5197,55 +5193,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C57" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D57" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E57" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F57" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H57" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I57" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J57" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K57" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L57" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M57" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N57" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O57" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5255,19 +5255,23 @@
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S57" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U57" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S57" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5279,57 +5283,57 @@
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C58" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D58" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E58" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F58" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H58" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I58" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J58" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K58" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L58" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M58" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N58" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O58" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5337,87 +5341,81 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W58" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>28967.5</v>
+        <v>29438.75</v>
       </c>
       <c r="C59" t="n">
-        <v>29498.25</v>
+        <v>29665.25</v>
       </c>
       <c r="D59" t="n">
-        <v>28957.75</v>
+        <v>29352.75</v>
       </c>
       <c r="E59" t="n">
-        <v>29446.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F59" t="n">
-        <v>483.25</v>
+        <v>166.93</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0057</v>
       </c>
       <c r="H59" t="n">
-        <v>540.5</v>
+        <v>312.5</v>
       </c>
       <c r="I59" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J59" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K59" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L59" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M59" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N59" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O59" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5428,20 +5426,18 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="10" t="inlineStr">
+      <c r="S59" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U59" s="8" t="n">
+        <v/>
       </c>
       <c r="V59" s="8" t="n">
         <v/>
@@ -5456,50 +5452,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29438.75</v>
+        <v>29938</v>
       </c>
       <c r="C60" t="n">
-        <v>29665.25</v>
+        <v>30862.75</v>
       </c>
       <c r="D60" t="n">
-        <v>29352.75</v>
+        <v>29904</v>
       </c>
       <c r="E60" t="n">
-        <v>29613.68</v>
+        <v>30784.75</v>
       </c>
       <c r="F60" t="n">
-        <v>166.93</v>
+        <v>1171.07</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0395</v>
       </c>
       <c r="H60" t="n">
-        <v>312.5</v>
+        <v>958.75</v>
       </c>
       <c r="I60" t="n">
-        <v>28417.25</v>
+        <v>29040.25</v>
       </c>
       <c r="J60" t="n">
-        <v>29015.62</v>
+        <v>29353.52</v>
       </c>
       <c r="K60" t="n">
-        <v>29176.5</v>
+        <v>29457.43</v>
       </c>
       <c r="L60" t="n">
-        <v>29337.38</v>
+        <v>29561.34</v>
       </c>
       <c r="M60" t="n">
-        <v>29717</v>
+        <v>29769.93</v>
       </c>
       <c r="N60" t="n">
-        <v>30096.62</v>
+        <v>29978.52</v>
       </c>
       <c r="O60" t="n">
-        <v>30038.75</v>
+        <v>29977.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5510,21 +5506,25 @@
       <c r="R60" s="6" t="n">
         <v/>
       </c>
-      <c r="S60" s="10" t="inlineStr">
+      <c r="S60" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U60" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U60" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V60" s="8" t="n">
-        <v/>
+      <c r="V60" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
@@ -5536,50 +5536,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>29938</v>
+        <v>30780</v>
       </c>
       <c r="C61" t="n">
-        <v>30862.75</v>
+        <v>31065.5</v>
       </c>
       <c r="D61" t="n">
-        <v>29904</v>
+        <v>30670</v>
       </c>
       <c r="E61" t="n">
-        <v>30784.75</v>
+        <v>31028.5</v>
       </c>
       <c r="F61" t="n">
-        <v>1171.07</v>
+        <v>243.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>958.75</v>
+        <v>395.5</v>
       </c>
       <c r="I61" t="n">
-        <v>29040.25</v>
+        <v>28945.25</v>
       </c>
       <c r="J61" t="n">
-        <v>29353.52</v>
+        <v>30026.69</v>
       </c>
       <c r="K61" t="n">
-        <v>29457.43</v>
+        <v>30305.38</v>
       </c>
       <c r="L61" t="n">
-        <v>29561.34</v>
+        <v>30584.06</v>
       </c>
       <c r="M61" t="n">
-        <v>29769.93</v>
+        <v>31264.12</v>
       </c>
       <c r="N61" t="n">
-        <v>29978.52</v>
+        <v>31944.19</v>
       </c>
       <c r="O61" t="n">
-        <v>29977.75</v>
+        <v>31821.5</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5590,25 +5590,21 @@
       <c r="R61" s="6" t="n">
         <v/>
       </c>
-      <c r="S61" s="10" t="inlineStr">
+      <c r="S61" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T61" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U61" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V61" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U61" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V61" s="8" t="n">
+        <v/>
       </c>
       <c r="W61" s="9" t="inlineStr">
         <is>
@@ -5620,50 +5616,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>30780</v>
       </c>
       <c r="C62" t="n">
-        <v>31065.5</v>
+        <v>30807</v>
       </c>
       <c r="D62" t="n">
-        <v>30670</v>
+        <v>30778</v>
       </c>
       <c r="E62" t="n">
-        <v>31028.5</v>
+        <v>30792</v>
       </c>
       <c r="F62" t="n">
-        <v>243.75</v>
+        <v>-236.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.0076</v>
       </c>
       <c r="H62" t="n">
-        <v>395.5</v>
+        <v>29</v>
       </c>
       <c r="I62" t="n">
-        <v>28945.25</v>
+        <v>30274.5</v>
       </c>
       <c r="J62" t="n">
-        <v>30026.69</v>
+        <v>30713.38</v>
       </c>
       <c r="K62" t="n">
-        <v>30305.38</v>
+        <v>30830.75</v>
       </c>
       <c r="L62" t="n">
-        <v>30584.06</v>
+        <v>30948.12</v>
       </c>
       <c r="M62" t="n">
-        <v>31264.12</v>
+        <v>31226.25</v>
       </c>
       <c r="N62" t="n">
-        <v>31944.19</v>
+        <v>31504.38</v>
       </c>
       <c r="O62" t="n">
-        <v>31821.5</v>
+        <v>31461</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5671,18 +5667,18 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="n">
-        <v/>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5695,87 +5691,9 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>31008.5</v>
-      </c>
-      <c r="C63" t="n">
-        <v>31094.75</v>
-      </c>
-      <c r="D63" t="n">
-        <v>30910.75</v>
-      </c>
-      <c r="E63" t="n">
-        <v>30956.75</v>
-      </c>
-      <c r="F63" t="n">
-        <v>-71.75</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>-0.0023</v>
-      </c>
-      <c r="H63" t="n">
-        <v>184</v>
-      </c>
-      <c r="I63" t="n">
-        <v>30274.5</v>
-      </c>
-      <c r="J63" t="n">
-        <v>30713.38</v>
-      </c>
-      <c r="K63" t="n">
-        <v>30830.75</v>
-      </c>
-      <c r="L63" t="n">
-        <v>30948.12</v>
-      </c>
-      <c r="M63" t="n">
-        <v>31226.25</v>
-      </c>
-      <c r="N63" t="n">
-        <v>31504.38</v>
-      </c>
-      <c r="O63" t="n">
-        <v>31461</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-29</t>
+          <t>2026-06-30</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29282.5</v>
+        <v>30007.25</v>
       </c>
       <c r="C2" t="n">
-        <v>30069.5</v>
+        <v>30599.75</v>
       </c>
       <c r="D2" t="n">
-        <v>29273.75</v>
+        <v>29934.75</v>
       </c>
       <c r="E2" t="n">
-        <v>30052.75</v>
+        <v>30523.5</v>
       </c>
       <c r="F2" t="n">
-        <v>684.5</v>
+        <v>470.75</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0233</v>
+        <v>0.0157</v>
       </c>
       <c r="H2" t="n">
-        <v>795.75</v>
+        <v>665</v>
       </c>
       <c r="I2" t="n">
-        <v>28428.25</v>
+        <v>28478</v>
       </c>
       <c r="J2" t="n">
-        <v>28556.81</v>
+        <v>29447.56</v>
       </c>
       <c r="K2" t="n">
-        <v>29002.12</v>
+        <v>29654.88</v>
       </c>
       <c r="L2" t="n">
-        <v>29447.44</v>
+        <v>29862.19</v>
       </c>
       <c r="M2" t="n">
-        <v>29734.38</v>
+        <v>30450.62</v>
       </c>
       <c r="N2" t="n">
-        <v>30021.31</v>
+        <v>31039.06</v>
       </c>
       <c r="O2" t="n">
-        <v>30625</v>
+        <v>30865.25</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -695,13 +695,11 @@
       </c>
       <c r="T2" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U2" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U2" s="8" t="n">
+        <v/>
       </c>
       <c r="V2" s="8" t="n">
         <v/>
@@ -716,50 +714,50 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C3" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D3" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E3" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F3" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H3" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I3" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J3" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K3" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L3" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M3" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N3" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O3" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -767,19 +765,19 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
+      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -791,65 +789,73 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C4" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D4" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E4" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F4" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H4" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I4" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J4" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K4" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L4" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M4" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N4" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O4" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R4" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
@@ -873,81 +879,77 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C5" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D5" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E5" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F5" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H5" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I5" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J5" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K5" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L5" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M5" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N5" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O5" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -961,160 +963,156 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C6" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D6" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E6" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F6" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H6" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I6" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J6" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K6" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L6" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M6" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N6" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O6" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
+        <v>30505</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
+      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W6" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C7" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D7" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E7" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F7" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H7" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I7" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J7" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K7" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L7" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M7" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N7" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O7" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q7" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1131,55 +1129,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C8" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D8" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E8" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F8" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H8" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I8" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J8" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K8" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L8" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M8" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N8" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O8" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1187,18 +1189,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1213,57 +1215,57 @@
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C9" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D9" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E9" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F9" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H9" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I9" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J9" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K9" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L9" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M9" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N9" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O9" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1304,70 +1306,74 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C10" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D10" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E10" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F10" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H10" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I10" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J10" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K10" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L10" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M10" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N10" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O10" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
+        <v>30480.5</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
+      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1379,83 +1385,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C11" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D11" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E11" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H11" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I11" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J11" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K11" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L11" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M11" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N11" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O11" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P11" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
-      </c>
       <c r="U11" s="8" t="n">
         <v/>
       </c>
@@ -1467,55 +1465,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C12" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D12" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E12" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F12" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H12" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I12" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J12" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K12" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L12" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M12" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N12" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O12" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1523,18 +1525,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1549,57 +1551,57 @@
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C13" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D13" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E13" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F13" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H13" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I13" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J13" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K13" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L13" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M13" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N13" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O13" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,12 +1611,12 @@
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S13" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1631,59 +1633,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C14" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D14" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E14" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H14" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I14" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J14" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K14" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L14" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M14" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N14" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O14" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1720,50 +1718,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C15" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D15" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E15" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F15" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H15" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I15" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J15" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K15" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L15" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M15" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N15" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O15" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1771,18 +1769,18 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R15" s="6" t="n">
+        <v/>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U15" s="8" t="n">
         <v/>
@@ -1795,55 +1793,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C16" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D16" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E16" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F16" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H16" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I16" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J16" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K16" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L16" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M16" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N16" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O16" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1854,9 +1856,9 @@
       <c r="R16" s="6" t="n">
         <v/>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T16" s="8" t="inlineStr">
@@ -1864,70 +1866,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W16" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C17" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D17" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E17" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F17" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H17" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I17" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J17" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K17" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L17" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M17" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N17" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O17" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1935,23 +1939,21 @@
       <c r="Q17" s="6" t="n">
         <v/>
       </c>
-      <c r="R17" s="6" t="n">
-        <v/>
+      <c r="R17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1963,72 +1965,76 @@
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C18" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D18" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E18" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F18" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H18" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I18" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J18" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K18" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L18" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M18" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N18" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O18" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P18" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T18" s="8" t="n">
@@ -2040,78 +2046,70 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W18" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C19" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D19" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E19" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F19" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H19" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I19" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J19" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K19" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L19" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M19" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N19" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O19" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P19" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S19" s="10" t="inlineStr">
@@ -2138,50 +2136,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C20" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D20" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E20" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F20" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H20" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I20" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J20" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K20" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L20" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M20" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N20" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O20" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2199,11 +2197,15 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2213,55 +2215,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr"/>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C21" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D21" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E21" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F21" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H21" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I21" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J21" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K21" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L21" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M21" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N21" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O21" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,15 +2285,11 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2297,69 +2299,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C22" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D22" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E22" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F22" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H22" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I22" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J22" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K22" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L22" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M22" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N22" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O22" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="n">
-        <v/>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R22" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S22" s="10" t="inlineStr">
@@ -2386,81 +2386,81 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C23" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D23" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E23" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H23" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I23" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J23" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K23" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L23" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M23" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N23" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O23" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
       </c>
-      <c r="Q23" s="6" t="inlineStr">
+      <c r="Q23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W23" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr"/>
@@ -2468,50 +2468,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C24" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D24" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E24" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F24" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H24" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I24" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J24" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K24" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L24" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M24" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N24" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O24" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2524,18 +2524,14 @@
       </c>
       <c r="S24" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2550,50 +2546,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C25" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D25" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E25" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F25" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H25" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I25" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J25" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K25" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L25" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M25" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N25" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O25" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2606,14 +2602,18 @@
       </c>
       <c r="S25" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
@@ -2628,50 +2628,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C26" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D26" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E26" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F26" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H26" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I26" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J26" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K26" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L26" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M26" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N26" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O26" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2697,8 +2697,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V26" s="8" t="n">
-        <v/>
+      <c r="V26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
@@ -2710,50 +2712,50 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C27" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D27" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E27" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F27" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H27" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I27" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J27" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K27" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L27" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M27" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N27" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O27" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2764,80 +2766,78 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V27" s="8" t="n">
+        <v/>
       </c>
       <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C28" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D28" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E28" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F28" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H28" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I28" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J28" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K28" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L28" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M28" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N28" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O28" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2845,12 +2845,14 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S28" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T28" s="8" t="n">
@@ -2869,57 +2871,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C29" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D29" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E29" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F29" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H29" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I29" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J29" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K29" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L29" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M29" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N29" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O29" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2927,22 +2929,24 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2951,59 +2955,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C30" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D30" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E30" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F30" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H30" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I30" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J30" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K30" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L30" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M30" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N30" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O30" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3014,20 +3014,16 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
@@ -3037,55 +3033,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C31" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D31" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E31" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F31" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H31" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I31" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J31" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K31" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L31" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M31" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N31" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O31" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3093,16 +3093,20 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S31" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3117,57 +3121,57 @@
       </c>
       <c r="X31" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C32" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D32" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E32" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F32" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H32" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I32" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J32" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K32" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L32" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M32" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N32" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O32" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3175,24 +3179,24 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="inlineStr">
+      <c r="R32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+      <c r="U32" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U32" s="8" t="n">
-        <v/>
-      </c>
       <c r="V32" s="8" t="n">
         <v/>
       </c>
@@ -3201,59 +3205,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C33" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D33" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E33" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F33" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H33" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I33" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J33" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K33" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L33" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M33" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N33" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O33" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="T33" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U33" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V33" s="8" t="n">
@@ -3292,50 +3292,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C34" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D34" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E34" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F34" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H34" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I34" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J34" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K34" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L34" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M34" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N34" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O34" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3348,18 +3348,14 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U34" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U34" s="8" t="n">
+        <v/>
       </c>
       <c r="V34" s="8" t="n">
         <v/>
@@ -3369,55 +3365,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C35" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D35" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E35" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F35" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G35" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H35" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I35" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J35" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K35" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L35" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M35" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N35" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O35" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3428,13 +3428,15 @@
       <c r="R35" s="6" t="n">
         <v/>
       </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U35" s="8" t="n">
         <v/>
@@ -3456,69 +3458,73 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C36" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D36" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E36" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F36" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H36" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I36" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J36" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K36" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L36" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M36" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N36" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O36" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+        <v>30631.5</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3526,83 +3532,73 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W36" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C37" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D37" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E37" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F37" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H37" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I37" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J37" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K37" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L37" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M37" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N37" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O37" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30728.5</v>
+      </c>
+      <c r="P37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3624,50 +3620,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C38" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D38" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E38" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F38" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H38" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I38" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J38" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K38" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L38" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M38" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N38" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O38" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3675,12 +3671,14 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="n">
-        <v/>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3702,50 +3700,50 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C39" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D39" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E39" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F39" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H39" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I39" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J39" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K39" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L39" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M39" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N39" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O39" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3753,14 +3751,12 @@
       <c r="Q39" s="6" t="n">
         <v/>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3777,68 +3773,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C40" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D40" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E40" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F40" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I40" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J40" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K40" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L40" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M40" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N40" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O40" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S40" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3855,81 +3859,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C41" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D41" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E41" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F41" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H41" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I41" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J41" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K41" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L41" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M41" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N41" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O41" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
+      <c r="Q41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R41" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R41" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
       <c r="U41" s="8" t="n">
         <v/>
       </c>
@@ -3941,55 +3939,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C42" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D42" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E42" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F42" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H42" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I42" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J42" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K42" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L42" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M42" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N42" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O42" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4002,13 +4004,11 @@
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
       </c>
       <c r="U42" s="8" t="n">
         <v/>
@@ -4023,57 +4023,57 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C43" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D43" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E43" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F43" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H43" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I43" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J43" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K43" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L43" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M43" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N43" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O43" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4086,100 +4086,100 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X43" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W43" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C44" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D44" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E44" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F44" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H44" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I44" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J44" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K44" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L44" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M44" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N44" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O44" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
       </c>
       <c r="V44" s="8" t="n">
         <v/>
@@ -4189,63 +4189,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X44" t="inlineStr"/>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C45" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D45" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E45" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F45" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H45" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I45" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J45" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K45" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L45" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M45" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N45" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O45" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
       </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q45" s="6" t="n">
+        <v/>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
@@ -4254,7 +4256,7 @@
       </c>
       <c r="S45" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4273,63 +4275,67 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C46" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D46" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E46" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F46" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H46" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I46" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J46" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K46" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L46" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M46" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N46" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O46" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P46" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q46" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
@@ -4338,7 +4344,7 @@
       </c>
       <c r="S46" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4350,83 +4356,77 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W46" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C47" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D47" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E47" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F47" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H47" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I47" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J47" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K47" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L47" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M47" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N47" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O47" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P47" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R47" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30140.5</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q47" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R47" s="6" t="n">
+        <v/>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T47" s="8" t="n">
@@ -4452,50 +4452,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C48" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D48" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E48" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F48" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H48" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I48" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J48" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K48" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L48" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M48" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N48" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O48" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4506,19 +4506,25 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U48" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V48" s="8" t="n">
-        <v/>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U48" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
@@ -4527,57 +4533,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C49" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D49" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E49" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F49" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H49" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I49" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J49" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K49" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L49" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M49" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N49" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O49" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4590,23 +4596,17 @@
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U49" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U49" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V49" s="8" t="n">
+        <v/>
       </c>
       <c r="W49" s="11" t="inlineStr">
         <is>
@@ -4622,50 +4622,50 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C50" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D50" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E50" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F50" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H50" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I50" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J50" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K50" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L50" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M50" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N50" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O50" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4673,16 +4673,20 @@
       <c r="Q50" s="6" t="n">
         <v/>
       </c>
-      <c r="R50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S50" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4697,57 +4701,57 @@
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C51" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D51" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E51" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F51" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H51" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I51" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J51" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K51" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L51" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M51" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N51" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O51" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4757,18 +4761,16 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4781,69 +4783,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C52" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D52" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E52" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F52" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H52" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I52" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J52" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K52" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L52" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M52" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N52" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O52" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S52" s="10" t="inlineStr">
@@ -4870,72 +4870,70 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C53" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D53" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E53" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F53" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H53" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I53" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J53" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K53" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L53" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M53" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N53" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O53" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
+      <c r="Q53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
       <c r="U53" s="8" t="n">
         <v/>
       </c>
@@ -4947,75 +4945,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C54" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D54" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E54" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F54" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H54" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I54" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J54" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K54" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L54" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M54" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N54" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O54" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R54" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S54" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="n">
+        <v/>
+      </c>
       <c r="U54" s="8" t="n">
         <v/>
       </c>
@@ -5027,67 +5031,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C55" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D55" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E55" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F55" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H55" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I55" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J55" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K55" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L55" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M55" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N55" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O55" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
       </c>
-      <c r="Q55" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q55" s="6" t="n">
+        <v/>
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
@@ -5113,55 +5111,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X55" t="inlineStr"/>
+      <c r="X55" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C56" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D56" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E56" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F56" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H56" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I56" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J56" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K56" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L56" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M56" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N56" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O56" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5171,19 +5173,23 @@
       </c>
       <c r="R56" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S56" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U56" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5195,57 +5201,57 @@
       </c>
       <c r="X56" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C57" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D57" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E57" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F57" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H57" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I57" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J57" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K57" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L57" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M57" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N57" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O57" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5253,87 +5259,81 @@
       <c r="Q57" s="6" t="n">
         <v/>
       </c>
-      <c r="R57" s="6" t="inlineStr">
+      <c r="R57" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S57" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S57" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X57" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W57" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>28967.5</v>
+        <v>29438.75</v>
       </c>
       <c r="C58" t="n">
-        <v>29498.25</v>
+        <v>29665.25</v>
       </c>
       <c r="D58" t="n">
-        <v>28957.75</v>
+        <v>29352.75</v>
       </c>
       <c r="E58" t="n">
-        <v>29446.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F58" t="n">
-        <v>483.25</v>
+        <v>166.93</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0057</v>
       </c>
       <c r="H58" t="n">
-        <v>540.5</v>
+        <v>312.5</v>
       </c>
       <c r="I58" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J58" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K58" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L58" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M58" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N58" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O58" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5351,13 +5351,11 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U58" s="8" t="n">
+        <v/>
       </c>
       <c r="V58" s="8" t="n">
         <v/>
@@ -5372,50 +5370,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29438.75</v>
+        <v>29938</v>
       </c>
       <c r="C59" t="n">
-        <v>29665.25</v>
+        <v>30862.75</v>
       </c>
       <c r="D59" t="n">
-        <v>29352.75</v>
+        <v>29904</v>
       </c>
       <c r="E59" t="n">
-        <v>29613.68</v>
+        <v>30784.75</v>
       </c>
       <c r="F59" t="n">
-        <v>166.93</v>
+        <v>1171.07</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0395</v>
       </c>
       <c r="H59" t="n">
-        <v>312.5</v>
+        <v>958.75</v>
       </c>
       <c r="I59" t="n">
-        <v>28417.25</v>
+        <v>29040.25</v>
       </c>
       <c r="J59" t="n">
-        <v>29015.62</v>
+        <v>29353.52</v>
       </c>
       <c r="K59" t="n">
-        <v>29176.5</v>
+        <v>29457.43</v>
       </c>
       <c r="L59" t="n">
-        <v>29337.38</v>
+        <v>29561.34</v>
       </c>
       <c r="M59" t="n">
-        <v>29717</v>
+        <v>29769.93</v>
       </c>
       <c r="N59" t="n">
-        <v>30096.62</v>
+        <v>29978.52</v>
       </c>
       <c r="O59" t="n">
-        <v>30038.75</v>
+        <v>29977.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5433,14 +5431,18 @@
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U59" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U59" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V59" s="8" t="n">
-        <v/>
+      <c r="V59" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
@@ -5452,50 +5454,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>29938</v>
+        <v>30780</v>
       </c>
       <c r="C60" t="n">
-        <v>30862.75</v>
+        <v>31065.5</v>
       </c>
       <c r="D60" t="n">
-        <v>29904</v>
+        <v>30670</v>
       </c>
       <c r="E60" t="n">
-        <v>30784.75</v>
+        <v>31028.5</v>
       </c>
       <c r="F60" t="n">
-        <v>1171.07</v>
+        <v>243.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>958.75</v>
+        <v>395.5</v>
       </c>
       <c r="I60" t="n">
-        <v>29040.25</v>
+        <v>28945.25</v>
       </c>
       <c r="J60" t="n">
-        <v>29353.52</v>
+        <v>30026.69</v>
       </c>
       <c r="K60" t="n">
-        <v>29457.43</v>
+        <v>30305.38</v>
       </c>
       <c r="L60" t="n">
-        <v>29561.34</v>
+        <v>30584.06</v>
       </c>
       <c r="M60" t="n">
-        <v>29769.93</v>
+        <v>31264.12</v>
       </c>
       <c r="N60" t="n">
-        <v>29978.52</v>
+        <v>31944.19</v>
       </c>
       <c r="O60" t="n">
-        <v>29977.75</v>
+        <v>31821.5</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5513,18 +5515,14 @@
       </c>
       <c r="T60" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U60" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V60" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U60" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V60" s="8" t="n">
+        <v/>
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
@@ -5536,70 +5534,72 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>30780</v>
+        <v>31008.5</v>
       </c>
       <c r="C61" t="n">
-        <v>31065.5</v>
+        <v>31094.75</v>
       </c>
       <c r="D61" t="n">
-        <v>30670</v>
+        <v>30642.75</v>
       </c>
       <c r="E61" t="n">
-        <v>31028.5</v>
+        <v>30764.75</v>
       </c>
       <c r="F61" t="n">
-        <v>243.75</v>
+        <v>-263.75</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H61" t="n">
-        <v>395.5</v>
+        <v>452</v>
       </c>
       <c r="I61" t="n">
-        <v>28945.25</v>
+        <v>30274.5</v>
       </c>
       <c r="J61" t="n">
-        <v>30026.69</v>
+        <v>30713.38</v>
       </c>
       <c r="K61" t="n">
-        <v>30305.38</v>
+        <v>30830.75</v>
       </c>
       <c r="L61" t="n">
-        <v>30584.06</v>
+        <v>30948.12</v>
       </c>
       <c r="M61" t="n">
-        <v>31264.12</v>
+        <v>31226.25</v>
       </c>
       <c r="N61" t="n">
-        <v>31944.19</v>
+        <v>31504.38</v>
       </c>
       <c r="O61" t="n">
-        <v>31821.5</v>
+        <v>31461</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
+      <c r="Q61" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
+      </c>
       <c r="U61" s="8" t="n">
         <v/>
       </c>
@@ -5611,55 +5611,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30780</v>
+        <v>30726.5</v>
       </c>
       <c r="C62" t="n">
-        <v>30807</v>
+        <v>30765.25</v>
       </c>
       <c r="D62" t="n">
-        <v>30778</v>
+        <v>30715.75</v>
       </c>
       <c r="E62" t="n">
-        <v>30792</v>
+        <v>30730.25</v>
       </c>
       <c r="F62" t="n">
-        <v>-236.5</v>
+        <v>-34.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0076</v>
+        <v>-0.0011</v>
       </c>
       <c r="H62" t="n">
-        <v>29</v>
+        <v>49.5</v>
       </c>
       <c r="I62" t="n">
-        <v>30274.5</v>
+        <v>30190.75</v>
       </c>
       <c r="J62" t="n">
-        <v>30713.38</v>
+        <v>30260.75</v>
       </c>
       <c r="K62" t="n">
-        <v>30830.75</v>
+        <v>30538.75</v>
       </c>
       <c r="L62" t="n">
-        <v>30948.12</v>
+        <v>30816.75</v>
       </c>
       <c r="M62" t="n">
-        <v>31226.25</v>
+        <v>30990.75</v>
       </c>
       <c r="N62" t="n">
-        <v>31504.38</v>
+        <v>31164.75</v>
       </c>
       <c r="O62" t="n">
-        <v>31461</v>
+        <v>31546.75</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5667,14 +5671,12 @@
       <c r="Q62" s="6" t="n">
         <v/>
       </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-06-30</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30007.25</v>
+        <v>30505.75</v>
       </c>
       <c r="C2" t="n">
-        <v>30599.75</v>
+        <v>30553.75</v>
       </c>
       <c r="D2" t="n">
-        <v>29934.75</v>
+        <v>30008.5</v>
       </c>
       <c r="E2" t="n">
-        <v>30523.5</v>
+        <v>30094.25</v>
       </c>
       <c r="F2" t="n">
-        <v>470.75</v>
+        <v>-429.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0157</v>
+        <v>-0.0141</v>
       </c>
       <c r="H2" t="n">
-        <v>665</v>
+        <v>545.25</v>
       </c>
       <c r="I2" t="n">
-        <v>28478</v>
+        <v>29269.75</v>
       </c>
       <c r="J2" t="n">
-        <v>29447.56</v>
+        <v>29986.62</v>
       </c>
       <c r="K2" t="n">
-        <v>29654.88</v>
+        <v>30191</v>
       </c>
       <c r="L2" t="n">
-        <v>29862.19</v>
+        <v>30395.38</v>
       </c>
       <c r="M2" t="n">
-        <v>30450.62</v>
+        <v>30856</v>
       </c>
       <c r="N2" t="n">
-        <v>31039.06</v>
+        <v>31316.62</v>
       </c>
       <c r="O2" t="n">
-        <v>30865.25</v>
+        <v>31264.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,68 +709,76 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C3" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D3" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E3" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F3" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H3" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I3" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J3" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K3" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L3" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M3" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N3" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O3" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R3" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -791,81 +799,77 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C4" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D4" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E4" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F4" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H4" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I4" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J4" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K4" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L4" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M4" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N4" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O4" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
-      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
@@ -879,76 +883,80 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C5" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D5" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E5" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F5" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H5" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I5" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J5" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K5" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L5" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M5" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N5" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O5" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
+        <v>30505</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -956,83 +964,75 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W5" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C6" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D6" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E6" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F6" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H6" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I6" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J6" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K6" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L6" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M6" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N6" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O6" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q6" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S6" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T6" s="8" t="n">
@@ -1049,55 +1049,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C7" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D7" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E7" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F7" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H7" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I7" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J7" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K7" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L7" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M7" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N7" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O7" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,18 +1109,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R7" s="6" t="n">
+        <v/>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1131,57 +1135,57 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C8" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D8" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E8" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F8" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H8" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I8" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J8" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K8" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L8" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M8" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N8" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O8" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1192,7 +1196,7 @@
       <c r="R8" s="6" t="n">
         <v/>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1222,69 +1226,73 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C9" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D9" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E9" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F9" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H9" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I9" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J9" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K9" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L9" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M9" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N9" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O9" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q9" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+        <v>30480.5</v>
+      </c>
+      <c r="P9" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1297,83 +1305,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C10" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D10" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E10" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H10" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I10" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J10" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K10" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L10" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M10" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N10" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O10" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P10" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R10" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
-      </c>
       <c r="U10" s="8" t="n">
         <v/>
       </c>
@@ -1385,55 +1385,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C11" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D11" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E11" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F11" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H11" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I11" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J11" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K11" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L11" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M11" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N11" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O11" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1441,18 +1445,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
+      <c r="R11" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1467,57 +1471,57 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C12" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D12" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E12" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H12" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I12" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J12" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K12" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L12" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M12" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N12" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O12" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1527,12 +1531,12 @@
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S12" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S12" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1549,59 +1553,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C13" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D13" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E13" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H13" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I13" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J13" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K13" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L13" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M13" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N13" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O13" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1614,7 +1614,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
+      <c r="S13" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1638,50 +1638,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C14" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D14" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E14" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F14" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H14" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I14" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J14" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K14" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L14" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M14" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N14" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O14" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,18 +1689,18 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="n">
-        <v/>
+      <c r="R14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U14" s="8" t="n">
         <v/>
@@ -1713,55 +1713,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C15" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D15" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E15" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F15" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H15" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I15" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J15" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K15" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L15" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M15" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N15" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O15" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1774,7 +1778,7 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T15" s="8" t="inlineStr">
@@ -1782,70 +1786,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W15" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C16" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D16" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E16" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F16" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H16" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I16" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J16" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K16" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L16" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M16" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N16" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O16" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1853,23 +1859,21 @@
       <c r="Q16" s="6" t="n">
         <v/>
       </c>
-      <c r="R16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T16" s="8" t="inlineStr">
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
@@ -1881,63 +1885,67 @@
       </c>
       <c r="X16" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C17" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D17" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E17" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F17" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H17" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I17" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J17" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K17" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L17" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M17" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N17" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O17" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P17" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
@@ -1946,7 +1954,7 @@
       </c>
       <c r="S17" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T17" s="8" t="n">
@@ -1958,81 +1966,73 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W17" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C18" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D18" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E18" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F18" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H18" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I18" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J18" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K18" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L18" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M18" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N18" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O18" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P18" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2056,50 +2056,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C19" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D19" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E19" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F19" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H19" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I19" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J19" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K19" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L19" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M19" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N19" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O19" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2112,16 +2112,20 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S19" s="10" t="inlineStr">
+      <c r="S19" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2131,55 +2135,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr"/>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C20" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D20" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E20" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F20" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H20" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I20" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J20" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K20" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L20" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M20" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N20" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O20" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2192,20 +2200,16 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
@@ -2215,72 +2219,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C21" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D21" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E21" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F21" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H21" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I21" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J21" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K21" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L21" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M21" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N21" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O21" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="n">
-        <v/>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R21" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S21" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2304,81 +2306,81 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C22" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D22" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E22" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F22" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H22" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I22" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J22" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K22" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L22" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M22" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N22" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O22" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
       </c>
-      <c r="Q22" s="6" t="inlineStr">
+      <c r="Q22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R22" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
-      </c>
       <c r="V22" s="8" t="n">
         <v/>
       </c>
-      <c r="W22" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W22" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X22" t="inlineStr"/>
@@ -2386,50 +2388,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C23" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D23" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E23" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F23" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H23" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I23" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J23" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K23" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L23" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M23" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N23" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O23" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2440,20 +2442,16 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2468,50 +2466,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C24" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D24" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E24" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F24" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H24" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I24" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J24" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K24" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L24" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M24" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N24" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O24" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2522,16 +2520,20 @@
       <c r="R24" s="6" t="n">
         <v/>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2546,50 +2548,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C25" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D25" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E25" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F25" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H25" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I25" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J25" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K25" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L25" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M25" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N25" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O25" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2600,7 +2602,7 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="7" t="inlineStr">
+      <c r="S25" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2615,8 +2617,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V25" s="8" t="n">
-        <v/>
+      <c r="V25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
@@ -2628,50 +2632,50 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C26" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D26" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E26" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F26" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H26" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I26" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J26" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K26" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L26" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M26" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N26" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O26" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2684,78 +2688,76 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V26" s="8" t="n">
+        <v/>
       </c>
       <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C27" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D27" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E27" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F27" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H27" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I27" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J27" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K27" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L27" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M27" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N27" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O27" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2763,12 +2765,14 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T27" s="8" t="n">
@@ -2787,57 +2791,57 @@
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C28" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D28" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E28" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F28" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H28" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I28" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J28" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K28" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L28" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M28" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N28" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O28" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2845,22 +2849,24 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
@@ -2869,59 +2875,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C29" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D29" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E29" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F29" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H29" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I29" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J29" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K29" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L29" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M29" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N29" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O29" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2934,18 +2936,14 @@
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
@@ -2955,55 +2953,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C30" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D30" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E30" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F30" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H30" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I30" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J30" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K30" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L30" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M30" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N30" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O30" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3011,16 +3013,20 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3035,57 +3041,57 @@
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C31" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D31" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E31" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F31" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H31" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I31" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J31" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K31" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L31" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M31" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N31" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O31" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3093,24 +3099,24 @@
       <c r="Q31" s="6" t="n">
         <v/>
       </c>
-      <c r="R31" s="6" t="inlineStr">
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
+      <c r="U31" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U31" s="8" t="n">
-        <v/>
-      </c>
       <c r="V31" s="8" t="n">
         <v/>
       </c>
@@ -3119,59 +3125,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C32" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D32" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E32" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F32" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H32" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I32" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J32" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K32" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L32" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M32" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N32" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O32" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3182,19 +3184,19 @@
       <c r="R32" s="6" t="n">
         <v/>
       </c>
-      <c r="S32" s="7" t="inlineStr">
+      <c r="S32" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T32" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U32" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V32" s="8" t="n">
@@ -3210,50 +3212,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C33" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D33" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E33" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F33" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H33" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I33" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J33" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K33" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L33" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M33" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N33" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O33" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3264,20 +3266,16 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U33" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U33" s="8" t="n">
+        <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
@@ -3287,55 +3285,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C34" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D34" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E34" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F34" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G34" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H34" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I34" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J34" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K34" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L34" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M34" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N34" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O34" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3348,11 +3350,13 @@
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3374,153 +3378,147 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C35" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D35" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E35" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F35" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H35" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I35" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J35" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K35" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L35" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M35" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N35" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O35" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="inlineStr">
+        <v>30631.5</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="n">
+        <v/>
+      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W35" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C36" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D36" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E36" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F36" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H36" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I36" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J36" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K36" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L36" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M36" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N36" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O36" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30728.5</v>
+      </c>
+      <c r="P36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3542,50 +3540,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C37" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D37" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E37" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F37" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H37" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I37" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J37" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K37" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L37" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M37" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N37" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O37" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3593,12 +3591,14 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3620,50 +3620,50 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C38" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D38" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E38" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F38" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H38" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I38" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J38" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K38" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L38" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M38" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N38" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O38" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3671,14 +3671,12 @@
       <c r="Q38" s="6" t="n">
         <v/>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R38" s="6" t="n">
+        <v/>
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3695,68 +3693,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C39" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D39" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E39" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F39" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I39" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J39" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K39" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L39" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M39" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N39" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O39" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S39" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T39" s="8" t="n">
@@ -3773,81 +3779,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C40" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D40" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E40" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F40" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H40" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I40" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J40" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K40" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L40" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M40" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N40" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O40" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
+      <c r="Q40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R40" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S40" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R40" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
       <c r="U40" s="8" t="n">
         <v/>
       </c>
@@ -3859,55 +3859,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C41" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D41" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E41" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F41" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H41" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I41" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J41" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K41" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L41" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M41" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N41" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O41" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3918,15 +3922,13 @@
       <c r="R41" s="6" t="n">
         <v/>
       </c>
-      <c r="S41" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S41" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
       </c>
       <c r="U41" s="8" t="n">
         <v/>
@@ -3941,57 +3943,57 @@
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C42" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D42" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E42" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F42" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H42" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I42" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J42" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K42" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L42" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M42" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N42" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O42" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
@@ -4002,102 +4004,102 @@
       <c r="R42" s="6" t="n">
         <v/>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U42" s="8" t="n">
-        <v/>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U42" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X42" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W42" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C43" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D43" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E43" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F43" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H43" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I43" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J43" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K43" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L43" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M43" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N43" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O43" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R43" s="6" t="n">
-        <v/>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U43" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U43" s="8" t="n">
+        <v/>
       </c>
       <c r="V43" s="8" t="n">
         <v/>
@@ -4107,72 +4109,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X43" t="inlineStr"/>
+      <c r="X43" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C44" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D44" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E44" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F44" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H44" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I44" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J44" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K44" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L44" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M44" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N44" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O44" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
       </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q44" s="6" t="n">
+        <v/>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S44" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S44" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4191,72 +4195,76 @@
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C45" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D45" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E45" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F45" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H45" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I45" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J45" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K45" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L45" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M45" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N45" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O45" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q45" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R45" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4268,83 +4276,77 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W45" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C46" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D46" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E46" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F46" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H46" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I46" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J46" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K46" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L46" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M46" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N46" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O46" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P46" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R46" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30140.5</v>
+      </c>
+      <c r="P46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R46" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T46" s="8" t="n">
@@ -4370,50 +4372,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C47" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D47" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E47" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F47" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H47" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I47" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J47" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K47" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L47" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M47" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N47" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O47" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4426,17 +4428,23 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U47" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V47" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U47" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
@@ -4445,57 +4453,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C48" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D48" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E48" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F48" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H48" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I48" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J48" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K48" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L48" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M48" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N48" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O48" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4506,25 +4514,19 @@
       <c r="R48" s="6" t="n">
         <v/>
       </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U48" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U48" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V48" s="8" t="n">
+        <v/>
       </c>
       <c r="W48" s="11" t="inlineStr">
         <is>
@@ -4540,50 +4542,50 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C49" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D49" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E49" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F49" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H49" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I49" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J49" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K49" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L49" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M49" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N49" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O49" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4591,16 +4593,20 @@
       <c r="Q49" s="6" t="n">
         <v/>
       </c>
-      <c r="R49" s="6" t="n">
-        <v/>
+      <c r="R49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4615,57 +4621,57 @@
       </c>
       <c r="X49" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C50" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D50" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E50" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F50" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H50" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I50" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J50" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K50" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L50" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M50" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N50" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O50" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
@@ -4675,18 +4681,16 @@
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4699,72 +4703,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C51" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D51" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E51" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F51" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H51" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I51" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J51" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K51" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L51" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M51" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N51" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O51" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S51" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4788,72 +4790,70 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C52" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D52" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E52" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F52" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H52" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I52" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J52" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K52" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L52" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M52" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N52" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O52" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
+      <c r="Q52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4865,74 +4865,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C53" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D53" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E53" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F53" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H53" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I53" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J53" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K53" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L53" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M53" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N53" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O53" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R53" s="6" t="n">
-        <v/>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R53" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S53" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="n">
+        <v/>
       </c>
       <c r="U53" s="8" t="n">
         <v/>
@@ -4945,74 +4951,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C54" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D54" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E54" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F54" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H54" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I54" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J54" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K54" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L54" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M54" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N54" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O54" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
       </c>
-      <c r="Q54" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q54" s="6" t="n">
+        <v/>
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S54" s="10" t="inlineStr">
+      <c r="S54" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -5031,55 +5031,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X54" t="inlineStr"/>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C55" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D55" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E55" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F55" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H55" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I55" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J55" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K55" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L55" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M55" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N55" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O55" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5089,19 +5093,23 @@
       </c>
       <c r="R55" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S55" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U55" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S55" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5113,57 +5121,57 @@
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C56" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D56" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E56" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F56" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H56" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I56" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J56" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K56" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L56" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M56" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N56" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O56" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5171,87 +5179,81 @@
       <c r="Q56" s="6" t="n">
         <v/>
       </c>
-      <c r="R56" s="6" t="inlineStr">
+      <c r="R56" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S56" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X56" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W56" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>28967.5</v>
+        <v>29438.75</v>
       </c>
       <c r="C57" t="n">
-        <v>29498.25</v>
+        <v>29665.25</v>
       </c>
       <c r="D57" t="n">
-        <v>28957.75</v>
+        <v>29352.75</v>
       </c>
       <c r="E57" t="n">
-        <v>29446.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F57" t="n">
-        <v>483.25</v>
+        <v>166.93</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0057</v>
       </c>
       <c r="H57" t="n">
-        <v>540.5</v>
+        <v>312.5</v>
       </c>
       <c r="I57" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J57" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K57" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L57" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M57" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N57" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O57" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5262,20 +5264,18 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="7" t="inlineStr">
+      <c r="S57" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U57" s="8" t="n">
+        <v/>
       </c>
       <c r="V57" s="8" t="n">
         <v/>
@@ -5290,50 +5290,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29438.75</v>
+        <v>29938</v>
       </c>
       <c r="C58" t="n">
-        <v>29665.25</v>
+        <v>30862.75</v>
       </c>
       <c r="D58" t="n">
-        <v>29352.75</v>
+        <v>29904</v>
       </c>
       <c r="E58" t="n">
-        <v>29613.68</v>
+        <v>30784.75</v>
       </c>
       <c r="F58" t="n">
-        <v>166.93</v>
+        <v>1171.07</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0395</v>
       </c>
       <c r="H58" t="n">
-        <v>312.5</v>
+        <v>958.75</v>
       </c>
       <c r="I58" t="n">
-        <v>28417.25</v>
+        <v>29040.25</v>
       </c>
       <c r="J58" t="n">
-        <v>29015.62</v>
+        <v>29353.52</v>
       </c>
       <c r="K58" t="n">
-        <v>29176.5</v>
+        <v>29457.43</v>
       </c>
       <c r="L58" t="n">
-        <v>29337.38</v>
+        <v>29561.34</v>
       </c>
       <c r="M58" t="n">
-        <v>29717</v>
+        <v>29769.93</v>
       </c>
       <c r="N58" t="n">
-        <v>30096.62</v>
+        <v>29978.52</v>
       </c>
       <c r="O58" t="n">
-        <v>30038.75</v>
+        <v>29977.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5344,21 +5344,25 @@
       <c r="R58" s="6" t="n">
         <v/>
       </c>
-      <c r="S58" s="7" t="inlineStr">
+      <c r="S58" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U58" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U58" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V58" s="8" t="n">
-        <v/>
+      <c r="V58" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5370,50 +5374,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>29938</v>
+        <v>30780</v>
       </c>
       <c r="C59" t="n">
-        <v>30862.75</v>
+        <v>31065.5</v>
       </c>
       <c r="D59" t="n">
-        <v>29904</v>
+        <v>30670</v>
       </c>
       <c r="E59" t="n">
-        <v>30784.75</v>
+        <v>31028.5</v>
       </c>
       <c r="F59" t="n">
-        <v>1171.07</v>
+        <v>243.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>958.75</v>
+        <v>395.5</v>
       </c>
       <c r="I59" t="n">
-        <v>29040.25</v>
+        <v>28945.25</v>
       </c>
       <c r="J59" t="n">
-        <v>29353.52</v>
+        <v>30026.69</v>
       </c>
       <c r="K59" t="n">
-        <v>29457.43</v>
+        <v>30305.38</v>
       </c>
       <c r="L59" t="n">
-        <v>29561.34</v>
+        <v>30584.06</v>
       </c>
       <c r="M59" t="n">
-        <v>29769.93</v>
+        <v>31264.12</v>
       </c>
       <c r="N59" t="n">
-        <v>29978.52</v>
+        <v>31944.19</v>
       </c>
       <c r="O59" t="n">
-        <v>29977.75</v>
+        <v>31821.5</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5424,25 +5428,21 @@
       <c r="R59" s="6" t="n">
         <v/>
       </c>
-      <c r="S59" s="7" t="inlineStr">
+      <c r="S59" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T59" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U59" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V59" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U59" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V59" s="8" t="n">
+        <v/>
       </c>
       <c r="W59" s="9" t="inlineStr">
         <is>
@@ -5454,69 +5454,71 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>30780</v>
+        <v>31008.5</v>
       </c>
       <c r="C60" t="n">
-        <v>31065.5</v>
+        <v>31094.75</v>
       </c>
       <c r="D60" t="n">
-        <v>30670</v>
+        <v>30642.75</v>
       </c>
       <c r="E60" t="n">
-        <v>31028.5</v>
+        <v>30764.75</v>
       </c>
       <c r="F60" t="n">
-        <v>243.75</v>
+        <v>-263.75</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H60" t="n">
-        <v>395.5</v>
+        <v>452</v>
       </c>
       <c r="I60" t="n">
-        <v>28945.25</v>
+        <v>30274.5</v>
       </c>
       <c r="J60" t="n">
-        <v>30026.69</v>
+        <v>30713.38</v>
       </c>
       <c r="K60" t="n">
-        <v>30305.38</v>
+        <v>30830.75</v>
       </c>
       <c r="L60" t="n">
-        <v>30584.06</v>
+        <v>30948.12</v>
       </c>
       <c r="M60" t="n">
-        <v>31264.12</v>
+        <v>31226.25</v>
       </c>
       <c r="N60" t="n">
-        <v>31944.19</v>
+        <v>31504.38</v>
       </c>
       <c r="O60" t="n">
-        <v>31821.5</v>
+        <v>31461</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5529,72 +5531,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>31008.5</v>
+        <v>30780</v>
       </c>
       <c r="C61" t="n">
-        <v>31094.75</v>
+        <v>30827.5</v>
       </c>
       <c r="D61" t="n">
-        <v>30642.75</v>
+        <v>30370</v>
       </c>
       <c r="E61" t="n">
-        <v>30764.75</v>
+        <v>30766.75</v>
       </c>
       <c r="F61" t="n">
-        <v>-263.75</v>
+        <v>2</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0001</v>
       </c>
       <c r="H61" t="n">
-        <v>452</v>
+        <v>457.5</v>
       </c>
       <c r="I61" t="n">
-        <v>30274.5</v>
+        <v>30190.75</v>
       </c>
       <c r="J61" t="n">
-        <v>30713.38</v>
+        <v>30260.75</v>
       </c>
       <c r="K61" t="n">
-        <v>30830.75</v>
+        <v>30538.75</v>
       </c>
       <c r="L61" t="n">
-        <v>30948.12</v>
+        <v>30816.75</v>
       </c>
       <c r="M61" t="n">
-        <v>31226.25</v>
+        <v>30990.75</v>
       </c>
       <c r="N61" t="n">
-        <v>31504.38</v>
+        <v>31164.75</v>
       </c>
       <c r="O61" t="n">
-        <v>31461</v>
+        <v>31546.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
       </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q61" s="6" t="n">
+        <v/>
       </c>
       <c r="R61" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S61" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S61" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5620,50 +5624,50 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B62" t="n">
         <v>30726.5</v>
       </c>
       <c r="C62" t="n">
-        <v>30765.25</v>
+        <v>30999.5</v>
       </c>
       <c r="D62" t="n">
-        <v>30715.75</v>
+        <v>30679</v>
       </c>
       <c r="E62" t="n">
-        <v>30730.25</v>
+        <v>30889.25</v>
       </c>
       <c r="F62" t="n">
-        <v>-34.5</v>
+        <v>122.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.0011</v>
+        <v>0.004</v>
       </c>
       <c r="H62" t="n">
-        <v>49.5</v>
+        <v>320.5</v>
       </c>
       <c r="I62" t="n">
-        <v>30190.75</v>
+        <v>29912.5</v>
       </c>
       <c r="J62" t="n">
-        <v>30260.75</v>
+        <v>30393.25</v>
       </c>
       <c r="K62" t="n">
-        <v>30538.75</v>
+        <v>30538</v>
       </c>
       <c r="L62" t="n">
-        <v>30816.75</v>
+        <v>30682.75</v>
       </c>
       <c r="M62" t="n">
-        <v>30990.75</v>
+        <v>30995.5</v>
       </c>
       <c r="N62" t="n">
-        <v>31164.75</v>
+        <v>31308.25</v>
       </c>
       <c r="O62" t="n">
-        <v>31546.75</v>
+        <v>31285</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5676,11 +5680,13 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5693,9 +5699,87 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-09-27</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>30870</v>
+      </c>
+      <c r="C63" t="n">
+        <v>30920.75</v>
+      </c>
+      <c r="D63" t="n">
+        <v>30816.25</v>
+      </c>
+      <c r="E63" t="n">
+        <v>30889.25</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="I63" t="n">
+        <v>30358.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>30593.75</v>
+      </c>
+      <c r="K63" t="n">
+        <v>30729</v>
+      </c>
+      <c r="L63" t="n">
+        <v>30864.25</v>
+      </c>
+      <c r="M63" t="n">
+        <v>31049.5</v>
+      </c>
+      <c r="N63" t="n">
+        <v>31234.75</v>
+      </c>
+      <c r="O63" t="n">
+        <v>31320</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,60 +634,64 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-07-02</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30505.75</v>
+        <v>30089.75</v>
       </c>
       <c r="C2" t="n">
-        <v>30553.75</v>
+        <v>30320</v>
       </c>
       <c r="D2" t="n">
-        <v>30008.5</v>
+        <v>29328.5</v>
       </c>
       <c r="E2" t="n">
-        <v>30094.25</v>
+        <v>29556</v>
       </c>
       <c r="F2" t="n">
-        <v>-429.25</v>
+        <v>-538.25</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0141</v>
+        <v>-0.0179</v>
       </c>
       <c r="H2" t="n">
-        <v>545.25</v>
+        <v>991.5</v>
       </c>
       <c r="I2" t="n">
-        <v>29269.75</v>
+        <v>29463.25</v>
       </c>
       <c r="J2" t="n">
-        <v>29986.62</v>
+        <v>29455.56</v>
       </c>
       <c r="K2" t="n">
-        <v>30191</v>
+        <v>29821.62</v>
       </c>
       <c r="L2" t="n">
-        <v>30395.38</v>
+        <v>30187.69</v>
       </c>
       <c r="M2" t="n">
-        <v>30856</v>
+        <v>30366.88</v>
       </c>
       <c r="N2" t="n">
-        <v>31316.62</v>
+        <v>30546.06</v>
       </c>
       <c r="O2" t="n">
-        <v>31264.75</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
+        <v>31099</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R2" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
@@ -711,81 +715,77 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C3" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D3" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E3" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F3" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H3" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I3" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J3" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K3" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L3" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M3" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N3" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O3" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
-      </c>
       <c r="U3" s="8" t="n">
         <v/>
       </c>
@@ -799,160 +799,156 @@
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C4" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D4" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E4" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F4" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H4" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I4" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J4" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K4" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L4" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M4" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N4" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O4" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S4" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
+        <v>30505</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S4" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
+      </c>
       <c r="U4" s="8" t="n">
         <v/>
       </c>
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C5" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D5" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E5" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F5" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H5" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I5" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J5" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K5" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L5" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M5" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N5" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O5" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q5" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T5" s="8" t="n">
@@ -969,55 +965,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C6" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D6" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E6" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F6" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H6" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I6" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J6" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K6" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L6" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M6" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N6" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O6" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1025,18 +1025,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1051,57 +1051,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C7" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D7" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E7" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F7" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H7" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I7" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J7" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K7" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L7" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M7" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N7" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O7" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1142,70 +1142,74 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C8" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D8" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E8" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F8" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H8" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I8" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J8" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K8" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L8" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M8" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N8" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O8" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R8" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S8" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
+        <v>30480.5</v>
+      </c>
+      <c r="P8" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
+      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1217,83 +1221,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C9" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D9" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E9" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F9" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H9" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I9" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J9" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K9" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L9" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M9" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N9" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O9" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P9" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
-      </c>
       <c r="U9" s="8" t="n">
         <v/>
       </c>
@@ -1305,55 +1301,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C10" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D10" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E10" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F10" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H10" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I10" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J10" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K10" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L10" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M10" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N10" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O10" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1361,18 +1361,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S10" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S10" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="n">
+        <v/>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1387,57 +1387,57 @@
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C11" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D11" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E11" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F11" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H11" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I11" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J11" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K11" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L11" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M11" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N11" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O11" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1447,12 +1447,12 @@
       </c>
       <c r="R11" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S11" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T11" s="8" t="n">
@@ -1469,59 +1469,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C12" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D12" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E12" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F12" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H12" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I12" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J12" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K12" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L12" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M12" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N12" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O12" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1558,50 +1554,50 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C13" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D13" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E13" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F13" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H13" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I13" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J13" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K13" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L13" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M13" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N13" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O13" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1609,18 +1605,18 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R13" s="6" t="n">
+        <v/>
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U13" s="8" t="n">
         <v/>
@@ -1633,55 +1629,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X13" t="inlineStr"/>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C14" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D14" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E14" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F14" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H14" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I14" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J14" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K14" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L14" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M14" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N14" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O14" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1692,9 +1692,9 @@
       <c r="R14" s="6" t="n">
         <v/>
       </c>
-      <c r="S14" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T14" s="8" t="inlineStr">
@@ -1702,70 +1702,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W14" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C15" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D15" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E15" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F15" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H15" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I15" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J15" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K15" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L15" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M15" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N15" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O15" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1773,23 +1775,21 @@
       <c r="Q15" s="6" t="n">
         <v/>
       </c>
-      <c r="R15" s="6" t="n">
-        <v/>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1801,72 +1801,76 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C16" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D16" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E16" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F16" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H16" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I16" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J16" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K16" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L16" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M16" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N16" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O16" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P16" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S16" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T16" s="8" t="n">
@@ -1878,78 +1882,70 @@
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W16" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C17" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D17" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E17" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F17" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H17" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I17" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J17" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K17" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L17" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M17" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N17" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O17" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P17" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="inlineStr">
         <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="Q17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
@@ -1976,50 +1972,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C18" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D18" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E18" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F18" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H18" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I18" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J18" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K18" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L18" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M18" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N18" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O18" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2037,11 +2033,15 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2051,55 +2051,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr"/>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C19" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D19" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E19" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F19" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H19" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I19" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J19" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K19" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L19" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M19" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N19" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O19" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2117,15 +2121,11 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2135,69 +2135,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C20" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D20" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E20" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F20" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H20" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I20" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J20" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K20" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L20" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M20" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N20" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O20" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="n">
-        <v/>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R20" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S20" s="7" t="inlineStr">
@@ -2224,81 +2222,81 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C21" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D21" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E21" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F21" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H21" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I21" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J21" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K21" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L21" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M21" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N21" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O21" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
       </c>
-      <c r="Q21" s="6" t="inlineStr">
+      <c r="Q21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R21" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
-      </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W21" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X21" t="inlineStr"/>
@@ -2306,50 +2304,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C22" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D22" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E22" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F22" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H22" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I22" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J22" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K22" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L22" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M22" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N22" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O22" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2362,18 +2360,14 @@
       </c>
       <c r="S22" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2388,50 +2382,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C23" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D23" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E23" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F23" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H23" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I23" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J23" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K23" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L23" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M23" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N23" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O23" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2444,14 +2438,18 @@
       </c>
       <c r="S23" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V23" s="8" t="n">
         <v/>
@@ -2466,50 +2464,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C24" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D24" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E24" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F24" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H24" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I24" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J24" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K24" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L24" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M24" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N24" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O24" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2535,8 +2533,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V24" s="8" t="n">
-        <v/>
+      <c r="V24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
@@ -2548,50 +2548,50 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C25" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D25" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E25" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F25" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H25" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I25" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J25" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K25" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L25" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M25" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N25" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O25" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2602,80 +2602,78 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V25" s="8" t="n">
+        <v/>
       </c>
       <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C26" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D26" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E26" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H26" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I26" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J26" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K26" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L26" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M26" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N26" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O26" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2683,12 +2681,14 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T26" s="8" t="n">
@@ -2707,57 +2707,57 @@
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C27" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D27" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E27" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F27" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H27" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I27" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J27" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K27" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L27" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M27" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N27" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O27" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2765,22 +2765,24 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
@@ -2789,59 +2791,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C28" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D28" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E28" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F28" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H28" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I28" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J28" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K28" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L28" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M28" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N28" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O28" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2852,20 +2850,16 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2875,55 +2869,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C29" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D29" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E29" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F29" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H29" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I29" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J29" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K29" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L29" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M29" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N29" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O29" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2931,16 +2929,20 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="n">
-        <v/>
+      <c r="R29" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S29" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2955,57 +2957,57 @@
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C30" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D30" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E30" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F30" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H30" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I30" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J30" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K30" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L30" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M30" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N30" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O30" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3013,24 +3015,24 @@
       <c r="Q30" s="6" t="n">
         <v/>
       </c>
-      <c r="R30" s="6" t="inlineStr">
+      <c r="R30" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+      <c r="U30" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U30" s="8" t="n">
-        <v/>
-      </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
@@ -3039,59 +3041,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C31" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D31" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E31" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F31" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H31" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I31" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J31" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K31" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L31" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M31" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N31" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O31" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3109,12 +3107,12 @@
       </c>
       <c r="T31" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U31" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V31" s="8" t="n">
@@ -3130,50 +3128,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C32" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D32" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E32" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F32" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H32" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I32" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J32" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K32" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L32" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M32" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N32" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O32" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3186,18 +3184,14 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U32" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U32" s="8" t="n">
+        <v/>
       </c>
       <c r="V32" s="8" t="n">
         <v/>
@@ -3207,55 +3201,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X32" t="inlineStr"/>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C33" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D33" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E33" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F33" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G33" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H33" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I33" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J33" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K33" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L33" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M33" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N33" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O33" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3266,13 +3264,15 @@
       <c r="R33" s="6" t="n">
         <v/>
       </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="n">
-        <v/>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U33" s="8" t="n">
         <v/>
@@ -3294,69 +3294,73 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C34" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D34" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E34" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F34" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H34" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I34" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J34" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K34" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L34" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M34" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N34" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O34" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+        <v>30631.5</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T34" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T34" s="8" t="n">
+        <v/>
       </c>
       <c r="U34" s="8" t="n">
         <v/>
@@ -3364,83 +3368,73 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W34" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C35" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D35" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E35" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F35" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H35" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I35" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J35" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K35" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L35" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M35" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N35" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O35" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30728.5</v>
+      </c>
+      <c r="P35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3462,50 +3456,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C36" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D36" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E36" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F36" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H36" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I36" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J36" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K36" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L36" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M36" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N36" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O36" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3513,12 +3507,14 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3540,50 +3536,50 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C37" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D37" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E37" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F37" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H37" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I37" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J37" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K37" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L37" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M37" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N37" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O37" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3591,14 +3587,12 @@
       <c r="Q37" s="6" t="n">
         <v/>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S37" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3615,68 +3609,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C38" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D38" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E38" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F38" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I38" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J38" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K38" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L38" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M38" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N38" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O38" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R38" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S38" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R38" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T38" s="8" t="n">
@@ -3693,81 +3695,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C39" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D39" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E39" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F39" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H39" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I39" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J39" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K39" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L39" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M39" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N39" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O39" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="inlineStr">
+      <c r="Q39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R39" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R39" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
       <c r="U39" s="8" t="n">
         <v/>
       </c>
@@ -3779,55 +3775,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C40" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D40" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E40" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F40" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H40" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I40" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J40" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K40" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L40" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M40" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N40" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O40" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3840,13 +3840,11 @@
       </c>
       <c r="S40" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
       </c>
       <c r="U40" s="8" t="n">
         <v/>
@@ -3861,57 +3859,57 @@
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C41" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D41" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E41" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F41" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H41" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I41" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J41" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K41" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L41" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M41" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N41" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O41" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
@@ -3924,100 +3922,100 @@
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U41" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U41" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X41" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W41" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C42" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D42" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E42" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F42" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H42" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I42" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J42" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K42" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L42" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M42" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N42" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O42" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T42" s="8" t="inlineStr">
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U42" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T42" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U42" s="8" t="n">
+        <v/>
       </c>
       <c r="V42" s="8" t="n">
         <v/>
@@ -4027,63 +4025,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X42" t="inlineStr"/>
+      <c r="X42" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C43" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D43" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E43" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F43" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H43" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I43" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J43" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K43" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L43" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M43" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N43" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O43" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
       </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q43" s="6" t="n">
+        <v/>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="S43" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4111,63 +4111,67 @@
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C44" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D44" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E44" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F44" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H44" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I44" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J44" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K44" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L44" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M44" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N44" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O44" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P44" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q44" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R44" s="6" t="inlineStr">
         <is>
@@ -4176,7 +4180,7 @@
       </c>
       <c r="S44" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4188,83 +4192,77 @@
       <c r="V44" s="8" t="n">
         <v/>
       </c>
-      <c r="W44" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W44" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C45" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D45" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E45" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F45" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H45" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I45" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J45" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K45" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L45" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M45" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N45" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O45" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P45" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R45" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30140.5</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q45" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R45" s="6" t="n">
+        <v/>
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T45" s="8" t="n">
@@ -4290,50 +4288,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C46" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D46" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E46" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F46" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H46" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I46" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J46" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K46" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L46" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M46" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N46" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O46" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4344,19 +4342,25 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U46" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V46" s="8" t="n">
-        <v/>
+      <c r="S46" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U46" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W46" s="11" t="inlineStr">
         <is>
@@ -4365,57 +4369,57 @@
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C47" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D47" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E47" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F47" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H47" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I47" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J47" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K47" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L47" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M47" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N47" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O47" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4428,23 +4432,17 @@
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U47" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U47" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V47" s="8" t="n">
+        <v/>
       </c>
       <c r="W47" s="11" t="inlineStr">
         <is>
@@ -4460,50 +4458,50 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C48" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D48" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E48" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F48" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H48" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I48" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J48" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K48" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L48" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M48" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N48" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O48" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4511,16 +4509,20 @@
       <c r="Q48" s="6" t="n">
         <v/>
       </c>
-      <c r="R48" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
+      <c r="R48" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4535,57 +4537,57 @@
       </c>
       <c r="X48" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C49" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D49" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E49" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F49" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H49" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I49" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J49" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K49" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L49" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M49" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N49" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O49" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
@@ -4595,18 +4597,16 @@
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S49" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
       </c>
       <c r="U49" s="8" t="n">
         <v/>
@@ -4619,69 +4619,67 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C50" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D50" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E50" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F50" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H50" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I50" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J50" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K50" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L50" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M50" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N50" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O50" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
@@ -4708,72 +4706,70 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C51" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D51" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E51" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F51" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H51" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I51" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J51" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K51" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L51" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M51" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N51" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O51" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
+      <c r="Q51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R51" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S51" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S51" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
       <c r="U51" s="8" t="n">
         <v/>
       </c>
@@ -4785,75 +4781,81 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C52" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D52" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E52" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F52" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H52" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I52" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J52" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K52" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L52" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M52" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N52" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O52" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R52" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="n">
+        <v/>
+      </c>
       <c r="U52" s="8" t="n">
         <v/>
       </c>
@@ -4865,67 +4867,61 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C53" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D53" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E53" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F53" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H53" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I53" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J53" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K53" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L53" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M53" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N53" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O53" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
       </c>
-      <c r="Q53" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q53" s="6" t="n">
+        <v/>
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
@@ -4951,55 +4947,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X53" t="inlineStr"/>
+      <c r="X53" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C54" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D54" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E54" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F54" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H54" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I54" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J54" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K54" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L54" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M54" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N54" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O54" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5009,19 +5009,23 @@
       </c>
       <c r="R54" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S54" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U54" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
@@ -5033,57 +5037,57 @@
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C55" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D55" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E55" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F55" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H55" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I55" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J55" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K55" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L55" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M55" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N55" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O55" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5091,87 +5095,81 @@
       <c r="Q55" s="6" t="n">
         <v/>
       </c>
-      <c r="R55" s="6" t="inlineStr">
+      <c r="R55" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S55" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T55" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S55" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
       </c>
-      <c r="W55" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X55" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W55" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>28967.5</v>
+        <v>29438.75</v>
       </c>
       <c r="C56" t="n">
-        <v>29498.25</v>
+        <v>29665.25</v>
       </c>
       <c r="D56" t="n">
-        <v>28957.75</v>
+        <v>29352.75</v>
       </c>
       <c r="E56" t="n">
-        <v>29446.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F56" t="n">
-        <v>483.25</v>
+        <v>166.93</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0057</v>
       </c>
       <c r="H56" t="n">
-        <v>540.5</v>
+        <v>312.5</v>
       </c>
       <c r="I56" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J56" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K56" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L56" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M56" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N56" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O56" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5189,13 +5187,11 @@
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U56" s="8" t="n">
+        <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
@@ -5210,50 +5206,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29438.75</v>
+        <v>29938</v>
       </c>
       <c r="C57" t="n">
-        <v>29665.25</v>
+        <v>30862.75</v>
       </c>
       <c r="D57" t="n">
-        <v>29352.75</v>
+        <v>29904</v>
       </c>
       <c r="E57" t="n">
-        <v>29613.68</v>
+        <v>30784.75</v>
       </c>
       <c r="F57" t="n">
-        <v>166.93</v>
+        <v>1171.07</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0395</v>
       </c>
       <c r="H57" t="n">
-        <v>312.5</v>
+        <v>958.75</v>
       </c>
       <c r="I57" t="n">
-        <v>28417.25</v>
+        <v>29040.25</v>
       </c>
       <c r="J57" t="n">
-        <v>29015.62</v>
+        <v>29353.52</v>
       </c>
       <c r="K57" t="n">
-        <v>29176.5</v>
+        <v>29457.43</v>
       </c>
       <c r="L57" t="n">
-        <v>29337.38</v>
+        <v>29561.34</v>
       </c>
       <c r="M57" t="n">
-        <v>29717</v>
+        <v>29769.93</v>
       </c>
       <c r="N57" t="n">
-        <v>30096.62</v>
+        <v>29978.52</v>
       </c>
       <c r="O57" t="n">
-        <v>30038.75</v>
+        <v>29977.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5271,14 +5267,18 @@
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U57" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U57" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V57" s="8" t="n">
-        <v/>
+      <c r="V57" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5290,50 +5290,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>29938</v>
+        <v>30780</v>
       </c>
       <c r="C58" t="n">
-        <v>30862.75</v>
+        <v>31065.5</v>
       </c>
       <c r="D58" t="n">
-        <v>29904</v>
+        <v>30670</v>
       </c>
       <c r="E58" t="n">
-        <v>30784.75</v>
+        <v>31028.5</v>
       </c>
       <c r="F58" t="n">
-        <v>1171.07</v>
+        <v>243.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>958.75</v>
+        <v>395.5</v>
       </c>
       <c r="I58" t="n">
-        <v>29040.25</v>
+        <v>28945.25</v>
       </c>
       <c r="J58" t="n">
-        <v>29353.52</v>
+        <v>30026.69</v>
       </c>
       <c r="K58" t="n">
-        <v>29457.43</v>
+        <v>30305.38</v>
       </c>
       <c r="L58" t="n">
-        <v>29561.34</v>
+        <v>30584.06</v>
       </c>
       <c r="M58" t="n">
-        <v>29769.93</v>
+        <v>31264.12</v>
       </c>
       <c r="N58" t="n">
-        <v>29978.52</v>
+        <v>31944.19</v>
       </c>
       <c r="O58" t="n">
-        <v>29977.75</v>
+        <v>31821.5</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5351,18 +5351,14 @@
       </c>
       <c r="T58" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U58" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V58" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U58" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V58" s="8" t="n">
+        <v/>
       </c>
       <c r="W58" s="9" t="inlineStr">
         <is>
@@ -5374,70 +5370,72 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>30780</v>
+        <v>31008.5</v>
       </c>
       <c r="C59" t="n">
-        <v>31065.5</v>
+        <v>31094.75</v>
       </c>
       <c r="D59" t="n">
-        <v>30670</v>
+        <v>30642.75</v>
       </c>
       <c r="E59" t="n">
-        <v>31028.5</v>
+        <v>30764.75</v>
       </c>
       <c r="F59" t="n">
-        <v>243.75</v>
+        <v>-263.75</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H59" t="n">
-        <v>395.5</v>
+        <v>452</v>
       </c>
       <c r="I59" t="n">
-        <v>28945.25</v>
+        <v>30274.5</v>
       </c>
       <c r="J59" t="n">
-        <v>30026.69</v>
+        <v>30713.38</v>
       </c>
       <c r="K59" t="n">
-        <v>30305.38</v>
+        <v>30830.75</v>
       </c>
       <c r="L59" t="n">
-        <v>30584.06</v>
+        <v>30948.12</v>
       </c>
       <c r="M59" t="n">
-        <v>31264.12</v>
+        <v>31226.25</v>
       </c>
       <c r="N59" t="n">
-        <v>31944.19</v>
+        <v>31504.38</v>
       </c>
       <c r="O59" t="n">
-        <v>31821.5</v>
+        <v>31461</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+      <c r="Q59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5449,63 +5447,65 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr"/>
+      <c r="X59" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>31008.5</v>
+        <v>30780</v>
       </c>
       <c r="C60" t="n">
-        <v>31094.75</v>
+        <v>30827.5</v>
       </c>
       <c r="D60" t="n">
-        <v>30642.75</v>
+        <v>30370</v>
       </c>
       <c r="E60" t="n">
-        <v>30764.75</v>
+        <v>30766.75</v>
       </c>
       <c r="F60" t="n">
-        <v>-263.75</v>
+        <v>2</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0001</v>
       </c>
       <c r="H60" t="n">
-        <v>452</v>
+        <v>457.5</v>
       </c>
       <c r="I60" t="n">
-        <v>30274.5</v>
+        <v>30190.75</v>
       </c>
       <c r="J60" t="n">
-        <v>30713.38</v>
+        <v>30260.75</v>
       </c>
       <c r="K60" t="n">
-        <v>30830.75</v>
+        <v>30538.75</v>
       </c>
       <c r="L60" t="n">
-        <v>30948.12</v>
+        <v>30816.75</v>
       </c>
       <c r="M60" t="n">
-        <v>31226.25</v>
+        <v>30990.75</v>
       </c>
       <c r="N60" t="n">
-        <v>31504.38</v>
+        <v>31164.75</v>
       </c>
       <c r="O60" t="n">
-        <v>31461</v>
+        <v>31546.75</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
       </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q60" s="6" t="n">
+        <v/>
       </c>
       <c r="R60" s="6" t="inlineStr">
         <is>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5540,50 +5540,50 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>30780</v>
+        <v>30726.5</v>
       </c>
       <c r="C61" t="n">
-        <v>30827.5</v>
+        <v>30999.5</v>
       </c>
       <c r="D61" t="n">
-        <v>30370</v>
+        <v>30679</v>
       </c>
       <c r="E61" t="n">
-        <v>30766.75</v>
+        <v>30889.25</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>122.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H61" t="n">
-        <v>457.5</v>
+        <v>320.5</v>
       </c>
       <c r="I61" t="n">
-        <v>30190.75</v>
+        <v>29912.5</v>
       </c>
       <c r="J61" t="n">
-        <v>30260.75</v>
+        <v>30393.25</v>
       </c>
       <c r="K61" t="n">
-        <v>30538.75</v>
+        <v>30538</v>
       </c>
       <c r="L61" t="n">
-        <v>30816.75</v>
+        <v>30682.75</v>
       </c>
       <c r="M61" t="n">
-        <v>30990.75</v>
+        <v>30995.5</v>
       </c>
       <c r="N61" t="n">
-        <v>31164.75</v>
+        <v>31308.25</v>
       </c>
       <c r="O61" t="n">
-        <v>31546.75</v>
+        <v>31285</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5591,18 +5591,18 @@
       <c r="Q61" s="6" t="n">
         <v/>
       </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S61" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+      <c r="R61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S61" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5615,173 +5615,89 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30726.5</v>
+        <v>30560.5</v>
       </c>
       <c r="C62" t="n">
-        <v>30999.5</v>
+        <v>30589</v>
       </c>
       <c r="D62" t="n">
-        <v>30679</v>
+        <v>30536.25</v>
       </c>
       <c r="E62" t="n">
-        <v>30889.25</v>
+        <v>30548.5</v>
       </c>
       <c r="F62" t="n">
-        <v>122.5</v>
+        <v>-340.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.011</v>
       </c>
       <c r="H62" t="n">
-        <v>320.5</v>
+        <v>52.75</v>
       </c>
       <c r="I62" t="n">
-        <v>29912.5</v>
+        <v>30358.5</v>
       </c>
       <c r="J62" t="n">
-        <v>30393.25</v>
+        <v>30593.75</v>
       </c>
       <c r="K62" t="n">
-        <v>30538</v>
+        <v>30729</v>
       </c>
       <c r="L62" t="n">
-        <v>30682.75</v>
+        <v>30864.25</v>
       </c>
       <c r="M62" t="n">
-        <v>30995.5</v>
+        <v>31049.5</v>
       </c>
       <c r="N62" t="n">
-        <v>31308.25</v>
+        <v>31234.75</v>
       </c>
       <c r="O62" t="n">
-        <v>31285</v>
+        <v>31320</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R62" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S62" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="inlineStr">
+      <c r="Q62" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R62" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S62" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="n">
+        <v/>
+      </c>
       <c r="U62" s="8" t="n">
         <v/>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W62" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>2026-09-27</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>30870</v>
-      </c>
-      <c r="C63" t="n">
-        <v>30920.75</v>
-      </c>
-      <c r="D63" t="n">
-        <v>30816.25</v>
-      </c>
-      <c r="E63" t="n">
-        <v>30889.25</v>
-      </c>
-      <c r="F63" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" t="n">
-        <v>104.5</v>
-      </c>
-      <c r="I63" t="n">
-        <v>30358.5</v>
-      </c>
-      <c r="J63" t="n">
-        <v>30593.75</v>
-      </c>
-      <c r="K63" t="n">
-        <v>30729</v>
-      </c>
-      <c r="L63" t="n">
-        <v>30864.25</v>
-      </c>
-      <c r="M63" t="n">
-        <v>31049.5</v>
-      </c>
-      <c r="N63" t="n">
-        <v>31234.75</v>
-      </c>
-      <c r="O63" t="n">
-        <v>31320</v>
-      </c>
-      <c r="P63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R63" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S63" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -634,74 +634,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-02</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>30089.75</v>
+        <v>29930.25</v>
       </c>
       <c r="C2" t="n">
-        <v>30320</v>
+        <v>30094</v>
       </c>
       <c r="D2" t="n">
-        <v>29328.5</v>
+        <v>29683</v>
       </c>
       <c r="E2" t="n">
-        <v>29556</v>
+        <v>29941</v>
       </c>
       <c r="F2" t="n">
-        <v>-538.25</v>
+        <v>385</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0179</v>
+        <v>0.013</v>
       </c>
       <c r="H2" t="n">
-        <v>991.5</v>
+        <v>411</v>
       </c>
       <c r="I2" t="n">
-        <v>29463.25</v>
+        <v>28337</v>
       </c>
       <c r="J2" t="n">
-        <v>29455.56</v>
+        <v>28430.38</v>
       </c>
       <c r="K2" t="n">
-        <v>29821.62</v>
+        <v>29060.25</v>
       </c>
       <c r="L2" t="n">
-        <v>30187.69</v>
+        <v>29690.12</v>
       </c>
       <c r="M2" t="n">
-        <v>30366.88</v>
+        <v>30051.75</v>
       </c>
       <c r="N2" t="n">
-        <v>30546.06</v>
+        <v>30413.38</v>
       </c>
       <c r="O2" t="n">
-        <v>31099</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
+        <v>31311.5</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S2" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S2" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
-      </c>
       <c r="U2" s="8" t="n">
         <v/>
       </c>
@@ -715,76 +711,80 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C3" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D3" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E3" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F3" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H3" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I3" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J3" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K3" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L3" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M3" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N3" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O3" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q3" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R3" s="6" t="n">
-        <v/>
+        <v>30505</v>
+      </c>
+      <c r="P3" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S3" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="n">
+        <v/>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -792,83 +792,75 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W3" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C4" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D4" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E4" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F4" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H4" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I4" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J4" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K4" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L4" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M4" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N4" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O4" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P4" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q4" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q4" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S4" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S4" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T4" s="8" t="n">
@@ -885,55 +877,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr"/>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C5" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D5" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E5" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F5" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H5" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I5" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J5" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K5" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L5" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M5" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N5" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O5" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -941,18 +937,18 @@
       <c r="Q5" s="6" t="n">
         <v/>
       </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R5" s="6" t="n">
+        <v/>
       </c>
       <c r="S5" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U5" s="8" t="n">
         <v/>
@@ -967,57 +963,57 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C6" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D6" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E6" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F6" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H6" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I6" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J6" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K6" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L6" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M6" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N6" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O6" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1028,7 +1024,7 @@
       <c r="R6" s="6" t="n">
         <v/>
       </c>
-      <c r="S6" s="10" t="inlineStr">
+      <c r="S6" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -1058,69 +1054,73 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C7" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D7" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E7" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F7" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H7" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I7" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J7" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K7" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L7" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M7" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N7" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O7" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R7" s="6" t="n">
-        <v/>
+        <v>30480.5</v>
+      </c>
+      <c r="P7" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S7" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1133,83 +1133,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C8" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D8" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E8" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H8" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I8" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J8" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K8" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L8" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M8" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N8" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O8" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P8" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R8" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S8" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R8" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S8" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="n">
-        <v/>
-      </c>
       <c r="U8" s="8" t="n">
         <v/>
       </c>
@@ -1221,55 +1213,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr"/>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C9" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D9" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E9" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F9" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H9" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I9" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J9" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K9" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L9" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M9" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N9" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O9" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1277,18 +1273,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="n">
-        <v/>
+      <c r="R9" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S9" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="n">
+        <v/>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1303,57 +1299,57 @@
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C10" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D10" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E10" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F10" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H10" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I10" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J10" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K10" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L10" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M10" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N10" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O10" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1363,12 +1359,12 @@
       </c>
       <c r="R10" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S10" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S10" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T10" s="8" t="n">
@@ -1385,59 +1381,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C11" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D11" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E11" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F11" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H11" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I11" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J11" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K11" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L11" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M11" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N11" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O11" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1450,7 +1442,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S11" s="7" t="inlineStr">
+      <c r="S11" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1474,50 +1466,50 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C12" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D12" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E12" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H12" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I12" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J12" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K12" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L12" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M12" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N12" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O12" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1525,18 +1517,18 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="n">
-        <v/>
+      <c r="R12" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U12" s="8" t="n">
         <v/>
@@ -1549,55 +1541,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X12" t="inlineStr"/>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C13" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D13" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E13" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F13" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H13" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I13" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J13" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K13" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L13" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M13" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N13" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O13" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1610,7 +1606,7 @@
       </c>
       <c r="S13" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T13" s="8" t="inlineStr">
@@ -1618,70 +1614,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="n">
-        <v/>
+      <c r="U13" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W13" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C14" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D14" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E14" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F14" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H14" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I14" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J14" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K14" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L14" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M14" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N14" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O14" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1689,23 +1687,21 @@
       <c r="Q14" s="6" t="n">
         <v/>
       </c>
-      <c r="R14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T14" s="8" t="inlineStr">
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U14" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S14" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T14" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U14" s="8" t="n">
+        <v/>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1717,63 +1713,67 @@
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C15" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D15" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E15" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F15" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H15" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I15" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J15" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K15" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L15" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M15" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N15" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O15" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P15" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q15" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R15" s="6" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="S15" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T15" s="8" t="n">
@@ -1794,81 +1794,73 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W15" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C16" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D16" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E16" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F16" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H16" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I16" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J16" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K16" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L16" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M16" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N16" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O16" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P16" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q16" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R16" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1892,50 +1884,50 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C17" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D17" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E17" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F17" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H17" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I17" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J17" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K17" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L17" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M17" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N17" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O17" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1948,16 +1940,20 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="7" t="inlineStr">
+      <c r="S17" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
@@ -1967,55 +1963,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr"/>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C18" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D18" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E18" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F18" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H18" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I18" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J18" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K18" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L18" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M18" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N18" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O18" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2028,20 +2028,16 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S18" s="7" t="inlineStr">
+      <c r="S18" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2051,72 +2047,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C19" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D19" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E19" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F19" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H19" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I19" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J19" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K19" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L19" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M19" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N19" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O19" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="n">
-        <v/>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R19" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S19" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2140,81 +2134,81 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C20" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D20" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E20" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F20" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H20" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I20" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J20" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K20" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L20" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M20" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N20" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O20" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
       </c>
-      <c r="Q20" s="6" t="inlineStr">
+      <c r="Q20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R20" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S20" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
-      </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W20" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X20" t="inlineStr"/>
@@ -2222,50 +2216,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C21" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D21" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E21" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F21" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H21" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I21" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J21" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K21" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L21" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M21" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N21" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O21" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2276,20 +2270,16 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S21" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
@@ -2304,50 +2294,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C22" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D22" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E22" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F22" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H22" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I22" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J22" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K22" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L22" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M22" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N22" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O22" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2358,16 +2348,20 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U22" s="8" t="n">
-        <v/>
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U22" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V22" s="8" t="n">
         <v/>
@@ -2382,50 +2376,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C23" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D23" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E23" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F23" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H23" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I23" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J23" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K23" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L23" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M23" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N23" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O23" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2436,7 +2430,7 @@
       <c r="R23" s="6" t="n">
         <v/>
       </c>
-      <c r="S23" s="10" t="inlineStr">
+      <c r="S23" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2451,8 +2445,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V23" s="8" t="n">
-        <v/>
+      <c r="V23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W23" s="9" t="inlineStr">
         <is>
@@ -2464,50 +2460,50 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C24" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D24" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E24" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F24" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H24" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I24" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J24" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K24" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L24" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M24" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N24" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O24" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2520,78 +2516,76 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V24" s="8" t="n">
+        <v/>
       </c>
       <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C25" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D25" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E25" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F25" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H25" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I25" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J25" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K25" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L25" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M25" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N25" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O25" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2599,12 +2593,14 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T25" s="8" t="n">
@@ -2623,57 +2619,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C26" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D26" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E26" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F26" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H26" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I26" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J26" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K26" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L26" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M26" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N26" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O26" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2681,22 +2677,24 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2705,59 +2703,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C27" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D27" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E27" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F27" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H27" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I27" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J27" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K27" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L27" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M27" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N27" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O27" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2770,18 +2764,14 @@
       </c>
       <c r="S27" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U27" s="8" t="n">
+        <v/>
       </c>
       <c r="V27" s="8" t="n">
         <v/>
@@ -2791,55 +2781,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr"/>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C28" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D28" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E28" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F28" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H28" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I28" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J28" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K28" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L28" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M28" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N28" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O28" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2847,16 +2841,20 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S28" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="n">
-        <v/>
+      <c r="R28" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U28" s="8" t="n">
         <v/>
@@ -2871,57 +2869,57 @@
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C29" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D29" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E29" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F29" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H29" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I29" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J29" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K29" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L29" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M29" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N29" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O29" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2929,24 +2927,24 @@
       <c r="Q29" s="6" t="n">
         <v/>
       </c>
-      <c r="R29" s="6" t="inlineStr">
+      <c r="R29" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S29" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S29" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
+      <c r="U29" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U29" s="8" t="n">
-        <v/>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
@@ -2955,59 +2953,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C30" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D30" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E30" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F30" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H30" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I30" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J30" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K30" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L30" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M30" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N30" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O30" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3018,19 +3012,19 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
+      <c r="S30" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T30" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U30" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V30" s="8" t="n">
@@ -3046,50 +3040,50 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C31" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D31" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E31" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F31" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H31" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I31" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J31" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K31" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L31" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M31" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N31" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O31" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3100,20 +3094,16 @@
       <c r="R31" s="6" t="n">
         <v/>
       </c>
-      <c r="S31" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U31" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S31" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U31" s="8" t="n">
+        <v/>
       </c>
       <c r="V31" s="8" t="n">
         <v/>
@@ -3123,55 +3113,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X31" t="inlineStr"/>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C32" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D32" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E32" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F32" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G32" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H32" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I32" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J32" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K32" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L32" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M32" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N32" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O32" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3184,11 +3178,13 @@
       </c>
       <c r="S32" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U32" s="8" t="n">
         <v/>
@@ -3210,153 +3206,147 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C33" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D33" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E33" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F33" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H33" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I33" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J33" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K33" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L33" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M33" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N33" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O33" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R33" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S33" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T33" s="8" t="inlineStr">
+        <v>30631.5</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S33" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T33" s="8" t="n">
+        <v/>
+      </c>
       <c r="U33" s="8" t="n">
         <v/>
       </c>
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W33" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C34" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D34" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E34" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F34" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H34" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I34" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J34" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K34" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L34" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M34" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N34" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O34" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30728.5</v>
+      </c>
+      <c r="P34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3378,50 +3368,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C35" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D35" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E35" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F35" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H35" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I35" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J35" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K35" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L35" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M35" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N35" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O35" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3429,12 +3419,14 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S35" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3456,50 +3448,50 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C36" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D36" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E36" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F36" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H36" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I36" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J36" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K36" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L36" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M36" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N36" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O36" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3507,14 +3499,12 @@
       <c r="Q36" s="6" t="n">
         <v/>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R36" s="6" t="n">
+        <v/>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3531,68 +3521,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C37" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D37" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E37" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F37" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H37" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I37" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J37" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K37" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L37" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M37" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N37" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O37" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R37" s="6" t="n">
-        <v/>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R37" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T37" s="8" t="n">
@@ -3609,81 +3607,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C38" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D38" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E38" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F38" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H38" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I38" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J38" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K38" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L38" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M38" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N38" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O38" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="inlineStr">
+      <c r="Q38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R38" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S38" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R38" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
       <c r="U38" s="8" t="n">
         <v/>
       </c>
@@ -3695,55 +3687,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X38" t="inlineStr"/>
+      <c r="X38" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C39" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D39" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E39" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F39" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H39" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I39" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J39" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K39" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L39" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M39" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N39" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O39" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3754,15 +3750,13 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
       </c>
       <c r="U39" s="8" t="n">
         <v/>
@@ -3777,57 +3771,57 @@
       </c>
       <c r="X39" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C40" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D40" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E40" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F40" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H40" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I40" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J40" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K40" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L40" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M40" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N40" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O40" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
@@ -3838,102 +3832,102 @@
       <c r="R40" s="6" t="n">
         <v/>
       </c>
-      <c r="S40" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U40" s="8" t="n">
-        <v/>
+      <c r="S40" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U40" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X40" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W40" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C41" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D41" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E41" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F41" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H41" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I41" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J41" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K41" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L41" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M41" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N41" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O41" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R41" s="6" t="n">
-        <v/>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S41" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T41" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U41" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T41" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U41" s="8" t="n">
+        <v/>
       </c>
       <c r="V41" s="8" t="n">
         <v/>
@@ -3943,72 +3937,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X41" t="inlineStr"/>
+      <c r="X41" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C42" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D42" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E42" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F42" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H42" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I42" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J42" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K42" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L42" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M42" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N42" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O42" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P42" s="6" t="n">
         <v/>
       </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q42" s="6" t="n">
+        <v/>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S42" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4027,72 +4023,76 @@
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C43" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D43" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E43" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F43" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H43" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I43" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J43" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K43" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L43" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M43" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N43" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O43" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P43" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q43" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R43" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4104,83 +4104,77 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W43" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C44" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D44" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E44" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F44" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H44" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I44" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J44" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K44" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L44" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M44" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N44" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O44" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P44" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R44" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S44" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30140.5</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R44" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S44" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T44" s="8" t="n">
@@ -4206,50 +4200,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C45" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D45" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E45" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F45" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H45" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I45" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J45" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K45" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L45" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M45" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N45" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O45" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4262,17 +4256,23 @@
       </c>
       <c r="S45" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U45" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V45" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U45" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W45" s="11" t="inlineStr">
         <is>
@@ -4281,57 +4281,57 @@
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C46" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D46" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E46" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F46" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H46" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I46" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J46" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K46" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L46" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M46" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N46" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O46" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4342,25 +4342,19 @@
       <c r="R46" s="6" t="n">
         <v/>
       </c>
-      <c r="S46" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U46" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="S46" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U46" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V46" s="8" t="n">
+        <v/>
       </c>
       <c r="W46" s="11" t="inlineStr">
         <is>
@@ -4376,50 +4370,50 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C47" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D47" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E47" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F47" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H47" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I47" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J47" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K47" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L47" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M47" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N47" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O47" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4427,16 +4421,20 @@
       <c r="Q47" s="6" t="n">
         <v/>
       </c>
-      <c r="R47" s="6" t="n">
-        <v/>
+      <c r="R47" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S47" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4451,57 +4449,57 @@
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C48" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D48" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E48" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F48" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H48" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I48" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J48" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K48" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L48" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M48" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N48" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O48" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
@@ -4511,18 +4509,16 @@
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="n">
+        <v/>
       </c>
       <c r="U48" s="8" t="n">
         <v/>
@@ -4535,72 +4531,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C49" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D49" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E49" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F49" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H49" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I49" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J49" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K49" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L49" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M49" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N49" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O49" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R49" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S49" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4624,72 +4618,70 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C50" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D50" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E50" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F50" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H50" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I50" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J50" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K50" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L50" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M50" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N50" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O50" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
+      <c r="Q50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R50" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S50" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S50" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="n">
-        <v/>
-      </c>
       <c r="U50" s="8" t="n">
         <v/>
       </c>
@@ -4701,74 +4693,80 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C51" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D51" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E51" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F51" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H51" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I51" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J51" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K51" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L51" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M51" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N51" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O51" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R51" s="6" t="n">
-        <v/>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R51" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S51" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="n">
+        <v/>
       </c>
       <c r="U51" s="8" t="n">
         <v/>
@@ -4781,74 +4779,68 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C52" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D52" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E52" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F52" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H52" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I52" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J52" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K52" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L52" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M52" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N52" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O52" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
       </c>
-      <c r="Q52" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q52" s="6" t="n">
+        <v/>
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
+      <c r="S52" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4867,55 +4859,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X52" t="inlineStr"/>
+      <c r="X52" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C53" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D53" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E53" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F53" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H53" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I53" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J53" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K53" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L53" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M53" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N53" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O53" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4925,19 +4921,23 @@
       </c>
       <c r="R53" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S53" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U53" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U53" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V53" s="8" t="n">
         <v/>
@@ -4949,57 +4949,57 @@
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C54" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D54" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E54" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F54" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H54" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I54" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J54" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K54" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L54" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M54" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N54" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O54" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5007,87 +5007,81 @@
       <c r="Q54" s="6" t="n">
         <v/>
       </c>
-      <c r="R54" s="6" t="inlineStr">
+      <c r="R54" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S54" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T54" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S54" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T54" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X54" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W54" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>28967.5</v>
+        <v>29438.75</v>
       </c>
       <c r="C55" t="n">
-        <v>29498.25</v>
+        <v>29665.25</v>
       </c>
       <c r="D55" t="n">
-        <v>28957.75</v>
+        <v>29352.75</v>
       </c>
       <c r="E55" t="n">
-        <v>29446.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F55" t="n">
-        <v>483.25</v>
+        <v>166.93</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0057</v>
       </c>
       <c r="H55" t="n">
-        <v>540.5</v>
+        <v>312.5</v>
       </c>
       <c r="I55" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J55" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K55" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L55" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M55" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N55" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O55" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5098,20 +5092,18 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="10" t="inlineStr">
+      <c r="S55" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
+      </c>
+      <c r="U55" s="8" t="n">
+        <v/>
       </c>
       <c r="V55" s="8" t="n">
         <v/>
@@ -5126,50 +5118,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29438.75</v>
+        <v>29938</v>
       </c>
       <c r="C56" t="n">
-        <v>29665.25</v>
+        <v>30862.75</v>
       </c>
       <c r="D56" t="n">
-        <v>29352.75</v>
+        <v>29904</v>
       </c>
       <c r="E56" t="n">
-        <v>29613.68</v>
+        <v>30784.75</v>
       </c>
       <c r="F56" t="n">
-        <v>166.93</v>
+        <v>1171.07</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0395</v>
       </c>
       <c r="H56" t="n">
-        <v>312.5</v>
+        <v>958.75</v>
       </c>
       <c r="I56" t="n">
-        <v>28417.25</v>
+        <v>29040.25</v>
       </c>
       <c r="J56" t="n">
-        <v>29015.62</v>
+        <v>29353.52</v>
       </c>
       <c r="K56" t="n">
-        <v>29176.5</v>
+        <v>29457.43</v>
       </c>
       <c r="L56" t="n">
-        <v>29337.38</v>
+        <v>29561.34</v>
       </c>
       <c r="M56" t="n">
-        <v>29717</v>
+        <v>29769.93</v>
       </c>
       <c r="N56" t="n">
-        <v>30096.62</v>
+        <v>29978.52</v>
       </c>
       <c r="O56" t="n">
-        <v>30038.75</v>
+        <v>29977.75</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5180,21 +5172,25 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="10" t="inlineStr">
+      <c r="S56" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U56" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U56" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V56" s="8" t="n">
-        <v/>
+      <c r="V56" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W56" s="9" t="inlineStr">
         <is>
@@ -5206,50 +5202,50 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>29938</v>
+        <v>30780</v>
       </c>
       <c r="C57" t="n">
-        <v>30862.75</v>
+        <v>31065.5</v>
       </c>
       <c r="D57" t="n">
-        <v>29904</v>
+        <v>30670</v>
       </c>
       <c r="E57" t="n">
-        <v>30784.75</v>
+        <v>31028.5</v>
       </c>
       <c r="F57" t="n">
-        <v>1171.07</v>
+        <v>243.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>958.75</v>
+        <v>395.5</v>
       </c>
       <c r="I57" t="n">
-        <v>29040.25</v>
+        <v>28945.25</v>
       </c>
       <c r="J57" t="n">
-        <v>29353.52</v>
+        <v>30026.69</v>
       </c>
       <c r="K57" t="n">
-        <v>29457.43</v>
+        <v>30305.38</v>
       </c>
       <c r="L57" t="n">
-        <v>29561.34</v>
+        <v>30584.06</v>
       </c>
       <c r="M57" t="n">
-        <v>29769.93</v>
+        <v>31264.12</v>
       </c>
       <c r="N57" t="n">
-        <v>29978.52</v>
+        <v>31944.19</v>
       </c>
       <c r="O57" t="n">
-        <v>29977.75</v>
+        <v>31821.5</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
@@ -5260,25 +5256,21 @@
       <c r="R57" s="6" t="n">
         <v/>
       </c>
-      <c r="S57" s="10" t="inlineStr">
+      <c r="S57" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T57" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U57" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V57" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="U57" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V57" s="8" t="n">
+        <v/>
       </c>
       <c r="W57" s="9" t="inlineStr">
         <is>
@@ -5290,69 +5282,71 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30780</v>
+        <v>31008.5</v>
       </c>
       <c r="C58" t="n">
-        <v>31065.5</v>
+        <v>31094.75</v>
       </c>
       <c r="D58" t="n">
-        <v>30670</v>
+        <v>30642.75</v>
       </c>
       <c r="E58" t="n">
-        <v>31028.5</v>
+        <v>30764.75</v>
       </c>
       <c r="F58" t="n">
-        <v>243.75</v>
+        <v>-263.75</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H58" t="n">
-        <v>395.5</v>
+        <v>452</v>
       </c>
       <c r="I58" t="n">
-        <v>28945.25</v>
+        <v>30274.5</v>
       </c>
       <c r="J58" t="n">
-        <v>30026.69</v>
+        <v>30713.38</v>
       </c>
       <c r="K58" t="n">
-        <v>30305.38</v>
+        <v>30830.75</v>
       </c>
       <c r="L58" t="n">
-        <v>30584.06</v>
+        <v>30948.12</v>
       </c>
       <c r="M58" t="n">
-        <v>31264.12</v>
+        <v>31226.25</v>
       </c>
       <c r="N58" t="n">
-        <v>31944.19</v>
+        <v>31504.38</v>
       </c>
       <c r="O58" t="n">
-        <v>31821.5</v>
+        <v>31461</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R58" s="6" t="n">
-        <v/>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R58" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S58" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="n">
+        <v/>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5365,72 +5359,74 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr"/>
+      <c r="X58" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>31008.5</v>
+        <v>30780</v>
       </c>
       <c r="C59" t="n">
-        <v>31094.75</v>
+        <v>30827.5</v>
       </c>
       <c r="D59" t="n">
-        <v>30642.75</v>
+        <v>30370</v>
       </c>
       <c r="E59" t="n">
-        <v>30764.75</v>
+        <v>30766.75</v>
       </c>
       <c r="F59" t="n">
-        <v>-263.75</v>
+        <v>2</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0001</v>
       </c>
       <c r="H59" t="n">
-        <v>452</v>
+        <v>457.5</v>
       </c>
       <c r="I59" t="n">
-        <v>30274.5</v>
+        <v>30190.75</v>
       </c>
       <c r="J59" t="n">
-        <v>30713.38</v>
+        <v>30260.75</v>
       </c>
       <c r="K59" t="n">
-        <v>30830.75</v>
+        <v>30538.75</v>
       </c>
       <c r="L59" t="n">
-        <v>30948.12</v>
+        <v>30816.75</v>
       </c>
       <c r="M59" t="n">
-        <v>31226.25</v>
+        <v>30990.75</v>
       </c>
       <c r="N59" t="n">
-        <v>31504.38</v>
+        <v>31164.75</v>
       </c>
       <c r="O59" t="n">
-        <v>31461</v>
+        <v>31546.75</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
       </c>
-      <c r="Q59" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q59" s="6" t="n">
+        <v/>
       </c>
       <c r="R59" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S59" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S59" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T59" s="8" t="n">
@@ -5456,50 +5452,50 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>30780</v>
+        <v>30726.5</v>
       </c>
       <c r="C60" t="n">
-        <v>30827.5</v>
+        <v>30999.5</v>
       </c>
       <c r="D60" t="n">
-        <v>30370</v>
+        <v>30679</v>
       </c>
       <c r="E60" t="n">
-        <v>30766.75</v>
+        <v>30889.25</v>
       </c>
       <c r="F60" t="n">
-        <v>2</v>
+        <v>122.5</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H60" t="n">
-        <v>457.5</v>
+        <v>320.5</v>
       </c>
       <c r="I60" t="n">
-        <v>30190.75</v>
+        <v>29912.5</v>
       </c>
       <c r="J60" t="n">
-        <v>30260.75</v>
+        <v>30393.25</v>
       </c>
       <c r="K60" t="n">
-        <v>30538.75</v>
+        <v>30538</v>
       </c>
       <c r="L60" t="n">
-        <v>30816.75</v>
+        <v>30682.75</v>
       </c>
       <c r="M60" t="n">
-        <v>30990.75</v>
+        <v>30995.5</v>
       </c>
       <c r="N60" t="n">
-        <v>31164.75</v>
+        <v>31308.25</v>
       </c>
       <c r="O60" t="n">
-        <v>31546.75</v>
+        <v>31285</v>
       </c>
       <c r="P60" s="6" t="n">
         <v/>
@@ -5507,18 +5503,18 @@
       <c r="Q60" s="6" t="n">
         <v/>
       </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R60" s="6" t="n">
+        <v/>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5531,78 +5527,78 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>30726.5</v>
+        <v>30870</v>
       </c>
       <c r="C61" t="n">
-        <v>30999.5</v>
+        <v>30920.75</v>
       </c>
       <c r="D61" t="n">
-        <v>30679</v>
+        <v>30356.75</v>
       </c>
       <c r="E61" t="n">
-        <v>30889.25</v>
+        <v>30566.25</v>
       </c>
       <c r="F61" t="n">
-        <v>122.5</v>
+        <v>-323</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0105</v>
       </c>
       <c r="H61" t="n">
-        <v>320.5</v>
+        <v>564</v>
       </c>
       <c r="I61" t="n">
-        <v>29912.5</v>
+        <v>30358.5</v>
       </c>
       <c r="J61" t="n">
-        <v>30393.25</v>
+        <v>30593.75</v>
       </c>
       <c r="K61" t="n">
-        <v>30538</v>
+        <v>30729</v>
       </c>
       <c r="L61" t="n">
-        <v>30682.75</v>
+        <v>30864.25</v>
       </c>
       <c r="M61" t="n">
-        <v>30995.5</v>
+        <v>31049.5</v>
       </c>
       <c r="N61" t="n">
-        <v>31308.25</v>
+        <v>31234.75</v>
       </c>
       <c r="O61" t="n">
-        <v>31285</v>
-      </c>
-      <c r="P61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q61" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R61" s="6" t="n">
-        <v/>
+        <v>31320</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R61" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="n">
+        <v/>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5610,9 +5606,9 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W61" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr"/>
@@ -5620,67 +5616,63 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30560.5</v>
+        <v>30657.25</v>
       </c>
       <c r="C62" t="n">
-        <v>30589</v>
+        <v>30697</v>
       </c>
       <c r="D62" t="n">
-        <v>30536.25</v>
+        <v>30655</v>
       </c>
       <c r="E62" t="n">
-        <v>30548.5</v>
+        <v>30695.25</v>
       </c>
       <c r="F62" t="n">
-        <v>-340.75</v>
+        <v>129</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>-0.011</v>
+        <v>0.0042</v>
       </c>
       <c r="H62" t="n">
-        <v>52.75</v>
+        <v>42</v>
       </c>
       <c r="I62" t="n">
-        <v>30358.5</v>
+        <v>29792.75</v>
       </c>
       <c r="J62" t="n">
-        <v>30593.75</v>
+        <v>29966</v>
       </c>
       <c r="K62" t="n">
-        <v>30729</v>
+        <v>30284.25</v>
       </c>
       <c r="L62" t="n">
-        <v>30864.25</v>
+        <v>30602.5</v>
       </c>
       <c r="M62" t="n">
-        <v>31049.5</v>
+        <v>30848.25</v>
       </c>
       <c r="N62" t="n">
-        <v>31234.75</v>
+        <v>31094</v>
       </c>
       <c r="O62" t="n">
-        <v>31320</v>
+        <v>31484.75</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
       </c>
-      <c r="Q62" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R62" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q62" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R62" s="6" t="n">
+        <v/>
       </c>
       <c r="S62" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="n">
@@ -5697,7 +5689,11 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X62" t="inlineStr"/>
+      <c r="X62" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -104,17 +104,17 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -634,69 +634,73 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-07-07</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29930.25</v>
+        <v>29960</v>
       </c>
       <c r="C2" t="n">
-        <v>30094</v>
+        <v>29973.75</v>
       </c>
       <c r="D2" t="n">
-        <v>29683</v>
+        <v>29210</v>
       </c>
       <c r="E2" t="n">
-        <v>29941</v>
+        <v>29391.5</v>
       </c>
       <c r="F2" t="n">
-        <v>385</v>
+        <v>-549.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.013</v>
+        <v>-0.0184</v>
       </c>
       <c r="H2" t="n">
-        <v>411</v>
+        <v>763.75</v>
       </c>
       <c r="I2" t="n">
-        <v>28337</v>
+        <v>29272</v>
       </c>
       <c r="J2" t="n">
-        <v>28430.38</v>
+        <v>29556.25</v>
       </c>
       <c r="K2" t="n">
-        <v>29060.25</v>
+        <v>29735.5</v>
       </c>
       <c r="L2" t="n">
-        <v>29690.12</v>
+        <v>29914.75</v>
       </c>
       <c r="M2" t="n">
-        <v>30051.75</v>
+        <v>30146.5</v>
       </c>
       <c r="N2" t="n">
-        <v>30413.38</v>
+        <v>30378.25</v>
       </c>
       <c r="O2" t="n">
-        <v>31311.5</v>
-      </c>
-      <c r="P2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q2" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R2" s="6" t="n">
-        <v/>
+        <v>30505</v>
+      </c>
+      <c r="P2" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="n">
+        <v/>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -706,81 +710,73 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C3" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D3" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E3" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F3" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H3" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I3" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J3" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K3" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L3" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M3" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N3" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O3" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P3" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q3" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R3" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S3" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T3" s="8" t="n">
@@ -792,60 +788,64 @@
       <c r="V3" s="8" t="n">
         <v/>
       </c>
-      <c r="W3" s="11" t="inlineStr">
+      <c r="W3" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr"/>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C4" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D4" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E4" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F4" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H4" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I4" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J4" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K4" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L4" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M4" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N4" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O4" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -853,18 +853,18 @@
       <c r="Q4" s="6" t="n">
         <v/>
       </c>
-      <c r="R4" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R4" s="6" t="n">
+        <v/>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -872,64 +872,64 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="11" t="inlineStr">
+      <c r="W4" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C5" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D5" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E5" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F5" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H5" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I5" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J5" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K5" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L5" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M5" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N5" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O5" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P5" s="6" t="n">
         <v/>
@@ -940,7 +940,7 @@
       <c r="R5" s="6" t="n">
         <v/>
       </c>
-      <c r="S5" s="7" t="inlineStr">
+      <c r="S5" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -956,7 +956,7 @@
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="11" t="inlineStr">
+      <c r="W5" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -970,69 +970,73 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C6" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D6" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E6" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F6" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H6" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I6" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J6" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K6" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L6" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M6" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N6" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O6" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q6" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+        <v>30480.5</v>
+      </c>
+      <c r="P6" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1040,148 +1044,144 @@
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="11" t="inlineStr">
+      <c r="W6" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C7" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D7" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E7" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F7" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H7" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I7" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J7" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K7" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L7" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M7" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N7" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O7" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P7" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R7" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R7" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="n">
-        <v/>
-      </c>
       <c r="U7" s="8" t="n">
         <v/>
       </c>
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="11" t="inlineStr">
+      <c r="W7" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr"/>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C8" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D8" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E8" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F8" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H8" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I8" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J8" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K8" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L8" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M8" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N8" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O8" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1189,18 +1189,18 @@
       <c r="Q8" s="6" t="n">
         <v/>
       </c>
-      <c r="R8" s="6" t="n">
-        <v/>
+      <c r="R8" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T8" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T8" s="8" t="n">
+        <v/>
       </c>
       <c r="U8" s="8" t="n">
         <v/>
@@ -1208,64 +1208,64 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="11" t="inlineStr">
+      <c r="W8" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C9" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D9" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E9" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F9" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H9" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I9" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J9" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K9" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L9" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M9" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N9" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O9" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="R9" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S9" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S9" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T9" s="8" t="n">
@@ -1292,64 +1292,60 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="11" t="inlineStr">
+      <c r="W9" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C10" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D10" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E10" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F10" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H10" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I10" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J10" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K10" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L10" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M10" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N10" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O10" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1362,7 +1358,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S10" s="10" t="inlineStr">
+      <c r="S10" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1376,7 +1372,7 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
+      <c r="W10" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1386,50 +1382,50 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C11" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D11" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E11" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F11" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H11" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I11" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J11" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K11" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L11" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M11" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N11" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O11" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1437,18 +1433,18 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="n">
-        <v/>
+      <c r="R11" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U11" s="8" t="n">
         <v/>
@@ -1456,60 +1452,64 @@
       <c r="V11" s="8" t="n">
         <v/>
       </c>
-      <c r="W11" s="11" t="inlineStr">
+      <c r="W11" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X11" t="inlineStr"/>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C12" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D12" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E12" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F12" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H12" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I12" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J12" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K12" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L12" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M12" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N12" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O12" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T12" s="8" t="inlineStr">
@@ -1530,70 +1530,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U12" s="8" t="n">
-        <v/>
+      <c r="U12" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
       <c r="W12" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C13" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D13" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E13" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F13" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H13" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I13" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J13" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K13" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L13" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M13" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N13" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O13" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P13" s="6" t="n">
         <v/>
@@ -1601,91 +1603,93 @@
       <c r="Q13" s="6" t="n">
         <v/>
       </c>
-      <c r="R13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T13" s="8" t="inlineStr">
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U13" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T13" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U13" s="8" t="n">
+        <v/>
       </c>
       <c r="V13" s="8" t="n">
         <v/>
       </c>
-      <c r="W13" s="9" t="inlineStr">
+      <c r="W13" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C14" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D14" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E14" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F14" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H14" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I14" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J14" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K14" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L14" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M14" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N14" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O14" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P14" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q14" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R14" s="6" t="inlineStr">
         <is>
@@ -1694,7 +1698,7 @@
       </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T14" s="8" t="n">
@@ -1708,79 +1712,71 @@
       </c>
       <c r="W14" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C15" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D15" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E15" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F15" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H15" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I15" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J15" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K15" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L15" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M15" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N15" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O15" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P15" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q15" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R15" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
+      <c r="S15" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1794,7 +1790,7 @@
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="11" t="inlineStr">
+      <c r="W15" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1804,50 +1800,50 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C16" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D16" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E16" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F16" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H16" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I16" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J16" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K16" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L16" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M16" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N16" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O16" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1860,74 +1856,82 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S16" s="10" t="inlineStr">
+      <c r="S16" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T16" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U16" s="8" t="n">
-        <v/>
+      <c r="T16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U16" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="11" t="inlineStr">
+      <c r="W16" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr"/>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C17" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D17" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E17" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F17" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H17" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I17" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J17" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K17" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L17" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M17" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N17" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O17" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
@@ -1940,95 +1944,89 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S17" s="10" t="inlineStr">
+      <c r="S17" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U17" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T17" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U17" s="8" t="n">
+        <v/>
       </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
+      <c r="W17" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C18" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D18" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E18" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F18" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H18" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I18" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J18" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K18" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L18" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M18" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N18" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O18" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="n">
-        <v/>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R18" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S18" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -2042,7 +2040,7 @@
       <c r="V18" s="8" t="n">
         <v/>
       </c>
-      <c r="W18" s="11" t="inlineStr">
+      <c r="W18" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -2052,81 +2050,81 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C19" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D19" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E19" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F19" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H19" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I19" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J19" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K19" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L19" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M19" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N19" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O19" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
       </c>
-      <c r="Q19" s="6" t="inlineStr">
+      <c r="Q19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R19" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
-      </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
       <c r="W19" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X19" t="inlineStr"/>
@@ -2134,50 +2132,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C20" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D20" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E20" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F20" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H20" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I20" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J20" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K20" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L20" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M20" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N20" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O20" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,25 +2186,21 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U20" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U20" s="8" t="n">
+        <v/>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="9" t="inlineStr">
+      <c r="W20" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2216,50 +2210,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C21" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D21" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E21" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F21" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H21" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I21" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J21" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K21" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L21" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M21" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N21" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O21" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2270,21 +2264,25 @@
       <c r="R21" s="6" t="n">
         <v/>
       </c>
-      <c r="S21" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U21" s="8" t="n">
-        <v/>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U21" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V21" s="8" t="n">
         <v/>
       </c>
-      <c r="W21" s="9" t="inlineStr">
+      <c r="W21" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2294,50 +2292,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C22" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D22" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E22" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F22" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H22" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I22" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J22" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K22" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L22" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M22" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N22" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O22" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2348,7 +2346,7 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="7" t="inlineStr">
+      <c r="S22" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2363,10 +2361,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V22" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W22" s="9" t="inlineStr">
+      <c r="V22" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W22" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2376,50 +2376,50 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C23" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D23" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E23" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F23" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H23" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I23" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J23" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K23" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L23" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M23" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N23" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O23" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2432,78 +2432,76 @@
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U23" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V23" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W23" s="9" t="inlineStr">
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V23" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W23" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr"/>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C24" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D24" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E24" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F24" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H24" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I24" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J24" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K24" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L24" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M24" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N24" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O24" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2511,12 +2509,14 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S24" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T24" s="8" t="n">
@@ -2528,64 +2528,64 @@
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="9" t="inlineStr">
+      <c r="W24" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X24" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C25" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D25" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E25" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F25" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H25" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I25" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J25" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K25" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L25" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M25" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N25" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O25" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2593,83 +2593,81 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="inlineStr">
+      <c r="R25" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U25" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U25" s="8" t="n">
-        <v/>
-      </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="9" t="inlineStr">
+      <c r="W25" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C26" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D26" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E26" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F26" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H26" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I26" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J26" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K26" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L26" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M26" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N26" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O26" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2682,76 +2680,76 @@
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U26" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U26" s="8" t="n">
+        <v/>
       </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="9" t="inlineStr">
+      <c r="W26" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr"/>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C27" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D27" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E27" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F27" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H27" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I27" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J27" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K27" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L27" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M27" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N27" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O27" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2759,16 +2757,20 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S27" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="n">
-        <v/>
+      <c r="R27" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S27" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U27" s="8" t="n">
         <v/>
@@ -2776,64 +2778,64 @@
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="9" t="inlineStr">
+      <c r="W27" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X27" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C28" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D28" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E28" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F28" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H28" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I28" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J28" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K28" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L28" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M28" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N28" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O28" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2841,85 +2843,81 @@
       <c r="Q28" s="6" t="n">
         <v/>
       </c>
-      <c r="R28" s="6" t="inlineStr">
+      <c r="R28" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S28" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
+      <c r="U28" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U28" s="8" t="n">
-        <v/>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="9" t="inlineStr">
+      <c r="W28" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C29" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D29" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E29" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F29" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H29" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I29" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J29" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K29" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L29" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M29" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N29" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O29" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2930,25 +2928,25 @@
       <c r="R29" s="6" t="n">
         <v/>
       </c>
-      <c r="S29" s="7" t="inlineStr">
+      <c r="S29" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T29" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U29" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="9" t="inlineStr">
+      <c r="W29" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2958,50 +2956,50 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C30" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D30" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E30" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F30" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H30" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I30" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J30" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K30" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L30" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M30" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N30" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O30" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3012,78 +3010,78 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U30" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U30" s="8" t="n">
+        <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
+      <c r="W30" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X30" t="inlineStr"/>
+      <c r="X30" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C31" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D31" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E31" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F31" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G31" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H31" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I31" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J31" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K31" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L31" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M31" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N31" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O31" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P31" s="6" t="n">
         <v/>
@@ -3096,11 +3094,13 @@
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3108,7 +3108,7 @@
       <c r="V31" s="8" t="n">
         <v/>
       </c>
-      <c r="W31" s="9" t="inlineStr">
+      <c r="W31" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3122,70 +3122,74 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C32" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D32" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E32" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F32" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H32" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I32" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J32" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K32" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L32" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M32" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N32" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O32" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T32" s="8" t="inlineStr">
+        <v>30631.5</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S32" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T32" s="8" t="n">
+        <v/>
+      </c>
       <c r="U32" s="8" t="n">
         <v/>
       </c>
@@ -3194,81 +3198,71 @@
       </c>
       <c r="W32" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C33" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D33" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E33" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F33" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H33" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I33" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J33" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K33" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L33" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M33" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N33" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O33" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S33" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30728.5</v>
+      </c>
+      <c r="P33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R33" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S33" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3280,7 +3274,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="11" t="inlineStr">
+      <c r="W33" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3290,50 +3284,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C34" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D34" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E34" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F34" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H34" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I34" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J34" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K34" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L34" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M34" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N34" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O34" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3341,12 +3335,14 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S34" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S34" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3358,7 +3354,7 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="11" t="inlineStr">
+      <c r="W34" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3368,50 +3364,50 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C35" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D35" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E35" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F35" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H35" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I35" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J35" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K35" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L35" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M35" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N35" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O35" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
@@ -3419,14 +3415,12 @@
       <c r="Q35" s="6" t="n">
         <v/>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R35" s="6" t="n">
+        <v/>
       </c>
       <c r="S35" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3438,73 +3432,81 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="11" t="inlineStr">
+      <c r="W35" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C36" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D36" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E36" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F36" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H36" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I36" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J36" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K36" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L36" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M36" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N36" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O36" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R36" s="6" t="n">
-        <v/>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R36" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S36" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T36" s="8" t="n">
@@ -3516,146 +3518,144 @@
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="11" t="inlineStr">
+      <c r="W36" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C37" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D37" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E37" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F37" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H37" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I37" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J37" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K37" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L37" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M37" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N37" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O37" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
       </c>
-      <c r="Q37" s="6" t="inlineStr">
+      <c r="Q37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R37" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S37" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R37" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
       <c r="U37" s="8" t="n">
         <v/>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
+      <c r="W37" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X37" t="inlineStr"/>
+      <c r="X37" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C38" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D38" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E38" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F38" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H38" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I38" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J38" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K38" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L38" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M38" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N38" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O38" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3666,15 +3666,13 @@
       <c r="R38" s="6" t="n">
         <v/>
       </c>
-      <c r="S38" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S38" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="n">
+        <v/>
       </c>
       <c r="U38" s="8" t="n">
         <v/>
@@ -3682,64 +3680,64 @@
       <c r="V38" s="8" t="n">
         <v/>
       </c>
-      <c r="W38" s="11" t="inlineStr">
+      <c r="W38" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X38" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C39" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D39" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E39" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F39" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H39" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I39" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J39" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K39" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L39" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M39" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N39" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O39" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
@@ -3750,177 +3748,179 @@
       <c r="R39" s="6" t="n">
         <v/>
       </c>
-      <c r="S39" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U39" s="8" t="n">
-        <v/>
+      <c r="S39" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U39" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
       <c r="W39" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X39" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C40" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D40" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E40" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F40" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H40" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I40" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J40" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K40" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L40" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M40" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N40" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O40" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R40" s="6" t="n">
-        <v/>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R40" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T40" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U40" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T40" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U40" s="8" t="n">
+        <v/>
       </c>
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="9" t="inlineStr">
+      <c r="W40" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X40" t="inlineStr"/>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C41" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D41" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E41" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F41" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H41" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I41" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J41" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K41" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L41" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M41" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N41" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O41" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P41" s="6" t="n">
         <v/>
       </c>
-      <c r="Q41" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q41" s="6" t="n">
+        <v/>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S41" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S41" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3932,79 +3932,83 @@
       <c r="V41" s="8" t="n">
         <v/>
       </c>
-      <c r="W41" s="9" t="inlineStr">
+      <c r="W41" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C42" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D42" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E42" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F42" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H42" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I42" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J42" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K42" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L42" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M42" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N42" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O42" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P42" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q42" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R42" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S42" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S42" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4018,81 +4022,75 @@
       </c>
       <c r="W42" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C43" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D43" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E43" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F43" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H43" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I43" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J43" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K43" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L43" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M43" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N43" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O43" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P43" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R43" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S43" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30140.5</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R43" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S43" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T43" s="8" t="n">
@@ -4104,7 +4102,7 @@
       <c r="V43" s="8" t="n">
         <v/>
       </c>
-      <c r="W43" s="11" t="inlineStr">
+      <c r="W43" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4118,50 +4116,50 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C44" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D44" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E44" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F44" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H44" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I44" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J44" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K44" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L44" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M44" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N44" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O44" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4174,76 +4172,82 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V44" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W44" s="11" t="inlineStr">
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U44" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V44" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W44" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X44" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C45" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D45" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E45" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F45" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H45" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I45" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J45" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K45" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L45" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M45" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N45" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O45" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4254,27 +4258,21 @@
       <c r="R45" s="6" t="n">
         <v/>
       </c>
-      <c r="S45" s="7" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U45" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V45" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W45" s="11" t="inlineStr">
+      <c r="S45" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V45" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W45" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4288,50 +4286,50 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C46" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D46" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E46" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F46" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H46" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I46" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J46" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K46" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L46" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M46" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N46" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O46" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4339,16 +4337,20 @@
       <c r="Q46" s="6" t="n">
         <v/>
       </c>
-      <c r="R46" s="6" t="n">
-        <v/>
+      <c r="R46" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4356,64 +4358,64 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="11" t="inlineStr">
+      <c r="W46" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C47" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D47" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E47" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F47" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H47" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I47" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J47" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K47" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L47" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M47" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N47" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O47" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
@@ -4423,18 +4425,16 @@
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S47" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T47" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S47" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T47" s="8" t="n">
+        <v/>
       </c>
       <c r="U47" s="8" t="n">
         <v/>
@@ -4442,77 +4442,75 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="11" t="inlineStr">
+      <c r="W47" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X47" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C48" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D48" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E48" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F48" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H48" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I48" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J48" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K48" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L48" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M48" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N48" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O48" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="n">
-        <v/>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R48" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S48" s="10" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S48" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4526,7 +4524,7 @@
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="11" t="inlineStr">
+      <c r="W48" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4536,151 +4534,155 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C49" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D49" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E49" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F49" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H49" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I49" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J49" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K49" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L49" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M49" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N49" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O49" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="inlineStr">
+      <c r="Q49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R49" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S49" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R49" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="n">
-        <v/>
-      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="11" t="inlineStr">
+      <c r="W49" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr"/>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C50" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D50" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E50" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F50" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H50" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I50" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J50" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K50" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L50" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M50" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N50" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O50" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R50" s="6" t="n">
-        <v/>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R50" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S50" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T50" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T50" s="8" t="n">
+        <v/>
       </c>
       <c r="U50" s="8" t="n">
         <v/>
@@ -4688,79 +4690,73 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="11" t="inlineStr">
+      <c r="W50" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C51" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D51" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E51" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F51" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H51" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I51" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J51" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K51" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L51" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M51" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N51" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O51" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
       </c>
-      <c r="Q51" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q51" s="6" t="n">
+        <v/>
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S51" s="10" t="inlineStr">
+      <c r="S51" s="7" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -4774,60 +4770,64 @@
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="11" t="inlineStr">
+      <c r="W51" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X51" t="inlineStr"/>
+      <c r="X51" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C52" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D52" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E52" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F52" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H52" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I52" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J52" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K52" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L52" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M52" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N52" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O52" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4837,81 +4837,85 @@
       </c>
       <c r="R52" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S52" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U52" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S52" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U52" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V52" s="8" t="n">
         <v/>
       </c>
-      <c r="W52" s="11" t="inlineStr">
+      <c r="W52" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X52" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C53" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D53" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E53" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F53" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H53" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I53" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J53" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K53" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L53" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M53" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N53" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O53" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4919,24 +4923,22 @@
       <c r="Q53" s="6" t="n">
         <v/>
       </c>
-      <c r="R53" s="6" t="inlineStr">
+      <c r="R53" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S53" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T53" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S53" s="10" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T53" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V53" s="8" t="n">
@@ -4944,62 +4946,58 @@
       </c>
       <c r="W53" s="11" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X53" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>28967.5</v>
+        <v>29438.75</v>
       </c>
       <c r="C54" t="n">
-        <v>29498.25</v>
+        <v>29665.25</v>
       </c>
       <c r="D54" t="n">
-        <v>28957.75</v>
+        <v>29352.75</v>
       </c>
       <c r="E54" t="n">
-        <v>29446.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F54" t="n">
-        <v>483.25</v>
+        <v>166.93</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0057</v>
       </c>
       <c r="H54" t="n">
-        <v>540.5</v>
+        <v>312.5</v>
       </c>
       <c r="I54" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J54" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K54" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L54" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M54" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N54" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O54" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5010,25 +5008,23 @@
       <c r="R54" s="6" t="n">
         <v/>
       </c>
-      <c r="S54" s="7" t="inlineStr">
+      <c r="S54" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U54" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U54" s="8" t="n">
+        <v/>
+      </c>
       <c r="V54" s="8" t="n">
         <v/>
       </c>
-      <c r="W54" s="9" t="inlineStr">
+      <c r="W54" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5038,50 +5034,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29438.75</v>
+        <v>29938</v>
       </c>
       <c r="C55" t="n">
-        <v>29665.25</v>
+        <v>30862.75</v>
       </c>
       <c r="D55" t="n">
-        <v>29352.75</v>
+        <v>29904</v>
       </c>
       <c r="E55" t="n">
-        <v>29613.68</v>
+        <v>30784.75</v>
       </c>
       <c r="F55" t="n">
-        <v>166.93</v>
+        <v>1171.07</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0395</v>
       </c>
       <c r="H55" t="n">
-        <v>312.5</v>
+        <v>958.75</v>
       </c>
       <c r="I55" t="n">
-        <v>28417.25</v>
+        <v>29040.25</v>
       </c>
       <c r="J55" t="n">
-        <v>29015.62</v>
+        <v>29353.52</v>
       </c>
       <c r="K55" t="n">
-        <v>29176.5</v>
+        <v>29457.43</v>
       </c>
       <c r="L55" t="n">
-        <v>29337.38</v>
+        <v>29561.34</v>
       </c>
       <c r="M55" t="n">
-        <v>29717</v>
+        <v>29769.93</v>
       </c>
       <c r="N55" t="n">
-        <v>30096.62</v>
+        <v>29978.52</v>
       </c>
       <c r="O55" t="n">
-        <v>30038.75</v>
+        <v>29977.75</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5092,23 +5088,27 @@
       <c r="R55" s="6" t="n">
         <v/>
       </c>
-      <c r="S55" s="7" t="inlineStr">
+      <c r="S55" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U55" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V55" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W55" s="9" t="inlineStr">
+      <c r="V55" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W55" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5118,50 +5118,50 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>29938</v>
+        <v>30780</v>
       </c>
       <c r="C56" t="n">
-        <v>30862.75</v>
+        <v>31065.5</v>
       </c>
       <c r="D56" t="n">
-        <v>29904</v>
+        <v>30670</v>
       </c>
       <c r="E56" t="n">
-        <v>30784.75</v>
+        <v>31028.5</v>
       </c>
       <c r="F56" t="n">
-        <v>1171.07</v>
+        <v>243.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>958.75</v>
+        <v>395.5</v>
       </c>
       <c r="I56" t="n">
-        <v>29040.25</v>
+        <v>28945.25</v>
       </c>
       <c r="J56" t="n">
-        <v>29353.52</v>
+        <v>30026.69</v>
       </c>
       <c r="K56" t="n">
-        <v>29457.43</v>
+        <v>30305.38</v>
       </c>
       <c r="L56" t="n">
-        <v>29561.34</v>
+        <v>30584.06</v>
       </c>
       <c r="M56" t="n">
-        <v>29769.93</v>
+        <v>31264.12</v>
       </c>
       <c r="N56" t="n">
-        <v>29978.52</v>
+        <v>31944.19</v>
       </c>
       <c r="O56" t="n">
-        <v>29977.75</v>
+        <v>31821.5</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
@@ -5172,27 +5172,23 @@
       <c r="R56" s="6" t="n">
         <v/>
       </c>
-      <c r="S56" s="7" t="inlineStr">
+      <c r="S56" s="10" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T56" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U56" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V56" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W56" s="9" t="inlineStr">
+      <c r="U56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V56" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W56" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5202,69 +5198,71 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>30780</v>
+        <v>31008.5</v>
       </c>
       <c r="C57" t="n">
-        <v>31065.5</v>
+        <v>31094.75</v>
       </c>
       <c r="D57" t="n">
-        <v>30670</v>
+        <v>30642.75</v>
       </c>
       <c r="E57" t="n">
-        <v>31028.5</v>
+        <v>30764.75</v>
       </c>
       <c r="F57" t="n">
-        <v>243.75</v>
+        <v>-263.75</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H57" t="n">
-        <v>395.5</v>
+        <v>452</v>
       </c>
       <c r="I57" t="n">
-        <v>28945.25</v>
+        <v>30274.5</v>
       </c>
       <c r="J57" t="n">
-        <v>30026.69</v>
+        <v>30713.38</v>
       </c>
       <c r="K57" t="n">
-        <v>30305.38</v>
+        <v>30830.75</v>
       </c>
       <c r="L57" t="n">
-        <v>30584.06</v>
+        <v>30948.12</v>
       </c>
       <c r="M57" t="n">
-        <v>31264.12</v>
+        <v>31226.25</v>
       </c>
       <c r="N57" t="n">
-        <v>31944.19</v>
+        <v>31504.38</v>
       </c>
       <c r="O57" t="n">
-        <v>31821.5</v>
+        <v>31461</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R57" s="6" t="n">
-        <v/>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R57" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T57" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T57" s="8" t="n">
+        <v/>
       </c>
       <c r="U57" s="8" t="n">
         <v/>
@@ -5272,77 +5270,79 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="9" t="inlineStr">
+      <c r="W57" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X57" t="inlineStr"/>
+      <c r="X57" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>31008.5</v>
+        <v>30780</v>
       </c>
       <c r="C58" t="n">
-        <v>31094.75</v>
+        <v>30827.5</v>
       </c>
       <c r="D58" t="n">
-        <v>30642.75</v>
+        <v>30370</v>
       </c>
       <c r="E58" t="n">
-        <v>30764.75</v>
+        <v>30766.75</v>
       </c>
       <c r="F58" t="n">
-        <v>-263.75</v>
+        <v>2</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0001</v>
       </c>
       <c r="H58" t="n">
-        <v>452</v>
+        <v>457.5</v>
       </c>
       <c r="I58" t="n">
-        <v>30274.5</v>
+        <v>30190.75</v>
       </c>
       <c r="J58" t="n">
-        <v>30713.38</v>
+        <v>30260.75</v>
       </c>
       <c r="K58" t="n">
-        <v>30830.75</v>
+        <v>30538.75</v>
       </c>
       <c r="L58" t="n">
-        <v>30948.12</v>
+        <v>30816.75</v>
       </c>
       <c r="M58" t="n">
-        <v>31226.25</v>
+        <v>30990.75</v>
       </c>
       <c r="N58" t="n">
-        <v>31504.38</v>
+        <v>31164.75</v>
       </c>
       <c r="O58" t="n">
-        <v>31461</v>
+        <v>31546.75</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
       </c>
-      <c r="Q58" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q58" s="6" t="n">
+        <v/>
       </c>
       <c r="R58" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S58" s="10" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="S58" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T58" s="8" t="n">
@@ -5354,7 +5354,7 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="9" t="inlineStr">
+      <c r="W58" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5368,50 +5368,50 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>30780</v>
+        <v>30726.5</v>
       </c>
       <c r="C59" t="n">
-        <v>30827.5</v>
+        <v>30999.5</v>
       </c>
       <c r="D59" t="n">
-        <v>30370</v>
+        <v>30679</v>
       </c>
       <c r="E59" t="n">
-        <v>30766.75</v>
+        <v>30889.25</v>
       </c>
       <c r="F59" t="n">
-        <v>2</v>
+        <v>122.5</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H59" t="n">
-        <v>457.5</v>
+        <v>320.5</v>
       </c>
       <c r="I59" t="n">
-        <v>30190.75</v>
+        <v>29912.5</v>
       </c>
       <c r="J59" t="n">
-        <v>30260.75</v>
+        <v>30393.25</v>
       </c>
       <c r="K59" t="n">
-        <v>30538.75</v>
+        <v>30538</v>
       </c>
       <c r="L59" t="n">
-        <v>30816.75</v>
+        <v>30682.75</v>
       </c>
       <c r="M59" t="n">
-        <v>30990.75</v>
+        <v>30995.5</v>
       </c>
       <c r="N59" t="n">
-        <v>31164.75</v>
+        <v>31308.25</v>
       </c>
       <c r="O59" t="n">
-        <v>31546.75</v>
+        <v>31285</v>
       </c>
       <c r="P59" s="6" t="n">
         <v/>
@@ -5419,18 +5419,18 @@
       <c r="Q59" s="6" t="n">
         <v/>
       </c>
-      <c r="R59" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R59" s="6" t="n">
+        <v/>
       </c>
       <c r="S59" s="10" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U59" s="8" t="n">
         <v/>
@@ -5438,83 +5438,83 @@
       <c r="V59" s="8" t="n">
         <v/>
       </c>
-      <c r="W59" s="9" t="inlineStr">
+      <c r="W59" s="11" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X59" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>30726.5</v>
+        <v>30870</v>
       </c>
       <c r="C60" t="n">
-        <v>30999.5</v>
+        <v>30920.75</v>
       </c>
       <c r="D60" t="n">
-        <v>30679</v>
+        <v>30356.75</v>
       </c>
       <c r="E60" t="n">
-        <v>30889.25</v>
+        <v>30566.25</v>
       </c>
       <c r="F60" t="n">
-        <v>122.5</v>
+        <v>-323</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0105</v>
       </c>
       <c r="H60" t="n">
-        <v>320.5</v>
+        <v>564</v>
       </c>
       <c r="I60" t="n">
-        <v>29912.5</v>
+        <v>30358.5</v>
       </c>
       <c r="J60" t="n">
-        <v>30393.25</v>
+        <v>30593.75</v>
       </c>
       <c r="K60" t="n">
-        <v>30538</v>
+        <v>30729</v>
       </c>
       <c r="L60" t="n">
-        <v>30682.75</v>
+        <v>30864.25</v>
       </c>
       <c r="M60" t="n">
-        <v>30995.5</v>
+        <v>31049.5</v>
       </c>
       <c r="N60" t="n">
-        <v>31308.25</v>
+        <v>31234.75</v>
       </c>
       <c r="O60" t="n">
-        <v>31285</v>
-      </c>
-      <c r="P60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q60" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R60" s="6" t="n">
-        <v/>
+        <v>31320</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R60" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S60" s="7" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T60" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T60" s="8" t="n">
+        <v/>
       </c>
       <c r="U60" s="8" t="n">
         <v/>
@@ -5524,7 +5524,7 @@
       </c>
       <c r="W60" s="9" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X60" t="inlineStr"/>
@@ -5532,69 +5532,63 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>30870</v>
+        <v>30560.5</v>
       </c>
       <c r="C61" t="n">
-        <v>30920.75</v>
+        <v>30725.5</v>
       </c>
       <c r="D61" t="n">
-        <v>30356.75</v>
+        <v>30372.25</v>
       </c>
       <c r="E61" t="n">
-        <v>30566.25</v>
+        <v>30613.25</v>
       </c>
       <c r="F61" t="n">
-        <v>-323</v>
+        <v>47</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0015</v>
       </c>
       <c r="H61" t="n">
-        <v>564</v>
+        <v>353.25</v>
       </c>
       <c r="I61" t="n">
-        <v>30358.5</v>
+        <v>29792.75</v>
       </c>
       <c r="J61" t="n">
-        <v>30593.75</v>
+        <v>29966</v>
       </c>
       <c r="K61" t="n">
-        <v>30729</v>
+        <v>30284.25</v>
       </c>
       <c r="L61" t="n">
-        <v>30864.25</v>
+        <v>30602.5</v>
       </c>
       <c r="M61" t="n">
-        <v>31049.5</v>
+        <v>30848.25</v>
       </c>
       <c r="N61" t="n">
-        <v>31234.75</v>
+        <v>31094</v>
       </c>
       <c r="O61" t="n">
-        <v>31320</v>
-      </c>
-      <c r="P61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q61" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R61" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>31484.75</v>
+      </c>
+      <c r="P61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q61" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R61" s="6" t="n">
+        <v/>
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T61" s="8" t="n">
@@ -5606,60 +5600,64 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="11" t="inlineStr">
+      <c r="W61" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X61" t="inlineStr"/>
+      <c r="X61" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30657.25</v>
+        <v>30707</v>
       </c>
       <c r="C62" t="n">
-        <v>30697</v>
+        <v>30735.75</v>
       </c>
       <c r="D62" t="n">
-        <v>30655</v>
+        <v>30684.5</v>
       </c>
       <c r="E62" t="n">
-        <v>30695.25</v>
+        <v>30729.25</v>
       </c>
       <c r="F62" t="n">
-        <v>129</v>
+        <v>116</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0042</v>
+        <v>0.0038</v>
       </c>
       <c r="H62" t="n">
-        <v>42</v>
+        <v>51.25</v>
       </c>
       <c r="I62" t="n">
-        <v>29792.75</v>
+        <v>30019</v>
       </c>
       <c r="J62" t="n">
-        <v>29966</v>
+        <v>30292.19</v>
       </c>
       <c r="K62" t="n">
-        <v>30284.25</v>
+        <v>30436.62</v>
       </c>
       <c r="L62" t="n">
-        <v>30602.5</v>
+        <v>30581.06</v>
       </c>
       <c r="M62" t="n">
-        <v>30848.25</v>
+        <v>30789.88</v>
       </c>
       <c r="N62" t="n">
-        <v>31094</v>
+        <v>30998.69</v>
       </c>
       <c r="O62" t="n">
-        <v>31484.75</v>
+        <v>31078.75</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5670,13 +5668,15 @@
       <c r="R62" s="6" t="n">
         <v/>
       </c>
-      <c r="S62" s="7" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T62" s="8" t="n">
-        <v/>
+      <c r="S62" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T62" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U62" s="8" t="n">
         <v/>
@@ -5684,14 +5684,14 @@
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="11" t="inlineStr">
+      <c r="W62" s="9" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X62"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -5618,25 +5618,25 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30707</v>
+        <v>30657.25</v>
       </c>
       <c r="C62" t="n">
-        <v>30735.75</v>
+        <v>30906</v>
       </c>
       <c r="D62" t="n">
-        <v>30684.5</v>
+        <v>30512.25</v>
       </c>
       <c r="E62" t="n">
-        <v>30729.25</v>
+        <v>30698.75</v>
       </c>
       <c r="F62" t="n">
-        <v>116</v>
+        <v>85.5</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0038</v>
+        <v>0.0028</v>
       </c>
       <c r="H62" t="n">
-        <v>51.25</v>
+        <v>393.75</v>
       </c>
       <c r="I62" t="n">
         <v>30019</v>
@@ -5692,6 +5692,88 @@
       <c r="X62" t="inlineStr">
         <is>
           <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="B63" t="n">
+        <v>30771.25</v>
+      </c>
+      <c r="C63" t="n">
+        <v>30790</v>
+      </c>
+      <c r="D63" t="n">
+        <v>30760.25</v>
+      </c>
+      <c r="E63" t="n">
+        <v>30786.75</v>
+      </c>
+      <c r="F63" t="n">
+        <v>88</v>
+      </c>
+      <c r="G63" s="5" t="n">
+        <v>0.0029</v>
+      </c>
+      <c r="H63" t="n">
+        <v>29.75</v>
+      </c>
+      <c r="I63" t="n">
+        <v>30118.5</v>
+      </c>
+      <c r="J63" t="n">
+        <v>30299.81</v>
+      </c>
+      <c r="K63" t="n">
+        <v>30501.88</v>
+      </c>
+      <c r="L63" t="n">
+        <v>30703.94</v>
+      </c>
+      <c r="M63" t="n">
+        <v>30895.62</v>
+      </c>
+      <c r="N63" t="n">
+        <v>31087.31</v>
+      </c>
+      <c r="O63" t="n">
+        <v>31299.75</v>
+      </c>
+      <c r="P63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R63" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S63" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="9" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>中警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -110,11 +110,11 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X63"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,69 +634,65 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-07</t>
+          <t>2026-07-08</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29960</v>
+        <v>29373.75</v>
       </c>
       <c r="C2" t="n">
-        <v>29973.75</v>
+        <v>29558.75</v>
       </c>
       <c r="D2" t="n">
-        <v>29210</v>
+        <v>28909.75</v>
       </c>
       <c r="E2" t="n">
-        <v>29391.5</v>
+        <v>29468.5</v>
       </c>
       <c r="F2" t="n">
-        <v>-549.5</v>
+        <v>77</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>-0.0184</v>
+        <v>0.0026</v>
       </c>
       <c r="H2" t="n">
-        <v>763.75</v>
+        <v>649</v>
       </c>
       <c r="I2" t="n">
-        <v>29272</v>
+        <v>28446.25</v>
       </c>
       <c r="J2" t="n">
-        <v>29556.25</v>
+        <v>28527.56</v>
       </c>
       <c r="K2" t="n">
-        <v>29735.5</v>
+        <v>29009.62</v>
       </c>
       <c r="L2" t="n">
-        <v>29914.75</v>
+        <v>29491.69</v>
       </c>
       <c r="M2" t="n">
-        <v>30146.5</v>
+        <v>29773.38</v>
       </c>
       <c r="N2" t="n">
-        <v>30378.25</v>
+        <v>30055.06</v>
       </c>
       <c r="O2" t="n">
-        <v>30505</v>
-      </c>
-      <c r="P2" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q2" s="6" t="inlineStr">
+        <v>30737.5</v>
+      </c>
+      <c r="P2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q2" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R2" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T2" s="8" t="n">
@@ -710,58 +706,62 @@
       </c>
       <c r="W2" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr"/>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C3" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D3" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E3" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F3" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H3" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I3" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J3" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K3" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L3" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M3" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N3" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O3" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -769,18 +769,18 @@
       <c r="Q3" s="6" t="n">
         <v/>
       </c>
-      <c r="R3" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S3" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T3" s="8" t="n">
-        <v/>
+      <c r="R3" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S3" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T3" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U3" s="8" t="n">
         <v/>
@@ -790,62 +790,58 @@
       </c>
       <c r="W3" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C4" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D4" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E4" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F4" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H4" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I4" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J4" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K4" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L4" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M4" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N4" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O4" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P4" s="6" t="n">
         <v/>
@@ -874,230 +870,226 @@
       </c>
       <c r="W4" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C5" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D5" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E5" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F5" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H5" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I5" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J5" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K5" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L5" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M5" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N5" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O5" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R5" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S5" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="inlineStr">
+        <v>30480.5</v>
+      </c>
+      <c r="P5" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="Q5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R5" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="n">
+        <v/>
+      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
       <c r="V5" s="8" t="n">
         <v/>
       </c>
-      <c r="W5" s="9" t="inlineStr">
+      <c r="W5" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C6" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D6" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E6" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F6" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H6" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I6" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J6" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K6" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L6" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M6" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N6" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O6" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P6" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R6" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S6" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R6" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S6" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="n">
-        <v/>
-      </c>
       <c r="U6" s="8" t="n">
         <v/>
       </c>
       <c r="V6" s="8" t="n">
         <v/>
       </c>
-      <c r="W6" s="9" t="inlineStr">
+      <c r="W6" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C7" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D7" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E7" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F7" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H7" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I7" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J7" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K7" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L7" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M7" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N7" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O7" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1105,18 +1097,18 @@
       <c r="Q7" s="6" t="n">
         <v/>
       </c>
-      <c r="R7" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S7" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T7" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R7" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S7" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T7" s="8" t="n">
+        <v/>
       </c>
       <c r="U7" s="8" t="n">
         <v/>
@@ -1124,64 +1116,64 @@
       <c r="V7" s="8" t="n">
         <v/>
       </c>
-      <c r="W7" s="9" t="inlineStr">
+      <c r="W7" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C8" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D8" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E8" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F8" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H8" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I8" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J8" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K8" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L8" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M8" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N8" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O8" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1191,12 +1183,12 @@
       </c>
       <c r="R8" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S8" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T8" s="8" t="n">
@@ -1208,64 +1200,60 @@
       <c r="V8" s="8" t="n">
         <v/>
       </c>
-      <c r="W8" s="9" t="inlineStr">
+      <c r="W8" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C9" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D9" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E9" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F9" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H9" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I9" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J9" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K9" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L9" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M9" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N9" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O9" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1292,7 +1280,7 @@
       <c r="V9" s="8" t="n">
         <v/>
       </c>
-      <c r="W9" s="9" t="inlineStr">
+      <c r="W9" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1302,50 +1290,50 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C10" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D10" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E10" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F10" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H10" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I10" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J10" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K10" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L10" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M10" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N10" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O10" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1353,18 +1341,18 @@
       <c r="Q10" s="6" t="n">
         <v/>
       </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R10" s="6" t="n">
+        <v/>
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T10" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T10" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U10" s="8" t="n">
         <v/>
@@ -1372,60 +1360,64 @@
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="9" t="inlineStr">
+      <c r="W10" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X10" t="inlineStr"/>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C11" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D11" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E11" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F11" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H11" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I11" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J11" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K11" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L11" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M11" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N11" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O11" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1436,9 +1428,9 @@
       <c r="R11" s="6" t="n">
         <v/>
       </c>
-      <c r="S11" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="S11" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
         </is>
       </c>
       <c r="T11" s="8" t="inlineStr">
@@ -1446,70 +1438,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="n">
-        <v/>
+      <c r="U11" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
       </c>
       <c r="W11" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C12" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D12" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E12" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F12" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H12" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I12" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J12" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K12" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L12" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M12" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N12" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O12" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P12" s="6" t="n">
         <v/>
@@ -1517,100 +1511,102 @@
       <c r="Q12" s="6" t="n">
         <v/>
       </c>
-      <c r="R12" s="6" t="n">
-        <v/>
+      <c r="R12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T12" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U12" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T12" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U12" s="8" t="n">
+        <v/>
       </c>
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="11" t="inlineStr">
+      <c r="W12" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C13" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D13" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E13" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F13" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H13" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I13" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J13" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K13" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L13" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M13" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N13" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O13" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P13" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q13" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R13" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="S13" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T13" s="8" t="n">
@@ -1624,78 +1620,70 @@
       </c>
       <c r="W13" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C14" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D14" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E14" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F14" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H14" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I14" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J14" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K14" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L14" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M14" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N14" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O14" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P14" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q14" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R14" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="S14" s="7" t="inlineStr">
         <is>
           <t>↓</t>
@@ -1710,7 +1698,7 @@
       <c r="V14" s="8" t="n">
         <v/>
       </c>
-      <c r="W14" s="9" t="inlineStr">
+      <c r="W14" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1720,50 +1708,50 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C15" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D15" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E15" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F15" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H15" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I15" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J15" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K15" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L15" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M15" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N15" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O15" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1781,69 +1769,77 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T15" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U15" s="8" t="n">
-        <v/>
+      <c r="T15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U15" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
       </c>
-      <c r="W15" s="9" t="inlineStr">
+      <c r="W15" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr"/>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C16" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D16" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E16" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F16" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H16" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I16" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J16" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K16" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L16" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M16" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N16" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O16" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
@@ -1861,87 +1857,81 @@
           <t>↓</t>
         </is>
       </c>
-      <c r="T16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U16" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T16" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U16" s="8" t="n">
+        <v/>
       </c>
       <c r="V16" s="8" t="n">
         <v/>
       </c>
-      <c r="W16" s="9" t="inlineStr">
+      <c r="W16" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C17" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D17" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E17" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F17" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H17" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I17" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J17" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K17" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L17" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M17" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N17" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O17" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="n">
-        <v/>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R17" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S17" s="7" t="inlineStr">
@@ -1958,7 +1948,7 @@
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="9" t="inlineStr">
+      <c r="W17" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -1968,81 +1958,81 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C18" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D18" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E18" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F18" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H18" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I18" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J18" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K18" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L18" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M18" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N18" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O18" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
       </c>
-      <c r="Q18" s="6" t="inlineStr">
+      <c r="Q18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R18" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U18" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S18" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U18" s="8" t="n">
-        <v/>
-      </c>
       <c r="V18" s="8" t="n">
         <v/>
       </c>
       <c r="W18" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
+          <t>多方</t>
         </is>
       </c>
       <c r="X18" t="inlineStr"/>
@@ -2050,50 +2040,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C19" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D19" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E19" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F19" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H19" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I19" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J19" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K19" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L19" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M19" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N19" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O19" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2106,23 +2096,19 @@
       </c>
       <c r="S19" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U19" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U19" s="8" t="n">
+        <v/>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
       </c>
-      <c r="W19" s="11" t="inlineStr">
+      <c r="W19" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2132,50 +2118,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C20" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D20" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E20" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F20" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H20" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I20" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J20" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K20" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L20" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M20" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N20" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O20" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2188,19 +2174,23 @@
       </c>
       <c r="S20" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T20" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U20" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U20" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V20" s="8" t="n">
         <v/>
       </c>
-      <c r="W20" s="11" t="inlineStr">
+      <c r="W20" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2210,50 +2200,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C21" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D21" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E21" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F21" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H21" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I21" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J21" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K21" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L21" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M21" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N21" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O21" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2279,10 +2269,12 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V21" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W21" s="11" t="inlineStr">
+      <c r="V21" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2292,50 +2284,50 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C22" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D22" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E22" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F22" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H22" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I22" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J22" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K22" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L22" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M22" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N22" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O22" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2346,80 +2338,78 @@
       <c r="R22" s="6" t="n">
         <v/>
       </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U22" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V22" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W22" s="11" t="inlineStr">
+      <c r="S22" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V22" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W22" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X22" t="inlineStr"/>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C23" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D23" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E23" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F23" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H23" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I23" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J23" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K23" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L23" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M23" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N23" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O23" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2427,12 +2417,14 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="n">
-        <v/>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S23" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T23" s="8" t="n">
@@ -2444,64 +2436,64 @@
       <c r="V23" s="8" t="n">
         <v/>
       </c>
-      <c r="W23" s="11" t="inlineStr">
+      <c r="W23" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C24" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D24" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E24" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F24" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H24" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I24" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J24" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K24" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L24" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M24" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N24" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O24" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2509,83 +2501,81 @@
       <c r="Q24" s="6" t="n">
         <v/>
       </c>
-      <c r="R24" s="6" t="inlineStr">
+      <c r="R24" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U24" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U24" s="8" t="n">
-        <v/>
-      </c>
       <c r="V24" s="8" t="n">
         <v/>
       </c>
-      <c r="W24" s="11" t="inlineStr">
+      <c r="W24" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C25" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D25" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E25" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F25" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H25" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I25" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J25" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K25" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L25" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M25" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N25" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O25" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2596,78 +2586,78 @@
       <c r="R25" s="6" t="n">
         <v/>
       </c>
-      <c r="S25" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U25" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S25" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U25" s="8" t="n">
+        <v/>
       </c>
       <c r="V25" s="8" t="n">
         <v/>
       </c>
-      <c r="W25" s="11" t="inlineStr">
+      <c r="W25" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X25" t="inlineStr"/>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C26" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D26" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E26" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F26" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H26" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I26" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J26" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K26" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L26" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M26" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N26" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O26" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2675,16 +2665,20 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="n">
-        <v/>
+      <c r="R26" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S26" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="n">
-        <v/>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U26" s="8" t="n">
         <v/>
@@ -2692,64 +2686,64 @@
       <c r="V26" s="8" t="n">
         <v/>
       </c>
-      <c r="W26" s="11" t="inlineStr">
+      <c r="W26" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C27" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D27" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E27" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F27" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H27" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I27" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J27" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K27" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L27" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M27" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N27" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O27" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2757,85 +2751,81 @@
       <c r="Q27" s="6" t="n">
         <v/>
       </c>
-      <c r="R27" s="6" t="inlineStr">
+      <c r="R27" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S27" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T27" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S27" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T27" s="8" t="inlineStr">
+      <c r="U27" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U27" s="8" t="n">
-        <v/>
-      </c>
       <c r="V27" s="8" t="n">
         <v/>
       </c>
-      <c r="W27" s="11" t="inlineStr">
+      <c r="W27" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C28" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D28" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E28" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F28" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H28" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I28" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J28" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K28" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L28" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M28" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N28" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O28" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2853,18 +2843,18 @@
       </c>
       <c r="T28" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U28" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="V28" s="8" t="n">
         <v/>
       </c>
-      <c r="W28" s="11" t="inlineStr">
+      <c r="W28" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -2874,50 +2864,50 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C29" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D29" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E29" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F29" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G29" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H29" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I29" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J29" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K29" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L29" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M29" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N29" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O29" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2930,76 +2920,76 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U29" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U29" s="8" t="n">
+        <v/>
       </c>
       <c r="V29" s="8" t="n">
         <v/>
       </c>
-      <c r="W29" s="11" t="inlineStr">
+      <c r="W29" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X29" t="inlineStr"/>
+      <c r="X29" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C30" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D30" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E30" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F30" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G30" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H30" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I30" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J30" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K30" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L30" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M30" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N30" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O30" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P30" s="6" t="n">
         <v/>
@@ -3010,13 +3000,15 @@
       <c r="R30" s="6" t="n">
         <v/>
       </c>
-      <c r="S30" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="n">
-        <v/>
+      <c r="S30" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U30" s="8" t="n">
         <v/>
@@ -3024,7 +3016,7 @@
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="11" t="inlineStr">
+      <c r="W30" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -3038,69 +3030,73 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C31" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D31" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E31" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F31" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H31" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I31" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J31" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K31" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L31" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M31" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N31" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O31" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q31" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R31" s="6" t="n">
-        <v/>
+        <v>30631.5</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R31" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S31" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T31" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T31" s="8" t="n">
+        <v/>
       </c>
       <c r="U31" s="8" t="n">
         <v/>
@@ -3110,81 +3106,71 @@
       </c>
       <c r="W31" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C32" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D32" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E32" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F32" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H32" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I32" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J32" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K32" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L32" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M32" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N32" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O32" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q32" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R32" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30728.5</v>
+      </c>
+      <c r="P32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q32" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R32" s="6" t="n">
+        <v/>
       </c>
       <c r="S32" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3196,7 +3182,7 @@
       <c r="V32" s="8" t="n">
         <v/>
       </c>
-      <c r="W32" s="9" t="inlineStr">
+      <c r="W32" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3206,50 +3192,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C33" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D33" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E33" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F33" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H33" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I33" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J33" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K33" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L33" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M33" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N33" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O33" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3257,12 +3243,14 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="n">
-        <v/>
+      <c r="R33" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3274,7 +3262,7 @@
       <c r="V33" s="8" t="n">
         <v/>
       </c>
-      <c r="W33" s="9" t="inlineStr">
+      <c r="W33" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -3284,50 +3272,50 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C34" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D34" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E34" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F34" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H34" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I34" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J34" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K34" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L34" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M34" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N34" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O34" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
@@ -3335,14 +3323,12 @@
       <c r="Q34" s="6" t="n">
         <v/>
       </c>
-      <c r="R34" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S34" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+      <c r="R34" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S34" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3354,73 +3340,81 @@
       <c r="V34" s="8" t="n">
         <v/>
       </c>
-      <c r="W34" s="9" t="inlineStr">
+      <c r="W34" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr"/>
+      <c r="X34" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C35" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D35" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E35" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F35" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H35" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I35" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J35" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K35" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L35" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M35" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N35" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O35" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R35" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S35" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R35" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T35" s="8" t="n">
@@ -3432,146 +3426,144 @@
       <c r="V35" s="8" t="n">
         <v/>
       </c>
-      <c r="W35" s="9" t="inlineStr">
+      <c r="W35" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C36" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D36" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E36" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F36" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H36" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I36" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J36" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K36" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L36" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M36" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N36" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O36" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
       </c>
-      <c r="Q36" s="6" t="inlineStr">
+      <c r="Q36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R36" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S36" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R36" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S36" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="n">
-        <v/>
-      </c>
       <c r="U36" s="8" t="n">
         <v/>
       </c>
       <c r="V36" s="8" t="n">
         <v/>
       </c>
-      <c r="W36" s="9" t="inlineStr">
+      <c r="W36" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X36" t="inlineStr"/>
+      <c r="X36" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C37" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D37" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E37" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F37" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H37" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I37" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J37" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K37" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L37" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M37" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N37" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O37" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3584,13 +3576,11 @@
       </c>
       <c r="S37" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="n">
+        <v/>
       </c>
       <c r="U37" s="8" t="n">
         <v/>
@@ -3598,64 +3588,64 @@
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="9" t="inlineStr">
+      <c r="W37" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X37" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C38" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D38" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E38" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F38" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H38" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I38" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J38" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K38" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L38" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M38" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N38" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O38" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
@@ -3668,166 +3658,168 @@
       </c>
       <c r="S38" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T38" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U38" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T38" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U38" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V38" s="8" t="n">
         <v/>
       </c>
       <c r="W38" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X38" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C39" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D39" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E39" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F39" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G39" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H39" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I39" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J39" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K39" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L39" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M39" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N39" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O39" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P39" s="6" t="n">
         <v/>
       </c>
-      <c r="Q39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R39" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S39" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T39" s="8" t="inlineStr">
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R39" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U39" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S39" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T39" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U39" s="8" t="n">
+        <v/>
       </c>
       <c r="V39" s="8" t="n">
         <v/>
       </c>
-      <c r="W39" s="11" t="inlineStr">
+      <c r="W39" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X39" t="inlineStr"/>
+      <c r="X39" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>29635.5</v>
+        <v>29540</v>
       </c>
       <c r="C40" t="n">
-        <v>29811.5</v>
+        <v>29546.25</v>
       </c>
       <c r="D40" t="n">
-        <v>29436.25</v>
+        <v>29273.5</v>
       </c>
       <c r="E40" t="n">
-        <v>29491.75</v>
+        <v>29513</v>
       </c>
       <c r="F40" t="n">
-        <v>-204</v>
+        <v>21.25</v>
       </c>
       <c r="G40" s="5" t="n">
-        <v>-0.0069</v>
+        <v>0.0007</v>
       </c>
       <c r="H40" t="n">
-        <v>375.25</v>
+        <v>272.75</v>
       </c>
       <c r="I40" t="n">
-        <v>29095.5</v>
+        <v>29061</v>
       </c>
       <c r="J40" t="n">
-        <v>29459.94</v>
+        <v>29050.44</v>
       </c>
       <c r="K40" t="n">
-        <v>29542.62</v>
+        <v>29304.12</v>
       </c>
       <c r="L40" t="n">
-        <v>29625.31</v>
+        <v>29557.81</v>
       </c>
       <c r="M40" t="n">
-        <v>29848.88</v>
+        <v>29679.38</v>
       </c>
       <c r="N40" t="n">
-        <v>30072.44</v>
+        <v>29800.94</v>
       </c>
       <c r="O40" t="n">
-        <v>30014.25</v>
+        <v>30186.75</v>
       </c>
       <c r="P40" s="6" t="n">
         <v/>
       </c>
-      <c r="Q40" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q40" s="6" t="n">
+        <v/>
       </c>
       <c r="R40" s="6" t="inlineStr">
         <is>
@@ -3836,7 +3828,7 @@
       </c>
       <c r="S40" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T40" s="8" t="n">
@@ -3848,70 +3840,74 @@
       <c r="V40" s="8" t="n">
         <v/>
       </c>
-      <c r="W40" s="11" t="inlineStr">
+      <c r="W40" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
       <c r="X40" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>29540</v>
+        <v>29518.25</v>
       </c>
       <c r="C41" t="n">
-        <v>29546.25</v>
+        <v>29571.25</v>
       </c>
       <c r="D41" t="n">
-        <v>29273.5</v>
+        <v>29002</v>
       </c>
       <c r="E41" t="n">
-        <v>29513</v>
+        <v>29125.5</v>
       </c>
       <c r="F41" t="n">
-        <v>21.25</v>
+        <v>-387.5</v>
       </c>
       <c r="G41" s="5" t="n">
-        <v>0.0007</v>
+        <v>-0.0131</v>
       </c>
       <c r="H41" t="n">
-        <v>272.75</v>
+        <v>569.25</v>
       </c>
       <c r="I41" t="n">
-        <v>29061</v>
+        <v>29000.75</v>
       </c>
       <c r="J41" t="n">
-        <v>29050.44</v>
+        <v>29291.81</v>
       </c>
       <c r="K41" t="n">
-        <v>29304.12</v>
+        <v>29376.62</v>
       </c>
       <c r="L41" t="n">
-        <v>29557.81</v>
+        <v>29461.44</v>
       </c>
       <c r="M41" t="n">
-        <v>29679.38</v>
+        <v>29649.38</v>
       </c>
       <c r="N41" t="n">
-        <v>29800.94</v>
+        <v>29837.31</v>
       </c>
       <c r="O41" t="n">
-        <v>30186.75</v>
-      </c>
-      <c r="P41" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q41" s="6" t="n">
-        <v/>
+        <v>29819</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R41" s="6" t="inlineStr">
         <is>
@@ -3920,7 +3916,7 @@
       </c>
       <c r="S41" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T41" s="8" t="n">
@@ -3934,81 +3930,75 @@
       </c>
       <c r="W41" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>29518.25</v>
+        <v>29136.5</v>
       </c>
       <c r="C42" t="n">
-        <v>29571.25</v>
+        <v>29213</v>
       </c>
       <c r="D42" t="n">
-        <v>29002</v>
+        <v>28927.25</v>
       </c>
       <c r="E42" t="n">
-        <v>29125.5</v>
+        <v>29186.25</v>
       </c>
       <c r="F42" t="n">
-        <v>-387.5</v>
+        <v>60.75</v>
       </c>
       <c r="G42" s="5" t="n">
-        <v>-0.0131</v>
+        <v>0.0021</v>
       </c>
       <c r="H42" t="n">
-        <v>569.25</v>
+        <v>285.75</v>
       </c>
       <c r="I42" t="n">
-        <v>29000.75</v>
+        <v>28432.75</v>
       </c>
       <c r="J42" t="n">
-        <v>29291.81</v>
+        <v>28475.69</v>
       </c>
       <c r="K42" t="n">
-        <v>29376.62</v>
+        <v>28840.88</v>
       </c>
       <c r="L42" t="n">
-        <v>29461.44</v>
+        <v>29206.06</v>
       </c>
       <c r="M42" t="n">
-        <v>29649.38</v>
+        <v>29410.12</v>
       </c>
       <c r="N42" t="n">
-        <v>29837.31</v>
+        <v>29614.19</v>
       </c>
       <c r="O42" t="n">
-        <v>29819</v>
-      </c>
-      <c r="P42" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="Q42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R42" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+        <v>30140.5</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q42" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R42" s="6" t="n">
+        <v/>
       </c>
       <c r="S42" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T42" s="8" t="n">
@@ -4020,7 +4010,7 @@
       <c r="V42" s="8" t="n">
         <v/>
       </c>
-      <c r="W42" s="9" t="inlineStr">
+      <c r="W42" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4034,50 +4024,50 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>29136.5</v>
+        <v>29177</v>
       </c>
       <c r="C43" t="n">
-        <v>29213</v>
+        <v>29584.25</v>
       </c>
       <c r="D43" t="n">
-        <v>28927.25</v>
+        <v>29075</v>
       </c>
       <c r="E43" t="n">
-        <v>29186.25</v>
+        <v>29524.75</v>
       </c>
       <c r="F43" t="n">
-        <v>60.75</v>
+        <v>338.5</v>
       </c>
       <c r="G43" s="5" t="n">
-        <v>0.0021</v>
+        <v>0.0116</v>
       </c>
       <c r="H43" t="n">
-        <v>285.75</v>
+        <v>509.25</v>
       </c>
       <c r="I43" t="n">
-        <v>28432.75</v>
+        <v>28641.5</v>
       </c>
       <c r="J43" t="n">
-        <v>28475.69</v>
+        <v>28958.56</v>
       </c>
       <c r="K43" t="n">
-        <v>28840.88</v>
+        <v>29043.38</v>
       </c>
       <c r="L43" t="n">
-        <v>29206.06</v>
+        <v>29128.19</v>
       </c>
       <c r="M43" t="n">
-        <v>29410.12</v>
+        <v>29329.12</v>
       </c>
       <c r="N43" t="n">
-        <v>29614.19</v>
+        <v>29530.06</v>
       </c>
       <c r="O43" t="n">
-        <v>30140.5</v>
+        <v>29498.75</v>
       </c>
       <c r="P43" s="6" t="n">
         <v/>
@@ -4088,78 +4078,84 @@
       <c r="R43" s="6" t="n">
         <v/>
       </c>
-      <c r="S43" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V43" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W43" s="9" t="inlineStr">
+      <c r="S43" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U43" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="V43" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W43" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>29177</v>
+        <v>29505</v>
       </c>
       <c r="C44" t="n">
-        <v>29584.25</v>
+        <v>29704.5</v>
       </c>
       <c r="D44" t="n">
-        <v>29075</v>
+        <v>29468</v>
       </c>
       <c r="E44" t="n">
-        <v>29524.75</v>
+        <v>29565.25</v>
       </c>
       <c r="F44" t="n">
-        <v>338.5</v>
+        <v>40.5</v>
       </c>
       <c r="G44" s="5" t="n">
-        <v>0.0116</v>
+        <v>0.0014</v>
       </c>
       <c r="H44" t="n">
-        <v>509.25</v>
+        <v>236.5</v>
       </c>
       <c r="I44" t="n">
-        <v>28641.5</v>
+        <v>28565.75</v>
       </c>
       <c r="J44" t="n">
-        <v>28958.56</v>
+        <v>29113.06</v>
       </c>
       <c r="K44" t="n">
-        <v>29043.38</v>
+        <v>29270.12</v>
       </c>
       <c r="L44" t="n">
-        <v>29128.19</v>
+        <v>29427.19</v>
       </c>
       <c r="M44" t="n">
-        <v>29329.12</v>
+        <v>29779.38</v>
       </c>
       <c r="N44" t="n">
-        <v>29530.06</v>
+        <v>30131.56</v>
       </c>
       <c r="O44" t="n">
-        <v>29498.75</v>
+        <v>30093.5</v>
       </c>
       <c r="P44" s="6" t="n">
         <v/>
@@ -4172,25 +4168,19 @@
       </c>
       <c r="S44" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U44" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V44" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W44" s="9" t="inlineStr">
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V44" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W44" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4204,50 +4194,50 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>29505</v>
+        <v>29535.25</v>
       </c>
       <c r="C45" t="n">
-        <v>29704.5</v>
+        <v>29764.75</v>
       </c>
       <c r="D45" t="n">
-        <v>29468</v>
+        <v>29424.75</v>
       </c>
       <c r="E45" t="n">
-        <v>29565.25</v>
+        <v>29538.75</v>
       </c>
       <c r="F45" t="n">
-        <v>40.5</v>
+        <v>-26.5</v>
       </c>
       <c r="G45" s="5" t="n">
-        <v>0.0014</v>
+        <v>-0.0009</v>
       </c>
       <c r="H45" t="n">
-        <v>236.5</v>
+        <v>340</v>
       </c>
       <c r="I45" t="n">
-        <v>28565.75</v>
+        <v>29231.5</v>
       </c>
       <c r="J45" t="n">
-        <v>29113.06</v>
+        <v>29318.25</v>
       </c>
       <c r="K45" t="n">
-        <v>29270.12</v>
+        <v>29447</v>
       </c>
       <c r="L45" t="n">
-        <v>29427.19</v>
+        <v>29575.75</v>
       </c>
       <c r="M45" t="n">
-        <v>29779.38</v>
+        <v>29683.5</v>
       </c>
       <c r="N45" t="n">
-        <v>30131.56</v>
+        <v>29791.25</v>
       </c>
       <c r="O45" t="n">
-        <v>30093.5</v>
+        <v>29941</v>
       </c>
       <c r="P45" s="6" t="n">
         <v/>
@@ -4255,16 +4245,20 @@
       <c r="Q45" s="6" t="n">
         <v/>
       </c>
-      <c r="R45" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S45" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T45" s="8" t="n">
-        <v/>
+      <c r="R45" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S45" s="7" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T45" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U45" s="8" t="n">
         <v/>
@@ -4272,64 +4266,64 @@
       <c r="V45" s="8" t="n">
         <v/>
       </c>
-      <c r="W45" s="9" t="inlineStr">
+      <c r="W45" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X45" t="inlineStr">
         <is>
-          <t>強警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>29535.25</v>
+        <v>29526.5</v>
       </c>
       <c r="C46" t="n">
-        <v>29764.75</v>
+        <v>29633.75</v>
       </c>
       <c r="D46" t="n">
-        <v>29424.75</v>
+        <v>29333</v>
       </c>
       <c r="E46" t="n">
-        <v>29538.75</v>
+        <v>29448.75</v>
       </c>
       <c r="F46" t="n">
-        <v>-26.5</v>
+        <v>-90</v>
       </c>
       <c r="G46" s="5" t="n">
-        <v>-0.0009</v>
+        <v>-0.003</v>
       </c>
       <c r="H46" t="n">
-        <v>340</v>
+        <v>300.75</v>
       </c>
       <c r="I46" t="n">
-        <v>29231.5</v>
+        <v>29084.75</v>
       </c>
       <c r="J46" t="n">
-        <v>29318.25</v>
+        <v>29170.75</v>
       </c>
       <c r="K46" t="n">
-        <v>29447</v>
+        <v>29368.75</v>
       </c>
       <c r="L46" t="n">
-        <v>29575.75</v>
+        <v>29566.75</v>
       </c>
       <c r="M46" t="n">
-        <v>29683.5</v>
+        <v>29708.75</v>
       </c>
       <c r="N46" t="n">
-        <v>29791.25</v>
+        <v>29850.75</v>
       </c>
       <c r="O46" t="n">
-        <v>29941</v>
+        <v>30104.75</v>
       </c>
       <c r="P46" s="6" t="n">
         <v/>
@@ -4339,18 +4333,16 @@
       </c>
       <c r="R46" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="S46" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T46" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T46" s="8" t="n">
+        <v/>
       </c>
       <c r="U46" s="8" t="n">
         <v/>
@@ -4358,74 +4350,72 @@
       <c r="V46" s="8" t="n">
         <v/>
       </c>
-      <c r="W46" s="9" t="inlineStr">
+      <c r="W46" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X46" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>29526.5</v>
+        <v>29458.5</v>
       </c>
       <c r="C47" t="n">
-        <v>29633.75</v>
+        <v>29508.25</v>
       </c>
       <c r="D47" t="n">
-        <v>29333</v>
+        <v>29043.25</v>
       </c>
       <c r="E47" t="n">
-        <v>29448.75</v>
+        <v>29135.25</v>
       </c>
       <c r="F47" t="n">
-        <v>-90</v>
+        <v>-313.5</v>
       </c>
       <c r="G47" s="5" t="n">
-        <v>-0.003</v>
+        <v>-0.0106</v>
       </c>
       <c r="H47" t="n">
-        <v>300.75</v>
+        <v>465</v>
       </c>
       <c r="I47" t="n">
-        <v>29084.75</v>
+        <v>29032.25</v>
       </c>
       <c r="J47" t="n">
-        <v>29170.75</v>
+        <v>29130.69</v>
       </c>
       <c r="K47" t="n">
-        <v>29368.75</v>
+        <v>29298.38</v>
       </c>
       <c r="L47" t="n">
-        <v>29566.75</v>
+        <v>29466.06</v>
       </c>
       <c r="M47" t="n">
-        <v>29708.75</v>
+        <v>29599.12</v>
       </c>
       <c r="N47" t="n">
-        <v>29850.75</v>
+        <v>29732.19</v>
       </c>
       <c r="O47" t="n">
-        <v>30104.75</v>
+        <v>29934.5</v>
       </c>
       <c r="P47" s="6" t="n">
         <v/>
       </c>
-      <c r="Q47" s="6" t="n">
-        <v/>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R47" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S47" s="7" t="inlineStr">
@@ -4442,7 +4432,7 @@
       <c r="V47" s="8" t="n">
         <v/>
       </c>
-      <c r="W47" s="9" t="inlineStr">
+      <c r="W47" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -4452,224 +4442,222 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>29458.5</v>
+        <v>29141</v>
       </c>
       <c r="C48" t="n">
-        <v>29508.25</v>
+        <v>29500.25</v>
       </c>
       <c r="D48" t="n">
-        <v>29043.25</v>
+        <v>29040.5</v>
       </c>
       <c r="E48" t="n">
-        <v>29135.25</v>
+        <v>29387</v>
       </c>
       <c r="F48" t="n">
-        <v>-313.5</v>
+        <v>251.75</v>
       </c>
       <c r="G48" s="5" t="n">
-        <v>-0.0106</v>
+        <v>0.0086</v>
       </c>
       <c r="H48" t="n">
-        <v>465</v>
+        <v>459.75</v>
       </c>
       <c r="I48" t="n">
-        <v>29032.25</v>
+        <v>28578.25</v>
       </c>
       <c r="J48" t="n">
-        <v>29130.69</v>
+        <v>28600</v>
       </c>
       <c r="K48" t="n">
-        <v>29298.38</v>
+        <v>28902.75</v>
       </c>
       <c r="L48" t="n">
-        <v>29466.06</v>
+        <v>29205.5</v>
       </c>
       <c r="M48" t="n">
-        <v>29599.12</v>
+        <v>29367.75</v>
       </c>
       <c r="N48" t="n">
-        <v>29732.19</v>
+        <v>29530</v>
       </c>
       <c r="O48" t="n">
-        <v>29934.5</v>
+        <v>29973.25</v>
       </c>
       <c r="P48" s="6" t="n">
         <v/>
       </c>
-      <c r="Q48" s="6" t="inlineStr">
+      <c r="Q48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R48" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S48" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T48" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R48" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S48" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T48" s="8" t="n">
-        <v/>
-      </c>
       <c r="U48" s="8" t="n">
         <v/>
       </c>
       <c r="V48" s="8" t="n">
         <v/>
       </c>
-      <c r="W48" s="9" t="inlineStr">
+      <c r="W48" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X48" t="inlineStr"/>
+      <c r="X48" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>29141</v>
+        <v>28997.75</v>
       </c>
       <c r="C49" t="n">
-        <v>29500.25</v>
+        <v>29303</v>
       </c>
       <c r="D49" t="n">
-        <v>29040.5</v>
+        <v>28816.25</v>
       </c>
       <c r="E49" t="n">
-        <v>29387</v>
+        <v>29152.25</v>
       </c>
       <c r="F49" t="n">
-        <v>251.75</v>
+        <v>-234.75</v>
       </c>
       <c r="G49" s="5" t="n">
-        <v>0.0086</v>
+        <v>-0.008</v>
       </c>
       <c r="H49" t="n">
-        <v>459.75</v>
+        <v>486.75</v>
       </c>
       <c r="I49" t="n">
-        <v>28578.25</v>
+        <v>28580.75</v>
       </c>
       <c r="J49" t="n">
-        <v>28600</v>
+        <v>28985.56</v>
       </c>
       <c r="K49" t="n">
-        <v>28902.75</v>
+        <v>29157.12</v>
       </c>
       <c r="L49" t="n">
-        <v>29205.5</v>
+        <v>29328.69</v>
       </c>
       <c r="M49" t="n">
-        <v>29367.75</v>
+        <v>29616.88</v>
       </c>
       <c r="N49" t="n">
-        <v>29530</v>
+        <v>29905.06</v>
       </c>
       <c r="O49" t="n">
-        <v>29973.25</v>
+        <v>29960</v>
       </c>
       <c r="P49" s="6" t="n">
         <v/>
       </c>
-      <c r="Q49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R49" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S49" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T49" s="8" t="inlineStr">
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R49" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="S49" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T49" s="8" t="n">
+        <v/>
+      </c>
       <c r="U49" s="8" t="n">
         <v/>
       </c>
       <c r="V49" s="8" t="n">
         <v/>
       </c>
-      <c r="W49" s="9" t="inlineStr">
+      <c r="W49" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X49" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28997.75</v>
+        <v>29200</v>
       </c>
       <c r="C50" t="n">
-        <v>29303</v>
+        <v>29200</v>
       </c>
       <c r="D50" t="n">
-        <v>28816.25</v>
+        <v>28918.75</v>
       </c>
       <c r="E50" t="n">
-        <v>29152.25</v>
+        <v>28955</v>
       </c>
       <c r="F50" t="n">
-        <v>-234.75</v>
+        <v>-197.25</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>-0.008</v>
+        <v>-0.0068</v>
       </c>
       <c r="H50" t="n">
-        <v>486.75</v>
+        <v>281.25</v>
       </c>
       <c r="I50" t="n">
-        <v>28580.75</v>
+        <v>28329.5</v>
       </c>
       <c r="J50" t="n">
-        <v>28985.56</v>
+        <v>28711.81</v>
       </c>
       <c r="K50" t="n">
-        <v>29157.12</v>
+        <v>28908.88</v>
       </c>
       <c r="L50" t="n">
-        <v>29328.69</v>
+        <v>29105.94</v>
       </c>
       <c r="M50" t="n">
-        <v>29616.88</v>
+        <v>29395.62</v>
       </c>
       <c r="N50" t="n">
-        <v>29905.06</v>
+        <v>29685.31</v>
       </c>
       <c r="O50" t="n">
-        <v>29960</v>
+        <v>29789.75</v>
       </c>
       <c r="P50" s="6" t="n">
         <v/>
       </c>
-      <c r="Q50" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="Q50" s="6" t="n">
+        <v/>
       </c>
       <c r="R50" s="6" t="inlineStr">
         <is>
@@ -4690,60 +4678,64 @@
       <c r="V50" s="8" t="n">
         <v/>
       </c>
-      <c r="W50" s="9" t="inlineStr">
+      <c r="W50" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X50" t="inlineStr"/>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>29200</v>
+        <v>28978.25</v>
       </c>
       <c r="C51" t="n">
-        <v>29200</v>
+        <v>29252.25</v>
       </c>
       <c r="D51" t="n">
-        <v>28918.75</v>
+        <v>28763.75</v>
       </c>
       <c r="E51" t="n">
-        <v>28955</v>
+        <v>28963.5</v>
       </c>
       <c r="F51" t="n">
-        <v>-197.25</v>
+        <v>8.5</v>
       </c>
       <c r="G51" s="5" t="n">
-        <v>-0.0068</v>
+        <v>0.0003</v>
       </c>
       <c r="H51" t="n">
-        <v>281.25</v>
+        <v>488.5</v>
       </c>
       <c r="I51" t="n">
-        <v>28329.5</v>
+        <v>28637.5</v>
       </c>
       <c r="J51" t="n">
-        <v>28711.81</v>
+        <v>28621.56</v>
       </c>
       <c r="K51" t="n">
-        <v>28908.88</v>
+        <v>28814.38</v>
       </c>
       <c r="L51" t="n">
-        <v>29105.94</v>
+        <v>29007.19</v>
       </c>
       <c r="M51" t="n">
-        <v>29395.62</v>
+        <v>29095.62</v>
       </c>
       <c r="N51" t="n">
-        <v>29685.31</v>
+        <v>29184.06</v>
       </c>
       <c r="O51" t="n">
-        <v>29789.75</v>
+        <v>29481.25</v>
       </c>
       <c r="P51" s="6" t="n">
         <v/>
@@ -4753,81 +4745,85 @@
       </c>
       <c r="R51" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
+          <t>✓</t>
         </is>
       </c>
       <c r="S51" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T51" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U51" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U51" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V51" s="8" t="n">
         <v/>
       </c>
-      <c r="W51" s="9" t="inlineStr">
+      <c r="W51" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X51" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>28978.25</v>
+        <v>28967.5</v>
       </c>
       <c r="C52" t="n">
-        <v>29252.25</v>
+        <v>29498.25</v>
       </c>
       <c r="D52" t="n">
-        <v>28763.75</v>
+        <v>28957.75</v>
       </c>
       <c r="E52" t="n">
-        <v>28963.5</v>
+        <v>29446.75</v>
       </c>
       <c r="F52" t="n">
-        <v>8.5</v>
+        <v>483.25</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0003</v>
+        <v>0.0167</v>
       </c>
       <c r="H52" t="n">
-        <v>488.5</v>
+        <v>540.5</v>
       </c>
       <c r="I52" t="n">
-        <v>28637.5</v>
+        <v>28275.25</v>
       </c>
       <c r="J52" t="n">
-        <v>28621.56</v>
+        <v>28452.75</v>
       </c>
       <c r="K52" t="n">
-        <v>28814.38</v>
+        <v>28719.25</v>
       </c>
       <c r="L52" t="n">
-        <v>29007.19</v>
+        <v>28985.75</v>
       </c>
       <c r="M52" t="n">
-        <v>29095.62</v>
+        <v>29207.75</v>
       </c>
       <c r="N52" t="n">
-        <v>29184.06</v>
+        <v>29429.75</v>
       </c>
       <c r="O52" t="n">
-        <v>29481.25</v>
+        <v>29740.75</v>
       </c>
       <c r="P52" s="6" t="n">
         <v/>
@@ -4835,24 +4831,22 @@
       <c r="Q52" s="6" t="n">
         <v/>
       </c>
-      <c r="R52" s="6" t="inlineStr">
+      <c r="R52" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S52" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T52" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="S52" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T52" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
       <c r="U52" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
+          <t>△C</t>
         </is>
       </c>
       <c r="V52" s="8" t="n">
@@ -4860,62 +4854,58 @@
       </c>
       <c r="W52" s="9" t="inlineStr">
         <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X52" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>28967.5</v>
+        <v>29438.75</v>
       </c>
       <c r="C53" t="n">
-        <v>29498.25</v>
+        <v>29665.25</v>
       </c>
       <c r="D53" t="n">
-        <v>28957.75</v>
+        <v>29352.75</v>
       </c>
       <c r="E53" t="n">
-        <v>29446.75</v>
+        <v>29613.68</v>
       </c>
       <c r="F53" t="n">
-        <v>483.25</v>
+        <v>166.93</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>0.0167</v>
+        <v>0.0057</v>
       </c>
       <c r="H53" t="n">
-        <v>540.5</v>
+        <v>312.5</v>
       </c>
       <c r="I53" t="n">
-        <v>28275.25</v>
+        <v>28417.25</v>
       </c>
       <c r="J53" t="n">
-        <v>28452.75</v>
+        <v>29015.62</v>
       </c>
       <c r="K53" t="n">
-        <v>28719.25</v>
+        <v>29176.5</v>
       </c>
       <c r="L53" t="n">
-        <v>28985.75</v>
+        <v>29337.38</v>
       </c>
       <c r="M53" t="n">
-        <v>29207.75</v>
+        <v>29717</v>
       </c>
       <c r="N53" t="n">
-        <v>29429.75</v>
+        <v>30096.62</v>
       </c>
       <c r="O53" t="n">
-        <v>29740.75</v>
+        <v>30038.75</v>
       </c>
       <c r="P53" s="6" t="n">
         <v/>
@@ -4933,18 +4923,16 @@
       </c>
       <c r="T53" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U53" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="U53" s="8" t="n">
+        <v/>
+      </c>
       <c r="V53" s="8" t="n">
         <v/>
       </c>
-      <c r="W53" s="11" t="inlineStr">
+      <c r="W53" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -4954,50 +4942,50 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>29438.75</v>
+        <v>29938</v>
       </c>
       <c r="C54" t="n">
-        <v>29665.25</v>
+        <v>30862.75</v>
       </c>
       <c r="D54" t="n">
-        <v>29352.75</v>
+        <v>29904</v>
       </c>
       <c r="E54" t="n">
-        <v>29613.68</v>
+        <v>30784.75</v>
       </c>
       <c r="F54" t="n">
-        <v>166.93</v>
+        <v>1171.07</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>0.0057</v>
+        <v>0.0395</v>
       </c>
       <c r="H54" t="n">
-        <v>312.5</v>
+        <v>958.75</v>
       </c>
       <c r="I54" t="n">
-        <v>28417.25</v>
+        <v>29040.25</v>
       </c>
       <c r="J54" t="n">
-        <v>29015.62</v>
+        <v>29353.52</v>
       </c>
       <c r="K54" t="n">
-        <v>29176.5</v>
+        <v>29457.43</v>
       </c>
       <c r="L54" t="n">
-        <v>29337.38</v>
+        <v>29561.34</v>
       </c>
       <c r="M54" t="n">
-        <v>29717</v>
+        <v>29769.93</v>
       </c>
       <c r="N54" t="n">
-        <v>30096.62</v>
+        <v>29978.52</v>
       </c>
       <c r="O54" t="n">
-        <v>30038.75</v>
+        <v>29977.75</v>
       </c>
       <c r="P54" s="6" t="n">
         <v/>
@@ -5015,16 +5003,20 @@
       </c>
       <c r="T54" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U54" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="U54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V54" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W54" s="11" t="inlineStr">
+      <c r="V54" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="W54" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5034,50 +5026,50 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>29938</v>
+        <v>30780</v>
       </c>
       <c r="C55" t="n">
-        <v>30862.75</v>
+        <v>31065.5</v>
       </c>
       <c r="D55" t="n">
-        <v>29904</v>
+        <v>30670</v>
       </c>
       <c r="E55" t="n">
-        <v>30784.75</v>
+        <v>31028.5</v>
       </c>
       <c r="F55" t="n">
-        <v>1171.07</v>
+        <v>243.75</v>
       </c>
       <c r="G55" s="5" t="n">
-        <v>0.0395</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="H55" t="n">
-        <v>958.75</v>
+        <v>395.5</v>
       </c>
       <c r="I55" t="n">
-        <v>29040.25</v>
+        <v>28945.25</v>
       </c>
       <c r="J55" t="n">
-        <v>29353.52</v>
+        <v>30026.69</v>
       </c>
       <c r="K55" t="n">
-        <v>29457.43</v>
+        <v>30305.38</v>
       </c>
       <c r="L55" t="n">
-        <v>29561.34</v>
+        <v>30584.06</v>
       </c>
       <c r="M55" t="n">
-        <v>29769.93</v>
+        <v>31264.12</v>
       </c>
       <c r="N55" t="n">
-        <v>29978.52</v>
+        <v>31944.19</v>
       </c>
       <c r="O55" t="n">
-        <v>29977.75</v>
+        <v>31821.5</v>
       </c>
       <c r="P55" s="6" t="n">
         <v/>
@@ -5095,20 +5087,16 @@
       </c>
       <c r="T55" s="8" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U55" s="8" t="inlineStr">
-        <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="V55" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="W55" s="11" t="inlineStr">
+      <c r="U55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V55" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W55" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5118,138 +5106,142 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>30780</v>
+        <v>31008.5</v>
       </c>
       <c r="C56" t="n">
-        <v>31065.5</v>
+        <v>31094.75</v>
       </c>
       <c r="D56" t="n">
-        <v>30670</v>
+        <v>30642.75</v>
       </c>
       <c r="E56" t="n">
-        <v>31028.5</v>
+        <v>30764.75</v>
       </c>
       <c r="F56" t="n">
-        <v>243.75</v>
+        <v>-263.75</v>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.007900000000000001</v>
+        <v>-0.008500000000000001</v>
       </c>
       <c r="H56" t="n">
-        <v>395.5</v>
+        <v>452</v>
       </c>
       <c r="I56" t="n">
-        <v>28945.25</v>
+        <v>30274.5</v>
       </c>
       <c r="J56" t="n">
-        <v>30026.69</v>
+        <v>30713.38</v>
       </c>
       <c r="K56" t="n">
-        <v>30305.38</v>
+        <v>30830.75</v>
       </c>
       <c r="L56" t="n">
-        <v>30584.06</v>
+        <v>30948.12</v>
       </c>
       <c r="M56" t="n">
-        <v>31264.12</v>
+        <v>31226.25</v>
       </c>
       <c r="N56" t="n">
-        <v>31944.19</v>
+        <v>31504.38</v>
       </c>
       <c r="O56" t="n">
-        <v>31821.5</v>
+        <v>31461</v>
       </c>
       <c r="P56" s="6" t="n">
         <v/>
       </c>
-      <c r="Q56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R56" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S56" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T56" s="8" t="inlineStr">
+      <c r="Q56" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R56" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S56" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T56" s="8" t="n">
+        <v/>
+      </c>
       <c r="U56" s="8" t="n">
         <v/>
       </c>
       <c r="V56" s="8" t="n">
         <v/>
       </c>
-      <c r="W56" s="11" t="inlineStr">
+      <c r="W56" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X56" t="inlineStr"/>
+      <c r="X56" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>31008.5</v>
+        <v>30780</v>
       </c>
       <c r="C57" t="n">
-        <v>31094.75</v>
+        <v>30827.5</v>
       </c>
       <c r="D57" t="n">
-        <v>30642.75</v>
+        <v>30370</v>
       </c>
       <c r="E57" t="n">
-        <v>30764.75</v>
+        <v>30766.75</v>
       </c>
       <c r="F57" t="n">
-        <v>-263.75</v>
+        <v>2</v>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.0001</v>
       </c>
       <c r="H57" t="n">
-        <v>452</v>
+        <v>457.5</v>
       </c>
       <c r="I57" t="n">
-        <v>30274.5</v>
+        <v>30190.75</v>
       </c>
       <c r="J57" t="n">
-        <v>30713.38</v>
+        <v>30260.75</v>
       </c>
       <c r="K57" t="n">
-        <v>30830.75</v>
+        <v>30538.75</v>
       </c>
       <c r="L57" t="n">
-        <v>30948.12</v>
+        <v>30816.75</v>
       </c>
       <c r="M57" t="n">
-        <v>31226.25</v>
+        <v>30990.75</v>
       </c>
       <c r="N57" t="n">
-        <v>31504.38</v>
+        <v>31164.75</v>
       </c>
       <c r="O57" t="n">
-        <v>31461</v>
+        <v>31546.75</v>
       </c>
       <c r="P57" s="6" t="n">
         <v/>
       </c>
-      <c r="Q57" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="Q57" s="6" t="n">
+        <v/>
       </c>
       <c r="R57" s="6" t="inlineStr">
         <is>
@@ -5258,7 +5250,7 @@
       </c>
       <c r="S57" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T57" s="8" t="n">
@@ -5270,7 +5262,7 @@
       <c r="V57" s="8" t="n">
         <v/>
       </c>
-      <c r="W57" s="11" t="inlineStr">
+      <c r="W57" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
@@ -5284,50 +5276,50 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30780</v>
+        <v>30726.5</v>
       </c>
       <c r="C58" t="n">
-        <v>30827.5</v>
+        <v>30999.5</v>
       </c>
       <c r="D58" t="n">
-        <v>30370</v>
+        <v>30679</v>
       </c>
       <c r="E58" t="n">
-        <v>30766.75</v>
+        <v>30889.25</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>122.5</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.0001</v>
+        <v>0.004</v>
       </c>
       <c r="H58" t="n">
-        <v>457.5</v>
+        <v>320.5</v>
       </c>
       <c r="I58" t="n">
-        <v>30190.75</v>
+        <v>29912.5</v>
       </c>
       <c r="J58" t="n">
-        <v>30260.75</v>
+        <v>30393.25</v>
       </c>
       <c r="K58" t="n">
-        <v>30538.75</v>
+        <v>30538</v>
       </c>
       <c r="L58" t="n">
-        <v>30816.75</v>
+        <v>30682.75</v>
       </c>
       <c r="M58" t="n">
-        <v>30990.75</v>
+        <v>30995.5</v>
       </c>
       <c r="N58" t="n">
-        <v>31164.75</v>
+        <v>31308.25</v>
       </c>
       <c r="O58" t="n">
-        <v>31546.75</v>
+        <v>31285</v>
       </c>
       <c r="P58" s="6" t="n">
         <v/>
@@ -5335,18 +5327,18 @@
       <c r="Q58" s="6" t="n">
         <v/>
       </c>
-      <c r="R58" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S58" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T58" s="8" t="n">
-        <v/>
+      <c r="R58" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S58" s="10" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T58" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U58" s="8" t="n">
         <v/>
@@ -5354,84 +5346,84 @@
       <c r="V58" s="8" t="n">
         <v/>
       </c>
-      <c r="W58" s="11" t="inlineStr">
+      <c r="W58" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X58" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>30726.5</v>
+        <v>30870</v>
       </c>
       <c r="C59" t="n">
-        <v>30999.5</v>
+        <v>30920.75</v>
       </c>
       <c r="D59" t="n">
-        <v>30679</v>
+        <v>30356.75</v>
       </c>
       <c r="E59" t="n">
-        <v>30889.25</v>
+        <v>30566.25</v>
       </c>
       <c r="F59" t="n">
-        <v>122.5</v>
+        <v>-323</v>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.004</v>
+        <v>-0.0105</v>
       </c>
       <c r="H59" t="n">
-        <v>320.5</v>
+        <v>564</v>
       </c>
       <c r="I59" t="n">
-        <v>29912.5</v>
+        <v>30358.5</v>
       </c>
       <c r="J59" t="n">
-        <v>30393.25</v>
+        <v>30593.75</v>
       </c>
       <c r="K59" t="n">
-        <v>30538</v>
+        <v>30729</v>
       </c>
       <c r="L59" t="n">
-        <v>30682.75</v>
+        <v>30864.25</v>
       </c>
       <c r="M59" t="n">
-        <v>30995.5</v>
+        <v>31049.5</v>
       </c>
       <c r="N59" t="n">
-        <v>31308.25</v>
+        <v>31234.75</v>
       </c>
       <c r="O59" t="n">
-        <v>31285</v>
-      </c>
-      <c r="P59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R59" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S59" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T59" s="8" t="inlineStr">
+        <v>31320</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
+      <c r="R59" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S59" s="7" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T59" s="8" t="n">
+        <v/>
+      </c>
       <c r="U59" s="8" t="n">
         <v/>
       </c>
@@ -5440,7 +5432,7 @@
       </c>
       <c r="W59" s="11" t="inlineStr">
         <is>
-          <t>多方</t>
+          <t>空方</t>
         </is>
       </c>
       <c r="X59" t="inlineStr"/>
@@ -5448,69 +5440,63 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>30870</v>
+        <v>30560.5</v>
       </c>
       <c r="C60" t="n">
-        <v>30920.75</v>
+        <v>30725.5</v>
       </c>
       <c r="D60" t="n">
-        <v>30356.75</v>
+        <v>30372.25</v>
       </c>
       <c r="E60" t="n">
-        <v>30566.25</v>
+        <v>30613.25</v>
       </c>
       <c r="F60" t="n">
-        <v>-323</v>
+        <v>47</v>
       </c>
       <c r="G60" s="5" t="n">
-        <v>-0.0105</v>
+        <v>0.0015</v>
       </c>
       <c r="H60" t="n">
-        <v>564</v>
+        <v>353.25</v>
       </c>
       <c r="I60" t="n">
-        <v>30358.5</v>
+        <v>29792.75</v>
       </c>
       <c r="J60" t="n">
-        <v>30593.75</v>
+        <v>29966</v>
       </c>
       <c r="K60" t="n">
-        <v>30729</v>
+        <v>30284.25</v>
       </c>
       <c r="L60" t="n">
-        <v>30864.25</v>
+        <v>30602.5</v>
       </c>
       <c r="M60" t="n">
-        <v>31049.5</v>
+        <v>30848.25</v>
       </c>
       <c r="N60" t="n">
-        <v>31234.75</v>
+        <v>31094</v>
       </c>
       <c r="O60" t="n">
-        <v>31320</v>
-      </c>
-      <c r="P60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q60" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R60" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S60" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>31484.75</v>
+      </c>
+      <c r="P60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R60" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S60" s="10" t="inlineStr">
+        <is>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T60" s="8" t="n">
@@ -5522,60 +5508,64 @@
       <c r="V60" s="8" t="n">
         <v/>
       </c>
-      <c r="W60" s="9" t="inlineStr">
+      <c r="W60" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X60" t="inlineStr"/>
+      <c r="X60" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>30560.5</v>
+        <v>30657.25</v>
       </c>
       <c r="C61" t="n">
-        <v>30725.5</v>
+        <v>30906</v>
       </c>
       <c r="D61" t="n">
-        <v>30372.25</v>
+        <v>30512.25</v>
       </c>
       <c r="E61" t="n">
-        <v>30613.25</v>
+        <v>30698.75</v>
       </c>
       <c r="F61" t="n">
-        <v>47</v>
+        <v>85.5</v>
       </c>
       <c r="G61" s="5" t="n">
-        <v>0.0015</v>
+        <v>0.0028</v>
       </c>
       <c r="H61" t="n">
-        <v>353.25</v>
+        <v>393.75</v>
       </c>
       <c r="I61" t="n">
-        <v>29792.75</v>
+        <v>30019</v>
       </c>
       <c r="J61" t="n">
-        <v>29966</v>
+        <v>30292.19</v>
       </c>
       <c r="K61" t="n">
-        <v>30284.25</v>
+        <v>30436.62</v>
       </c>
       <c r="L61" t="n">
-        <v>30602.5</v>
+        <v>30581.06</v>
       </c>
       <c r="M61" t="n">
-        <v>30848.25</v>
+        <v>30789.88</v>
       </c>
       <c r="N61" t="n">
-        <v>31094</v>
+        <v>30998.69</v>
       </c>
       <c r="O61" t="n">
-        <v>31484.75</v>
+        <v>31078.75</v>
       </c>
       <c r="P61" s="6" t="n">
         <v/>
@@ -5588,11 +5578,13 @@
       </c>
       <c r="S61" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T61" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T61" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U61" s="8" t="n">
         <v/>
@@ -5600,64 +5592,64 @@
       <c r="V61" s="8" t="n">
         <v/>
       </c>
-      <c r="W61" s="9" t="inlineStr">
+      <c r="W61" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
       <c r="X61" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>30657.25</v>
+        <v>30707</v>
       </c>
       <c r="C62" t="n">
-        <v>30906</v>
+        <v>31151.5</v>
       </c>
       <c r="D62" t="n">
-        <v>30512.25</v>
+        <v>30529.25</v>
       </c>
       <c r="E62" t="n">
-        <v>30698.75</v>
+        <v>30760.5</v>
       </c>
       <c r="F62" t="n">
-        <v>85.5</v>
+        <v>61.75</v>
       </c>
       <c r="G62" s="5" t="n">
-        <v>0.0028</v>
+        <v>0.002</v>
       </c>
       <c r="H62" t="n">
-        <v>393.75</v>
+        <v>622.25</v>
       </c>
       <c r="I62" t="n">
-        <v>30019</v>
+        <v>30118.5</v>
       </c>
       <c r="J62" t="n">
-        <v>30292.19</v>
+        <v>30299.81</v>
       </c>
       <c r="K62" t="n">
-        <v>30436.62</v>
+        <v>30501.88</v>
       </c>
       <c r="L62" t="n">
-        <v>30581.06</v>
+        <v>30703.94</v>
       </c>
       <c r="M62" t="n">
-        <v>30789.88</v>
+        <v>30895.62</v>
       </c>
       <c r="N62" t="n">
-        <v>30998.69</v>
+        <v>31087.31</v>
       </c>
       <c r="O62" t="n">
-        <v>31078.75</v>
+        <v>31299.75</v>
       </c>
       <c r="P62" s="6" t="n">
         <v/>
@@ -5670,21 +5662,23 @@
       </c>
       <c r="S62" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T62" s="8" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="U62" s="8" t="n">
-        <v/>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U62" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V62" s="8" t="n">
         <v/>
       </c>
-      <c r="W62" s="9" t="inlineStr">
+      <c r="W62" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
@@ -5698,50 +5692,50 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B63" t="n">
         <v>30771.25</v>
       </c>
       <c r="C63" t="n">
-        <v>30790</v>
+        <v>31282.5</v>
       </c>
       <c r="D63" t="n">
         <v>30760.25</v>
       </c>
       <c r="E63" t="n">
-        <v>30786.75</v>
+        <v>31061.75</v>
       </c>
       <c r="F63" t="n">
-        <v>88</v>
+        <v>301.25</v>
       </c>
       <c r="G63" s="5" t="n">
-        <v>0.0029</v>
+        <v>0.0098</v>
       </c>
       <c r="H63" t="n">
-        <v>29.75</v>
+        <v>522.25</v>
       </c>
       <c r="I63" t="n">
-        <v>30118.5</v>
+        <v>29907</v>
       </c>
       <c r="J63" t="n">
-        <v>30299.81</v>
+        <v>30098.31</v>
       </c>
       <c r="K63" t="n">
-        <v>30501.88</v>
+        <v>30449.38</v>
       </c>
       <c r="L63" t="n">
-        <v>30703.94</v>
+        <v>30800.44</v>
       </c>
       <c r="M63" t="n">
-        <v>30895.62</v>
+        <v>31071.62</v>
       </c>
       <c r="N63" t="n">
-        <v>31087.31</v>
+        <v>31342.81</v>
       </c>
       <c r="O63" t="n">
-        <v>31299.75</v>
+        <v>31773.75</v>
       </c>
       <c r="P63" s="6" t="n">
         <v/>
@@ -5754,26 +5748,110 @@
       </c>
       <c r="S63" s="10" t="inlineStr">
         <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T63" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="U63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V63" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W63" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X63" t="inlineStr">
+        <is>
+          <t>強警訊</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="B64" t="n">
+        <v>31059</v>
+      </c>
+      <c r="C64" t="n">
+        <v>31134</v>
+      </c>
+      <c r="D64" t="n">
+        <v>31059</v>
+      </c>
+      <c r="E64" t="n">
+        <v>31061.75</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>75</v>
+      </c>
+      <c r="I64" t="n">
+        <v>30238</v>
+      </c>
+      <c r="J64" t="n">
+        <v>30559.69</v>
+      </c>
+      <c r="K64" t="n">
+        <v>30800.62</v>
+      </c>
+      <c r="L64" t="n">
+        <v>31041.56</v>
+      </c>
+      <c r="M64" t="n">
+        <v>31322.88</v>
+      </c>
+      <c r="N64" t="n">
+        <v>31604.19</v>
+      </c>
+      <c r="O64" t="n">
+        <v>31804.75</v>
+      </c>
+      <c r="P64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R64" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S64" s="10" t="inlineStr">
+        <is>
           <t>↑C</t>
         </is>
       </c>
-      <c r="T63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="V63" s="8" t="n">
-        <v/>
-      </c>
-      <c r="W63" s="9" t="inlineStr">
+      <c r="T64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V64" s="8" t="n">
+        <v/>
+      </c>
+      <c r="W64" s="11" t="inlineStr">
         <is>
           <t>空方</t>
         </is>
       </c>
-      <c r="X63" t="inlineStr">
-        <is>
-          <t>中警訊</t>
+      <c r="X64" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>

--- a/three_gate/analysis/NQ_daily.xlsx
+++ b/three_gate/analysis/NQ_daily.xlsx
@@ -104,14 +104,14 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X64"/>
+  <dimension ref="A1:X63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -634,50 +634,50 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-07-08</t>
+          <t>2026-07-09</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>29373.75</v>
+        <v>29412</v>
       </c>
       <c r="C2" t="n">
-        <v>29558.75</v>
+        <v>29993.5</v>
       </c>
       <c r="D2" t="n">
-        <v>28909.75</v>
+        <v>29395</v>
       </c>
       <c r="E2" t="n">
-        <v>29468.5</v>
+        <v>29937</v>
       </c>
       <c r="F2" t="n">
-        <v>77</v>
+        <v>468.5</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.0026</v>
+        <v>0.0159</v>
       </c>
       <c r="H2" t="n">
-        <v>649</v>
+        <v>598.5</v>
       </c>
       <c r="I2" t="n">
-        <v>28446.25</v>
+        <v>28260.75</v>
       </c>
       <c r="J2" t="n">
-        <v>28527.56</v>
+        <v>28936.62</v>
       </c>
       <c r="K2" t="n">
-        <v>29009.62</v>
+        <v>29144</v>
       </c>
       <c r="L2" t="n">
-        <v>29491.69</v>
+        <v>29351.38</v>
       </c>
       <c r="M2" t="n">
-        <v>29773.38</v>
+        <v>29793</v>
       </c>
       <c r="N2" t="n">
-        <v>30055.06</v>
+        <v>30234.62</v>
       </c>
       <c r="O2" t="n">
-        <v>30737.5</v>
+        <v>30207.75</v>
       </c>
       <c r="P2" s="6" t="n">
         <v/>
@@ -685,18 +685,18 @@
       <c r="Q2" s="6" t="n">
         <v/>
       </c>
-      <c r="R2" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="R2" s="6" t="n">
+        <v/>
       </c>
       <c r="S2" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T2" s="8" t="n">
-        <v/>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T2" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="U2" s="8" t="n">
         <v/>
@@ -709,59 +709,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-07-09</t>
+          <t>2026-07-10</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>29412</v>
+        <v>29937.75</v>
       </c>
       <c r="C3" t="n">
-        <v>29993.5</v>
+        <v>30077.75</v>
       </c>
       <c r="D3" t="n">
-        <v>29395</v>
+        <v>29675</v>
       </c>
       <c r="E3" t="n">
-        <v>29937</v>
+        <v>30032.25</v>
       </c>
       <c r="F3" t="n">
-        <v>468.5</v>
+        <v>95.25</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.0159</v>
+        <v>0.0032</v>
       </c>
       <c r="H3" t="n">
-        <v>598.5</v>
+        <v>402.75</v>
       </c>
       <c r="I3" t="n">
-        <v>28260.75</v>
+        <v>28796.5</v>
       </c>
       <c r="J3" t="n">
-        <v>28936.62</v>
+        <v>29459.88</v>
       </c>
       <c r="K3" t="n">
-        <v>29144</v>
+        <v>29637.75</v>
       </c>
       <c r="L3" t="n">
-        <v>29351.38</v>
+        <v>29815.62</v>
       </c>
       <c r="M3" t="n">
-        <v>29793</v>
+        <v>30236.25</v>
       </c>
       <c r="N3" t="n">
-        <v>30234.62</v>
+        <v>30656.88</v>
       </c>
       <c r="O3" t="n">
-        <v>30207.75</v>
+        <v>30592</v>
       </c>
       <c r="P3" s="6" t="n">
         <v/>
@@ -772,7 +768,7 @@
       <c r="R3" s="6" t="n">
         <v/>
       </c>
-      <c r="S3" s="10" t="inlineStr">
+      <c r="S3" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -798,69 +794,73 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-07-10</t>
+          <t>2026-07-13</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>29937.75</v>
+        <v>29952</v>
       </c>
       <c r="C4" t="n">
-        <v>30077.75</v>
+        <v>30041</v>
       </c>
       <c r="D4" t="n">
-        <v>29675</v>
+        <v>29386.5</v>
       </c>
       <c r="E4" t="n">
-        <v>30032.25</v>
+        <v>29475.75</v>
       </c>
       <c r="F4" t="n">
-        <v>95.25</v>
+        <v>-556.5</v>
       </c>
       <c r="G4" s="5" t="n">
-        <v>0.0032</v>
+        <v>-0.0185</v>
       </c>
       <c r="H4" t="n">
-        <v>402.75</v>
+        <v>654.5</v>
       </c>
       <c r="I4" t="n">
-        <v>28796.5</v>
+        <v>29272.25</v>
       </c>
       <c r="J4" t="n">
-        <v>29459.88</v>
+        <v>29707.44</v>
       </c>
       <c r="K4" t="n">
-        <v>29637.75</v>
+        <v>29830.88</v>
       </c>
       <c r="L4" t="n">
-        <v>29815.62</v>
+        <v>29954.31</v>
       </c>
       <c r="M4" t="n">
-        <v>30236.25</v>
+        <v>30233.62</v>
       </c>
       <c r="N4" t="n">
-        <v>30656.88</v>
+        <v>30512.94</v>
       </c>
       <c r="O4" t="n">
-        <v>30592</v>
-      </c>
-      <c r="P4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q4" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R4" s="6" t="n">
-        <v/>
+        <v>30480.5</v>
+      </c>
+      <c r="P4" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="R4" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S4" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T4" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T4" s="8" t="n">
+        <v/>
       </c>
       <c r="U4" s="8" t="n">
         <v/>
@@ -868,9 +868,9 @@
       <c r="V4" s="8" t="n">
         <v/>
       </c>
-      <c r="W4" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
+      <c r="W4" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
         </is>
       </c>
       <c r="X4" t="inlineStr"/>
@@ -878,74 +878,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-07-13</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29952</v>
+        <v>29446</v>
       </c>
       <c r="C5" t="n">
-        <v>30041</v>
+        <v>29921.75</v>
       </c>
       <c r="D5" t="n">
-        <v>29386.5</v>
+        <v>29303.5</v>
       </c>
       <c r="E5" t="n">
-        <v>29475.75</v>
+        <v>29790.25</v>
       </c>
       <c r="F5" t="n">
-        <v>-556.5</v>
+        <v>314.5</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>-0.0185</v>
+        <v>0.0107</v>
       </c>
       <c r="H5" t="n">
-        <v>654.5</v>
+        <v>618.25</v>
       </c>
       <c r="I5" t="n">
-        <v>29272.25</v>
+        <v>28732</v>
       </c>
       <c r="J5" t="n">
-        <v>29707.44</v>
+        <v>28702.25</v>
       </c>
       <c r="K5" t="n">
-        <v>29830.88</v>
+        <v>29148.5</v>
       </c>
       <c r="L5" t="n">
-        <v>29954.31</v>
+        <v>29594.75</v>
       </c>
       <c r="M5" t="n">
-        <v>30233.62</v>
+        <v>29803</v>
       </c>
       <c r="N5" t="n">
-        <v>30512.94</v>
+        <v>30011.25</v>
       </c>
       <c r="O5" t="n">
-        <v>30480.5</v>
-      </c>
-      <c r="P5" s="6" t="inlineStr">
+        <v>30695.5</v>
+      </c>
+      <c r="P5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R5" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S5" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T5" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R5" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S5" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T5" s="8" t="n">
-        <v/>
-      </c>
       <c r="U5" s="8" t="n">
         <v/>
       </c>
@@ -957,55 +953,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr"/>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-07-14</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>29446</v>
+        <v>29805</v>
       </c>
       <c r="C6" t="n">
-        <v>29921.75</v>
+        <v>30062.5</v>
       </c>
       <c r="D6" t="n">
-        <v>29303.5</v>
+        <v>29397</v>
       </c>
       <c r="E6" t="n">
-        <v>29790.25</v>
+        <v>29693.25</v>
       </c>
       <c r="F6" t="n">
-        <v>314.5</v>
+        <v>-97</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0107</v>
+        <v>-0.0033</v>
       </c>
       <c r="H6" t="n">
-        <v>618.25</v>
+        <v>665.5</v>
       </c>
       <c r="I6" t="n">
-        <v>28732</v>
+        <v>28685.25</v>
       </c>
       <c r="J6" t="n">
-        <v>28702.25</v>
+        <v>29260.81</v>
       </c>
       <c r="K6" t="n">
-        <v>29148.5</v>
+        <v>29481.12</v>
       </c>
       <c r="L6" t="n">
-        <v>29594.75</v>
+        <v>29701.44</v>
       </c>
       <c r="M6" t="n">
-        <v>29803</v>
+        <v>30099.38</v>
       </c>
       <c r="N6" t="n">
-        <v>30011.25</v>
+        <v>30497.31</v>
       </c>
       <c r="O6" t="n">
-        <v>30695.5</v>
+        <v>30540</v>
       </c>
       <c r="P6" s="6" t="n">
         <v/>
@@ -1013,18 +1013,18 @@
       <c r="Q6" s="6" t="n">
         <v/>
       </c>
-      <c r="R6" s="6" t="n">
-        <v/>
+      <c r="R6" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S6" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T6" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T6" s="8" t="n">
+        <v/>
       </c>
       <c r="U6" s="8" t="n">
         <v/>
@@ -1039,57 +1039,57 @@
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>29805</v>
+        <v>29709</v>
       </c>
       <c r="C7" t="n">
-        <v>30062.5</v>
+        <v>29797</v>
       </c>
       <c r="D7" t="n">
-        <v>29397</v>
+        <v>29078.5</v>
       </c>
       <c r="E7" t="n">
-        <v>29693.25</v>
+        <v>29225.75</v>
       </c>
       <c r="F7" t="n">
-        <v>-97</v>
+        <v>-467.5</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0157</v>
       </c>
       <c r="H7" t="n">
-        <v>665.5</v>
+        <v>718.5</v>
       </c>
       <c r="I7" t="n">
-        <v>28685.25</v>
+        <v>28731.5</v>
       </c>
       <c r="J7" t="n">
-        <v>29260.81</v>
+        <v>29009.5</v>
       </c>
       <c r="K7" t="n">
-        <v>29481.12</v>
+        <v>29360.5</v>
       </c>
       <c r="L7" t="n">
-        <v>29701.44</v>
+        <v>29711.5</v>
       </c>
       <c r="M7" t="n">
-        <v>30099.38</v>
+        <v>30026</v>
       </c>
       <c r="N7" t="n">
-        <v>30497.31</v>
+        <v>30340.5</v>
       </c>
       <c r="O7" t="n">
-        <v>30540</v>
+        <v>30728</v>
       </c>
       <c r="P7" s="6" t="n">
         <v/>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="R7" s="6" t="inlineStr">
         <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S7" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S7" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T7" s="8" t="n">
@@ -1121,59 +1121,55 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-07-17</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>29709</v>
+        <v>29191</v>
       </c>
       <c r="C8" t="n">
-        <v>29797</v>
+        <v>29220</v>
       </c>
       <c r="D8" t="n">
-        <v>29078.5</v>
+        <v>28408.25</v>
       </c>
       <c r="E8" t="n">
-        <v>29225.75</v>
+        <v>28773.25</v>
       </c>
       <c r="F8" t="n">
-        <v>-467.5</v>
+        <v>-452.5</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>-0.0157</v>
+        <v>-0.0155</v>
       </c>
       <c r="H8" t="n">
-        <v>718.5</v>
+        <v>811.75</v>
       </c>
       <c r="I8" t="n">
-        <v>28731.5</v>
+        <v>28360</v>
       </c>
       <c r="J8" t="n">
-        <v>29009.5</v>
+        <v>28401.25</v>
       </c>
       <c r="K8" t="n">
-        <v>29360.5</v>
+        <v>28866.5</v>
       </c>
       <c r="L8" t="n">
-        <v>29711.5</v>
+        <v>29331.75</v>
       </c>
       <c r="M8" t="n">
-        <v>30026</v>
+        <v>29585</v>
       </c>
       <c r="N8" t="n">
-        <v>30340.5</v>
+        <v>29838.25</v>
       </c>
       <c r="O8" t="n">
-        <v>30728</v>
+        <v>30515.5</v>
       </c>
       <c r="P8" s="6" t="n">
         <v/>
@@ -1186,7 +1182,7 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S8" s="7" t="inlineStr">
+      <c r="S8" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1210,50 +1206,50 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-07-17</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>29191</v>
+        <v>28747.75</v>
       </c>
       <c r="C9" t="n">
-        <v>29220</v>
+        <v>29192.5</v>
       </c>
       <c r="D9" t="n">
-        <v>28408.25</v>
+        <v>28709.75</v>
       </c>
       <c r="E9" t="n">
-        <v>28773.25</v>
+        <v>28778.75</v>
       </c>
       <c r="F9" t="n">
-        <v>-452.5</v>
+        <v>5.5</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>-0.0155</v>
+        <v>0.0002</v>
       </c>
       <c r="H9" t="n">
-        <v>811.75</v>
+        <v>482.75</v>
       </c>
       <c r="I9" t="n">
-        <v>28360</v>
+        <v>27596.5</v>
       </c>
       <c r="J9" t="n">
-        <v>28401.25</v>
+        <v>27941.06</v>
       </c>
       <c r="K9" t="n">
-        <v>28866.5</v>
+        <v>28367.38</v>
       </c>
       <c r="L9" t="n">
-        <v>29331.75</v>
+        <v>28793.69</v>
       </c>
       <c r="M9" t="n">
-        <v>29585</v>
+        <v>29179.12</v>
       </c>
       <c r="N9" t="n">
-        <v>29838.25</v>
+        <v>29564.56</v>
       </c>
       <c r="O9" t="n">
-        <v>30515.5</v>
+        <v>30031.75</v>
       </c>
       <c r="P9" s="6" t="n">
         <v/>
@@ -1261,18 +1257,18 @@
       <c r="Q9" s="6" t="n">
         <v/>
       </c>
-      <c r="R9" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S9" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T9" s="8" t="n">
-        <v/>
+      <c r="R9" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S9" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T9" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U9" s="8" t="n">
         <v/>
@@ -1285,55 +1281,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>28747.75</v>
+        <v>28778.25</v>
       </c>
       <c r="C10" t="n">
-        <v>29192.5</v>
+        <v>29364.75</v>
       </c>
       <c r="D10" t="n">
-        <v>28709.75</v>
+        <v>28701</v>
       </c>
       <c r="E10" t="n">
-        <v>28778.75</v>
+        <v>29316</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5</v>
+        <v>537.25</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>0.0002</v>
+        <v>0.0187</v>
       </c>
       <c r="H10" t="n">
-        <v>482.75</v>
+        <v>663.75</v>
       </c>
       <c r="I10" t="n">
-        <v>27596.5</v>
+        <v>28227</v>
       </c>
       <c r="J10" t="n">
-        <v>27941.06</v>
+        <v>28209.81</v>
       </c>
       <c r="K10" t="n">
-        <v>28367.38</v>
+        <v>28537.38</v>
       </c>
       <c r="L10" t="n">
-        <v>28793.69</v>
+        <v>28864.94</v>
       </c>
       <c r="M10" t="n">
-        <v>29179.12</v>
+        <v>29020.12</v>
       </c>
       <c r="N10" t="n">
-        <v>29564.56</v>
+        <v>29175.31</v>
       </c>
       <c r="O10" t="n">
-        <v>30031.75</v>
+        <v>29675.25</v>
       </c>
       <c r="P10" s="6" t="n">
         <v/>
@@ -1346,7 +1346,7 @@
       </c>
       <c r="S10" s="7" t="inlineStr">
         <is>
-          <t>↓C</t>
+          <t>↑</t>
         </is>
       </c>
       <c r="T10" s="8" t="inlineStr">
@@ -1354,70 +1354,72 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="U10" s="8" t="n">
-        <v/>
+      <c r="U10" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V10" s="8" t="n">
         <v/>
       </c>
-      <c r="W10" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W10" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>弱警訊</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>28778.25</v>
+        <v>29310.75</v>
       </c>
       <c r="C11" t="n">
-        <v>29364.75</v>
+        <v>29342.25</v>
       </c>
       <c r="D11" t="n">
-        <v>28701</v>
+        <v>28952</v>
       </c>
       <c r="E11" t="n">
-        <v>29316</v>
+        <v>29181.25</v>
       </c>
       <c r="F11" t="n">
-        <v>537.25</v>
+        <v>-134.75</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>0.0187</v>
+        <v>-0.0046</v>
       </c>
       <c r="H11" t="n">
-        <v>663.75</v>
+        <v>390.25</v>
       </c>
       <c r="I11" t="n">
-        <v>28227</v>
+        <v>28037.25</v>
       </c>
       <c r="J11" t="n">
-        <v>28209.81</v>
+        <v>28793.81</v>
       </c>
       <c r="K11" t="n">
-        <v>28537.38</v>
+        <v>28984.12</v>
       </c>
       <c r="L11" t="n">
-        <v>28864.94</v>
+        <v>29174.44</v>
       </c>
       <c r="M11" t="n">
-        <v>29020.12</v>
+        <v>29647.88</v>
       </c>
       <c r="N11" t="n">
-        <v>29175.31</v>
+        <v>30121.31</v>
       </c>
       <c r="O11" t="n">
-        <v>29675.25</v>
+        <v>30028.5</v>
       </c>
       <c r="P11" s="6" t="n">
         <v/>
@@ -1425,23 +1427,21 @@
       <c r="Q11" s="6" t="n">
         <v/>
       </c>
-      <c r="R11" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S11" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T11" s="8" t="inlineStr">
+      <c r="R11" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U11" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S11" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T11" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U11" s="8" t="n">
+        <v/>
       </c>
       <c r="V11" s="8" t="n">
         <v/>
@@ -1453,63 +1453,67 @@
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>中警訊</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>29310.75</v>
+        <v>29100</v>
       </c>
       <c r="C12" t="n">
-        <v>29342.25</v>
+        <v>29282.5</v>
       </c>
       <c r="D12" t="n">
-        <v>28952</v>
+        <v>28432.5</v>
       </c>
       <c r="E12" t="n">
-        <v>29181.25</v>
+        <v>28620.75</v>
       </c>
       <c r="F12" t="n">
-        <v>-134.75</v>
+        <v>-560.5</v>
       </c>
       <c r="G12" s="5" t="n">
-        <v>-0.0046</v>
+        <v>-0.0192</v>
       </c>
       <c r="H12" t="n">
-        <v>390.25</v>
+        <v>850</v>
       </c>
       <c r="I12" t="n">
-        <v>28037.25</v>
+        <v>28561.75</v>
       </c>
       <c r="J12" t="n">
-        <v>28793.81</v>
+        <v>28808.06</v>
       </c>
       <c r="K12" t="n">
-        <v>28984.12</v>
+        <v>28986.12</v>
       </c>
       <c r="L12" t="n">
-        <v>29174.44</v>
+        <v>29164.19</v>
       </c>
       <c r="M12" t="n">
-        <v>29647.88</v>
+        <v>29376.38</v>
       </c>
       <c r="N12" t="n">
-        <v>30121.31</v>
+        <v>29588.56</v>
       </c>
       <c r="O12" t="n">
-        <v>30028.5</v>
-      </c>
-      <c r="P12" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q12" s="6" t="n">
-        <v/>
+        <v>29732.5</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="R12" s="6" t="inlineStr">
         <is>
@@ -1518,7 +1522,7 @@
       </c>
       <c r="S12" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T12" s="8" t="n">
@@ -1530,81 +1534,73 @@
       <c r="V12" s="8" t="n">
         <v/>
       </c>
-      <c r="W12" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="W12" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>29100</v>
+        <v>28700.25</v>
       </c>
       <c r="C13" t="n">
-        <v>29282.5</v>
+        <v>28736</v>
       </c>
       <c r="D13" t="n">
-        <v>28432.5</v>
+        <v>28212.5</v>
       </c>
       <c r="E13" t="n">
-        <v>28620.75</v>
+        <v>28282.25</v>
       </c>
       <c r="F13" t="n">
-        <v>-560.5</v>
+        <v>-338.5</v>
       </c>
       <c r="G13" s="5" t="n">
-        <v>-0.0192</v>
+        <v>-0.0118</v>
       </c>
       <c r="H13" t="n">
-        <v>850</v>
+        <v>523.5</v>
       </c>
       <c r="I13" t="n">
-        <v>28561.75</v>
+        <v>27582.5</v>
       </c>
       <c r="J13" t="n">
-        <v>28808.06</v>
+        <v>27652.38</v>
       </c>
       <c r="K13" t="n">
-        <v>28986.12</v>
+        <v>28195.75</v>
       </c>
       <c r="L13" t="n">
-        <v>29164.19</v>
+        <v>28739.12</v>
       </c>
       <c r="M13" t="n">
-        <v>29376.38</v>
+        <v>29045.75</v>
       </c>
       <c r="N13" t="n">
-        <v>29588.56</v>
+        <v>29352.38</v>
       </c>
       <c r="O13" t="n">
-        <v>29732.5</v>
-      </c>
-      <c r="P13" s="6" t="inlineStr">
+        <v>30132.5</v>
+      </c>
+      <c r="P13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q13" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R13" s="6" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="Q13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S13" s="7" t="inlineStr">
+      <c r="S13" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1628,50 +1624,50 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>28700.25</v>
+        <v>28500</v>
       </c>
       <c r="C14" t="n">
-        <v>28736</v>
+        <v>28763.25</v>
       </c>
       <c r="D14" t="n">
-        <v>28212.5</v>
+        <v>27939</v>
       </c>
       <c r="E14" t="n">
-        <v>28282.25</v>
+        <v>28190</v>
       </c>
       <c r="F14" t="n">
-        <v>-338.5</v>
+        <v>-92.25</v>
       </c>
       <c r="G14" s="5" t="n">
-        <v>-0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H14" t="n">
-        <v>523.5</v>
+        <v>824.25</v>
       </c>
       <c r="I14" t="n">
-        <v>27582.5</v>
+        <v>27689</v>
       </c>
       <c r="J14" t="n">
-        <v>27652.38</v>
+        <v>27662.75</v>
       </c>
       <c r="K14" t="n">
-        <v>28195.75</v>
+        <v>28020.5</v>
       </c>
       <c r="L14" t="n">
-        <v>28739.12</v>
+        <v>28378.25</v>
       </c>
       <c r="M14" t="n">
-        <v>29045.75</v>
+        <v>28544</v>
       </c>
       <c r="N14" t="n">
-        <v>29352.38</v>
+        <v>28709.75</v>
       </c>
       <c r="O14" t="n">
-        <v>30132.5</v>
+        <v>29259.5</v>
       </c>
       <c r="P14" s="6" t="n">
         <v/>
@@ -1684,16 +1680,20 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S14" s="7" t="inlineStr">
+      <c r="S14" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T14" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U14" s="8" t="n">
-        <v/>
+      <c r="T14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U14" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="V14" s="8" t="n">
         <v/>
@@ -1703,55 +1703,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X14" t="inlineStr"/>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-07-28</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>28500</v>
+        <v>28210.5</v>
       </c>
       <c r="C15" t="n">
-        <v>28763.25</v>
+        <v>28228</v>
       </c>
       <c r="D15" t="n">
-        <v>27939</v>
+        <v>27603.5</v>
       </c>
       <c r="E15" t="n">
-        <v>28190</v>
+        <v>27922</v>
       </c>
       <c r="F15" t="n">
-        <v>-92.25</v>
+        <v>-268</v>
       </c>
       <c r="G15" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0095</v>
       </c>
       <c r="H15" t="n">
-        <v>824.25</v>
+        <v>624.5</v>
       </c>
       <c r="I15" t="n">
-        <v>27689</v>
+        <v>27114.75</v>
       </c>
       <c r="J15" t="n">
-        <v>27662.75</v>
+        <v>27285.19</v>
       </c>
       <c r="K15" t="n">
-        <v>28020.5</v>
+        <v>27777.88</v>
       </c>
       <c r="L15" t="n">
-        <v>28378.25</v>
+        <v>28270.56</v>
       </c>
       <c r="M15" t="n">
-        <v>28544</v>
+        <v>28602.12</v>
       </c>
       <c r="N15" t="n">
-        <v>28709.75</v>
+        <v>28933.69</v>
       </c>
       <c r="O15" t="n">
-        <v>29259.5</v>
+        <v>29587.5</v>
       </c>
       <c r="P15" s="6" t="n">
         <v/>
@@ -1764,20 +1768,16 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="S15" s="7" t="inlineStr">
+      <c r="S15" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
       </c>
-      <c r="T15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U15" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+      <c r="T15" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U15" s="8" t="n">
+        <v/>
       </c>
       <c r="V15" s="8" t="n">
         <v/>
@@ -1787,72 +1787,70 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="X15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-07-28</t>
+          <t>2026-07-29</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>28210.5</v>
+        <v>27962</v>
       </c>
       <c r="C16" t="n">
-        <v>28228</v>
+        <v>28178.25</v>
       </c>
       <c r="D16" t="n">
-        <v>27603.5</v>
+        <v>27201.5</v>
       </c>
       <c r="E16" t="n">
-        <v>27922</v>
+        <v>27342</v>
       </c>
       <c r="F16" t="n">
-        <v>-268</v>
+        <v>-580</v>
       </c>
       <c r="G16" s="5" t="n">
-        <v>-0.0095</v>
+        <v>-0.0208</v>
       </c>
       <c r="H16" t="n">
-        <v>624.5</v>
+        <v>976.75</v>
       </c>
       <c r="I16" t="n">
-        <v>27114.75</v>
+        <v>26979</v>
       </c>
       <c r="J16" t="n">
-        <v>27285.19</v>
+        <v>27300.62</v>
       </c>
       <c r="K16" t="n">
-        <v>27777.88</v>
+        <v>27609.75</v>
       </c>
       <c r="L16" t="n">
-        <v>28270.56</v>
+        <v>27918.88</v>
       </c>
       <c r="M16" t="n">
-        <v>28602.12</v>
+        <v>28234.25</v>
       </c>
       <c r="N16" t="n">
-        <v>28933.69</v>
+        <v>28549.62</v>
       </c>
       <c r="O16" t="n">
-        <v>29587.5</v>
+        <v>28852.5</v>
       </c>
       <c r="P16" s="6" t="n">
         <v/>
       </c>
-      <c r="Q16" s="6" t="n">
-        <v/>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="R16" s="6" t="inlineStr">
         <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
         <is>
           <t>↓</t>
         </is>
@@ -1876,81 +1874,81 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-07-29</t>
+          <t>2026-07-30</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>27962</v>
+        <v>27202</v>
       </c>
       <c r="C17" t="n">
-        <v>28178.25</v>
+        <v>28414.5</v>
       </c>
       <c r="D17" t="n">
-        <v>27201.5</v>
+        <v>27202</v>
       </c>
       <c r="E17" t="n">
-        <v>27342</v>
+        <v>28237.75</v>
       </c>
       <c r="F17" t="n">
-        <v>-580</v>
+        <v>895.75</v>
       </c>
       <c r="G17" s="5" t="n">
-        <v>-0.0208</v>
+        <v>0.0328</v>
       </c>
       <c r="H17" t="n">
-        <v>976.75</v>
+        <v>1212.5</v>
       </c>
       <c r="I17" t="n">
-        <v>26979</v>
+        <v>26224.75</v>
       </c>
       <c r="J17" t="n">
-        <v>27300.62</v>
+        <v>26191.31</v>
       </c>
       <c r="K17" t="n">
-        <v>27609.75</v>
+        <v>26853.62</v>
       </c>
       <c r="L17" t="n">
-        <v>27918.88</v>
+        <v>27515.94</v>
       </c>
       <c r="M17" t="n">
-        <v>28234.25</v>
+        <v>27830.38</v>
       </c>
       <c r="N17" t="n">
-        <v>28549.62</v>
+        <v>28144.81</v>
       </c>
       <c r="O17" t="n">
-        <v>28852.5</v>
+        <v>29155</v>
       </c>
       <c r="P17" s="6" t="n">
         <v/>
       </c>
-      <c r="Q17" s="6" t="inlineStr">
+      <c r="Q17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R17" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S17" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T17" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U17" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T17" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U17" s="8" t="n">
-        <v/>
-      </c>
       <c r="V17" s="8" t="n">
         <v/>
       </c>
-      <c r="W17" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
+      <c r="W17" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
         </is>
       </c>
       <c r="X17" t="inlineStr"/>
@@ -1958,50 +1956,50 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-07-30</t>
+          <t>2026-07-31</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>27202</v>
+        <v>28317</v>
       </c>
       <c r="C18" t="n">
-        <v>28414.5</v>
+        <v>28725.75</v>
       </c>
       <c r="D18" t="n">
-        <v>27202</v>
+        <v>28079.75</v>
       </c>
       <c r="E18" t="n">
-        <v>28237.75</v>
+        <v>28404.25</v>
       </c>
       <c r="F18" t="n">
-        <v>895.75</v>
+        <v>166.5</v>
       </c>
       <c r="G18" s="5" t="n">
-        <v>0.0328</v>
+        <v>0.0059</v>
       </c>
       <c r="H18" t="n">
-        <v>1212.5</v>
+        <v>646</v>
       </c>
       <c r="I18" t="n">
-        <v>26224.75</v>
+        <v>25989.5</v>
       </c>
       <c r="J18" t="n">
-        <v>26191.31</v>
+        <v>27240</v>
       </c>
       <c r="K18" t="n">
-        <v>26853.62</v>
+        <v>27631.5</v>
       </c>
       <c r="L18" t="n">
-        <v>27515.94</v>
+        <v>28023</v>
       </c>
       <c r="M18" t="n">
-        <v>27830.38</v>
+        <v>28844</v>
       </c>
       <c r="N18" t="n">
-        <v>28144.81</v>
+        <v>29665</v>
       </c>
       <c r="O18" t="n">
-        <v>29155</v>
+        <v>29627</v>
       </c>
       <c r="P18" s="6" t="n">
         <v/>
@@ -2012,20 +2010,16 @@
       <c r="R18" s="6" t="n">
         <v/>
       </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T18" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U18" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S18" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T18" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U18" s="8" t="n">
+        <v/>
       </c>
       <c r="V18" s="8" t="n">
         <v/>
@@ -2040,50 +2034,50 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-07-31</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>28317</v>
+        <v>28565</v>
       </c>
       <c r="C19" t="n">
-        <v>28725.75</v>
+        <v>28964.25</v>
       </c>
       <c r="D19" t="n">
-        <v>28079.75</v>
+        <v>28313.5</v>
       </c>
       <c r="E19" t="n">
-        <v>28404.25</v>
+        <v>28891.75</v>
       </c>
       <c r="F19" t="n">
-        <v>166.5</v>
+        <v>487.5</v>
       </c>
       <c r="G19" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0172</v>
       </c>
       <c r="H19" t="n">
-        <v>646</v>
+        <v>650.75</v>
       </c>
       <c r="I19" t="n">
-        <v>25989.5</v>
+        <v>27433.75</v>
       </c>
       <c r="J19" t="n">
-        <v>27240</v>
+        <v>27759</v>
       </c>
       <c r="K19" t="n">
-        <v>27631.5</v>
+        <v>28081.25</v>
       </c>
       <c r="L19" t="n">
-        <v>28023</v>
+        <v>28403.5</v>
       </c>
       <c r="M19" t="n">
-        <v>28844</v>
+        <v>28727.25</v>
       </c>
       <c r="N19" t="n">
-        <v>29665</v>
+        <v>29051</v>
       </c>
       <c r="O19" t="n">
-        <v>29627</v>
+        <v>29371.75</v>
       </c>
       <c r="P19" s="6" t="n">
         <v/>
@@ -2094,16 +2088,20 @@
       <c r="R19" s="6" t="n">
         <v/>
       </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T19" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U19" s="8" t="n">
-        <v/>
+      <c r="S19" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T19" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U19" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V19" s="8" t="n">
         <v/>
@@ -2118,50 +2116,50 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-04</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>28565</v>
+        <v>28930</v>
       </c>
       <c r="C20" t="n">
-        <v>28964.25</v>
+        <v>29956.5</v>
       </c>
       <c r="D20" t="n">
-        <v>28313.5</v>
+        <v>28831.75</v>
       </c>
       <c r="E20" t="n">
-        <v>28891.75</v>
+        <v>29863.5</v>
       </c>
       <c r="F20" t="n">
-        <v>487.5</v>
+        <v>971.75</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>0.0172</v>
+        <v>0.0336</v>
       </c>
       <c r="H20" t="n">
-        <v>650.75</v>
+        <v>1124.75</v>
       </c>
       <c r="I20" t="n">
-        <v>27433.75</v>
+        <v>27662.75</v>
       </c>
       <c r="J20" t="n">
-        <v>27759</v>
+        <v>28367.44</v>
       </c>
       <c r="K20" t="n">
-        <v>28081.25</v>
+        <v>28566.38</v>
       </c>
       <c r="L20" t="n">
-        <v>28403.5</v>
+        <v>28765.31</v>
       </c>
       <c r="M20" t="n">
-        <v>28727.25</v>
+        <v>29217.12</v>
       </c>
       <c r="N20" t="n">
-        <v>29051</v>
+        <v>29668.94</v>
       </c>
       <c r="O20" t="n">
-        <v>29371.75</v>
+        <v>29615</v>
       </c>
       <c r="P20" s="6" t="n">
         <v/>
@@ -2172,7 +2170,7 @@
       <c r="R20" s="6" t="n">
         <v/>
       </c>
-      <c r="S20" s="10" t="inlineStr">
+      <c r="S20" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
@@ -2187,8 +2185,10 @@
           <t>△C</t>
         </is>
       </c>
-      <c r="V20" s="8" t="n">
-        <v/>
+      <c r="V20" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="W20" s="9" t="inlineStr">
         <is>
@@ -2200,50 +2200,50 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-08-04</t>
+          <t>2026-08-05</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>28930</v>
+        <v>29777.25</v>
       </c>
       <c r="C21" t="n">
-        <v>29956.5</v>
+        <v>30074</v>
       </c>
       <c r="D21" t="n">
-        <v>28831.75</v>
+        <v>29530.75</v>
       </c>
       <c r="E21" t="n">
-        <v>29863.5</v>
+        <v>29615</v>
       </c>
       <c r="F21" t="n">
-        <v>971.75</v>
+        <v>-248.5</v>
       </c>
       <c r="G21" s="5" t="n">
-        <v>0.0336</v>
+        <v>-0.0083</v>
       </c>
       <c r="H21" t="n">
-        <v>1124.75</v>
+        <v>543.25</v>
       </c>
       <c r="I21" t="n">
-        <v>27662.75</v>
+        <v>27707</v>
       </c>
       <c r="J21" t="n">
-        <v>28367.44</v>
+        <v>28973.44</v>
       </c>
       <c r="K21" t="n">
-        <v>28566.38</v>
+        <v>29301.12</v>
       </c>
       <c r="L21" t="n">
-        <v>28765.31</v>
+        <v>29628.81</v>
       </c>
       <c r="M21" t="n">
-        <v>29217.12</v>
+        <v>30425.88</v>
       </c>
       <c r="N21" t="n">
-        <v>29668.94</v>
+        <v>31222.94</v>
       </c>
       <c r="O21" t="n">
-        <v>29615</v>
+        <v>31081.25</v>
       </c>
       <c r="P21" s="6" t="n">
         <v/>
@@ -2256,78 +2256,76 @@
       </c>
       <c r="S21" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U21" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="V21" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U21" s="8" t="n">
+        <v/>
+      </c>
+      <c r="V21" s="8" t="n">
+        <v/>
       </c>
       <c r="W21" s="9" t="inlineStr">
         <is>
           <t>多方</t>
         </is>
       </c>
-      <c r="X21" t="inlineStr"/>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-08-05</t>
+          <t>2026-08-06</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>29777.25</v>
+        <v>29569.5</v>
       </c>
       <c r="C22" t="n">
-        <v>30074</v>
+        <v>29686.25</v>
       </c>
       <c r="D22" t="n">
-        <v>29530.75</v>
+        <v>29241.25</v>
       </c>
       <c r="E22" t="n">
-        <v>29615</v>
+        <v>29488.25</v>
       </c>
       <c r="F22" t="n">
-        <v>-248.5</v>
+        <v>-126.75</v>
       </c>
       <c r="G22" s="5" t="n">
-        <v>-0.0083</v>
+        <v>-0.0043</v>
       </c>
       <c r="H22" t="n">
-        <v>543.25</v>
+        <v>445</v>
       </c>
       <c r="I22" t="n">
-        <v>27707</v>
+        <v>28987.5</v>
       </c>
       <c r="J22" t="n">
-        <v>28973.44</v>
+        <v>28978.06</v>
       </c>
       <c r="K22" t="n">
-        <v>29301.12</v>
+        <v>29343.38</v>
       </c>
       <c r="L22" t="n">
-        <v>29628.81</v>
+        <v>29708.69</v>
       </c>
       <c r="M22" t="n">
-        <v>30425.88</v>
+        <v>29886.62</v>
       </c>
       <c r="N22" t="n">
-        <v>31222.94</v>
+        <v>30064.56</v>
       </c>
       <c r="O22" t="n">
-        <v>31081.25</v>
+        <v>30617.25</v>
       </c>
       <c r="P22" s="6" t="n">
         <v/>
@@ -2335,12 +2333,14 @@
       <c r="Q22" s="6" t="n">
         <v/>
       </c>
-      <c r="R22" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T22" s="8" t="n">
@@ -2359,57 +2359,57 @@
       </c>
       <c r="X22" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-08-07</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>29569.5</v>
+        <v>29514.25</v>
       </c>
       <c r="C23" t="n">
-        <v>29686.25</v>
+        <v>29867.75</v>
       </c>
       <c r="D23" t="n">
-        <v>29241.25</v>
+        <v>29453.5</v>
       </c>
       <c r="E23" t="n">
-        <v>29488.25</v>
+        <v>29834.75</v>
       </c>
       <c r="F23" t="n">
-        <v>-126.75</v>
+        <v>346.5</v>
       </c>
       <c r="G23" s="5" t="n">
-        <v>-0.0043</v>
+        <v>0.0118</v>
       </c>
       <c r="H23" t="n">
-        <v>445</v>
+        <v>414.25</v>
       </c>
       <c r="I23" t="n">
-        <v>28987.5</v>
+        <v>28796.25</v>
       </c>
       <c r="J23" t="n">
-        <v>28978.06</v>
+        <v>29055.5</v>
       </c>
       <c r="K23" t="n">
-        <v>29343.38</v>
+        <v>29265.75</v>
       </c>
       <c r="L23" t="n">
-        <v>29708.69</v>
+        <v>29476</v>
       </c>
       <c r="M23" t="n">
-        <v>29886.62</v>
+        <v>29710.75</v>
       </c>
       <c r="N23" t="n">
-        <v>30064.56</v>
+        <v>29945.5</v>
       </c>
       <c r="O23" t="n">
-        <v>30617.25</v>
+        <v>30131.25</v>
       </c>
       <c r="P23" s="6" t="n">
         <v/>
@@ -2417,22 +2417,24 @@
       <c r="Q23" s="6" t="n">
         <v/>
       </c>
-      <c r="R23" s="6" t="inlineStr">
+      <c r="R23" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S23" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T23" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U23" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S23" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T23" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U23" s="8" t="n">
-        <v/>
-      </c>
       <c r="V23" s="8" t="n">
         <v/>
       </c>
@@ -2441,59 +2443,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-08-07</t>
+          <t>2026-08-10</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>29514.25</v>
+        <v>29851.25</v>
       </c>
       <c r="C24" t="n">
-        <v>29867.75</v>
+        <v>29984</v>
       </c>
       <c r="D24" t="n">
-        <v>29453.5</v>
+        <v>29718.75</v>
       </c>
       <c r="E24" t="n">
-        <v>29834.75</v>
+        <v>29737</v>
       </c>
       <c r="F24" t="n">
-        <v>346.5</v>
+        <v>-97.75</v>
       </c>
       <c r="G24" s="5" t="n">
-        <v>0.0118</v>
+        <v>-0.0033</v>
       </c>
       <c r="H24" t="n">
-        <v>414.25</v>
+        <v>265.25</v>
       </c>
       <c r="I24" t="n">
-        <v>28796.25</v>
+        <v>29039.25</v>
       </c>
       <c r="J24" t="n">
-        <v>29055.5</v>
+        <v>29507.56</v>
       </c>
       <c r="K24" t="n">
-        <v>29265.75</v>
+        <v>29627.62</v>
       </c>
       <c r="L24" t="n">
-        <v>29476</v>
+        <v>29747.69</v>
       </c>
       <c r="M24" t="n">
-        <v>29710.75</v>
+        <v>30041.88</v>
       </c>
       <c r="N24" t="n">
-        <v>29945.5</v>
+        <v>30336.06</v>
       </c>
       <c r="O24" t="n">
-        <v>30131.25</v>
+        <v>30282</v>
       </c>
       <c r="P24" s="6" t="n">
         <v/>
@@ -2506,18 +2504,14 @@
       </c>
       <c r="S24" s="10" t="inlineStr">
         <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T24" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U24" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T24" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U24" s="8" t="n">
+        <v/>
       </c>
       <c r="V24" s="8" t="n">
         <v/>
@@ -2527,55 +2521,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X24" t="inlineStr"/>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>29851.25</v>
+        <v>29764.5</v>
       </c>
       <c r="C25" t="n">
-        <v>29984</v>
+        <v>29886.75</v>
       </c>
       <c r="D25" t="n">
-        <v>29718.75</v>
+        <v>29533.5</v>
       </c>
       <c r="E25" t="n">
-        <v>29737</v>
+        <v>29626</v>
       </c>
       <c r="F25" t="n">
-        <v>-97.75</v>
+        <v>-111</v>
       </c>
       <c r="G25" s="5" t="n">
-        <v>-0.0033</v>
+        <v>-0.0037</v>
       </c>
       <c r="H25" t="n">
-        <v>265.25</v>
+        <v>353.25</v>
       </c>
       <c r="I25" t="n">
-        <v>29039.25</v>
+        <v>29453.5</v>
       </c>
       <c r="J25" t="n">
-        <v>29507.56</v>
+        <v>29414.56</v>
       </c>
       <c r="K25" t="n">
-        <v>29627.62</v>
+        <v>29604.38</v>
       </c>
       <c r="L25" t="n">
-        <v>29747.69</v>
+        <v>29794.19</v>
       </c>
       <c r="M25" t="n">
-        <v>30041.88</v>
+        <v>29869.62</v>
       </c>
       <c r="N25" t="n">
-        <v>30336.06</v>
+        <v>29945.06</v>
       </c>
       <c r="O25" t="n">
-        <v>30282</v>
+        <v>30249.25</v>
       </c>
       <c r="P25" s="6" t="n">
         <v/>
@@ -2583,16 +2581,20 @@
       <c r="Q25" s="6" t="n">
         <v/>
       </c>
-      <c r="R25" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T25" s="8" t="n">
-        <v/>
+      <c r="R25" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T25" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U25" s="8" t="n">
         <v/>
@@ -2607,57 +2609,57 @@
       </c>
       <c r="X25" t="inlineStr">
         <is>
-          <t>弱警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-08-11</t>
+          <t>2026-08-12</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>29764.5</v>
+        <v>29657.75</v>
       </c>
       <c r="C26" t="n">
-        <v>29886.75</v>
+        <v>30001.75</v>
       </c>
       <c r="D26" t="n">
-        <v>29533.5</v>
+        <v>29624.5</v>
       </c>
       <c r="E26" t="n">
-        <v>29626</v>
+        <v>29853.25</v>
       </c>
       <c r="F26" t="n">
-        <v>-111</v>
+        <v>227.25</v>
       </c>
       <c r="G26" s="5" t="n">
-        <v>-0.0037</v>
+        <v>0.0077</v>
       </c>
       <c r="H26" t="n">
-        <v>353.25</v>
+        <v>377.25</v>
       </c>
       <c r="I26" t="n">
-        <v>29453.5</v>
+        <v>29180.25</v>
       </c>
       <c r="J26" t="n">
-        <v>29414.56</v>
+        <v>29230.69</v>
       </c>
       <c r="K26" t="n">
-        <v>29604.38</v>
+        <v>29449.38</v>
       </c>
       <c r="L26" t="n">
-        <v>29794.19</v>
+        <v>29668.06</v>
       </c>
       <c r="M26" t="n">
-        <v>29869.62</v>
+        <v>29802.62</v>
       </c>
       <c r="N26" t="n">
-        <v>29945.06</v>
+        <v>29937.19</v>
       </c>
       <c r="O26" t="n">
-        <v>30249.25</v>
+        <v>30240</v>
       </c>
       <c r="P26" s="6" t="n">
         <v/>
@@ -2665,24 +2667,24 @@
       <c r="Q26" s="6" t="n">
         <v/>
       </c>
-      <c r="R26" s="6" t="inlineStr">
+      <c r="R26" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S26" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T26" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T26" s="8" t="inlineStr">
+      <c r="U26" s="8" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
-      <c r="U26" s="8" t="n">
-        <v/>
-      </c>
       <c r="V26" s="8" t="n">
         <v/>
       </c>
@@ -2691,59 +2693,55 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X26" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="X26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-08-12</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>29657.75</v>
+        <v>29825</v>
       </c>
       <c r="C27" t="n">
-        <v>30001.75</v>
+        <v>30272.75</v>
       </c>
       <c r="D27" t="n">
-        <v>29624.5</v>
+        <v>29780.5</v>
       </c>
       <c r="E27" t="n">
-        <v>29853.25</v>
+        <v>30188.5</v>
       </c>
       <c r="F27" t="n">
-        <v>227.25</v>
+        <v>335.25</v>
       </c>
       <c r="G27" s="5" t="n">
-        <v>0.0077</v>
+        <v>0.0112</v>
       </c>
       <c r="H27" t="n">
-        <v>377.25</v>
+        <v>492.25</v>
       </c>
       <c r="I27" t="n">
-        <v>29180.25</v>
+        <v>29247.25</v>
       </c>
       <c r="J27" t="n">
-        <v>29230.69</v>
+        <v>29496.06</v>
       </c>
       <c r="K27" t="n">
-        <v>29449.38</v>
+        <v>29664.62</v>
       </c>
       <c r="L27" t="n">
-        <v>29668.06</v>
+        <v>29833.19</v>
       </c>
       <c r="M27" t="n">
-        <v>29802.62</v>
+        <v>30041.88</v>
       </c>
       <c r="N27" t="n">
-        <v>29937.19</v>
+        <v>30250.56</v>
       </c>
       <c r="O27" t="n">
-        <v>30240</v>
+        <v>30379</v>
       </c>
       <c r="P27" s="6" t="n">
         <v/>
@@ -2754,19 +2752,19 @@
       <c r="R27" s="6" t="n">
         <v/>
       </c>
-      <c r="S27" s="10" t="inlineStr">
+      <c r="S27" s="7" t="inlineStr">
         <is>
           <t>↑</t>
         </is>
       </c>
       <c r="T27" s="8" t="inlineStr">
         <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U27" s="8" t="inlineStr">
+        <is>
           <t>△C</t>
-        </is>
-      </c>
-      <c r="U27" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
         </is>
       </c>
       <c r="V27" s="8" t="n">
@@ -2782,50 +2780,50 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>29825</v>
+        <v>30210.75</v>
       </c>
       <c r="C28" t="n">
-        <v>30272.75</v>
+        <v>30283</v>
       </c>
       <c r="D28" t="n">
-        <v>29780.5</v>
+        <v>30028.5</v>
       </c>
       <c r="E28" t="n">
-        <v>30188.5</v>
+        <v>30141.75</v>
       </c>
       <c r="F28" t="n">
-        <v>335.25</v>
+        <v>-46.75</v>
       </c>
       <c r="G28" s="5" t="n">
-        <v>0.0112</v>
+        <v>-0.0015</v>
       </c>
       <c r="H28" t="n">
-        <v>492.25</v>
+        <v>254.5</v>
       </c>
       <c r="I28" t="n">
-        <v>29247.25</v>
+        <v>29288.25</v>
       </c>
       <c r="J28" t="n">
-        <v>29496.06</v>
+        <v>29777.19</v>
       </c>
       <c r="K28" t="n">
-        <v>29664.62</v>
+        <v>29942.38</v>
       </c>
       <c r="L28" t="n">
-        <v>29833.19</v>
+        <v>30107.56</v>
       </c>
       <c r="M28" t="n">
-        <v>30041.88</v>
+        <v>30434.62</v>
       </c>
       <c r="N28" t="n">
-        <v>30250.56</v>
+        <v>30761.69</v>
       </c>
       <c r="O28" t="n">
-        <v>30379</v>
+        <v>30765</v>
       </c>
       <c r="P28" s="6" t="n">
         <v/>
@@ -2836,20 +2834,16 @@
       <c r="R28" s="6" t="n">
         <v/>
       </c>
-      <c r="S28" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T28" s="8" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="U28" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S28" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T28" s="8" t="n">
+        <v/>
+      </c>
+      <c r="U28" s="8" t="n">
+        <v/>
       </c>
       <c r="V28" s="8" t="n">
         <v/>
@@ -2859,55 +2853,59 @@
           <t>多方</t>
         </is>
       </c>
-      <c r="X28" t="inlineStr"/>
+      <c r="X28" t="inlineStr">
+        <is>
+          <t>弱警訊</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>30210.75</v>
+        <v>30170</v>
       </c>
       <c r="C29" t="n">
-        <v>30283</v>
+        <v>30343</v>
       </c>
       <c r="D29" t="n">
-        <v>30028.5</v>
+        <v>30054.5</v>
       </c>
       <c r="E29" t="n">
-        <v>30141.75</v>
+        <v>30096</v>
       </c>
       <c r="F29" t="n">
-        <v>-46.75</v>
+        <v>-45.75</v>
       </c>
       <c r="G29" s="5" t="n">
         <v>-0.0015</v>
       </c>
       <c r="H29" t="n">
-        <v>254.5</v>
+        <v>288.5</v>
       </c>
       <c r="I29" t="n">
-        <v>29288.25</v>
+        <v>29774</v>
       </c>
       <c r="J29" t="n">
-        <v>29777.19</v>
+        <v>29880.25</v>
       </c>
       <c r="K29" t="n">
-        <v>29942.38</v>
+        <v>30014.5</v>
       </c>
       <c r="L29" t="n">
-        <v>30107.56</v>
+        <v>30148.75</v>
       </c>
       <c r="M29" t="n">
-        <v>30434.62</v>
+        <v>30269</v>
       </c>
       <c r="N29" t="n">
-        <v>30761.69</v>
+        <v>30389.25</v>
       </c>
       <c r="O29" t="n">
-        <v>30765</v>
+        <v>30537.5</v>
       </c>
       <c r="P29" s="6" t="n">
         <v/>
@@ -2920,11 +2918,13 @@
       </c>
       <c r="S29" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T29" s="8" t="n">
-        <v/>
+          <t>↓C</t>
+        </is>
+      </c>
+      <c r="T29" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="U29" s="8" t="n">
         <v/>
@@ -2946,153 +2946,147 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>30170</v>
+        <v>30077</v>
       </c>
       <c r="C30" t="n">
-        <v>30343</v>
+        <v>30121.25</v>
       </c>
       <c r="D30" t="n">
-        <v>30054.5</v>
+        <v>29514</v>
       </c>
       <c r="E30" t="n">
-        <v>30096</v>
+        <v>29586</v>
       </c>
       <c r="F30" t="n">
-        <v>-45.75</v>
+        <v>-510</v>
       </c>
       <c r="G30" s="5" t="n">
-        <v>-0.0015</v>
+        <v>-0.0169</v>
       </c>
       <c r="H30" t="n">
-        <v>288.5</v>
+        <v>607.25</v>
       </c>
       <c r="I30" t="n">
-        <v>29774</v>
+        <v>29766</v>
       </c>
       <c r="J30" t="n">
-        <v>29880.25</v>
+        <v>29756.12</v>
       </c>
       <c r="K30" t="n">
-        <v>30014.5</v>
+        <v>29951.75</v>
       </c>
       <c r="L30" t="n">
-        <v>30148.75</v>
+        <v>30147.38</v>
       </c>
       <c r="M30" t="n">
-        <v>30269</v>
+        <v>30240.25</v>
       </c>
       <c r="N30" t="n">
-        <v>30389.25</v>
+        <v>30333.12</v>
       </c>
       <c r="O30" t="n">
-        <v>30537.5</v>
-      </c>
-      <c r="P30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="Q30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R30" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S30" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
-        </is>
-      </c>
-      <c r="T30" s="8" t="inlineStr">
+        <v>30631.5</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
         <is>
           <t>✓</t>
         </is>
       </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R30" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="S30" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
+        </is>
+      </c>
+      <c r="T30" s="8" t="n">
+        <v/>
+      </c>
       <c r="U30" s="8" t="n">
         <v/>
       </c>
       <c r="V30" s="8" t="n">
         <v/>
       </c>
-      <c r="W30" s="9" t="inlineStr">
-        <is>
-          <t>多方</t>
-        </is>
-      </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>弱警訊</t>
-        </is>
-      </c>
+      <c r="W30" s="11" t="inlineStr">
+        <is>
+          <t>空方</t>
+        </is>
+      </c>
+      <c r="X30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>30077</v>
+        <v>29566.5</v>
       </c>
       <c r="C31" t="n">
-        <v>30121.25</v>
+        <v>29757.25</v>
       </c>
       <c r="D31" t="n">
-        <v>29514</v>
+        <v>29375.75</v>
       </c>
       <c r="E31" t="n">
-        <v>29586</v>
+        <v>29512.75</v>
       </c>
       <c r="F31" t="n">
-        <v>-510</v>
+        <v>-73.25</v>
       </c>
       <c r="G31" s="5" t="n">
-        <v>-0.0169</v>
+        <v>-0.0025</v>
       </c>
       <c r="H31" t="n">
-        <v>607.25</v>
+        <v>381.5</v>
       </c>
       <c r="I31" t="n">
-        <v>29766</v>
+        <v>28906.75</v>
       </c>
       <c r="J31" t="n">
-        <v>29756.12</v>
+        <v>28862.94</v>
       </c>
       <c r="K31" t="n">
-        <v>29951.75</v>
+        <v>29282.38</v>
       </c>
       <c r="L31" t="n">
-        <v>30147.38</v>
+        <v>29701.81</v>
       </c>
       <c r="M31" t="n">
-        <v>30240.25</v>
+        <v>29889.62</v>
       </c>
       <c r="N31" t="n">
-        <v>30333.12</v>
+        <v>30077.44</v>
       </c>
       <c r="O31" t="n">
-        <v>30631.5</v>
-      </c>
-      <c r="P31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="Q31" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
-      </c>
-      <c r="R31" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S31" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
+        <v>30728.5</v>
+      </c>
+      <c r="P31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="Q31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R31" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S31" s="10" t="inlineStr">
+        <is>
+          <t>↓C</t>
         </is>
       </c>
       <c r="T31" s="8" t="n">
@@ -3114,50 +3108,50 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>29566.5</v>
+        <v>29561.5</v>
       </c>
       <c r="C32" t="n">
-        <v>29757.25</v>
+        <v>29689.75</v>
       </c>
       <c r="D32" t="n">
-        <v>29375.75</v>
+        <v>29202.75</v>
       </c>
       <c r="E32" t="n">
-        <v>29512.75</v>
+        <v>29300.5</v>
       </c>
       <c r="F32" t="n">
-        <v>-73.25</v>
+        <v>-212.25</v>
       </c>
       <c r="G32" s="5" t="n">
-        <v>-0.0025</v>
+        <v>-0.0072</v>
       </c>
       <c r="H32" t="n">
-        <v>381.5</v>
+        <v>487</v>
       </c>
       <c r="I32" t="n">
-        <v>28906.75</v>
+        <v>28994.25</v>
       </c>
       <c r="J32" t="n">
-        <v>28862.94</v>
+        <v>29104.38</v>
       </c>
       <c r="K32" t="n">
-        <v>29282.38</v>
+        <v>29322</v>
       </c>
       <c r="L32" t="n">
-        <v>29701.81</v>
+        <v>29539.62</v>
       </c>
       <c r="M32" t="n">
-        <v>29889.62</v>
+        <v>29703.5</v>
       </c>
       <c r="N32" t="n">
-        <v>30077.44</v>
+        <v>29867.38</v>
       </c>
       <c r="O32" t="n">
-        <v>30728.5</v>
+        <v>30138.75</v>
       </c>
       <c r="P32" s="6" t="n">
         <v/>
@@ -3165,12 +3159,14 @@
       <c r="Q32" s="6" t="n">
         <v/>
       </c>
-      <c r="R32" s="6" t="n">
-        <v/>
-      </c>
-      <c r="S32" s="7" t="inlineStr">
-        <is>
-          <t>↓C</t>
+      <c r="R32" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="S32" s="10" t="inlineStr">
+        <is>
+          <t>↓</t>
         </is>
       </c>
       <c r="T32" s="8" t="n">
@@ -3192,50 +3188,50 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>29561.5</v>
+        <v>29327</v>
       </c>
       <c r="C33" t="n">
-        <v>29689.75</v>
+        <v>29539</v>
       </c>
       <c r="D33" t="n">
-        <v>29202.75</v>
+        <v>29220</v>
       </c>
       <c r="E33" t="n">
-        <v>29300.5</v>
+        <v>29387.75</v>
       </c>
       <c r="F33" t="n">
-        <v>-212.25</v>
+        <v>87.25</v>
       </c>
       <c r="G33" s="5" t="n">
-        <v>-0.0072</v>
+        <v>0.003</v>
       </c>
       <c r="H33" t="n">
-        <v>487</v>
+        <v>319</v>
       </c>
       <c r="I33" t="n">
-        <v>28994.25</v>
+        <v>28715.75</v>
       </c>
       <c r="J33" t="n">
-        <v>29104.38</v>
+        <v>28740.62</v>
       </c>
       <c r="K33" t="n">
-        <v>29322</v>
+        <v>29057</v>
       </c>
       <c r="L33" t="n">
-        <v>29539.62</v>
+        <v>29373.38</v>
       </c>
       <c r="M33" t="n">
-        <v>29703.5</v>
+        <v>29544</v>
       </c>
       <c r="N33" t="n">
-        <v>29867.38</v>
+        <v>29714.62</v>
       </c>
       <c r="O33" t="n">
-        <v>30138.75</v>
+        <v>30176.75</v>
       </c>
       <c r="P33" s="6" t="n">
         <v/>
@@ -3243,14 +3239,12 @@
       <c r="Q33" s="6" t="n">
         <v/>
       </c>
-      <c r="R33" s="6" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="R33" s="6" t="n">
+        <v/>
       </c>
       <c r="S33" s="7" t="inlineStr">
         <is>
-          <t>↓</t>
+          <t>↑C</t>
         </is>
       </c>
       <c r="T33" s="8" t="n">
@@ -3267,68 +3261,76 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X33" t="inlineStr"/>
+      <c r="X33" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>29327</v>
+        <v>29392.25</v>
       </c>
       <c r="C34" t="n">
-        <v>29539</v>
+        <v>29480.5</v>
       </c>
       <c r="D34" t="n">
-        <v>29220</v>
+        <v>28946.75</v>
       </c>
       <c r="E34" t="n">
-        <v>29387.75</v>
+        <v>29105.75</v>
       </c>
       <c r="F34" t="n">
-        <v>87.25</v>
+        <v>-282</v>
       </c>
       <c r="G34" s="5" t="n">
-        <v>0.003</v>
+        <v>-0.009599999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>319</v>
+        <v>533.75</v>
       </c>
       <c r="I34" t="n">
-        <v>28715.75</v>
+        <v>28901</v>
       </c>
       <c r="J34" t="n">
-        <v>28740.62</v>
+        <v>29072.88</v>
       </c>
       <c r="K34" t="n">
-        <v>29057</v>
+        <v>29228.25</v>
       </c>
       <c r="L34" t="n">
-        <v>29373.38</v>
+        <v>29383.62</v>
       </c>
       <c r="M34" t="n">
-        <v>29544</v>
+        <v>29547.25</v>
       </c>
       <c r="N34" t="n">
-        <v>29714.62</v>
+        <v>29710.88</v>
       </c>
       <c r="O34" t="n">
-        <v>30176.75</v>
+        <v>29858</v>
       </c>
       <c r="P34" s="6" t="n">
         <v/>
       </c>
-      <c r="Q34" s="6" t="n">
-        <v/>
-      </c>
-      <c r="R34" s="6" t="n">
-        <v/>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
+      </c>
+      <c r="R34" s="6" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
       </c>
       <c r="S34" s="10" t="inlineStr">
         <is>
-          <t>↑C</t>
+          <t>↓</t>
         </is>
       </c>
       <c r="T34" s="8" t="n">
@@ -3345,81 +3347,75 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X34" t="inlineStr">
-        <is>
-          <t>中警訊</t>
-        </is>
-      </c>
+      <c r="X34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>29392.25</v>
+        <v>29140.5</v>
       </c>
       <c r="C35" t="n">
-        <v>29480.5</v>
+        <v>29425.75</v>
       </c>
       <c r="D35" t="n">
-        <v>28946.75</v>
+        <v>29017</v>
       </c>
       <c r="E35" t="n">
-        <v>29105.75</v>
+        <v>29276.75</v>
       </c>
       <c r="F35" t="n">
-        <v>-282</v>
+        <v>171</v>
       </c>
       <c r="G35" s="5" t="n">
-        <v>-0.009599999999999999</v>
+        <v>0.0059</v>
       </c>
       <c r="H35" t="n">
-        <v>533.75</v>
+        <v>408.75</v>
       </c>
       <c r="I35" t="n">
-        <v>28901</v>
+        <v>28413</v>
       </c>
       <c r="J35" t="n">
-        <v>29072.88</v>
+        <v>28518.06</v>
       </c>
       <c r="K35" t="n">
-        <v>29228.25</v>
+        <v>28838.88</v>
       </c>
       <c r="L35" t="n">
-        <v>29383.62</v>
+        <v>29159.69</v>
       </c>
       <c r="M35" t="n">
-        <v>29547.25</v>
+        <v>29372.62</v>
       </c>
       <c r="N35" t="n">
-        <v>29710.88</v>
+        <v>29585.56</v>
       </c>
       <c r="O35" t="n">
-        <v>29858</v>
+        <v>30014.25</v>
       </c>
       <c r="P35" s="6" t="n">
         <v/>
       </c>
-      <c r="Q35" s="6" t="inlineStr">
+      <c r="Q35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="R35" s="6" t="n">
+        <v/>
+      </c>
+      <c r="S35" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T35" s="8" t="inlineStr">
         <is>
           <t>△C</t>
         </is>
       </c>
-      <c r="R35" s="6" t="inlineStr">
-        <is>
-          <t>✓</t>
-        </is>
-      </c>
-      <c r="S35" s="7" t="inlineStr">
-        <is>
-          <t>↓</t>
-        </is>
-      </c>
-      <c r="T35" s="8" t="n">
-        <v/>
-      </c>
       <c r="U35" s="8" t="n">
         <v/>
       </c>
@@ -3431,55 +3427,59 @@
           <t>空方</t>
         </is>
       </c>
-      <c r="X35" t="inlineStr"/>
+      <c r="X35" t="inlineStr">
+        <is>
+          <t>中警訊</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-08-26</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>29140.5</v>
+        <v>29288</v>
       </c>
       <c r="C36" t="n">
-        <v>29425.75</v>
+        <v>29437.75</v>
       </c>
       <c r="D36" t="n">
-        <v>29017</v>
+        <v>29096</v>
       </c>
       <c r="E36" t="n">
-        <v>29276.75</v>
+        <v>29289.5</v>
       </c>
       <c r="F36" t="n">
-        <v>171</v>
+        <v>12.75</v>
       </c>
       <c r="G36" s="5" t="n">
-        <v>0.0059</v>
+        <v>0.0004</v>
       </c>
       <c r="H36" t="n">
-        <v>408.75</v>
+        <v>341.75</v>
       </c>
       <c r="I36" t="n">
-        <v>28413</v>
+        <v>28608.25</v>
       </c>
       <c r="J36" t="n">
-        <v>28518.06</v>
+        <v>28895.69</v>
       </c>
       <c r="K36" t="n">
-        <v>28838.88</v>
+        <v>29072.38</v>
       </c>
       <c r="L36" t="n">
-        <v>29159.69</v>
+        <v>29249.06</v>
       </c>
       <c r="M36" t="n">
-        <v>29372.62</v>
+        <v>29481.12</v>
       </c>
       <c r="N36" t="n">
-        <v>29585.56</v>
+        <v>29713.19</v>
       </c>
       <c r="O36" t="n">
-        <v>30014.25</v>
+        <v>29834.5</v>
       </c>
       <c r="P36" s="6" t="n">
         <v/>
@@ -3490,15 +3490,13 @@
       <c r="R36" s="6" t="n">
         <v/>
       </c>
-      <c r="S36" s="10" t="inlineStr">
-        <is>
-          <t>↑</t>
-        </is>
-      </c>
-      <c r="T36" s="8" t="inlineStr">
-        <is>
-          <t>△C</t>
-        </is>
+      <c r="S36" s="7" t="inlineStr">
+        <is>
+          <t>↑C</t>
+        </is>
+      </c>
+      <c r="T36" s="8" t="n">
+        <v/>
       </c>
       <c r="U36" s="8" t="n">
         <v/>
@@ -3513,57 +3511,57 @@
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>中警訊</t>
+          <t>強警訊</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>29288</v>
+        <v>29499.5</v>
       </c>
       <c r="C37" t="n">
-        <v>29437.75</v>
+        <v>29708</v>
       </c>
       <c r="D37" t="n">
-        <v>29096</v>
+        <v>29401.75</v>
       </c>
       <c r="E37" t="n">
-        <v>29289.5</v>
+        <v>29695.75</v>
       </c>
       <c r="F37" t="n">
-        <v>12.75</v>
+        <v>406.25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0004</v>
+        <v>0.0139</v>
       </c>
       <c r="H37" t="n">
-        <v>341.75</v>
+        <v>306.25</v>
       </c>
       <c r="I37" t="n">
-        <v>28608.25</v>
+        <v>28754.25</v>
       </c>
       <c r="J37" t="n">
-        <v>28895.69</v>
+        <v>28959.06</v>
       </c>
       <c r="K37" t="n">
-        <v>29072.38</v>
+        <v>29118.62</v>
       </c>
       <c r="L37" t="n">
-        <v>29249.06</v>
+        <v>29278.19</v>
       </c>
       <c r="M37" t="n">
-        <v>29481.12</v>
+        <v>29460.38</v>
       </c>
       <c r="N37" t="n">
-        <v>29713.19</v>
+        <v>29642.56</v>
       </c>
       <c r="O37" t="n">
-        <v>29834.5</v>
+        <v>29779.5</v>
       </c>
       <c r="P37" s="6" t="n">
         <v/>
@@ -3574,102 +3572,102 @@
       <c r="R37" s="6" t="n">
         <v/>
       </c>
-      <c r="S37" s="10" t="inlineStr">
-        <is>
-          <t>↑C</t>
-        </is>
-      </c>
-      <c r="T37" s="8" t="n">
-        <v/>
-      </c>
-      <c r="U37" s="8" t="n">
-        <v/>
+      <c r="S37" s="7" t="inlineStr">
+        <is>
+          <t>↑</t>
+        </is>
+      </c>
+      <c r="T37" s="8" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="U37" s="8" t="inlineStr">
+        <is>
+          <t>△C</t>
+        </is>
       </c>
       <c r="V37" s="8" t="n">
         <v/>
       </c>
-      <c r="W37" s="11" t="inlineStr">
-        <is>
-          <t>空方</t>
-        </is>
-      </c>
-      <c r="X37" t="inlineStr">
-        <is>
-          <t>強警訊</t>
-        </is>
-      </c>
+      <c r="W37" s="9" t="inlineStr">
+        <is>
+          <t>多方</t>
+        </is>
+      </c>
+      <c r="X37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>29499.5</v>
+        <v>29635.5</v>
       </c>
       <c r="C38" t="n">
-        <v>29708</v>
+        <v>29811.5</v>
       </c>
       <c r="D38" t="n">
-        <v>29401.75</v>
+        <v>29436.25</v>
       </c>
       <c r="E38" t="n">
-        <v>29695.75</v>
+        <v>29491.75</v>
       </c>
       <c r="F38" t="n">
-        <v>406.25</v>
+        <v>-204</v>
       </c>
       <c r="G38" s="5" t="n">
-        <v>0.0139</v>
+        <v>-0.0069</v>
       </c>
       <c r="H38" t="n">
-        <v>306.25</v>
+        <v>375.25</v>
       </c>
       <c r="I38" t="n">
-        <v>28754.25</v>
+        <v>29095.5</v>
       </c>
       <c r="J38" t="n">
-        <v>28959.06</v>
+        <v>29459.94</v>
       </c>
       <c r="K38" t="n">
-        <v>29118.62</v>
+        <v>29542.62</v>
       </c>
       <c r="L38" t="n">
-        <v>29278.19</v>
+        <v>29625.31</v>
       </c>
       <c r="M38" t="n">
-        <v>29460.38</v>
+        <v>29848.88</v>
       </c>
       <c r="N38" t="n">
-        <v>29642.56</v>
+        <v>30072.44</v>
       </c>
       <c r="O38" t="n">
-        <v>29779.5</v>
+        <v>30014.25</v>
       </c>
       <c r="P38" s="6" t="n">
         <v/>
       </c>
-      <c r="Q38" s="6" t="n">
-        <v/>
-      </c>
-  